--- a/irrbb_calc/output/eba_sot_results.xlsx
+++ b/irrbb_calc/output/eba_sot_results.xlsx
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-835777401.8599999</v>
+        <v>-837973082.6800001</v>
       </c>
       <c r="E2" t="n">
         <v>0.9975215395798449</v>
@@ -495,10 +495,10 @@
         <v>-0.001075339705425948</v>
       </c>
       <c r="H2" t="n">
-        <v>898744.6251177967</v>
+        <v>901105.7278839851</v>
       </c>
       <c r="I2" t="n">
-        <v>449372.3125588984</v>
+        <v>450552.8639419926</v>
       </c>
     </row>
     <row r="3">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>47727447.23</v>
+        <v>19495500.62999999</v>
       </c>
       <c r="E3" t="n">
         <v>0.9903615297882993</v>
@@ -530,10 +530,10 @@
         <v>-0.004118598226101611</v>
       </c>
       <c r="H3" t="n">
-        <v>-196570.1794978362</v>
+        <v>-80294.1343116808</v>
       </c>
       <c r="I3" t="n">
-        <v>-196570.1794978362</v>
+        <v>-80294.1343116808</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>192923172.86</v>
+        <v>110748422.65</v>
       </c>
       <c r="E4" t="n">
         <v>0.9786688180301472</v>
@@ -565,10 +565,10 @@
         <v>-0.009135282621367979</v>
       </c>
       <c r="H4" t="n">
-        <v>-1762407.708287128</v>
+        <v>-1011718.140778461</v>
       </c>
       <c r="I4" t="n">
-        <v>-1762407.708287128</v>
+        <v>-1011718.140778461</v>
       </c>
     </row>
     <row r="5">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-68061780.77000001</v>
+        <v>28459734.17999999</v>
       </c>
       <c r="E5" t="n">
         <v>0.9655145554862491</v>
@@ -600,10 +600,10 @@
         <v>-0.01497137919106994</v>
       </c>
       <c r="H5" t="n">
-        <v>1018978.728327143</v>
+        <v>-426081.472085834</v>
       </c>
       <c r="I5" t="n">
-        <v>509489.3641635713</v>
+        <v>-426081.472085834</v>
       </c>
     </row>
     <row r="6">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-151998857.02</v>
+        <v>120520575.19</v>
       </c>
       <c r="E6" t="n">
         <v>0.9530263468310431</v>
@@ -635,10 +635,10 @@
         <v>-0.02062335501537482</v>
       </c>
       <c r="H6" t="n">
-        <v>3134726.390254658</v>
+        <v>-2485538.608800545</v>
       </c>
       <c r="I6" t="n">
-        <v>1567363.195127329</v>
+        <v>-2485538.608800545</v>
       </c>
     </row>
     <row r="7">
@@ -658,22 +658,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>603399642.77</v>
+        <v>41495736.82999998</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9361136309390247</v>
+        <v>0.93726391898459</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9073120306403207</v>
+        <v>0.9084269373918286</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.02880160029870393</v>
+        <v>-0.02883698159276149</v>
       </c>
       <c r="H7" t="n">
-        <v>-17378875.33144228</v>
+        <v>-1196611.799144784</v>
       </c>
       <c r="I7" t="n">
-        <v>-17378875.33144228</v>
+        <v>-1196611.799144784</v>
       </c>
     </row>
     <row r="8">
@@ -693,22 +693,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>64469088.74</v>
+        <v>34519707.57000002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.911712454789054</v>
+        <v>0.9132428090891569</v>
       </c>
       <c r="F8" t="n">
-        <v>0.872684646475107</v>
+        <v>0.8741495039644692</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.03902780831394703</v>
+        <v>-0.03909330512468767</v>
       </c>
       <c r="H8" t="n">
-        <v>-2516087.237519561</v>
+        <v>-1349489.460849001</v>
       </c>
       <c r="I8" t="n">
-        <v>-2516087.237519561</v>
+        <v>-1349489.460849001</v>
       </c>
     </row>
     <row r="9">
@@ -728,22 +728,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>865567509.3200001</v>
+        <v>874279275.16</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8762998001065606</v>
+        <v>0.8783257731734563</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8232069173152246</v>
+        <v>0.8251101553569301</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.05309288279133606</v>
+        <v>-0.05321561781652617</v>
       </c>
       <c r="H9" t="n">
-        <v>-45955474.32031544</v>
+        <v>-46525311.77182408</v>
       </c>
       <c r="I9" t="n">
-        <v>-45955474.32031544</v>
+        <v>-46525311.77182408</v>
       </c>
     </row>
     <row r="10">
@@ -763,22 +763,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>977328303.03</v>
+        <v>857185142.1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8312220858082966</v>
+        <v>0.8337865285685646</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7615810462804143</v>
+        <v>0.7639306370293591</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.06964103952788225</v>
+        <v>-0.06985589153920546</v>
       </c>
       <c r="H10" t="n">
-        <v>-68062158.98303032</v>
+        <v>-59879432.31555602</v>
       </c>
       <c r="I10" t="n">
-        <v>-68062158.98303032</v>
+        <v>-59879432.31555602</v>
       </c>
     </row>
     <row r="11">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>851357508.95</v>
+        <v>929236654.11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7884803464202387</v>
+        <v>0.7914638140234228</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7045838647724482</v>
+        <v>0.7072498853543311</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.08389648164779051</v>
+        <v>-0.08421392866909172</v>
       </c>
       <c r="H11" t="n">
-        <v>-71425899.62533233</v>
+        <v>-78254669.305925</v>
       </c>
       <c r="I11" t="n">
-        <v>-71425899.62533233</v>
+        <v>-78254669.305925</v>
       </c>
     </row>
     <row r="12">
@@ -833,22 +833,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>166983145.53</v>
+        <v>165783076.62</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7479582619448154</v>
+        <v>0.751260515961125</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6518711440980189</v>
+        <v>0.6547491807474654</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.09608711784679647</v>
+        <v>-0.09651133521365962</v>
       </c>
       <c r="H12" t="n">
-        <v>-16044929.18296987</v>
+        <v>-15999946.08042464</v>
       </c>
       <c r="I12" t="n">
-        <v>-16044929.18296987</v>
+        <v>-15999946.08042464</v>
       </c>
     </row>
     <row r="13">
@@ -868,22 +868,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>348227628.42</v>
+        <v>347766801.69</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7095426017048249</v>
+        <v>0.7130798016126879</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6031222483587468</v>
+        <v>0.6061289235629088</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.106420353346078</v>
+        <v>-0.1069508780497791</v>
       </c>
       <c r="H13" t="n">
-        <v>-37058507.26132316</v>
+        <v>-37193964.7973089</v>
       </c>
       <c r="I13" t="n">
-        <v>-37058507.26132316</v>
+        <v>-37193964.7973089</v>
       </c>
     </row>
     <row r="14">
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>288111618.53</v>
+        <v>286514959.36</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6731240468715646</v>
+        <v>0.6768263201051378</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5580391821454744</v>
+        <v>0.5611084780344545</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1150848647260901</v>
+        <v>-0.1157178420706833</v>
       </c>
       <c r="H14" t="n">
-        <v>-33157286.64453993</v>
+        <v>-33154892.81810871</v>
       </c>
       <c r="I14" t="n">
-        <v>-33157286.64453993</v>
+        <v>-33154892.81810871</v>
       </c>
     </row>
     <row r="15">
@@ -938,22 +938,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>205794092.73</v>
+        <v>200982460.28</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6385990212135747</v>
+        <v>0.6424083347829114</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5163455629063576</v>
+        <v>0.5194256295822366</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1222534583072171</v>
+        <v>-0.1229827052006748</v>
       </c>
       <c r="H15" t="n">
-        <v>-25159039.53543863</v>
+        <v>-24717366.66312157</v>
       </c>
       <c r="I15" t="n">
-        <v>-25159039.53543863</v>
+        <v>-24717366.66312157</v>
       </c>
     </row>
     <row r="16">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11939309.63</v>
+        <v>8804292.67</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6058679493535214</v>
+        <v>0.6097363477190296</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4777853084205886</v>
+        <v>0.4808359175133123</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1280826409329328</v>
+        <v>-0.1289004302057173</v>
       </c>
       <c r="H16" t="n">
-        <v>-1529218.308326397</v>
+        <v>-1134877.112820043</v>
       </c>
       <c r="I16" t="n">
-        <v>-1529218.308326397</v>
+        <v>-1134877.112820043</v>
       </c>
     </row>
     <row r="17">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-835777401.8599999</v>
+        <v>-837973082.6800001</v>
       </c>
       <c r="E17" t="n">
         <v>0.9975215395798449</v>
@@ -1020,10 +1020,10 @@
         <v>0.001071141156266053</v>
       </c>
       <c r="H17" t="n">
-        <v>-895235.5726093582</v>
+        <v>-897587.4567016844</v>
       </c>
       <c r="I17" t="n">
-        <v>-895235.5726093582</v>
+        <v>-897587.4567016844</v>
       </c>
     </row>
     <row r="18">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>47727447.23</v>
+        <v>19495500.62999999</v>
       </c>
       <c r="E18" t="n">
         <v>0.9903615297882993</v>
@@ -1055,10 +1055,10 @@
         <v>0.004134433531466697</v>
       </c>
       <c r="H18" t="n">
-        <v>197325.9581990193</v>
+        <v>80602.85151740207</v>
       </c>
       <c r="I18" t="n">
-        <v>98662.97909950967</v>
+        <v>40301.42575870104</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>192923172.86</v>
+        <v>110748422.65</v>
       </c>
       <c r="E19" t="n">
         <v>0.9786688180301472</v>
@@ -1090,10 +1090,10 @@
         <v>0.009214966721668216</v>
       </c>
       <c r="H19" t="n">
-        <v>1777780.617743545</v>
+        <v>1020543.029196997</v>
       </c>
       <c r="I19" t="n">
-        <v>888890.3088717724</v>
+        <v>510271.5145984983</v>
       </c>
     </row>
     <row r="20">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-68061780.77000001</v>
+        <v>28459734.17999999</v>
       </c>
       <c r="E20" t="n">
         <v>0.9655145554862491</v>
@@ -1125,10 +1125,10 @@
         <v>0.01520208972261294</v>
       </c>
       <c r="H20" t="n">
-        <v>-1034681.297946352</v>
+        <v>432647.4324860742</v>
       </c>
       <c r="I20" t="n">
-        <v>-1034681.297946352</v>
+        <v>216323.7162430371</v>
       </c>
     </row>
     <row r="21">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-151998857.02</v>
+        <v>120520575.19</v>
       </c>
       <c r="E21" t="n">
         <v>0.9530263468310431</v>
@@ -1160,10 +1160,10 @@
         <v>0.02107476671306407</v>
       </c>
       <c r="H21" t="n">
-        <v>-3203340.452348882</v>
+        <v>2539943.006253548</v>
       </c>
       <c r="I21" t="n">
-        <v>-3203340.452348882</v>
+        <v>1269971.503126774</v>
       </c>
     </row>
     <row r="22">
@@ -1183,22 +1183,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>603399642.77</v>
+        <v>41495736.82999998</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9361136309390247</v>
+        <v>0.93726391898459</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9658286240687762</v>
+        <v>0.9670154398695024</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02971499312975157</v>
+        <v>0.0297515208849124</v>
       </c>
       <c r="H22" t="n">
-        <v>17930016.2394051</v>
+        <v>1234561.280932573</v>
       </c>
       <c r="I22" t="n">
-        <v>8965008.11970255</v>
+        <v>617280.6404662866</v>
       </c>
     </row>
     <row r="23">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>64469088.74</v>
+        <v>34519707.57000002</v>
       </c>
       <c r="E23" t="n">
-        <v>0.911712454789054</v>
+        <v>0.9132428090891569</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9524849025730056</v>
+        <v>0.9540837026613954</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0407724477839515</v>
+        <v>0.04084089357223852</v>
       </c>
       <c r="H23" t="n">
-        <v>2628562.554330586</v>
+        <v>1409815.703011167</v>
       </c>
       <c r="I23" t="n">
-        <v>1314281.277165293</v>
+        <v>704907.8515055836</v>
       </c>
     </row>
     <row r="24">
@@ -1253,22 +1253,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>865567509.3200001</v>
+        <v>874279275.16</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8762998001065606</v>
+        <v>0.8783257731734563</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9328156461763848</v>
+        <v>0.934972302134487</v>
       </c>
       <c r="G24" t="n">
-        <v>0.05651584606982418</v>
+        <v>0.05664652896103073</v>
       </c>
       <c r="H24" t="n">
-        <v>48918280.11977023</v>
+        <v>49524886.28037989</v>
       </c>
       <c r="I24" t="n">
-        <v>24459140.05988511</v>
+        <v>24762443.14018995</v>
       </c>
     </row>
     <row r="25">
@@ -1288,22 +1288,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>977328303.03</v>
+        <v>857185142.1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8312220858082966</v>
+        <v>0.8337865285685646</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9072305279191392</v>
+        <v>0.9100294844453058</v>
       </c>
       <c r="G25" t="n">
-        <v>0.07600844211084257</v>
+        <v>0.07624295587674124</v>
       </c>
       <c r="H25" t="n">
-        <v>74285201.74414375</v>
+        <v>65354328.96732847</v>
       </c>
       <c r="I25" t="n">
-        <v>37142600.87207188</v>
+        <v>32677164.48366423</v>
       </c>
     </row>
     <row r="26">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>851357508.95</v>
+        <v>929236654.11</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7884803464202387</v>
+        <v>0.7914638140234228</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8823663740141201</v>
+        <v>0.8857050952684282</v>
       </c>
       <c r="G26" t="n">
-        <v>0.09388602759388143</v>
+        <v>0.09424128124500541</v>
       </c>
       <c r="H26" t="n">
-        <v>79930574.57753786</v>
+        <v>87572452.86314833</v>
       </c>
       <c r="I26" t="n">
-        <v>39965287.28876893</v>
+        <v>43786226.43157417</v>
       </c>
     </row>
     <row r="27">
@@ -1358,22 +1358,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>166983145.53</v>
+        <v>165783076.62</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7479582619448154</v>
+        <v>0.751260515961125</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8582083601415686</v>
+        <v>0.861997376412613</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1102500981967532</v>
+        <v>0.110736860451488</v>
       </c>
       <c r="H27" t="n">
-        <v>18409908.19188524</v>
+        <v>18358297.42088728</v>
       </c>
       <c r="I27" t="n">
-        <v>9204954.095942618</v>
+        <v>9179148.710443642</v>
       </c>
     </row>
     <row r="28">
@@ -1393,22 +1393,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>348227628.42</v>
+        <v>347766801.69</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7095426017048249</v>
+        <v>0.7130798016126879</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8347396675430204</v>
+        <v>0.838901007195674</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1251970658381956</v>
+        <v>0.125821205582986</v>
       </c>
       <c r="H28" t="n">
-        <v>43597077.32197744</v>
+        <v>43756438.25037502</v>
       </c>
       <c r="I28" t="n">
-        <v>21798538.66098872</v>
+        <v>21878219.12518751</v>
       </c>
     </row>
     <row r="29">
@@ -1428,22 +1428,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>288111618.53</v>
+        <v>286514959.36</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6731240468715646</v>
+        <v>0.6768263201051378</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8119422188903385</v>
+        <v>0.8164080226826227</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1388181720187739</v>
+        <v>0.1395817025774849</v>
       </c>
       <c r="H29" t="n">
-        <v>39995128.2217049</v>
+        <v>39992245.8413877</v>
       </c>
       <c r="I29" t="n">
-        <v>19997564.11085245</v>
+        <v>19996122.92069385</v>
       </c>
     </row>
     <row r="30">
@@ -1463,22 +1463,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>205794092.73</v>
+        <v>200982460.28</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6385990212135747</v>
+        <v>0.6424083347829114</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7897972294011097</v>
+        <v>0.7945084565797302</v>
       </c>
       <c r="G30" t="n">
-        <v>0.151198208187535</v>
+        <v>0.1521001217968189</v>
       </c>
       <c r="H30" t="n">
-        <v>31115698.07635543</v>
+        <v>30569456.68761231</v>
       </c>
       <c r="I30" t="n">
-        <v>15557849.03817772</v>
+        <v>15284728.34380616</v>
       </c>
     </row>
     <row r="31">
@@ -1498,22 +1498,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11939309.63</v>
+        <v>8804292.67</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6058679493535214</v>
+        <v>0.6097363477190296</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7682855614345683</v>
+        <v>0.7731909832372605</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1624176120810469</v>
+        <v>0.1634546355182309</v>
       </c>
       <c r="H31" t="n">
-        <v>1939154.160000847</v>
+        <v>1439102.449370682</v>
       </c>
       <c r="I31" t="n">
-        <v>969577.0800004237</v>
+        <v>719551.224685341</v>
       </c>
     </row>
     <row r="32">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-835777401.8599999</v>
+        <v>-837973082.6800001</v>
       </c>
       <c r="E32" t="n">
         <v>0.9975215395798449</v>
@@ -1545,10 +1545,10 @@
         <v>0.0008556326727643393</v>
       </c>
       <c r="H32" t="n">
-        <v>-715118.452189507</v>
+        <v>-716997.1484380611</v>
       </c>
       <c r="I32" t="n">
-        <v>-715118.452189507</v>
+        <v>-716997.1484380611</v>
       </c>
     </row>
     <row r="33">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>47727447.23</v>
+        <v>19495500.62999999</v>
       </c>
       <c r="E33" t="n">
         <v>0.9903615297882993</v>
@@ -1580,10 +1580,10 @@
         <v>0.002828930695566667</v>
       </c>
       <c r="H33" t="n">
-        <v>135017.6404899853</v>
+        <v>55151.42015764627</v>
       </c>
       <c r="I33" t="n">
-        <v>67508.82024499266</v>
+        <v>27575.71007882314</v>
       </c>
     </row>
     <row r="34">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>192923172.86</v>
+        <v>110748422.65</v>
       </c>
       <c r="E34" t="n">
         <v>0.9786688180301472</v>
@@ -1615,10 +1615,10 @@
         <v>0.004154192302518012</v>
       </c>
       <c r="H34" t="n">
-        <v>801439.9596723637</v>
+        <v>460070.2448886415</v>
       </c>
       <c r="I34" t="n">
-        <v>400719.9798361819</v>
+        <v>230035.1224443207</v>
       </c>
     </row>
     <row r="35">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-68061780.77000001</v>
+        <v>28459734.17999999</v>
       </c>
       <c r="E35" t="n">
         <v>0.9655145554862491</v>
@@ -1650,10 +1650,10 @@
         <v>0.003541509817362121</v>
       </c>
       <c r="H35" t="n">
-        <v>-241041.4647841034</v>
+        <v>100790.4279979863</v>
       </c>
       <c r="I35" t="n">
-        <v>-241041.4647841034</v>
+        <v>50395.21399899314</v>
       </c>
     </row>
     <row r="36">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-151998857.02</v>
+        <v>120520575.19</v>
       </c>
       <c r="E36" t="n">
         <v>0.9530263468310431</v>
@@ -1685,10 +1685,10 @@
         <v>0.001327621072548912</v>
       </c>
       <c r="H36" t="n">
-        <v>-201796.8855831012</v>
+        <v>160005.6552979596</v>
       </c>
       <c r="I36" t="n">
-        <v>-201796.8855831012</v>
+        <v>80002.82764897982</v>
       </c>
     </row>
     <row r="37">
@@ -1708,22 +1708,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>603399642.77</v>
+        <v>41495736.82999998</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9361136309390247</v>
+        <v>0.93726391898459</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9324750830178969</v>
+        <v>0.9336209204226615</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.003638547921127722</v>
+        <v>-0.003642998561928512</v>
       </c>
       <c r="H37" t="n">
-        <v>-2195498.515809993</v>
+        <v>-151168.9095978539</v>
       </c>
       <c r="I37" t="n">
-        <v>-2195498.515809993</v>
+        <v>-151168.9095978539</v>
       </c>
     </row>
     <row r="38">
@@ -1743,22 +1743,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>64469088.74</v>
+        <v>34519707.57000002</v>
       </c>
       <c r="E38" t="n">
-        <v>0.911712454789054</v>
+        <v>0.9132428090891569</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9002953298849412</v>
+        <v>0.9018065269889697</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.01141712490411284</v>
+        <v>-0.01143628210018721</v>
       </c>
       <c r="H38" t="n">
-        <v>-736051.6385989147</v>
+        <v>-394777.1137864882</v>
       </c>
       <c r="I38" t="n">
-        <v>-736051.6385989147</v>
+        <v>-394777.1137864882</v>
       </c>
     </row>
     <row r="39">
@@ -1778,22 +1778,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>865567509.3200001</v>
+        <v>874279275.16</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8762998001065606</v>
+        <v>0.8783257731734563</v>
       </c>
       <c r="F39" t="n">
-        <v>0.853543845915927</v>
+        <v>0.8555172260785272</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.02275595419063359</v>
+        <v>-0.02280854709492908</v>
       </c>
       <c r="H39" t="n">
-        <v>-19696814.59098673</v>
+        <v>-19941040.02160732</v>
       </c>
       <c r="I39" t="n">
-        <v>-19696814.59098673</v>
+        <v>-19941040.02160732</v>
       </c>
     </row>
     <row r="40">
@@ -1813,22 +1813,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>977328303.03</v>
+        <v>857185142.1</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8312220858082966</v>
+        <v>0.8337865285685646</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7959036446626433</v>
+        <v>0.7983591398693224</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0353184411456533</v>
+        <v>-0.03542738869924222</v>
       </c>
       <c r="H40" t="n">
-        <v>-34517712.15054627</v>
+        <v>-30367831.21639188</v>
       </c>
       <c r="I40" t="n">
-        <v>-34517712.15054627</v>
+        <v>-30367831.21639188</v>
       </c>
     </row>
     <row r="41">
@@ -1848,22 +1848,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>851357508.95</v>
+        <v>929236654.11</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7884803464202387</v>
+        <v>0.7914638140234228</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7433519114744698</v>
+        <v>0.7461646182699713</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.0451284349457689</v>
+        <v>-0.04529919575345154</v>
       </c>
       <c r="H41" t="n">
-        <v>-38420431.95824195</v>
+        <v>-42093673.09581123</v>
       </c>
       <c r="I41" t="n">
-        <v>-38420431.95824195</v>
+        <v>-42093673.09581123</v>
       </c>
     </row>
     <row r="42">
@@ -1883,22 +1883,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>166983145.53</v>
+        <v>165783076.62</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7479582619448154</v>
+        <v>0.751260515961125</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6949999435267605</v>
+        <v>0.6980683865100574</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.05295831841805487</v>
+        <v>-0.05319212945106755</v>
       </c>
       <c r="H42" t="n">
-        <v>-8843146.591426136</v>
+        <v>-8818354.872367291</v>
       </c>
       <c r="I42" t="n">
-        <v>-8843146.591426136</v>
+        <v>-8818354.872367291</v>
       </c>
     </row>
     <row r="43">
@@ -1918,22 +1918,22 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>348227628.42</v>
+        <v>347766801.69</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7095426017048249</v>
+        <v>0.7130798016126879</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6501637228391821</v>
+        <v>0.6534049109648621</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.05937887886564275</v>
+        <v>-0.05967489064782583</v>
       </c>
       <c r="H43" t="n">
-        <v>-20677366.16562124</v>
+        <v>-20752945.86179488</v>
       </c>
       <c r="I43" t="n">
-        <v>-20677366.16562124</v>
+        <v>-20752945.86179488</v>
       </c>
     </row>
     <row r="44">
@@ -1953,22 +1953,22 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>288111618.53</v>
+        <v>286514959.36</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6731240468715646</v>
+        <v>0.6768263201051378</v>
       </c>
       <c r="F44" t="n">
-        <v>0.6083981823442015</v>
+        <v>0.6117444625408259</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.06472586452736306</v>
+        <v>-0.06508185756431184</v>
       </c>
       <c r="H44" t="n">
-        <v>-18648273.58973208</v>
+        <v>-18646925.77511211</v>
       </c>
       <c r="I44" t="n">
-        <v>-18648273.58973208</v>
+        <v>-18646925.77511211</v>
       </c>
     </row>
     <row r="45">
@@ -1988,22 +1988,22 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>205794092.73</v>
+        <v>200982460.28</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6385990212135747</v>
+        <v>0.6424083347829114</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5694032802684611</v>
+        <v>0.5727998443035995</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.0691957409451136</v>
+        <v>-0.06960849047931184</v>
       </c>
       <c r="H45" t="n">
-        <v>-14240074.72857977</v>
+        <v>-13990085.67290905</v>
       </c>
       <c r="I45" t="n">
-        <v>-14240074.72857977</v>
+        <v>-13990085.67290905</v>
       </c>
     </row>
     <row r="46">
@@ -2023,22 +2023,22 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11939309.63</v>
+        <v>8804292.67</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6058679493535214</v>
+        <v>0.6097363477190296</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5329551509496505</v>
+        <v>0.5363580128366308</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.07291279840387088</v>
+        <v>-0.07337833488239887</v>
       </c>
       <c r="H46" t="n">
-        <v>-870528.4761335843</v>
+        <v>-646044.3359419097</v>
       </c>
       <c r="I46" t="n">
-        <v>-870528.4761335843</v>
+        <v>-646044.3359419097</v>
       </c>
     </row>
     <row r="47">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-835777401.8599999</v>
+        <v>-837973082.6800001</v>
       </c>
       <c r="E47" t="n">
         <v>0.9975215395798449</v>
@@ -2070,10 +2070,10 @@
         <v>-0.001075593329743385</v>
       </c>
       <c r="H47" t="n">
-        <v>898956.5985908725</v>
+        <v>901318.2582351102</v>
       </c>
       <c r="I47" t="n">
-        <v>449478.2992954362</v>
+        <v>450659.1291175551</v>
       </c>
     </row>
     <row r="48">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>47727447.23</v>
+        <v>19495500.62999999</v>
       </c>
       <c r="E48" t="n">
         <v>0.9903615297882993</v>
@@ -2105,10 +2105,10 @@
         <v>-0.003609302003152015</v>
       </c>
       <c r="H48" t="n">
-        <v>-172262.7708925711</v>
+        <v>-70365.14947631034</v>
       </c>
       <c r="I48" t="n">
-        <v>-172262.7708925711</v>
+        <v>-70365.14947631034</v>
       </c>
     </row>
     <row r="49">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>192923172.86</v>
+        <v>110748422.65</v>
       </c>
       <c r="E49" t="n">
         <v>0.9786688180301472</v>
@@ -2140,10 +2140,10 @@
         <v>-0.005714096573316341</v>
       </c>
       <c r="H49" t="n">
-        <v>-1102381.640952642</v>
+        <v>-632827.1823645548</v>
       </c>
       <c r="I49" t="n">
-        <v>-1102381.640952642</v>
+        <v>-632827.1823645548</v>
       </c>
     </row>
     <row r="50">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-68061780.77000001</v>
+        <v>28459734.17999999</v>
       </c>
       <c r="E50" t="n">
         <v>0.9655145554862491</v>
@@ -2175,10 +2175,10 @@
         <v>-0.005846989353867849</v>
       </c>
       <c r="H50" t="n">
-        <v>397956.5075674775</v>
+        <v>-166403.7627643689</v>
       </c>
       <c r="I50" t="n">
-        <v>198978.2537837388</v>
+        <v>-166403.7627643689</v>
       </c>
     </row>
     <row r="51">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-151998857.02</v>
+        <v>120520575.19</v>
       </c>
       <c r="E51" t="n">
         <v>0.9530263468310431</v>
@@ -2210,10 +2210,10 @@
         <v>-0.004239805017471676</v>
       </c>
       <c r="H51" t="n">
-        <v>644445.5166433559</v>
+        <v>-510983.7393991344</v>
       </c>
       <c r="I51" t="n">
-        <v>322222.758321678</v>
+        <v>-510983.7393991344</v>
       </c>
     </row>
     <row r="52">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>603399642.77</v>
+        <v>41495736.82999998</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9361136309390247</v>
+        <v>0.93726391898459</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9361199196302535</v>
+        <v>0.9372702303708811</v>
       </c>
       <c r="G52" t="n">
-        <v>6.288691228872878e-06</v>
+        <v>6.311386291035781e-06</v>
       </c>
       <c r="H52" t="n">
-        <v>3794.594040992727</v>
+        <v>261.8956245652905</v>
       </c>
       <c r="I52" t="n">
-        <v>1897.297020496363</v>
+        <v>130.9478122826452</v>
       </c>
     </row>
     <row r="53">
@@ -2268,22 +2268,22 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>64469088.74</v>
+        <v>34519707.57000002</v>
       </c>
       <c r="E53" t="n">
-        <v>0.911712454789054</v>
+        <v>0.9132428090891569</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9188067972807237</v>
+        <v>0.9203490736599507</v>
       </c>
       <c r="G53" t="n">
-        <v>0.007094342491669625</v>
+        <v>0.007106264570793774</v>
       </c>
       <c r="H53" t="n">
-        <v>457365.7956474018</v>
+        <v>245306.1748988528</v>
       </c>
       <c r="I53" t="n">
-        <v>228682.8978237009</v>
+        <v>122653.0874494264</v>
       </c>
     </row>
     <row r="54">
@@ -2303,22 +2303,22 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>865567509.3200001</v>
+        <v>874279275.16</v>
       </c>
       <c r="E54" t="n">
-        <v>0.8762998001065606</v>
+        <v>0.8783257731734563</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8940642073626408</v>
+        <v>0.8961312669792393</v>
       </c>
       <c r="G54" t="n">
-        <v>0.01776440725608019</v>
+        <v>0.017805493805783</v>
       </c>
       <c r="H54" t="n">
-        <v>15376293.74319147</v>
+        <v>15566974.21838583</v>
       </c>
       <c r="I54" t="n">
-        <v>7688146.871595736</v>
+        <v>7783487.109192916</v>
       </c>
     </row>
     <row r="55">
@@ -2338,22 +2338,22 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>977328303.03</v>
+        <v>857185142.1</v>
       </c>
       <c r="E55" t="n">
-        <v>0.8312220858082966</v>
+        <v>0.8337865285685646</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8610244949836867</v>
+        <v>0.8636808908085251</v>
       </c>
       <c r="G55" t="n">
-        <v>0.02980240917539012</v>
+        <v>0.02989436223996045</v>
       </c>
       <c r="H55" t="n">
-        <v>29126737.98558973</v>
+        <v>25625003.14464937</v>
       </c>
       <c r="I55" t="n">
-        <v>14563368.99279486</v>
+        <v>12812501.57232469</v>
       </c>
     </row>
     <row r="56">
@@ -2373,22 +2373,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>851357508.95</v>
+        <v>929236654.11</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7884803464202387</v>
+        <v>0.7914638140234228</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8277988480481667</v>
+        <v>0.8309310899662787</v>
       </c>
       <c r="G56" t="n">
-        <v>0.03931850162792805</v>
+        <v>0.03946727594285593</v>
       </c>
       <c r="H56" t="n">
-        <v>33474101.60159935</v>
+        <v>36674439.44397554</v>
       </c>
       <c r="I56" t="n">
-        <v>16737050.80079967</v>
+        <v>18337219.72198777</v>
       </c>
     </row>
     <row r="57">
@@ -2408,22 +2408,22 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>166983145.53</v>
+        <v>165783076.62</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7479582619448154</v>
+        <v>0.751260515961125</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7949980267368288</v>
+        <v>0.7985079617097887</v>
       </c>
       <c r="G57" t="n">
-        <v>0.04703976479201344</v>
+        <v>0.04724744574866369</v>
       </c>
       <c r="H57" t="n">
-        <v>7854847.88996175</v>
+        <v>7832826.918650005</v>
       </c>
       <c r="I57" t="n">
-        <v>3927423.944980875</v>
+        <v>3916413.459325003</v>
       </c>
     </row>
     <row r="58">
@@ -2443,22 +2443,22 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>348227628.42</v>
+        <v>347766801.69</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7095426017048249</v>
+        <v>0.7130798016126879</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7630787832539362</v>
+        <v>0.766882878767156</v>
       </c>
       <c r="G58" t="n">
-        <v>0.05353618154911133</v>
+        <v>0.05380307715446808</v>
       </c>
       <c r="H58" t="n">
-        <v>18642777.5355096</v>
+        <v>18710924.06308967</v>
       </c>
       <c r="I58" t="n">
-        <v>9321388.767754801</v>
+        <v>9355462.031544836</v>
       </c>
     </row>
     <row r="59">
@@ -2478,22 +2478,22 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>288111618.53</v>
+        <v>286514959.36</v>
       </c>
       <c r="E59" t="n">
-        <v>0.6731240468715646</v>
+        <v>0.6768263201051378</v>
       </c>
       <c r="F59" t="n">
-        <v>0.7322641766750169</v>
+        <v>0.7362917336347434</v>
       </c>
       <c r="G59" t="n">
-        <v>0.05914012980345229</v>
+        <v>0.05946541352960566</v>
       </c>
       <c r="H59" t="n">
-        <v>17038958.51774693</v>
+        <v>17037730.54076056</v>
       </c>
       <c r="I59" t="n">
-        <v>8519479.258873465</v>
+        <v>8518865.270380281</v>
       </c>
     </row>
     <row r="60">
@@ -2513,22 +2513,22 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>205794092.73</v>
+        <v>200982460.28</v>
       </c>
       <c r="E60" t="n">
-        <v>0.6385990212135747</v>
+        <v>0.6424083347829114</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7026320481484367</v>
+        <v>0.7068233232621161</v>
       </c>
       <c r="G60" t="n">
-        <v>0.06403302693486201</v>
+        <v>0.06441498847920468</v>
       </c>
       <c r="H60" t="n">
-        <v>13177618.68281558</v>
+        <v>12946282.86345841</v>
       </c>
       <c r="I60" t="n">
-        <v>6588809.34140779</v>
+        <v>6473141.431729207</v>
       </c>
     </row>
     <row r="61">
@@ -2548,22 +2548,22 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11939309.63</v>
+        <v>8804292.67</v>
       </c>
       <c r="E61" t="n">
-        <v>0.6058679493535214</v>
+        <v>0.6097363477190296</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6741877096380062</v>
+        <v>0.6784923310968078</v>
       </c>
       <c r="G61" t="n">
-        <v>0.06831976028448483</v>
+        <v>0.06875598337777822</v>
       </c>
       <c r="H61" t="n">
-        <v>815690.7718838414</v>
+        <v>605347.8004716146</v>
       </c>
       <c r="I61" t="n">
-        <v>407845.3859419207</v>
+        <v>302673.9002358073</v>
       </c>
     </row>
     <row r="62">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-835777401.8599999</v>
+        <v>-837973082.6800001</v>
       </c>
       <c r="E62" t="n">
         <v>0.9975215395798449</v>
@@ -2595,10 +2595,10 @@
         <v>-0.00138963539714354</v>
       </c>
       <c r="H62" t="n">
-        <v>1161425.861757317</v>
+        <v>1164477.057545619</v>
       </c>
       <c r="I62" t="n">
-        <v>580712.9308786587</v>
+        <v>582238.5287728094</v>
       </c>
     </row>
     <row r="63">
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>47727447.23</v>
+        <v>19495500.62999999</v>
       </c>
       <c r="E63" t="n">
         <v>0.9903615297882993</v>
@@ -2630,10 +2630,10 @@
         <v>-0.004868292240044036</v>
       </c>
       <c r="H63" t="n">
-        <v>-232351.1609869203</v>
+        <v>-94909.79443280258</v>
       </c>
       <c r="I63" t="n">
-        <v>-232351.1609869203</v>
+        <v>-94909.79443280258</v>
       </c>
     </row>
     <row r="64">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>192923172.86</v>
+        <v>110748422.65</v>
       </c>
       <c r="E64" t="n">
         <v>0.9786688180301472</v>
@@ -2665,10 +2665,10 @@
         <v>-0.008752967619160001</v>
       </c>
       <c r="H64" t="n">
-        <v>-1688650.285029188</v>
+        <v>-969377.3573284962</v>
       </c>
       <c r="I64" t="n">
-        <v>-1688650.285029188</v>
+        <v>-969377.3573284962</v>
       </c>
     </row>
     <row r="65">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-68061780.77000001</v>
+        <v>28459734.17999999</v>
       </c>
       <c r="E65" t="n">
         <v>0.9655145554862491</v>
@@ -2700,10 +2700,10 @@
         <v>-0.01121800353180191</v>
       </c>
       <c r="H65" t="n">
-        <v>763517.2970585875</v>
+        <v>-319261.3985453835</v>
       </c>
       <c r="I65" t="n">
-        <v>381758.6485292938</v>
+        <v>-319261.3985453835</v>
       </c>
     </row>
     <row r="66">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>-151998857.02</v>
+        <v>120520575.19</v>
       </c>
       <c r="E66" t="n">
         <v>0.9530263468310431</v>
@@ -2735,10 +2735,10 @@
         <v>-0.0120777624290116</v>
       </c>
       <c r="H66" t="n">
-        <v>1835806.084568862</v>
+        <v>-1455618.874952649</v>
       </c>
       <c r="I66" t="n">
-        <v>917903.0422844308</v>
+        <v>-1455618.874952649</v>
       </c>
     </row>
     <row r="67">
@@ -2758,22 +2758,22 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>603399642.77</v>
+        <v>41495736.82999998</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9361136309390247</v>
+        <v>0.93726391898459</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9244537320677408</v>
+        <v>0.9255897136521459</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.01165989887128382</v>
+        <v>-0.01167420533244412</v>
       </c>
       <c r="H67" t="n">
-        <v>-7035578.813666986</v>
+        <v>-484429.7521744837</v>
       </c>
       <c r="I67" t="n">
-        <v>-7035578.813666986</v>
+        <v>-484429.7521744837</v>
       </c>
     </row>
     <row r="68">
@@ -2793,22 +2793,22 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>64469088.74</v>
+        <v>34519707.57000002</v>
       </c>
       <c r="E68" t="n">
-        <v>0.911712454789054</v>
+        <v>0.9132428090891569</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9020597771058859</v>
+        <v>0.9035739413886649</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.009652677683168132</v>
+        <v>-0.009668867700492023</v>
       </c>
       <c r="H68" t="n">
-        <v>-622299.3341347839</v>
+        <v>-333766.4855540032</v>
       </c>
       <c r="I68" t="n">
-        <v>-622299.3341347839</v>
+        <v>-333766.4855540032</v>
       </c>
     </row>
     <row r="69">
@@ -2828,22 +2828,22 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>865567509.3200001</v>
+        <v>874279275.16</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8762998001065606</v>
+        <v>0.8783257731734563</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8700274714769884</v>
+        <v>0.8720389628503553</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.006272328629572166</v>
+        <v>-0.006286810323100966</v>
       </c>
       <c r="H69" t="n">
-        <v>-5429123.869535309</v>
+        <v>-5496427.972349118</v>
       </c>
       <c r="I69" t="n">
-        <v>-5429123.869535309</v>
+        <v>-5496427.972349118</v>
       </c>
     </row>
     <row r="70">
@@ -2863,22 +2863,22 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>977328303.03</v>
+        <v>857185142.1</v>
       </c>
       <c r="E70" t="n">
-        <v>0.8312220858082966</v>
+        <v>0.8337865285685646</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8281523730651644</v>
+        <v>0.8307073618477882</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.003069712743132169</v>
+        <v>-0.003079166720776461</v>
       </c>
       <c r="H70" t="n">
-        <v>-3000117.146034929</v>
+        <v>-2639415.963098362</v>
       </c>
       <c r="I70" t="n">
-        <v>-3000117.146034929</v>
+        <v>-2639415.963098362</v>
       </c>
     </row>
     <row r="71">
@@ -2898,22 +2898,22 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>851357508.95</v>
+        <v>929236654.11</v>
       </c>
       <c r="E71" t="n">
-        <v>0.7884803464202387</v>
+        <v>0.7914638140234228</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7871018476811552</v>
+        <v>0.7900801060240177</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.001378498739083467</v>
+        <v>-0.001383707999405126</v>
       </c>
       <c r="H71" t="n">
-        <v>-1173595.252596817</v>
+        <v>-1285792.191632461</v>
       </c>
       <c r="I71" t="n">
-        <v>-1173595.252596817</v>
+        <v>-1285792.191632461</v>
       </c>
     </row>
     <row r="72">
@@ -2933,22 +2933,22 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>166983145.53</v>
+        <v>165783076.62</v>
       </c>
       <c r="E72" t="n">
-        <v>0.7479582619448154</v>
+        <v>0.751260515961125</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7473698415243564</v>
+        <v>0.7506694989807172</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.0005884204204590349</v>
+        <v>-0.0005910169804077547</v>
       </c>
       <c r="H72" t="n">
-        <v>-98256.2927023348</v>
+        <v>-97980.61334665984</v>
       </c>
       <c r="I72" t="n">
-        <v>-98256.2927023348</v>
+        <v>-97980.61334665984</v>
       </c>
     </row>
     <row r="73">
@@ -2968,22 +2968,22 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>348227628.42</v>
+        <v>347766801.69</v>
       </c>
       <c r="E73" t="n">
-        <v>0.7095426017048249</v>
+        <v>0.7130798016126879</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7092994694404136</v>
+        <v>0.7128354683771767</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.0002431322644113054</v>
+        <v>-0.0002443332355112071</v>
       </c>
       <c r="H73" t="n">
-        <v>-84665.37182833326</v>
+        <v>-84970.98786030203</v>
       </c>
       <c r="I73" t="n">
-        <v>-84665.37182833326</v>
+        <v>-84970.98786030203</v>
       </c>
     </row>
     <row r="74">
@@ -3003,22 +3003,22 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>288111618.53</v>
+        <v>286514959.36</v>
       </c>
       <c r="E74" t="n">
-        <v>0.6731240468715646</v>
+        <v>0.6768263201051378</v>
       </c>
       <c r="F74" t="n">
-        <v>0.6730260087674014</v>
+        <v>0.676727750575811</v>
       </c>
       <c r="G74" t="n">
-        <v>-9.803810416320058e-05</v>
+        <v>-9.85695293267419e-05</v>
       </c>
       <c r="H74" t="n">
-        <v>-28245.91686807245</v>
+        <v>-28241.64468918578</v>
       </c>
       <c r="I74" t="n">
-        <v>-28245.91686807245</v>
+        <v>-28241.64468918578</v>
       </c>
     </row>
     <row r="75">
@@ -3038,22 +3038,22 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>205794092.73</v>
+        <v>200982460.28</v>
       </c>
       <c r="E75" t="n">
-        <v>0.6385990212135747</v>
+        <v>0.6424083347829114</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6385600345043863</v>
+        <v>0.642369122932283</v>
       </c>
       <c r="G75" t="n">
-        <v>-3.898670918844882e-05</v>
+        <v>-3.92118506283845e-05</v>
       </c>
       <c r="H75" t="n">
-        <v>-8023.234445965179</v>
+        <v>-7880.894211424582</v>
       </c>
       <c r="I75" t="n">
-        <v>-8023.234445965179</v>
+        <v>-7880.894211424582</v>
       </c>
     </row>
     <row r="76">
@@ -3073,22 +3073,22 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11939309.63</v>
+        <v>8804292.67</v>
       </c>
       <c r="E76" t="n">
-        <v>0.6058679493535214</v>
+        <v>0.6097363477190296</v>
       </c>
       <c r="F76" t="n">
-        <v>0.6058525305053886</v>
+        <v>0.6097208321734507</v>
       </c>
       <c r="G76" t="n">
-        <v>-1.541884813283101e-05</v>
+        <v>-1.551554557888135e-05</v>
       </c>
       <c r="H76" t="n">
-        <v>-184.0904019958168</v>
+        <v>-136.603404211196</v>
       </c>
       <c r="I76" t="n">
-        <v>-184.0904019958168</v>
+        <v>-136.603404211196</v>
       </c>
     </row>
     <row r="77">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-835777401.8599999</v>
+        <v>-837973082.6800001</v>
       </c>
       <c r="E77" t="n">
         <v>0.9975215395798449</v>
@@ -3120,10 +3120,10 @@
         <v>0.001386210407362531</v>
       </c>
       <c r="H77" t="n">
-        <v>-1158563.332696749</v>
+        <v>-1161607.008300679</v>
       </c>
       <c r="I77" t="n">
-        <v>-1158563.332696749</v>
+        <v>-1161607.008300679</v>
       </c>
     </row>
     <row r="78">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>47727447.23</v>
+        <v>19495500.62999999</v>
       </c>
       <c r="E78" t="n">
         <v>0.9903615297882993</v>
@@ -3155,10 +3155,10 @@
         <v>0.004890978187868655</v>
       </c>
       <c r="H78" t="n">
-        <v>233433.9033645823</v>
+        <v>95352.06834290958</v>
       </c>
       <c r="I78" t="n">
-        <v>116716.9516822912</v>
+        <v>47676.03417145479</v>
       </c>
     </row>
     <row r="79">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>192923172.86</v>
+        <v>110748422.65</v>
       </c>
       <c r="E79" t="n">
         <v>0.9786688180301472</v>
@@ -3190,10 +3190,10 @@
         <v>0.008825570306637109</v>
       </c>
       <c r="H79" t="n">
-        <v>1702657.025855434</v>
+        <v>977417.9904467367</v>
       </c>
       <c r="I79" t="n">
-        <v>851328.5129277171</v>
+        <v>488708.9952233683</v>
       </c>
     </row>
     <row r="80">
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-68061780.77000001</v>
+        <v>28459734.17999999</v>
       </c>
       <c r="E80" t="n">
         <v>0.9655145554862491</v>
@@ -3225,10 +3225,10 @@
         <v>0.01134479629056684</v>
       </c>
       <c r="H80" t="n">
-        <v>-772147.0380088695</v>
+        <v>322869.8867557822</v>
       </c>
       <c r="I80" t="n">
-        <v>-772147.0380088695</v>
+        <v>161434.9433778911</v>
       </c>
     </row>
     <row r="81">
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-151998857.02</v>
+        <v>120520575.19</v>
       </c>
       <c r="E81" t="n">
         <v>0.9530263468310431</v>
@@ -3260,10 +3260,10 @@
         <v>0.0122280753910069</v>
       </c>
       <c r="H81" t="n">
-        <v>-1858653.482987438</v>
+        <v>1473734.679590835</v>
       </c>
       <c r="I81" t="n">
-        <v>-1858653.482987438</v>
+        <v>736867.3397954177</v>
       </c>
     </row>
     <row r="82">
@@ -3283,22 +3283,22 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>603399642.77</v>
+        <v>41495736.82999998</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9361136309390247</v>
+        <v>0.93726391898459</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9479197183316199</v>
+        <v>0.9490845285066654</v>
       </c>
       <c r="G82" t="n">
-        <v>0.01180608739259525</v>
+        <v>0.01182060952207531</v>
       </c>
       <c r="H82" t="n">
-        <v>7123788.915203378</v>
+        <v>490504.9018982289</v>
       </c>
       <c r="I82" t="n">
-        <v>3561894.457601689</v>
+        <v>245252.4509491145</v>
       </c>
     </row>
     <row r="83">
@@ -3318,22 +3318,22 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>64469088.74</v>
+        <v>34519707.57000002</v>
       </c>
       <c r="E83" t="n">
-        <v>0.911712454789054</v>
+        <v>0.9132428090891569</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9214677004806544</v>
+        <v>0.9230144382935129</v>
       </c>
       <c r="G83" t="n">
-        <v>0.009755245691600356</v>
+        <v>0.009771629204356036</v>
       </c>
       <c r="H83" t="n">
-        <v>628911.800172286</v>
+        <v>337313.7826168423</v>
       </c>
       <c r="I83" t="n">
-        <v>314455.900086143</v>
+        <v>168656.8913084212</v>
       </c>
     </row>
     <row r="84">
@@ -3353,22 +3353,22 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>865567509.3200001</v>
+        <v>874279275.16</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8762998001065606</v>
+        <v>0.8783257731734563</v>
       </c>
       <c r="F84" t="n">
-        <v>0.8826161392294317</v>
+        <v>0.8846567405439828</v>
       </c>
       <c r="G84" t="n">
-        <v>0.006316339122871106</v>
+        <v>0.006330967370526519</v>
       </c>
       <c r="H84" t="n">
-        <v>5467217.922604017</v>
+        <v>5535033.563765536</v>
       </c>
       <c r="I84" t="n">
-        <v>2733608.961302008</v>
+        <v>2767516.781882768</v>
       </c>
     </row>
     <row r="85">
@@ -3388,22 +3388,22 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>977328303.03</v>
+        <v>857185142.1</v>
       </c>
       <c r="E85" t="n">
-        <v>0.8312220858082966</v>
+        <v>0.8337865285685646</v>
       </c>
       <c r="F85" t="n">
-        <v>0.834302471445618</v>
+        <v>0.8368764237722052</v>
       </c>
       <c r="G85" t="n">
-        <v>0.003080385637321381</v>
+        <v>0.003089895203640558</v>
       </c>
       <c r="H85" t="n">
-        <v>3010548.067601291</v>
+        <v>2648612.25920674</v>
       </c>
       <c r="I85" t="n">
-        <v>1505274.033800645</v>
+        <v>1324306.12960337</v>
       </c>
     </row>
     <row r="86">
@@ -3423,22 +3423,22 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>851357508.95</v>
+        <v>929236654.11</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7884803464202387</v>
+        <v>0.7914638140234228</v>
       </c>
       <c r="F86" t="n">
-        <v>0.7898610767706593</v>
+        <v>0.7928497625860698</v>
       </c>
       <c r="G86" t="n">
-        <v>0.001380730350420634</v>
+        <v>0.001385948562646955</v>
       </c>
       <c r="H86" t="n">
-        <v>1175495.151665771</v>
+        <v>1287874.20512262</v>
       </c>
       <c r="I86" t="n">
-        <v>587747.5758328857</v>
+        <v>643937.1025613101</v>
       </c>
     </row>
     <row r="87">
@@ -3458,22 +3458,22 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>166983145.53</v>
+        <v>165783076.62</v>
       </c>
       <c r="E87" t="n">
-        <v>0.7479582619448154</v>
+        <v>0.751260515961125</v>
       </c>
       <c r="F87" t="n">
-        <v>0.7485467538993952</v>
+        <v>0.7518516126765387</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0005884919545797729</v>
+        <v>0.0005910967154136859</v>
       </c>
       <c r="H87" t="n">
-        <v>98268.23769482836</v>
+        <v>97993.83206125743</v>
       </c>
       <c r="I87" t="n">
-        <v>49134.11884741418</v>
+        <v>48996.91603062872</v>
       </c>
     </row>
     <row r="88">
@@ -3493,22 +3493,22 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>348227628.42</v>
+        <v>347766801.69</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7095426017048249</v>
+        <v>0.7130798016126879</v>
       </c>
       <c r="F88" t="n">
-        <v>0.7097849113610617</v>
+        <v>0.7133233293846294</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0002423096562368388</v>
+        <v>0.0002435277719414763</v>
       </c>
       <c r="H88" t="n">
-        <v>84378.91693461983</v>
+        <v>84690.87437077895</v>
       </c>
       <c r="I88" t="n">
-        <v>42189.45846730992</v>
+        <v>42345.43718538948</v>
       </c>
     </row>
     <row r="89">
@@ -3528,22 +3528,22 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>288111618.53</v>
+        <v>286514959.36</v>
       </c>
       <c r="E89" t="n">
-        <v>0.6731240468715646</v>
+        <v>0.6768263201051378</v>
       </c>
       <c r="F89" t="n">
-        <v>0.6732214938079154</v>
+        <v>0.6769243027127022</v>
       </c>
       <c r="G89" t="n">
-        <v>9.744693635083124e-05</v>
+        <v>9.798260756443966e-05</v>
       </c>
       <c r="H89" t="n">
-        <v>28075.59455282788</v>
+        <v>28073.48282431226</v>
       </c>
       <c r="I89" t="n">
-        <v>14037.79727641394</v>
+        <v>14036.74141215613</v>
       </c>
     </row>
     <row r="90">
@@ -3563,22 +3563,22 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>205794092.73</v>
+        <v>200982460.28</v>
       </c>
       <c r="E90" t="n">
-        <v>0.6385990212135747</v>
+        <v>0.6424083347829114</v>
       </c>
       <c r="F90" t="n">
-        <v>0.638637362916028</v>
+        <v>0.6424469098247421</v>
       </c>
       <c r="G90" t="n">
-        <v>3.834170245331503e-05</v>
+        <v>3.857504183069072e-05</v>
       </c>
       <c r="H90" t="n">
-        <v>7890.495870103581</v>
+        <v>7752.906812536135</v>
       </c>
       <c r="I90" t="n">
-        <v>3945.247935051791</v>
+        <v>3876.453406268068</v>
       </c>
     </row>
     <row r="91">
@@ -3598,22 +3598,22 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11939309.63</v>
+        <v>8804292.67</v>
       </c>
       <c r="E91" t="n">
-        <v>0.6058679493535214</v>
+        <v>0.6097363477190296</v>
       </c>
       <c r="F91" t="n">
-        <v>0.6058826883966526</v>
+        <v>0.6097511888543204</v>
       </c>
       <c r="G91" t="n">
-        <v>1.473904313120666e-05</v>
+        <v>1.484113529082176e-05</v>
       </c>
       <c r="H91" t="n">
-        <v>175.9739995934011</v>
+        <v>130.6656986554603</v>
       </c>
       <c r="I91" t="n">
-        <v>87.98699979670054</v>
+        <v>65.33284932773017</v>
       </c>
     </row>
     <row r="92">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-835777401.8599999</v>
+        <v>-837973082.6800001</v>
       </c>
       <c r="E92" t="n">
         <v>0.9975215395798449</v>
@@ -3645,10 +3645,10 @@
         <v>0.0004267113511314813</v>
       </c>
       <c r="H92" t="n">
-        <v>-356635.7043928396</v>
+        <v>-357572.6263221953</v>
       </c>
       <c r="I92" t="n">
-        <v>-356635.7043928396</v>
+        <v>-357572.6263221953</v>
       </c>
     </row>
     <row r="93">
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>47727447.23</v>
+        <v>19495500.62999999</v>
       </c>
       <c r="E93" t="n">
         <v>0.9903615297882993</v>
@@ -3680,10 +3680,10 @@
         <v>0.001651293781163021</v>
       </c>
       <c r="H93" t="n">
-        <v>78812.03680168527</v>
+        <v>32192.79895097875</v>
       </c>
       <c r="I93" t="n">
-        <v>39406.01840084264</v>
+        <v>16096.39947548938</v>
       </c>
     </row>
     <row r="94">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>192923172.86</v>
+        <v>110748422.65</v>
       </c>
       <c r="E94" t="n">
         <v>0.9786688180301472</v>
@@ -3715,10 +3715,10 @@
         <v>0.003673721028352284</v>
       </c>
       <c r="H94" t="n">
-        <v>708745.9169922245</v>
+        <v>406858.8091461514</v>
       </c>
       <c r="I94" t="n">
-        <v>354372.9584961123</v>
+        <v>203429.4045730757</v>
       </c>
     </row>
     <row r="95">
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-68061780.77000001</v>
+        <v>28459734.17999999</v>
       </c>
       <c r="E95" t="n">
         <v>0.9655145554862491</v>
@@ -3750,10 +3750,10 @@
         <v>0.006050833538578271</v>
       </c>
       <c r="H95" t="n">
-        <v>-411830.5057784776</v>
+        <v>172205.1140753663</v>
       </c>
       <c r="I95" t="n">
-        <v>-411830.5057784776</v>
+        <v>86102.55703768316</v>
       </c>
     </row>
     <row r="96">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-151998857.02</v>
+        <v>120520575.19</v>
       </c>
       <c r="E96" t="n">
         <v>0.9530263468310431</v>
@@ -3785,10 +3785,10 @@
         <v>0.008373224807978752</v>
       </c>
       <c r="H96" t="n">
-        <v>-1272720.600384279</v>
+        <v>1009145.870052776</v>
       </c>
       <c r="I96" t="n">
-        <v>-1272720.600384279</v>
+        <v>504572.9350263882</v>
       </c>
     </row>
     <row r="97">
@@ -3808,22 +3808,22 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>603399642.77</v>
+        <v>41495736.82999998</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9361136309390247</v>
+        <v>0.93726391898459</v>
       </c>
       <c r="F97" t="n">
-        <v>0.9478880569000612</v>
+        <v>0.9490528208351157</v>
       </c>
       <c r="G97" t="n">
-        <v>0.01177442596103651</v>
+        <v>0.01178890185052561</v>
       </c>
       <c r="H97" t="n">
-        <v>7104684.418711241</v>
+        <v>489189.1687041106</v>
       </c>
       <c r="I97" t="n">
-        <v>3552342.209355621</v>
+        <v>244594.5843520553</v>
       </c>
     </row>
     <row r="98">
@@ -3843,22 +3843,22 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>64469088.74</v>
+        <v>34519707.57000002</v>
       </c>
       <c r="E98" t="n">
-        <v>0.911712454789054</v>
+        <v>0.9132428090891569</v>
       </c>
       <c r="F98" t="n">
-        <v>0.9278074829601938</v>
+        <v>0.9293648610540347</v>
       </c>
       <c r="G98" t="n">
-        <v>0.01609502817113972</v>
+        <v>0.01612205196487781</v>
       </c>
       <c r="H98" t="n">
-        <v>1037631.799438007</v>
+        <v>556528.5192559264</v>
       </c>
       <c r="I98" t="n">
-        <v>518815.8997190034</v>
+        <v>278264.2596279632</v>
       </c>
     </row>
     <row r="99">
@@ -3878,22 +3878,22 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>865567509.3200001</v>
+        <v>874279275.16</v>
       </c>
       <c r="E99" t="n">
-        <v>0.8762998001065606</v>
+        <v>0.8783257731734563</v>
       </c>
       <c r="F99" t="n">
-        <v>0.8984828178067027</v>
+        <v>0.9005600940055343</v>
       </c>
       <c r="G99" t="n">
-        <v>0.02218301770014208</v>
+        <v>0.02223432083207799</v>
       </c>
       <c r="H99" t="n">
-        <v>19200899.37991346</v>
+        <v>19439005.90074403</v>
       </c>
       <c r="I99" t="n">
-        <v>9600449.689956728</v>
+        <v>9719502.950372016</v>
       </c>
     </row>
     <row r="100">
@@ -3913,22 +3913,22 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>977328303.03</v>
+        <v>857185142.1</v>
       </c>
       <c r="E100" t="n">
-        <v>0.8312220858082966</v>
+        <v>0.8337865285685646</v>
       </c>
       <c r="F100" t="n">
-        <v>0.8608296090849302</v>
+        <v>0.863485402981736</v>
       </c>
       <c r="G100" t="n">
-        <v>0.02960752327663363</v>
+        <v>0.02969887441317143</v>
       </c>
       <c r="H100" t="n">
-        <v>28936270.48087357</v>
+        <v>25457433.88406441</v>
       </c>
       <c r="I100" t="n">
-        <v>14468135.24043678</v>
+        <v>12728716.9420322</v>
       </c>
     </row>
     <row r="101">
@@ -3948,22 +3948,22 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>851357508.95</v>
+        <v>929236654.11</v>
       </c>
       <c r="E101" t="n">
-        <v>0.7884803464202387</v>
+        <v>0.7914638140234228</v>
       </c>
       <c r="F101" t="n">
-        <v>0.8247723135866096</v>
+        <v>0.8278931061235369</v>
       </c>
       <c r="G101" t="n">
-        <v>0.03629196716637095</v>
+        <v>0.03642929210011414</v>
       </c>
       <c r="H101" t="n">
-        <v>30897438.76165676</v>
+        <v>33851433.50270592</v>
       </c>
       <c r="I101" t="n">
-        <v>15448719.38082838</v>
+        <v>16925716.75135296</v>
       </c>
     </row>
     <row r="102">
@@ -3983,22 +3983,22 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>166983145.53</v>
+        <v>165783076.62</v>
       </c>
       <c r="E102" t="n">
-        <v>0.7479582619448154</v>
+        <v>0.751260515961125</v>
       </c>
       <c r="F102" t="n">
-        <v>0.7902480681791287</v>
+        <v>0.7937370416694218</v>
       </c>
       <c r="G102" t="n">
-        <v>0.04228980623431333</v>
+        <v>0.04247652570829685</v>
       </c>
       <c r="H102" t="n">
-        <v>7061684.868859844</v>
+        <v>7041889.116049977</v>
       </c>
       <c r="I102" t="n">
-        <v>3530842.434429922</v>
+        <v>3520944.558024989</v>
       </c>
     </row>
     <row r="103">
@@ -4018,22 +4018,22 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>348227628.42</v>
+        <v>347766801.69</v>
       </c>
       <c r="E103" t="n">
-        <v>0.7095426017048249</v>
+        <v>0.7130798016126879</v>
       </c>
       <c r="F103" t="n">
-        <v>0.7571943060295172</v>
+        <v>0.7609690657464063</v>
       </c>
       <c r="G103" t="n">
-        <v>0.04765170432469235</v>
+        <v>0.04788926413371841</v>
       </c>
       <c r="H103" t="n">
-        <v>16593639.98715867</v>
+        <v>16654296.22307088</v>
       </c>
       <c r="I103" t="n">
-        <v>8296819.993579337</v>
+        <v>8327148.11153544</v>
       </c>
     </row>
     <row r="104">
@@ -4053,22 +4053,22 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>288111618.53</v>
+        <v>286514959.36</v>
       </c>
       <c r="E104" t="n">
-        <v>0.6731240468715646</v>
+        <v>0.6768263201051378</v>
       </c>
       <c r="F104" t="n">
-        <v>0.725549413614877</v>
+        <v>0.7295400427060942</v>
       </c>
       <c r="G104" t="n">
-        <v>0.05242536674331244</v>
+        <v>0.05271372260095641</v>
       </c>
       <c r="H104" t="n">
-        <v>15104357.26444458</v>
+        <v>15103270.08872734</v>
       </c>
       <c r="I104" t="n">
-        <v>7552178.63222229</v>
+        <v>7551635.044363671</v>
       </c>
     </row>
     <row r="105">
@@ -4088,22 +4088,22 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>205794092.73</v>
+        <v>200982460.28</v>
       </c>
       <c r="E105" t="n">
-        <v>0.6385990212135747</v>
+        <v>0.6424083347829114</v>
       </c>
       <c r="F105" t="n">
-        <v>0.695253298738266</v>
+        <v>0.6994005629016571</v>
       </c>
       <c r="G105" t="n">
-        <v>0.05665427752469132</v>
+        <v>0.05699222811874571</v>
       </c>
       <c r="H105" t="n">
-        <v>11659115.64246748</v>
+        <v>11454438.22414451</v>
       </c>
       <c r="I105" t="n">
-        <v>5829557.82123374</v>
+        <v>5727219.112072255</v>
       </c>
     </row>
     <row r="106">
@@ -4123,22 +4123,22 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11939309.63</v>
+        <v>8804292.67</v>
       </c>
       <c r="E106" t="n">
-        <v>0.6058679493535214</v>
+        <v>0.6097363477190296</v>
       </c>
       <c r="F106" t="n">
-        <v>0.6662476753767248</v>
+        <v>0.6705016035786937</v>
       </c>
       <c r="G106" t="n">
-        <v>0.06037972602320341</v>
+        <v>0.06076525585966408</v>
       </c>
       <c r="H106" t="n">
-        <v>720892.2443655941</v>
+        <v>534995.096755915</v>
       </c>
       <c r="I106" t="n">
-        <v>360446.1221827971</v>
+        <v>267497.5483779575</v>
       </c>
     </row>
   </sheetData>
@@ -4214,22 +4214,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2768013599.56</v>
+        <v>2424318031.05</v>
       </c>
       <c r="D2" t="n">
-        <v>2669863190.42</v>
+        <v>2289576861.54</v>
       </c>
       <c r="E2" t="n">
-        <v>-98150409.13999987</v>
+        <v>-134741169.5100002</v>
       </c>
       <c r="F2" t="n">
-        <v>-98150409.13999987</v>
+        <v>-134741169.5100002</v>
       </c>
       <c r="G2" t="n">
-        <v>-5.452800507777771</v>
+        <v>-8.421323094375015</v>
       </c>
       <c r="H2" t="n">
-        <v>-5.452800507777771</v>
+        <v>-8.421323094375015</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -4247,22 +4247,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2768013599.56</v>
+        <v>2424318031.05</v>
       </c>
       <c r="D3" t="n">
-        <v>2975572356.07</v>
+        <v>2570934764.39</v>
       </c>
       <c r="E3" t="n">
-        <v>207558756.5100002</v>
+        <v>146616733.3399997</v>
       </c>
       <c r="F3" t="n">
-        <v>103779378.2550001</v>
+        <v>73308366.66999984</v>
       </c>
       <c r="G3" t="n">
-        <v>11.53104202833335</v>
+        <v>9.16354583374998</v>
       </c>
       <c r="H3" t="n">
-        <v>5.765521014166673</v>
+        <v>4.58177291687499</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -4280,22 +4280,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2768013599.56</v>
+        <v>2424318031.05</v>
       </c>
       <c r="D4" t="n">
-        <v>2768916924.63</v>
+        <v>2378544175.29</v>
       </c>
       <c r="E4" t="n">
-        <v>903325.0700001717</v>
+        <v>-45773855.76000023</v>
       </c>
       <c r="F4" t="n">
-        <v>451662.5350000858</v>
+        <v>-45773855.76000023</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05018472611112065</v>
+        <v>-2.860865985000014</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02509236305556032</v>
+        <v>-2.860865985000014</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -4313,22 +4313,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2768013599.56</v>
+        <v>2424318031.05</v>
       </c>
       <c r="D5" t="n">
-        <v>2850719213.32</v>
+        <v>2458096736.1</v>
       </c>
       <c r="E5" t="n">
-        <v>82705613.76000023</v>
+        <v>33778705.04999971</v>
       </c>
       <c r="F5" t="n">
-        <v>41352806.88000011</v>
+        <v>16889352.52499986</v>
       </c>
       <c r="G5" t="n">
-        <v>4.594756320000013</v>
+        <v>2.111169065624982</v>
       </c>
       <c r="H5" t="n">
-        <v>2.297378160000006</v>
+        <v>1.055584532812491</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -4346,22 +4346,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2768013599.56</v>
+        <v>2424318031.05</v>
       </c>
       <c r="D6" t="n">
-        <v>2785181870.94</v>
+        <v>2397400495.19</v>
       </c>
       <c r="E6" t="n">
-        <v>17168271.38000011</v>
+        <v>-26917535.86000013</v>
       </c>
       <c r="F6" t="n">
-        <v>8584135.690000057</v>
+        <v>-26917535.86000013</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9537928544444508</v>
+        <v>-1.682345991250008</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4768964272222254</v>
+        <v>-1.682345991250008</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -4379,22 +4379,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2768013599.56</v>
+        <v>2424318031.05</v>
       </c>
       <c r="D7" t="n">
-        <v>2849113659.19</v>
+        <v>2452319419.53</v>
       </c>
       <c r="E7" t="n">
-        <v>81100059.63000011</v>
+        <v>28001388.48000002</v>
       </c>
       <c r="F7" t="n">
-        <v>40550029.81500006</v>
+        <v>14000694.24000001</v>
       </c>
       <c r="G7" t="n">
-        <v>4.50555886833334</v>
+        <v>1.750086780000001</v>
       </c>
       <c r="H7" t="n">
-        <v>2.25277943416667</v>
+        <v>0.8750433900000005</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -4412,22 +4412,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2768013599.56</v>
+        <v>2424318031.05</v>
       </c>
       <c r="D8" t="n">
-        <v>2878978573.31</v>
+        <v>2481860090.69</v>
       </c>
       <c r="E8" t="n">
-        <v>110964973.75</v>
+        <v>57542059.63999987</v>
       </c>
       <c r="F8" t="n">
-        <v>55482486.875</v>
+        <v>28771029.81999993</v>
       </c>
       <c r="G8" t="n">
-        <v>6.164720763888889</v>
+        <v>3.596378727499991</v>
       </c>
       <c r="H8" t="n">
-        <v>3.082360381944445</v>
+        <v>1.798189363749996</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -4557,19 +4557,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G2" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="J2" t="n">
         <v>-640000000</v>
       </c>
       <c r="K2" t="n">
-        <v>-299442484.0499998</v>
+        <v>-303055643.3100001</v>
       </c>
       <c r="L2" t="n">
         <v>0.1050151041880321</v>
@@ -4581,10 +4581,10 @@
         <v>-0.02747158338321065</v>
       </c>
       <c r="O2" t="n">
-        <v>8203621.746674323</v>
+        <v>8302609.009532409</v>
       </c>
       <c r="P2" t="n">
-        <v>4101810.873337161</v>
+        <v>4151304.504766204</v>
       </c>
     </row>
     <row r="3">
@@ -4615,19 +4615,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G3" t="n">
-        <v>575699100.39</v>
+        <v>548709791.53</v>
       </c>
       <c r="H3" t="n">
-        <v>-555063100.8309005</v>
+        <v>-484035602.7846395</v>
       </c>
       <c r="I3" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="J3" t="n">
         <v>-64000000</v>
       </c>
       <c r="K3" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="L3" t="n">
         <v>0.05822765833026367</v>
@@ -4639,10 +4639,10 @@
         <v>0.02514989940008316</v>
       </c>
       <c r="O3" t="n">
-        <v>475743.8701872187</v>
+        <v>1491003.562333822</v>
       </c>
       <c r="P3" t="n">
-        <v>237871.9350936094</v>
+        <v>745501.7811669109</v>
       </c>
     </row>
     <row r="4">
@@ -4673,19 +4673,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>1961135371.76</v>
+        <v>1990072267.9</v>
       </c>
       <c r="H4" t="n">
-        <v>-507481570.8511116</v>
+        <v>-446135269.4812486</v>
       </c>
       <c r="I4" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="J4" t="n">
         <v>-64000000</v>
       </c>
       <c r="K4" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="L4" t="n">
         <v>0.05839364669442126</v>
@@ -4697,10 +4697,10 @@
         <v>0.02530014515467949</v>
       </c>
       <c r="O4" t="n">
-        <v>30648043.47303869</v>
+        <v>32551525.14139548</v>
       </c>
       <c r="P4" t="n">
-        <v>15324021.73651935</v>
+        <v>16275762.57069774</v>
       </c>
     </row>
     <row r="5">
@@ -4731,19 +4731,19 @@
         <v>0.75</v>
       </c>
       <c r="G5" t="n">
-        <v>531970690.13</v>
+        <v>321318332.1300001</v>
       </c>
       <c r="H5" t="n">
-        <v>-557976082.4163486</v>
+        <v>-496658630.361554</v>
       </c>
       <c r="I5" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="J5" t="n">
         <v>-64000000</v>
       </c>
       <c r="K5" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="L5" t="n">
         <v>0.05851824187679444</v>
@@ -4755,10 +4755,10 @@
         <v>0.02544697899977066</v>
       </c>
       <c r="O5" t="n">
-        <v>-496319.0035436328</v>
+        <v>-3346410.665183908</v>
       </c>
       <c r="P5" t="n">
-        <v>-496319.0035436328</v>
+        <v>-3346410.665183908</v>
       </c>
     </row>
     <row r="6">
@@ -4789,19 +4789,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>78498009.31000002</v>
+        <v>82481230.3</v>
       </c>
       <c r="H6" t="n">
-        <v>-149884271.2777902</v>
+        <v>-119458296.2048057</v>
       </c>
       <c r="I6" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="J6" t="n">
         <v>-64000000</v>
       </c>
       <c r="K6" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="L6" t="n">
         <v>0.05821004393128892</v>
@@ -4813,10 +4813,10 @@
         <v>0.02559354982454409</v>
       </c>
       <c r="O6" t="n">
-        <v>-1218018.568307064</v>
+        <v>-630916.2524000645</v>
       </c>
       <c r="P6" t="n">
-        <v>-1218018.568307064</v>
+        <v>-630916.2524000645</v>
       </c>
     </row>
     <row r="7">
@@ -4847,19 +4847,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>517889994.42</v>
+        <v>518697858.84</v>
       </c>
       <c r="H7" t="n">
-        <v>-149844342.9148888</v>
+        <v>-119426252.4590164</v>
       </c>
       <c r="I7" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="J7" t="n">
         <v>-64000000</v>
       </c>
       <c r="K7" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="L7" t="n">
         <v>0.05808035784574397</v>
@@ -4871,10 +4871,10 @@
         <v>0.02573959809769572</v>
       </c>
       <c r="O7" t="n">
-        <v>5526119.171618581</v>
+        <v>5994969.563372931</v>
       </c>
       <c r="P7" t="n">
-        <v>2763059.58580929</v>
+        <v>2997484.781686465</v>
       </c>
     </row>
     <row r="8">
@@ -4905,19 +4905,19 @@
         <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>902503166.1700001</v>
+        <v>669118580.01</v>
       </c>
       <c r="H8" t="n">
-        <v>-297430610.8241635</v>
+        <v>-207983441.3653717</v>
       </c>
       <c r="I8" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="J8" t="n">
         <v>-32000000</v>
       </c>
       <c r="K8" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="L8" t="n">
         <v>0.0579990267461179</v>
@@ -4929,10 +4929,10 @@
         <v>0.02588744766971374</v>
       </c>
       <c r="O8" t="n">
-        <v>7831892.056447658</v>
+        <v>5968805.885164502</v>
       </c>
       <c r="P8" t="n">
-        <v>3915946.028223829</v>
+        <v>2984402.942582251</v>
       </c>
     </row>
     <row r="9">
@@ -4963,19 +4963,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G9" t="n">
-        <v>-154283223.6</v>
+        <v>-153952841.84</v>
       </c>
       <c r="H9" t="n">
-        <v>63482820.57040198</v>
+        <v>61685111.16101505</v>
       </c>
       <c r="I9" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="J9" t="n">
         <v>-32000000</v>
       </c>
       <c r="K9" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="L9" t="n">
         <v>0.05738520780446178</v>
@@ -4987,10 +4987,10 @@
         <v>0.02602676969992171</v>
       </c>
       <c r="O9" t="n">
-        <v>-984683.8242964256</v>
+        <v>-1000596.240465143</v>
       </c>
       <c r="P9" t="n">
-        <v>-984683.8242964256</v>
+        <v>-1000596.240465143</v>
       </c>
     </row>
     <row r="10">
@@ -5021,19 +5021,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G10" t="n">
-        <v>-105494922.47</v>
+        <v>-105287618.79</v>
       </c>
       <c r="H10" t="n">
-        <v>11318465.07972154</v>
+        <v>9506772.962048057</v>
       </c>
       <c r="I10" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="J10" t="n">
         <v>-32000000</v>
       </c>
       <c r="K10" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="L10" t="n">
         <v>0.05695407285841891</v>
@@ -5045,10 +5045,10 @@
         <v>0.02616692125524978</v>
       </c>
       <c r="O10" t="n">
-        <v>-821435.9815432675</v>
+        <v>-835429.9501804125</v>
       </c>
       <c r="P10" t="n">
-        <v>-821435.9815432675</v>
+        <v>-835429.9501804125</v>
       </c>
     </row>
     <row r="11">
@@ -5079,19 +5079,19 @@
         <v>0.25</v>
       </c>
       <c r="G11" t="n">
-        <v>-106354032.72</v>
+        <v>-8670744.480000019</v>
       </c>
       <c r="H11" t="n">
-        <v>63470643.38648102</v>
+        <v>61673328.09342016</v>
       </c>
       <c r="I11" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="J11" t="n">
         <v>-32000000</v>
       </c>
       <c r="K11" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="L11" t="n">
         <v>0.05664439372837885</v>
@@ -5103,10 +5103,10 @@
         <v>0.02630835803903212</v>
       </c>
       <c r="O11" t="n">
-        <v>-282047.8901283572</v>
+        <v>348602.7366738985</v>
       </c>
       <c r="P11" t="n">
-        <v>-282047.8901283572</v>
+        <v>174301.3683369493</v>
       </c>
     </row>
     <row r="12">
@@ -5137,19 +5137,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G12" t="n">
-        <v>-105737558.25</v>
+        <v>-105791543.79</v>
       </c>
       <c r="H12" t="n">
-        <v>11243431.39456546</v>
+        <v>9444482.371434988</v>
       </c>
       <c r="I12" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="J12" t="n">
         <v>-32000000</v>
       </c>
       <c r="K12" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="L12" t="n">
         <v>0.05642057743315654</v>
@@ -5161,10 +5161,10 @@
         <v>0.02645013495868191</v>
       </c>
       <c r="O12" t="n">
-        <v>-416563.7346881752</v>
+        <v>-424732.1295655764</v>
       </c>
       <c r="P12" t="n">
-        <v>-416563.7346881752</v>
+        <v>-424732.1295655764</v>
       </c>
     </row>
     <row r="13">
@@ -5195,19 +5195,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G13" t="n">
-        <v>-105013009.69</v>
+        <v>-105084497.29</v>
       </c>
       <c r="H13" t="n">
-        <v>11307685.82977768</v>
+        <v>9498456.09701325</v>
       </c>
       <c r="I13" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="J13" t="n">
         <v>-32000000</v>
       </c>
       <c r="K13" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="L13" t="n">
         <v>0.05625883751011833</v>
@@ -5219,10 +5219,10 @@
         <v>0.02659286987606641</v>
       </c>
       <c r="O13" t="n">
-        <v>-207657.7903424628</v>
+        <v>-211825.5962844518</v>
       </c>
       <c r="P13" t="n">
-        <v>-207657.7903424628</v>
+        <v>-211825.5962844518</v>
       </c>
     </row>
     <row r="14">
@@ -5253,34 +5253,34 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-86650256.47999999</v>
+        <v>26344865.39000002</v>
       </c>
       <c r="H14" t="n">
-        <v>11236273.29889962</v>
+        <v>9437731.866157647</v>
       </c>
       <c r="I14" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="J14" t="n">
         <v>-32000000</v>
       </c>
       <c r="K14" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05612986869467673</v>
+        <v>0.05612125523607059</v>
       </c>
       <c r="M14" t="n">
-        <v>0.08286595312469469</v>
+        <v>0.08285710130558432</v>
       </c>
       <c r="N14" t="n">
-        <v>0.02673608443001796</v>
+        <v>0.02673584606951374</v>
       </c>
       <c r="O14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5311,19 +5311,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G15" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="J15" t="n">
         <v>-640000000</v>
       </c>
       <c r="K15" t="n">
-        <v>-299442484.0499998</v>
+        <v>-303055643.3100001</v>
       </c>
       <c r="L15" t="n">
         <v>0.1050151041880321</v>
@@ -5335,10 +5335,10 @@
         <v>-0.07747761902794248</v>
       </c>
       <c r="O15" t="n">
-        <v>23136528.80767785</v>
+        <v>23415700.82821106</v>
       </c>
       <c r="P15" t="n">
-        <v>11568264.40383892</v>
+        <v>11707850.41410553</v>
       </c>
     </row>
     <row r="16">
@@ -5369,19 +5369,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G16" t="n">
-        <v>575699100.39</v>
+        <v>548709791.53</v>
       </c>
       <c r="H16" t="n">
-        <v>-555063100.8309005</v>
+        <v>-484035602.7846395</v>
       </c>
       <c r="I16" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="J16" t="n">
         <v>-64000000</v>
       </c>
       <c r="K16" t="n">
-        <v>84635999.55909944</v>
+        <v>128674188.7453604</v>
       </c>
       <c r="L16" t="n">
         <v>0.05822765833026367</v>
@@ -5393,10 +5393,10 @@
         <v>-0.02509271293939896</v>
       </c>
       <c r="O16" t="n">
-        <v>-1946767.937835948</v>
+        <v>-2959719.107489256</v>
       </c>
       <c r="P16" t="n">
-        <v>-1946767.937835948</v>
+        <v>-2959719.107489256</v>
       </c>
     </row>
     <row r="17">
@@ -5427,19 +5427,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G17" t="n">
-        <v>1961135371.76</v>
+        <v>1990072267.9</v>
       </c>
       <c r="H17" t="n">
-        <v>-507481570.8511116</v>
+        <v>-446135269.4812486</v>
       </c>
       <c r="I17" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="J17" t="n">
         <v>-64000000</v>
       </c>
       <c r="K17" t="n">
-        <v>1517653800.908888</v>
+        <v>1607936998.418751</v>
       </c>
       <c r="L17" t="n">
         <v>0.05839364669442126</v>
@@ -5451,10 +5451,10 @@
         <v>-0.02518665410778054</v>
       </c>
       <c r="O17" t="n">
-        <v>-31853851.11570883</v>
+        <v>-33748794.17189663</v>
       </c>
       <c r="P17" t="n">
-        <v>-31853851.11570883</v>
+        <v>-33748794.17189663</v>
       </c>
     </row>
     <row r="18">
@@ -5485,19 +5485,19 @@
         <v>0.75</v>
       </c>
       <c r="G18" t="n">
-        <v>531970690.13</v>
+        <v>321318332.1300001</v>
       </c>
       <c r="H18" t="n">
-        <v>-557976082.4163486</v>
+        <v>-496658630.361554</v>
       </c>
       <c r="I18" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="J18" t="n">
         <v>-64000000</v>
       </c>
       <c r="K18" t="n">
-        <v>37994607.71365142</v>
+        <v>-111340298.2315539</v>
       </c>
       <c r="L18" t="n">
         <v>0.05851824187679444</v>
@@ -5509,10 +5509,10 @@
         <v>-0.02528484926412755</v>
       </c>
       <c r="O18" t="n">
-        <v>-720515.9466670005</v>
+        <v>2111416.993355886</v>
       </c>
       <c r="P18" t="n">
-        <v>-720515.9466670005</v>
+        <v>1055708.496677943</v>
       </c>
     </row>
     <row r="19">
@@ -5543,19 +5543,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>78498009.31000002</v>
+        <v>82481230.3</v>
       </c>
       <c r="H19" t="n">
-        <v>-149884271.2777902</v>
+        <v>-119458296.2048057</v>
       </c>
       <c r="I19" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="J19" t="n">
         <v>-64000000</v>
       </c>
       <c r="K19" t="n">
-        <v>-7386261.967790231</v>
+        <v>27022934.09519425</v>
       </c>
       <c r="L19" t="n">
         <v>0.05821004393128892</v>
@@ -5567,10 +5567,10 @@
         <v>-0.02537722477452231</v>
       </c>
       <c r="O19" t="n">
-        <v>124961.8868000788</v>
+        <v>-457178.0484005649</v>
       </c>
       <c r="P19" t="n">
-        <v>62480.9434000394</v>
+        <v>-457178.0484005649</v>
       </c>
     </row>
     <row r="20">
@@ -5601,19 +5601,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>517889994.42</v>
+        <v>518697858.84</v>
       </c>
       <c r="H20" t="n">
-        <v>-149844342.9148888</v>
+        <v>-119426252.4590164</v>
       </c>
       <c r="I20" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="J20" t="n">
         <v>-64000000</v>
       </c>
       <c r="K20" t="n">
-        <v>432045651.5051111</v>
+        <v>463271606.3809837</v>
       </c>
       <c r="L20" t="n">
         <v>0.05808035784574397</v>
@@ -5625,10 +5625,10 @@
         <v>-0.02547134730704866</v>
       </c>
       <c r="O20" t="n">
-        <v>-6419457.824492295</v>
+        <v>-6883421.99044755</v>
       </c>
       <c r="P20" t="n">
-        <v>-6419457.824492295</v>
+        <v>-6883421.99044755</v>
       </c>
     </row>
     <row r="21">
@@ -5659,19 +5659,19 @@
         <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>902503166.1700001</v>
+        <v>669118580.01</v>
       </c>
       <c r="H21" t="n">
-        <v>-297430610.8241635</v>
+        <v>-207983441.3653717</v>
       </c>
       <c r="I21" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="J21" t="n">
         <v>-32000000</v>
       </c>
       <c r="K21" t="n">
-        <v>637072555.3458366</v>
+        <v>493135138.6446283</v>
       </c>
       <c r="L21" t="n">
         <v>0.0579990267461179</v>
@@ -5683,10 +5683,10 @@
         <v>-0.02556388968728518</v>
       </c>
       <c r="O21" t="n">
-        <v>-8143026.263828925</v>
+        <v>-6303226.14261768</v>
       </c>
       <c r="P21" t="n">
-        <v>-8143026.263828925</v>
+        <v>-6303226.14261768</v>
       </c>
     </row>
     <row r="22">
@@ -5717,19 +5717,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G22" t="n">
-        <v>-154283223.6</v>
+        <v>-153952841.84</v>
       </c>
       <c r="H22" t="n">
-        <v>63482820.57040198</v>
+        <v>61685111.16101505</v>
       </c>
       <c r="I22" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="J22" t="n">
         <v>-32000000</v>
       </c>
       <c r="K22" t="n">
-        <v>-58800403.02959804</v>
+        <v>-60267730.67898495</v>
       </c>
       <c r="L22" t="n">
         <v>0.05738520780446178</v>
@@ -5741,10 +5741,10 @@
         <v>-0.02564879692438105</v>
       </c>
       <c r="O22" t="n">
-        <v>628399.8318241333</v>
+        <v>644081.1605327394</v>
       </c>
       <c r="P22" t="n">
-        <v>314199.9159120666</v>
+        <v>322040.5802663697</v>
       </c>
     </row>
     <row r="23">
@@ -5775,19 +5775,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>-105494922.47</v>
+        <v>-105287618.79</v>
       </c>
       <c r="H23" t="n">
-        <v>11318465.07972154</v>
+        <v>9506772.962048057</v>
       </c>
       <c r="I23" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="J23" t="n">
         <v>-32000000</v>
       </c>
       <c r="K23" t="n">
-        <v>-62176457.39027846</v>
+        <v>-63780845.82795194</v>
       </c>
       <c r="L23" t="n">
         <v>0.05695407285841891</v>
@@ -5799,10 +5799,10 @@
         <v>-0.02573394353653935</v>
       </c>
       <c r="O23" t="n">
-        <v>533348.481261157</v>
+        <v>547110.895083079</v>
       </c>
       <c r="P23" t="n">
-        <v>266674.2406305785</v>
+        <v>273555.4475415395</v>
       </c>
     </row>
     <row r="24">
@@ -5833,19 +5833,19 @@
         <v>0.25</v>
       </c>
       <c r="G24" t="n">
-        <v>-106354032.72</v>
+        <v>-8670744.480000019</v>
       </c>
       <c r="H24" t="n">
-        <v>63470643.38648102</v>
+        <v>61673328.09342016</v>
       </c>
       <c r="I24" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="J24" t="n">
         <v>-32000000</v>
       </c>
       <c r="K24" t="n">
-        <v>-10883389.333519</v>
+        <v>85002583.61342014</v>
       </c>
       <c r="L24" t="n">
         <v>0.05664439372837885</v>
@@ -5857,10 +5857,10 @@
         <v>-0.02581887365352179</v>
       </c>
       <c r="O24" t="n">
-        <v>70249.21353105344</v>
+        <v>-548667.7416344541</v>
       </c>
       <c r="P24" t="n">
-        <v>35124.60676552672</v>
+        <v>-548667.7416344541</v>
       </c>
     </row>
     <row r="25">
@@ -5891,19 +5891,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G25" t="n">
-        <v>-105737558.25</v>
+        <v>-105791543.79</v>
       </c>
       <c r="H25" t="n">
-        <v>11243431.39456546</v>
+        <v>9444482.371434988</v>
       </c>
       <c r="I25" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="J25" t="n">
         <v>-32000000</v>
       </c>
       <c r="K25" t="n">
-        <v>-62494126.85543452</v>
+        <v>-64347061.41856501</v>
       </c>
       <c r="L25" t="n">
         <v>0.05642057743315654</v>
@@ -5915,10 +5915,10 @@
         <v>-0.02590450870981425</v>
       </c>
       <c r="O25" t="n">
-        <v>269813.2755731399</v>
+        <v>277813.1688280281</v>
       </c>
       <c r="P25" t="n">
-        <v>134906.6377865699</v>
+        <v>138906.5844140141</v>
       </c>
     </row>
     <row r="26">
@@ -5949,19 +5949,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G26" t="n">
-        <v>-105013009.69</v>
+        <v>-105084497.29</v>
       </c>
       <c r="H26" t="n">
-        <v>11307685.82977768</v>
+        <v>9498456.09701325</v>
       </c>
       <c r="I26" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="J26" t="n">
         <v>-32000000</v>
       </c>
       <c r="K26" t="n">
-        <v>-61705323.86022232</v>
+        <v>-63586041.19298677</v>
       </c>
       <c r="L26" t="n">
         <v>0.05625883751011833</v>
@@ -5973,10 +5973,10 @@
         <v>-0.025990262065432</v>
       </c>
       <c r="O26" t="n">
-        <v>133644.7948299611</v>
+        <v>137718.1561924235</v>
       </c>
       <c r="P26" t="n">
-        <v>66822.39741498054</v>
+        <v>68859.07809621173</v>
       </c>
     </row>
     <row r="27">
@@ -6007,34 +6007,34 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-86650256.47999999</v>
+        <v>26344865.39000002</v>
       </c>
       <c r="H27" t="n">
-        <v>11236273.29889962</v>
+        <v>9437731.866157647</v>
       </c>
       <c r="I27" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="J27" t="n">
         <v>-32000000</v>
       </c>
       <c r="K27" t="n">
-        <v>-43413983.18110037</v>
+        <v>67782597.25615767</v>
       </c>
       <c r="L27" t="n">
-        <v>0.05612986869467673</v>
+        <v>0.05612125523607059</v>
       </c>
       <c r="M27" t="n">
-        <v>0.03005395945905409</v>
+        <v>0.030045538435584</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.02607590923562264</v>
+        <v>-0.02607571680048659</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="28">
@@ -6065,19 +6065,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G28" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="J28" t="n">
         <v>-640000000</v>
       </c>
       <c r="K28" t="n">
-        <v>-299442484.0499998</v>
+        <v>-303055643.3100001</v>
       </c>
       <c r="L28" t="n">
         <v>0.1050151041880321</v>
@@ -6089,10 +6089,10 @@
         <v>-0.07502986587896165</v>
       </c>
       <c r="O28" t="n">
-        <v>22405575.63751067</v>
+        <v>22675927.76655857</v>
       </c>
       <c r="P28" t="n">
-        <v>11202787.81875534</v>
+        <v>11337963.88327928</v>
       </c>
     </row>
     <row r="29">
@@ -6123,19 +6123,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G29" t="n">
-        <v>575699100.39</v>
+        <v>548709791.53</v>
       </c>
       <c r="H29" t="n">
-        <v>-555063100.8309005</v>
+        <v>-484035602.7846395</v>
       </c>
       <c r="I29" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="J29" t="n">
         <v>-64000000</v>
       </c>
       <c r="K29" t="n">
-        <v>84635999.55909944</v>
+        <v>128674188.7453604</v>
       </c>
       <c r="L29" t="n">
         <v>0.05822765833026367</v>
@@ -6147,10 +6147,10 @@
         <v>-0.01988106139069767</v>
       </c>
       <c r="O29" t="n">
-        <v>-1542432.377839391</v>
+        <v>-2344997.825357669</v>
       </c>
       <c r="P29" t="n">
-        <v>-1542432.377839391</v>
+        <v>-2344997.825357669</v>
       </c>
     </row>
     <row r="30">
@@ -6181,19 +6181,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G30" t="n">
-        <v>1961135371.76</v>
+        <v>1990072267.9</v>
       </c>
       <c r="H30" t="n">
-        <v>-507481570.8511116</v>
+        <v>-446135269.4812486</v>
       </c>
       <c r="I30" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="J30" t="n">
         <v>-64000000</v>
       </c>
       <c r="K30" t="n">
-        <v>1517653800.908888</v>
+        <v>1607936998.418751</v>
       </c>
       <c r="L30" t="n">
         <v>0.05839364669442126</v>
@@ -6205,10 +6205,10 @@
         <v>-0.01725628309459371</v>
       </c>
       <c r="O30" t="n">
-        <v>-21824219.69005828</v>
+        <v>-23122513.36915437</v>
       </c>
       <c r="P30" t="n">
-        <v>-21824219.69005828</v>
+        <v>-23122513.36915437</v>
       </c>
     </row>
     <row r="31">
@@ -6239,19 +6239,19 @@
         <v>0.75</v>
       </c>
       <c r="G31" t="n">
-        <v>531970690.13</v>
+        <v>321318332.1300001</v>
       </c>
       <c r="H31" t="n">
-        <v>-557976082.4163486</v>
+        <v>-496658630.361554</v>
       </c>
       <c r="I31" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="J31" t="n">
         <v>-64000000</v>
       </c>
       <c r="K31" t="n">
-        <v>37994607.71365142</v>
+        <v>-111340298.2315539</v>
       </c>
       <c r="L31" t="n">
         <v>0.05851824187679444</v>
@@ -6263,10 +6263,10 @@
         <v>-0.01489062910622074</v>
       </c>
       <c r="O31" t="n">
-        <v>-424322.7086252528</v>
+        <v>1243445.314156556</v>
       </c>
       <c r="P31" t="n">
-        <v>-424322.7086252528</v>
+        <v>621722.657078278</v>
       </c>
     </row>
     <row r="32">
@@ -6297,19 +6297,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G32" t="n">
-        <v>78498009.31000002</v>
+        <v>82481230.3</v>
       </c>
       <c r="H32" t="n">
-        <v>-149884271.2777902</v>
+        <v>-119458296.2048057</v>
       </c>
       <c r="I32" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="J32" t="n">
         <v>-64000000</v>
       </c>
       <c r="K32" t="n">
-        <v>-7386261.967790231</v>
+        <v>27022934.09519425</v>
       </c>
       <c r="L32" t="n">
         <v>0.05821004393128892</v>
@@ -6321,10 +6321,10 @@
         <v>-0.01266202848122933</v>
       </c>
       <c r="O32" t="n">
-        <v>62350.03960398726</v>
+        <v>-228110.1074398218</v>
       </c>
       <c r="P32" t="n">
-        <v>31175.01980199363</v>
+        <v>-228110.1074398218</v>
       </c>
     </row>
     <row r="33">
@@ -6355,19 +6355,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G33" t="n">
-        <v>517889994.42</v>
+        <v>518697858.84</v>
       </c>
       <c r="H33" t="n">
-        <v>-149844342.9148888</v>
+        <v>-119426252.4590164</v>
       </c>
       <c r="I33" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="J33" t="n">
         <v>-64000000</v>
       </c>
       <c r="K33" t="n">
-        <v>432045651.5051111</v>
+        <v>463271606.3809837</v>
       </c>
       <c r="L33" t="n">
         <v>0.05808035784574397</v>
@@ -6379,10 +6379,10 @@
         <v>-0.01061579379409725</v>
       </c>
       <c r="O33" t="n">
-        <v>-2675462.735175219</v>
+        <v>-2868830.909000414</v>
       </c>
       <c r="P33" t="n">
-        <v>-2675462.735175219</v>
+        <v>-2868830.909000414</v>
       </c>
     </row>
     <row r="34">
@@ -6413,19 +6413,19 @@
         <v>0.5</v>
       </c>
       <c r="G34" t="n">
-        <v>902503166.1700001</v>
+        <v>669118580.01</v>
       </c>
       <c r="H34" t="n">
-        <v>-297430610.8241635</v>
+        <v>-207983441.3653717</v>
       </c>
       <c r="I34" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="J34" t="n">
         <v>-32000000</v>
       </c>
       <c r="K34" t="n">
-        <v>637072555.3458366</v>
+        <v>493135138.6446283</v>
       </c>
       <c r="L34" t="n">
         <v>0.0579990267461179</v>
@@ -6437,10 +6437,10 @@
         <v>-0.008701770963537303</v>
       </c>
       <c r="O34" t="n">
-        <v>-2771829.731887456</v>
+        <v>-2145574.515278884</v>
       </c>
       <c r="P34" t="n">
-        <v>-2771829.731887456</v>
+        <v>-2145574.515278884</v>
       </c>
     </row>
     <row r="35">
@@ -6471,19 +6471,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G35" t="n">
-        <v>-154283223.6</v>
+        <v>-153952841.84</v>
       </c>
       <c r="H35" t="n">
-        <v>63482820.57040198</v>
+        <v>61685111.16101505</v>
       </c>
       <c r="I35" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="J35" t="n">
         <v>-32000000</v>
       </c>
       <c r="K35" t="n">
-        <v>-58800403.02959804</v>
+        <v>-60267730.67898495</v>
       </c>
       <c r="L35" t="n">
         <v>0.05738520780446178</v>
@@ -6495,10 +6495,10 @@
         <v>-0.006933843412663093</v>
       </c>
       <c r="O35" t="n">
-        <v>169880.3280036305</v>
+        <v>174119.5864019305</v>
       </c>
       <c r="P35" t="n">
-        <v>84940.16400181527</v>
+        <v>87059.79320096526</v>
       </c>
     </row>
     <row r="36">
@@ -6529,19 +6529,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G36" t="n">
-        <v>-105494922.47</v>
+        <v>-105287618.79</v>
       </c>
       <c r="H36" t="n">
-        <v>11318465.07972154</v>
+        <v>9506772.962048057</v>
       </c>
       <c r="I36" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="J36" t="n">
         <v>-32000000</v>
       </c>
       <c r="K36" t="n">
-        <v>-62176457.39027846</v>
+        <v>-63780845.82795194</v>
       </c>
       <c r="L36" t="n">
         <v>0.05695407285841891</v>
@@ -6553,10 +6553,10 @@
         <v>-0.005293779960104272</v>
       </c>
       <c r="O36" t="n">
-        <v>109716.1613743111</v>
+        <v>112547.2544941707</v>
       </c>
       <c r="P36" t="n">
-        <v>54858.08068715555</v>
+        <v>56273.62724708537</v>
       </c>
     </row>
     <row r="37">
@@ -6587,19 +6587,19 @@
         <v>0.25</v>
       </c>
       <c r="G37" t="n">
-        <v>-106354032.72</v>
+        <v>-8670744.480000019</v>
       </c>
       <c r="H37" t="n">
-        <v>63470643.38648102</v>
+        <v>61673328.09342016</v>
       </c>
       <c r="I37" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="J37" t="n">
         <v>-32000000</v>
       </c>
       <c r="K37" t="n">
-        <v>-10883389.333519</v>
+        <v>85002583.61342014</v>
       </c>
       <c r="L37" t="n">
         <v>0.05664439372837885</v>
@@ -6611,10 +6611,10 @@
         <v>-0.003768699327115023</v>
       </c>
       <c r="O37" t="n">
-        <v>10254.05551449096</v>
+        <v>-80087.29491673374</v>
       </c>
       <c r="P37" t="n">
-        <v>5127.027757245482</v>
+        <v>-80087.29491673374</v>
       </c>
     </row>
     <row r="38">
@@ -6645,19 +6645,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G38" t="n">
-        <v>-105737558.25</v>
+        <v>-105791543.79</v>
       </c>
       <c r="H38" t="n">
-        <v>11243431.39456546</v>
+        <v>9444482.371434988</v>
       </c>
       <c r="I38" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="J38" t="n">
         <v>-32000000</v>
       </c>
       <c r="K38" t="n">
-        <v>-62494126.85543452</v>
+        <v>-64347061.41856501</v>
       </c>
       <c r="L38" t="n">
         <v>0.05642057743315654</v>
@@ -6669,10 +6669,10 @@
         <v>-0.002356874069323035</v>
       </c>
       <c r="O38" t="n">
-        <v>24548.46451175965</v>
+        <v>25276.32008242542</v>
       </c>
       <c r="P38" t="n">
-        <v>12274.23225587983</v>
+        <v>12638.16004121271</v>
       </c>
     </row>
     <row r="39">
@@ -6703,19 +6703,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G39" t="n">
-        <v>-105013009.69</v>
+        <v>-105084497.29</v>
       </c>
       <c r="H39" t="n">
-        <v>11307685.82977768</v>
+        <v>9498456.09701325</v>
       </c>
       <c r="I39" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="J39" t="n">
         <v>-32000000</v>
       </c>
       <c r="K39" t="n">
-        <v>-61705323.86022232</v>
+        <v>-63586041.19298677</v>
       </c>
       <c r="L39" t="n">
         <v>0.05625883751011833</v>
@@ -6727,10 +6727,10 @@
         <v>-0.001044890098674874</v>
       </c>
       <c r="O39" t="n">
-        <v>5372.94016142273</v>
+        <v>5536.702071373712</v>
       </c>
       <c r="P39" t="n">
-        <v>2686.470080711365</v>
+        <v>2768.351035686856</v>
       </c>
     </row>
     <row r="40">
@@ -6761,34 +6761,34 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-86650256.47999999</v>
+        <v>26344865.39000002</v>
       </c>
       <c r="H40" t="n">
-        <v>11236273.29889962</v>
+        <v>9437731.866157647</v>
       </c>
       <c r="I40" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="J40" t="n">
         <v>-32000000</v>
       </c>
       <c r="K40" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="L40" t="n">
-        <v>0.05612986869467673</v>
+        <v>0.05612125523607059</v>
       </c>
       <c r="M40" t="n">
-        <v>0.05630391743831353</v>
+        <v>0.05629528248589444</v>
       </c>
       <c r="N40" t="n">
-        <v>0.000174048743636801</v>
+        <v>0.0001740272498238493</v>
       </c>
       <c r="O40" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -6819,19 +6819,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G41" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="J41" t="n">
         <v>-640000000</v>
       </c>
       <c r="K41" t="n">
-        <v>-299442484.0499998</v>
+        <v>-303055643.3100001</v>
       </c>
       <c r="L41" t="n">
         <v>0.1050151041880321</v>
@@ -6843,10 +6843,10 @@
         <v>-0.02468474605999638</v>
       </c>
       <c r="O41" t="n">
-        <v>7371410.550462875</v>
+        <v>7460356.113328367</v>
       </c>
       <c r="P41" t="n">
-        <v>3685705.275231437</v>
+        <v>3730178.056664183</v>
       </c>
     </row>
     <row r="42">
@@ -6877,19 +6877,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G42" t="n">
-        <v>575699100.39</v>
+        <v>548709791.53</v>
       </c>
       <c r="H42" t="n">
-        <v>-555063100.8309005</v>
+        <v>-484035602.7846395</v>
       </c>
       <c r="I42" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="J42" t="n">
         <v>-64000000</v>
       </c>
       <c r="K42" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="L42" t="n">
         <v>0.05822765833026367</v>
@@ -6901,10 +6901,10 @@
         <v>0.02495849603761435</v>
       </c>
       <c r="O42" t="n">
-        <v>472123.2204589952</v>
+        <v>1479656.276575584</v>
       </c>
       <c r="P42" t="n">
-        <v>236061.6102294976</v>
+        <v>739828.1382877921</v>
       </c>
     </row>
     <row r="43">
@@ -6935,19 +6935,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G43" t="n">
-        <v>1961135371.76</v>
+        <v>1990072267.9</v>
       </c>
       <c r="H43" t="n">
-        <v>-507481570.8511116</v>
+        <v>-446135269.4812486</v>
       </c>
       <c r="I43" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="J43" t="n">
         <v>-64000000</v>
       </c>
       <c r="K43" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="L43" t="n">
         <v>0.05839364669442126</v>
@@ -6959,10 +6959,10 @@
         <v>0.02216014487646945</v>
       </c>
       <c r="O43" t="n">
-        <v>26844315.69030953</v>
+        <v>28511556.30425076</v>
       </c>
       <c r="P43" t="n">
-        <v>13422157.84515477</v>
+        <v>14255778.15212538</v>
       </c>
     </row>
     <row r="44">
@@ -6993,19 +6993,19 @@
         <v>0.75</v>
       </c>
       <c r="G44" t="n">
-        <v>531970690.13</v>
+        <v>321318332.1300001</v>
       </c>
       <c r="H44" t="n">
-        <v>-557976082.4163486</v>
+        <v>-496658630.361554</v>
       </c>
       <c r="I44" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="J44" t="n">
         <v>-64000000</v>
       </c>
       <c r="K44" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="L44" t="n">
         <v>0.05851824187679444</v>
@@ -7017,10 +7017,10 @@
         <v>0.01962016480210327</v>
       </c>
       <c r="O44" t="n">
-        <v>-382672.5618011282</v>
+        <v>-2580154.160814768</v>
       </c>
       <c r="P44" t="n">
-        <v>-382672.5618011282</v>
+        <v>-2580154.160814768</v>
       </c>
     </row>
     <row r="45">
@@ -7051,19 +7051,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G45" t="n">
-        <v>78498009.31000002</v>
+        <v>82481230.3</v>
       </c>
       <c r="H45" t="n">
-        <v>-149884271.2777902</v>
+        <v>-119458296.2048057</v>
       </c>
       <c r="I45" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="J45" t="n">
         <v>-64000000</v>
       </c>
       <c r="K45" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="L45" t="n">
         <v>0.05821004393128892</v>
@@ -7075,10 +7075,10 @@
         <v>0.01722340313955706</v>
       </c>
       <c r="O45" t="n">
-        <v>-819676.245664854</v>
+        <v>-424580.6086642931</v>
       </c>
       <c r="P45" t="n">
-        <v>-819676.245664854</v>
+        <v>-424580.6086642931</v>
       </c>
     </row>
     <row r="46">
@@ -7109,19 +7109,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G46" t="n">
-        <v>517889994.42</v>
+        <v>518697858.84</v>
       </c>
       <c r="H46" t="n">
-        <v>-149844342.9148888</v>
+        <v>-119426252.4590164</v>
       </c>
       <c r="I46" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="J46" t="n">
         <v>-64000000</v>
       </c>
       <c r="K46" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="L46" t="n">
         <v>0.05808035784574397</v>
@@ -7133,10 +7133,10 @@
         <v>0.01501522413586098</v>
       </c>
       <c r="O46" t="n">
-        <v>3223667.970587295</v>
+        <v>3497172.385522508</v>
       </c>
       <c r="P46" t="n">
-        <v>1611833.985293648</v>
+        <v>1748586.192761254</v>
       </c>
     </row>
     <row r="47">
@@ -7167,19 +7167,19 @@
         <v>0.5</v>
       </c>
       <c r="G47" t="n">
-        <v>902503166.1700001</v>
+        <v>669118580.01</v>
       </c>
       <c r="H47" t="n">
-        <v>-297430610.8241635</v>
+        <v>-207983441.3653717</v>
       </c>
       <c r="I47" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="J47" t="n">
         <v>-32000000</v>
       </c>
       <c r="K47" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="L47" t="n">
         <v>0.0579990267461179</v>
@@ -7191,10 +7191,10 @@
         <v>0.01294941997535037</v>
       </c>
       <c r="O47" t="n">
-        <v>3917669.317365836</v>
+        <v>2985716.287850357</v>
       </c>
       <c r="P47" t="n">
-        <v>1958834.658682918</v>
+        <v>1492858.143925178</v>
       </c>
     </row>
     <row r="48">
@@ -7225,19 +7225,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G48" t="n">
-        <v>-154283223.6</v>
+        <v>-153952841.84</v>
       </c>
       <c r="H48" t="n">
-        <v>63482820.57040198</v>
+        <v>61685111.16101505</v>
       </c>
       <c r="I48" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="J48" t="n">
         <v>-32000000</v>
       </c>
       <c r="K48" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="L48" t="n">
         <v>0.05738520780446178</v>
@@ -7249,10 +7249,10 @@
         <v>0.01103784963125674</v>
       </c>
       <c r="O48" t="n">
-        <v>-417600.4979575885</v>
+        <v>-424348.8904383044</v>
       </c>
       <c r="P48" t="n">
-        <v>-417600.4979575885</v>
+        <v>-424348.8904383044</v>
       </c>
     </row>
     <row r="49">
@@ -7283,19 +7283,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G49" t="n">
-        <v>-105494922.47</v>
+        <v>-105287618.79</v>
       </c>
       <c r="H49" t="n">
-        <v>11318465.07972154</v>
+        <v>9506772.962048057</v>
       </c>
       <c r="I49" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="J49" t="n">
         <v>-32000000</v>
       </c>
       <c r="K49" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="L49" t="n">
         <v>0.05695407285841891</v>
@@ -7307,10 +7307,10 @@
         <v>0.009264716116377802</v>
       </c>
       <c r="O49" t="n">
-        <v>-290839.3808556934</v>
+        <v>-295794.115327508</v>
       </c>
       <c r="P49" t="n">
-        <v>-290839.3808556934</v>
+        <v>-295794.115327508</v>
       </c>
     </row>
     <row r="50">
@@ -7341,19 +7341,19 @@
         <v>0.25</v>
       </c>
       <c r="G50" t="n">
-        <v>-106354032.72</v>
+        <v>-8670744.480000019</v>
       </c>
       <c r="H50" t="n">
-        <v>63470643.38648102</v>
+        <v>61673328.09342016</v>
       </c>
       <c r="I50" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="J50" t="n">
         <v>-32000000</v>
       </c>
       <c r="K50" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="L50" t="n">
         <v>0.05664439372837885</v>
@@ -7365,10 +7365,10 @@
         <v>0.007618063727031256</v>
       </c>
       <c r="O50" t="n">
-        <v>-81672.09819346003</v>
+        <v>100944.2649160843</v>
       </c>
       <c r="P50" t="n">
-        <v>-81672.09819346003</v>
+        <v>50472.13245804216</v>
       </c>
     </row>
     <row r="51">
@@ -7399,19 +7399,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G51" t="n">
-        <v>-105737558.25</v>
+        <v>-105791543.79</v>
       </c>
       <c r="H51" t="n">
-        <v>11243431.39456546</v>
+        <v>9444482.371434988</v>
       </c>
       <c r="I51" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="J51" t="n">
         <v>-32000000</v>
       </c>
       <c r="K51" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="L51" t="n">
         <v>0.05642057743315654</v>
@@ -7423,10 +7423,10 @@
         <v>0.006094907231449384</v>
       </c>
       <c r="O51" t="n">
-        <v>-95988.82285011387</v>
+        <v>-97871.06689481827</v>
       </c>
       <c r="P51" t="n">
-        <v>-95988.82285011387</v>
+        <v>-97871.06689481827</v>
       </c>
     </row>
     <row r="52">
@@ -7457,19 +7457,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G52" t="n">
-        <v>-105013009.69</v>
+        <v>-105084497.29</v>
       </c>
       <c r="H52" t="n">
-        <v>11307685.82977768</v>
+        <v>9498456.09701325</v>
       </c>
       <c r="I52" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="J52" t="n">
         <v>-32000000</v>
       </c>
       <c r="K52" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="L52" t="n">
         <v>0.05625883751011833</v>
@@ -7481,10 +7481,10 @@
         <v>0.004682431355023151</v>
       </c>
       <c r="O52" t="n">
-        <v>-36564.06221464201</v>
+        <v>-37297.923032048</v>
       </c>
       <c r="P52" t="n">
-        <v>-36564.06221464201</v>
+        <v>-37297.923032048</v>
       </c>
     </row>
     <row r="53">
@@ -7515,34 +7515,34 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>-86650256.47999999</v>
+        <v>26344865.39000002</v>
       </c>
       <c r="H53" t="n">
-        <v>11236273.29889962</v>
+        <v>9437731.866157647</v>
       </c>
       <c r="I53" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="J53" t="n">
         <v>-32000000</v>
       </c>
       <c r="K53" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="L53" t="n">
-        <v>0.05612986869467673</v>
+        <v>0.05612125523607059</v>
       </c>
       <c r="M53" t="n">
-        <v>0.05950311578357481</v>
+        <v>0.05949445427920219</v>
       </c>
       <c r="N53" t="n">
-        <v>0.003373247088898079</v>
+        <v>0.003373199043131603</v>
       </c>
       <c r="O53" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -7573,19 +7573,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G54" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="J54" t="n">
         <v>-640000000</v>
       </c>
       <c r="K54" t="n">
-        <v>-299442484.0499998</v>
+        <v>-303055643.3100001</v>
       </c>
       <c r="L54" t="n">
         <v>0.1050151041880321</v>
@@ -7597,10 +7597,10 @@
         <v>-0.01765980557248192</v>
       </c>
       <c r="O54" t="n">
-        <v>5273608.114084664</v>
+        <v>5337240.988529545</v>
       </c>
       <c r="P54" t="n">
-        <v>2636804.057042332</v>
+        <v>2668620.494264773</v>
       </c>
     </row>
     <row r="55">
@@ -7631,19 +7631,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G55" t="n">
-        <v>575699100.39</v>
+        <v>548709791.53</v>
       </c>
       <c r="H55" t="n">
-        <v>-555063100.8309005</v>
+        <v>-484035602.7846395</v>
       </c>
       <c r="I55" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="J55" t="n">
         <v>-64000000</v>
       </c>
       <c r="K55" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="L55" t="n">
         <v>0.05822765833026367</v>
@@ -7655,10 +7655,10 @@
         <v>0.03235719235381929</v>
       </c>
       <c r="O55" t="n">
-        <v>612079.4232181845</v>
+        <v>1918285.568430772</v>
       </c>
       <c r="P55" t="n">
-        <v>306039.7116090923</v>
+        <v>959142.7842153859</v>
       </c>
     </row>
     <row r="56">
@@ -7689,19 +7689,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G56" t="n">
-        <v>1961135371.76</v>
+        <v>1990072267.9</v>
       </c>
       <c r="H56" t="n">
-        <v>-507481570.8511116</v>
+        <v>-446135269.4812486</v>
       </c>
       <c r="I56" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="J56" t="n">
         <v>-64000000</v>
       </c>
       <c r="K56" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="L56" t="n">
         <v>0.05839364669442126</v>
@@ -7713,10 +7713,10 @@
         <v>0.02992819194854235</v>
       </c>
       <c r="O56" t="n">
-        <v>36254358.31694114</v>
+        <v>38506035.70427726</v>
       </c>
       <c r="P56" t="n">
-        <v>18127179.15847057</v>
+        <v>19253017.85213863</v>
       </c>
     </row>
     <row r="57">
@@ -7747,19 +7747,19 @@
         <v>0.75</v>
       </c>
       <c r="G57" t="n">
-        <v>531970690.13</v>
+        <v>321318332.1300001</v>
       </c>
       <c r="H57" t="n">
-        <v>-557976082.4163486</v>
+        <v>-496658630.361554</v>
       </c>
       <c r="I57" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="J57" t="n">
         <v>-64000000</v>
       </c>
       <c r="K57" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="L57" t="n">
         <v>0.05851824187679444</v>
@@ -7771,10 +7771,10 @@
         <v>0.02772661859587089</v>
       </c>
       <c r="O57" t="n">
-        <v>-540781.1950196924</v>
+        <v>-3646195.180164413</v>
       </c>
       <c r="P57" t="n">
-        <v>-540781.1950196924</v>
+        <v>-3646195.180164413</v>
       </c>
     </row>
     <row r="58">
@@ -7805,19 +7805,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G58" t="n">
-        <v>78498009.31000002</v>
+        <v>82481230.3</v>
       </c>
       <c r="H58" t="n">
-        <v>-149884271.2777902</v>
+        <v>-119458296.2048057</v>
       </c>
       <c r="I58" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="J58" t="n">
         <v>-64000000</v>
       </c>
       <c r="K58" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="L58" t="n">
         <v>0.05821004393128892</v>
@@ -7829,10 +7829,10 @@
         <v>0.02564903369930005</v>
       </c>
       <c r="O58" t="n">
-        <v>-1220659.092585942</v>
+        <v>-632284.0063290679</v>
       </c>
       <c r="P58" t="n">
-        <v>-1220659.092585942</v>
+        <v>-632284.0063290679</v>
       </c>
     </row>
     <row r="59">
@@ -7863,19 +7863,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G59" t="n">
-        <v>517889994.42</v>
+        <v>518697858.84</v>
       </c>
       <c r="H59" t="n">
-        <v>-149844342.9148888</v>
+        <v>-119426252.4590164</v>
       </c>
       <c r="I59" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="J59" t="n">
         <v>-64000000</v>
       </c>
       <c r="K59" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="L59" t="n">
         <v>0.05808035784574397</v>
@@ -7887,10 +7887,10 @@
         <v>0.02373722363569292</v>
       </c>
       <c r="O59" t="n">
-        <v>5096222.797120655</v>
+        <v>5528599.657027863</v>
       </c>
       <c r="P59" t="n">
-        <v>2548111.398560327</v>
+        <v>2764299.828513931</v>
       </c>
     </row>
     <row r="60">
@@ -7921,19 +7921,19 @@
         <v>0.5</v>
       </c>
       <c r="G60" t="n">
-        <v>902503166.1700001</v>
+        <v>669118580.01</v>
       </c>
       <c r="H60" t="n">
-        <v>-297430610.8241635</v>
+        <v>-207983441.3653717</v>
       </c>
       <c r="I60" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="J60" t="n">
         <v>-32000000</v>
       </c>
       <c r="K60" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="L60" t="n">
         <v>0.0579990267461179</v>
@@ -7945,10 +7945,10 @@
         <v>0.02195017150422629</v>
       </c>
       <c r="O60" t="n">
-        <v>6640723.181170784</v>
+        <v>5060997.689937379</v>
       </c>
       <c r="P60" t="n">
-        <v>3320361.590585392</v>
+        <v>2530498.84496869</v>
       </c>
     </row>
     <row r="61">
@@ -7979,19 +7979,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G61" t="n">
-        <v>-154283223.6</v>
+        <v>-153952841.84</v>
       </c>
       <c r="H61" t="n">
-        <v>63482820.57040198</v>
+        <v>61685111.16101505</v>
       </c>
       <c r="I61" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="J61" t="n">
         <v>-32000000</v>
       </c>
       <c r="K61" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="L61" t="n">
         <v>0.05738520780446178</v>
@@ -8003,10 +8003,10 @@
         <v>0.02029522229252897</v>
       </c>
       <c r="O61" t="n">
-        <v>-767839.318223714</v>
+        <v>-780247.5435654979</v>
       </c>
       <c r="P61" t="n">
-        <v>-767839.318223714</v>
+        <v>-780247.5435654979</v>
       </c>
     </row>
     <row r="62">
@@ -8037,19 +8037,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G62" t="n">
-        <v>-105494922.47</v>
+        <v>-105287618.79</v>
       </c>
       <c r="H62" t="n">
-        <v>11318465.07972154</v>
+        <v>9506772.962048057</v>
       </c>
       <c r="I62" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="J62" t="n">
         <v>-32000000</v>
       </c>
       <c r="K62" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="L62" t="n">
         <v>0.05695407285841891</v>
@@ -8061,10 +8061,10 @@
         <v>0.01876196760334525</v>
       </c>
       <c r="O62" t="n">
-        <v>-588978.5475180765</v>
+        <v>-599012.3754816803</v>
       </c>
       <c r="P62" t="n">
-        <v>-588978.5475180765</v>
+        <v>-599012.3754816803</v>
       </c>
     </row>
     <row r="63">
@@ -8095,19 +8095,19 @@
         <v>0.25</v>
       </c>
       <c r="G63" t="n">
-        <v>-106354032.72</v>
+        <v>-8670744.480000019</v>
       </c>
       <c r="H63" t="n">
-        <v>63470643.38648102</v>
+        <v>61673328.09342016</v>
       </c>
       <c r="I63" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="J63" t="n">
         <v>-32000000</v>
       </c>
       <c r="K63" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="L63" t="n">
         <v>0.05664439372837885</v>
@@ -8119,10 +8119,10 @@
         <v>0.01733996627504109</v>
       </c>
       <c r="O63" t="n">
-        <v>-185899.1312006691</v>
+        <v>229765.7530866877</v>
       </c>
       <c r="P63" t="n">
-        <v>-185899.1312006691</v>
+        <v>114882.8765433439</v>
       </c>
     </row>
     <row r="64">
@@ -8153,19 +8153,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G64" t="n">
-        <v>-105737558.25</v>
+        <v>-105791543.79</v>
       </c>
       <c r="H64" t="n">
-        <v>11243431.39456546</v>
+        <v>9444482.371434988</v>
       </c>
       <c r="I64" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="J64" t="n">
         <v>-32000000</v>
       </c>
       <c r="K64" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="L64" t="n">
         <v>0.05642057743315654</v>
@@ -8177,10 +8177,10 @@
         <v>0.01602670204966161</v>
       </c>
       <c r="O64" t="n">
-        <v>-252404.8694258294</v>
+        <v>-257354.2744526314</v>
       </c>
       <c r="P64" t="n">
-        <v>-252404.8694258294</v>
+        <v>-257354.2744526314</v>
       </c>
     </row>
     <row r="65">
@@ -8211,19 +8211,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G65" t="n">
-        <v>-105013009.69</v>
+        <v>-105084497.29</v>
       </c>
       <c r="H65" t="n">
-        <v>11307685.82977768</v>
+        <v>9498456.09701325</v>
       </c>
       <c r="I65" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="J65" t="n">
         <v>-32000000</v>
       </c>
       <c r="K65" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="L65" t="n">
         <v>0.05625883751011833</v>
@@ -8235,10 +8235,10 @@
         <v>0.01481092208165177</v>
       </c>
       <c r="O65" t="n">
-        <v>-115655.1875274748</v>
+        <v>-117976.4506835737</v>
       </c>
       <c r="P65" t="n">
-        <v>-115655.1875274748</v>
+        <v>-117976.4506835737</v>
       </c>
     </row>
     <row r="66">
@@ -8269,34 +8269,34 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>-86650256.47999999</v>
+        <v>26344865.39000002</v>
       </c>
       <c r="H66" t="n">
-        <v>11236273.29889962</v>
+        <v>9437731.866157647</v>
       </c>
       <c r="I66" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="J66" t="n">
         <v>-32000000</v>
       </c>
       <c r="K66" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="L66" t="n">
-        <v>0.05612986869467673</v>
+        <v>0.05612125523607059</v>
       </c>
       <c r="M66" t="n">
-        <v>0.06981591961576861</v>
+        <v>0.06980717394620273</v>
       </c>
       <c r="N66" t="n">
-        <v>0.01368605092109187</v>
+        <v>0.01368591871013214</v>
       </c>
       <c r="O66" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -8327,19 +8327,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G67" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="J67" t="n">
         <v>-640000000</v>
       </c>
       <c r="K67" t="n">
-        <v>-299442484.0499998</v>
+        <v>-303055643.3100001</v>
       </c>
       <c r="L67" t="n">
         <v>0.1050151041880321</v>
@@ -8351,10 +8351,10 @@
         <v>-0.08728823124945828</v>
       </c>
       <c r="O67" t="n">
-        <v>26066194.36957637</v>
+        <v>26380716.57860157</v>
       </c>
       <c r="P67" t="n">
-        <v>13033097.18478818</v>
+        <v>13190358.28930079</v>
       </c>
     </row>
     <row r="68">
@@ -8385,19 +8385,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G68" t="n">
-        <v>575699100.39</v>
+        <v>548709791.53</v>
       </c>
       <c r="H68" t="n">
-        <v>-555063100.8309005</v>
+        <v>-484035602.7846395</v>
       </c>
       <c r="I68" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="J68" t="n">
         <v>-64000000</v>
       </c>
       <c r="K68" t="n">
-        <v>84635999.55909944</v>
+        <v>128674188.7453604</v>
       </c>
       <c r="L68" t="n">
         <v>0.05822765833026367</v>
@@ -8409,10 +8409,10 @@
         <v>-0.03226565096877909</v>
       </c>
       <c r="O68" t="n">
-        <v>-2503265.98607034</v>
+        <v>-3805776.757519552</v>
       </c>
       <c r="P68" t="n">
-        <v>-2503265.98607034</v>
+        <v>-3805776.757519552</v>
       </c>
     </row>
     <row r="69">
@@ -8443,19 +8443,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G69" t="n">
-        <v>1961135371.76</v>
+        <v>1990072267.9</v>
       </c>
       <c r="H69" t="n">
-        <v>-507481570.8511116</v>
+        <v>-446135269.4812486</v>
       </c>
       <c r="I69" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="J69" t="n">
         <v>-64000000</v>
       </c>
       <c r="K69" t="n">
-        <v>1517653800.908888</v>
+        <v>1607936998.418751</v>
       </c>
       <c r="L69" t="n">
         <v>0.05839364669442126</v>
@@ -8467,10 +8467,10 @@
         <v>-0.0297728173926024</v>
       </c>
       <c r="O69" t="n">
-        <v>-37654024.56637441</v>
+        <v>-39894012.19394226</v>
       </c>
       <c r="P69" t="n">
-        <v>-37654024.56637441</v>
+        <v>-39894012.19394226</v>
       </c>
     </row>
     <row r="70">
@@ -8501,19 +8501,19 @@
         <v>0.75</v>
       </c>
       <c r="G70" t="n">
-        <v>531970690.13</v>
+        <v>321318332.1300001</v>
       </c>
       <c r="H70" t="n">
-        <v>-557976082.4163486</v>
+        <v>-496658630.361554</v>
       </c>
       <c r="I70" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="J70" t="n">
         <v>-64000000</v>
       </c>
       <c r="K70" t="n">
-        <v>37994607.71365142</v>
+        <v>-111340298.2315539</v>
       </c>
       <c r="L70" t="n">
         <v>0.05851824187679444</v>
@@ -8525,10 +8525,10 @@
         <v>-0.02753489969717293</v>
       </c>
       <c r="O70" t="n">
-        <v>-784633.2843216185</v>
+        <v>2299307.958044368</v>
       </c>
       <c r="P70" t="n">
-        <v>-784633.2843216185</v>
+        <v>1149653.979022184</v>
       </c>
     </row>
     <row r="71">
@@ -8559,19 +8559,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G71" t="n">
-        <v>78498009.31000002</v>
+        <v>82481230.3</v>
       </c>
       <c r="H71" t="n">
-        <v>-149884271.2777902</v>
+        <v>-119458296.2048057</v>
       </c>
       <c r="I71" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="J71" t="n">
         <v>-64000000</v>
       </c>
       <c r="K71" t="n">
-        <v>-7386261.967790231</v>
+        <v>27022934.09519425</v>
       </c>
       <c r="L71" t="n">
         <v>0.05821004393128892</v>
@@ -8583,10 +8583,10 @@
         <v>-0.02543179398870032</v>
       </c>
       <c r="O71" t="n">
-        <v>125230.5951409423</v>
+        <v>-458161.1285861375</v>
       </c>
       <c r="P71" t="n">
-        <v>62615.29757047114</v>
+        <v>-458161.1285861375</v>
       </c>
     </row>
     <row r="72">
@@ -8617,19 +8617,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G72" t="n">
-        <v>517889994.42</v>
+        <v>518697858.84</v>
       </c>
       <c r="H72" t="n">
-        <v>-149844342.9148888</v>
+        <v>-119426252.4590164</v>
       </c>
       <c r="I72" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="J72" t="n">
         <v>-64000000</v>
       </c>
       <c r="K72" t="n">
-        <v>432045651.5051111</v>
+        <v>463271606.3809837</v>
       </c>
       <c r="L72" t="n">
         <v>0.05808035784574397</v>
@@ -8641,10 +8641,10 @@
         <v>-0.02350867571892774</v>
       </c>
       <c r="O72" t="n">
-        <v>-5924812.318253805</v>
+        <v>-6353026.145781747</v>
       </c>
       <c r="P72" t="n">
-        <v>-5924812.318253805</v>
+        <v>-6353026.145781747</v>
       </c>
     </row>
     <row r="73">
@@ -8675,19 +8675,19 @@
         <v>0.5</v>
       </c>
       <c r="G73" t="n">
-        <v>902503166.1700001</v>
+        <v>669118580.01</v>
       </c>
       <c r="H73" t="n">
-        <v>-297430610.8241635</v>
+        <v>-207983441.3653717</v>
       </c>
       <c r="I73" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="J73" t="n">
         <v>-32000000</v>
       </c>
       <c r="K73" t="n">
-        <v>637072555.3458366</v>
+        <v>493135138.6446283</v>
       </c>
       <c r="L73" t="n">
         <v>0.0579990267461179</v>
@@ -8699,10 +8699,10 @@
         <v>-0.02171656780992581</v>
       </c>
       <c r="O73" t="n">
-        <v>-6917514.674005289</v>
+        <v>-5354601.338916618</v>
       </c>
       <c r="P73" t="n">
-        <v>-6917514.674005289</v>
+        <v>-5354601.338916618</v>
       </c>
     </row>
     <row r="74">
@@ -8733,19 +8733,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G74" t="n">
-        <v>-154283223.6</v>
+        <v>-153952841.84</v>
       </c>
       <c r="H74" t="n">
-        <v>63482820.57040198</v>
+        <v>61685111.16101505</v>
       </c>
       <c r="I74" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="J74" t="n">
         <v>-32000000</v>
       </c>
       <c r="K74" t="n">
-        <v>-58800403.02959804</v>
+        <v>-60267730.67898495</v>
       </c>
       <c r="L74" t="n">
         <v>0.05738520780446178</v>
@@ -8757,10 +8757,10 @@
         <v>-0.02006419037968943</v>
       </c>
       <c r="O74" t="n">
-        <v>491576.0336618008</v>
+        <v>503843.0092062514</v>
       </c>
       <c r="P74" t="n">
-        <v>245788.0168309004</v>
+        <v>251921.5046031257</v>
       </c>
     </row>
     <row r="75">
@@ -8791,19 +8791,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G75" t="n">
-        <v>-105494922.47</v>
+        <v>-105287618.79</v>
       </c>
       <c r="H75" t="n">
-        <v>11318465.07972154</v>
+        <v>9506772.962048057</v>
       </c>
       <c r="I75" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="J75" t="n">
         <v>-32000000</v>
       </c>
       <c r="K75" t="n">
-        <v>-62176457.39027846</v>
+        <v>-63780845.82795194</v>
       </c>
       <c r="L75" t="n">
         <v>0.05695407285841891</v>
@@ -8815,10 +8815,10 @@
         <v>-0.01853809135614659</v>
       </c>
       <c r="O75" t="n">
-        <v>384210.949100846</v>
+        <v>394125.0489102915</v>
       </c>
       <c r="P75" t="n">
-        <v>192105.474550423</v>
+        <v>197062.5244551457</v>
       </c>
     </row>
     <row r="76">
@@ -8849,19 +8849,19 @@
         <v>0.25</v>
       </c>
       <c r="G76" t="n">
-        <v>-106354032.72</v>
+        <v>-8670744.480000019</v>
       </c>
       <c r="H76" t="n">
-        <v>63470643.38648102</v>
+        <v>61673328.09342016</v>
       </c>
       <c r="I76" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="J76" t="n">
         <v>-32000000</v>
       </c>
       <c r="K76" t="n">
-        <v>-10883389.333519</v>
+        <v>85002583.61342014</v>
       </c>
       <c r="L76" t="n">
         <v>0.05664439372837885</v>
@@ -8873,10 +8873,10 @@
         <v>-0.01712553721773909</v>
       </c>
       <c r="O76" t="n">
-        <v>46595.97227158104</v>
+        <v>-363928.7273189013</v>
       </c>
       <c r="P76" t="n">
-        <v>23297.98613579052</v>
+        <v>-363928.7273189013</v>
       </c>
     </row>
     <row r="77">
@@ -8907,19 +8907,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G77" t="n">
-        <v>-105737558.25</v>
+        <v>-105791543.79</v>
       </c>
       <c r="H77" t="n">
-        <v>11243431.39456546</v>
+        <v>9444482.371434988</v>
       </c>
       <c r="I77" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="J77" t="n">
         <v>-32000000</v>
       </c>
       <c r="K77" t="n">
-        <v>-62494126.85543452</v>
+        <v>-64347061.41856501</v>
       </c>
       <c r="L77" t="n">
         <v>0.05642057743315654</v>
@@ -8931,10 +8931,10 @@
         <v>-0.01582455504283544</v>
       </c>
       <c r="O77" t="n">
-        <v>164823.625046294</v>
+        <v>169710.6025437991</v>
       </c>
       <c r="P77" t="n">
-        <v>82411.81252314699</v>
+        <v>84855.30127189953</v>
       </c>
     </row>
     <row r="78">
@@ -8965,19 +8965,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G78" t="n">
-        <v>-105013009.69</v>
+        <v>-105084497.29</v>
       </c>
       <c r="H78" t="n">
-        <v>11307685.82977768</v>
+        <v>9498456.09701325</v>
       </c>
       <c r="I78" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="J78" t="n">
         <v>-32000000</v>
       </c>
       <c r="K78" t="n">
-        <v>-61705323.86022232</v>
+        <v>-63586041.19298677</v>
       </c>
       <c r="L78" t="n">
         <v>0.05625883751011833</v>
@@ -8989,10 +8989,10 @@
         <v>-0.01462200030522725</v>
       </c>
       <c r="O78" t="n">
-        <v>75187.93869319312</v>
+        <v>77479.59281100379</v>
       </c>
       <c r="P78" t="n">
-        <v>37593.96934659656</v>
+        <v>38739.7964055019</v>
       </c>
     </row>
     <row r="79">
@@ -9023,34 +9023,34 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>-86650256.47999999</v>
+        <v>26344865.39000002</v>
       </c>
       <c r="H79" t="n">
-        <v>11236273.29889962</v>
+        <v>9437731.866157647</v>
       </c>
       <c r="I79" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="J79" t="n">
         <v>-32000000</v>
       </c>
       <c r="K79" t="n">
-        <v>-43413983.18110037</v>
+        <v>67782597.25615767</v>
       </c>
       <c r="L79" t="n">
-        <v>0.05612986869467673</v>
+        <v>0.05612125523607059</v>
       </c>
       <c r="M79" t="n">
-        <v>0.04261896504062945</v>
+        <v>0.04261044181554507</v>
       </c>
       <c r="N79" t="n">
-        <v>-0.01351090365404728</v>
+        <v>-0.01351081342052551</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="80">
@@ -9081,19 +9081,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G80" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="J80" t="n">
         <v>-640000000</v>
       </c>
       <c r="K80" t="n">
-        <v>-299442484.0499998</v>
+        <v>-303055643.3100001</v>
       </c>
       <c r="L80" t="n">
         <v>0.1050151041880321</v>
@@ -9105,10 +9105,10 @@
         <v>-0.06247613761654947</v>
       </c>
       <c r="O80" t="n">
-        <v>18656755.02026496</v>
+        <v>18881872.79998446</v>
       </c>
       <c r="P80" t="n">
-        <v>9328377.51013248</v>
+        <v>9440936.399992229</v>
       </c>
     </row>
     <row r="81">
@@ -9139,19 +9139,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G81" t="n">
-        <v>575699100.39</v>
+        <v>548709791.53</v>
       </c>
       <c r="H81" t="n">
-        <v>-555063100.8309005</v>
+        <v>-484035602.7846395</v>
       </c>
       <c r="I81" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="J81" t="n">
         <v>-64000000</v>
       </c>
       <c r="K81" t="n">
-        <v>84635999.55909944</v>
+        <v>128674188.7453604</v>
       </c>
       <c r="L81" t="n">
         <v>0.05822765833026367</v>
@@ -9163,10 +9163,10 @@
         <v>-0.01004192341464538</v>
       </c>
       <c r="O81" t="n">
-        <v>-779082.5402199004</v>
+        <v>-1184458.31975399</v>
       </c>
       <c r="P81" t="n">
-        <v>-779082.5402199004</v>
+        <v>-1184458.31975399</v>
       </c>
     </row>
     <row r="82">
@@ -9197,19 +9197,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G82" t="n">
-        <v>1961135371.76</v>
+        <v>1990072267.9</v>
       </c>
       <c r="H82" t="n">
-        <v>-507481570.8511116</v>
+        <v>-446135269.4812486</v>
       </c>
       <c r="I82" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="J82" t="n">
         <v>-64000000</v>
       </c>
       <c r="K82" t="n">
-        <v>1517653800.908888</v>
+        <v>1607936998.418751</v>
       </c>
       <c r="L82" t="n">
         <v>0.05839364669442126</v>
@@ -9221,10 +9221,10 @@
         <v>-0.01008473632087492</v>
       </c>
       <c r="O82" t="n">
-        <v>-12754282.00711645</v>
+        <v>-13513017.20802682</v>
       </c>
       <c r="P82" t="n">
-        <v>-12754282.00711645</v>
+        <v>-13513017.20802682</v>
       </c>
     </row>
     <row r="83">
@@ -9255,19 +9255,19 @@
         <v>0.75</v>
       </c>
       <c r="G83" t="n">
-        <v>531970690.13</v>
+        <v>321318332.1300001</v>
       </c>
       <c r="H83" t="n">
-        <v>-557976082.4163486</v>
+        <v>-496658630.361554</v>
       </c>
       <c r="I83" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="J83" t="n">
         <v>-64000000</v>
       </c>
       <c r="K83" t="n">
-        <v>37994607.71365142</v>
+        <v>-111340298.2315539</v>
       </c>
       <c r="L83" t="n">
         <v>0.05851824187679444</v>
@@ -9279,10 +9279,10 @@
         <v>-0.01013182991584927</v>
       </c>
       <c r="O83" t="n">
-        <v>-288716.177305598</v>
+        <v>846060.7233465279</v>
       </c>
       <c r="P83" t="n">
-        <v>-288716.177305598</v>
+        <v>423030.3616732639</v>
       </c>
     </row>
     <row r="84">
@@ -9313,19 +9313,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G84" t="n">
-        <v>78498009.31000002</v>
+        <v>82481230.3</v>
       </c>
       <c r="H84" t="n">
-        <v>-149884271.2777902</v>
+        <v>-119458296.2048057</v>
       </c>
       <c r="I84" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="J84" t="n">
         <v>-64000000</v>
       </c>
       <c r="K84" t="n">
-        <v>-7386261.967790231</v>
+        <v>27022934.09519425</v>
       </c>
       <c r="L84" t="n">
         <v>0.05821004393128892</v>
@@ -9337,10 +9337,10 @@
         <v>-0.01017508542911516</v>
       </c>
       <c r="O84" t="n">
-        <v>50103.89768272657</v>
+        <v>-183307.1086426336</v>
       </c>
       <c r="P84" t="n">
-        <v>25051.94884136329</v>
+        <v>-183307.1086426336</v>
       </c>
     </row>
     <row r="85">
@@ -9371,19 +9371,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G85" t="n">
-        <v>517889994.42</v>
+        <v>518697858.84</v>
       </c>
       <c r="H85" t="n">
-        <v>-149844342.9148888</v>
+        <v>-119426252.4590164</v>
       </c>
       <c r="I85" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="J85" t="n">
         <v>-64000000</v>
       </c>
       <c r="K85" t="n">
-        <v>432045651.5051111</v>
+        <v>463271606.3809837</v>
       </c>
       <c r="L85" t="n">
         <v>0.05808035784574397</v>
@@ -9395,10 +9395,10 @@
         <v>-0.01021994033044944</v>
       </c>
       <c r="O85" t="n">
-        <v>-2575697.12074056</v>
+        <v>-2761854.76816965</v>
       </c>
       <c r="P85" t="n">
-        <v>-2575697.12074056</v>
+        <v>-2761854.76816965</v>
       </c>
     </row>
     <row r="86">
@@ -9429,19 +9429,19 @@
         <v>0.5</v>
       </c>
       <c r="G86" t="n">
-        <v>902503166.1700001</v>
+        <v>669118580.01</v>
       </c>
       <c r="H86" t="n">
-        <v>-297430610.8241635</v>
+        <v>-207983441.3653717</v>
       </c>
       <c r="I86" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="J86" t="n">
         <v>-32000000</v>
       </c>
       <c r="K86" t="n">
-        <v>637072555.3458366</v>
+        <v>493135138.6446283</v>
       </c>
       <c r="L86" t="n">
         <v>0.0579990267461179</v>
@@ -9453,10 +9453,10 @@
         <v>-0.01026331977023442</v>
       </c>
       <c r="O86" t="n">
-        <v>-3269239.676177345</v>
+        <v>-2530601.808924354</v>
       </c>
       <c r="P86" t="n">
-        <v>-3269239.676177345</v>
+        <v>-2530601.808924354</v>
       </c>
     </row>
     <row r="87">
@@ -9487,19 +9487,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G87" t="n">
-        <v>-154283223.6</v>
+        <v>-153952841.84</v>
       </c>
       <c r="H87" t="n">
-        <v>63482820.57040198</v>
+        <v>61685111.16101505</v>
       </c>
       <c r="I87" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="J87" t="n">
         <v>-32000000</v>
       </c>
       <c r="K87" t="n">
-        <v>-58800403.02959804</v>
+        <v>-60267730.67898495</v>
       </c>
       <c r="L87" t="n">
         <v>0.05738520780446178</v>
@@ -9511,10 +9511,10 @@
         <v>-0.01030407096516736</v>
       </c>
       <c r="O87" t="n">
-        <v>252451.4689989251</v>
+        <v>258751.2390941062</v>
       </c>
       <c r="P87" t="n">
-        <v>126225.7344994625</v>
+        <v>129375.6195470531</v>
       </c>
     </row>
     <row r="88">
@@ -9545,19 +9545,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G88" t="n">
-        <v>-105494922.47</v>
+        <v>-105287618.79</v>
       </c>
       <c r="H88" t="n">
-        <v>11318465.07972154</v>
+        <v>9506772.962048057</v>
       </c>
       <c r="I88" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="J88" t="n">
         <v>-32000000</v>
       </c>
       <c r="K88" t="n">
-        <v>-62176457.39027846</v>
+        <v>-63780845.82795194</v>
       </c>
       <c r="L88" t="n">
         <v>0.05695407285841891</v>
@@ -9569,10 +9569,10 @@
         <v>-0.01034491853166675</v>
       </c>
       <c r="O88" t="n">
-        <v>214403.4620966932</v>
+        <v>219935.8846569866</v>
       </c>
       <c r="P88" t="n">
-        <v>107201.7310483466</v>
+        <v>109967.9423284933</v>
       </c>
     </row>
     <row r="89">
@@ -9603,19 +9603,19 @@
         <v>0.25</v>
       </c>
       <c r="G89" t="n">
-        <v>-106354032.72</v>
+        <v>-8670744.480000019</v>
       </c>
       <c r="H89" t="n">
-        <v>63470643.38648102</v>
+        <v>61673328.09342016</v>
       </c>
       <c r="I89" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="J89" t="n">
         <v>-32000000</v>
       </c>
       <c r="K89" t="n">
-        <v>-10883389.333519</v>
+        <v>85002583.61342014</v>
       </c>
       <c r="L89" t="n">
         <v>0.05664439372837885</v>
@@ -9627,10 +9627,10 @@
         <v>-0.01038544122264451</v>
       </c>
       <c r="O89" t="n">
-        <v>28257.20005660443</v>
+        <v>-220697.3339725251</v>
       </c>
       <c r="P89" t="n">
-        <v>14128.60002830222</v>
+        <v>-220697.3339725251</v>
       </c>
     </row>
     <row r="90">
@@ -9661,19 +9661,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>-105737558.25</v>
+        <v>-105791543.79</v>
       </c>
       <c r="H90" t="n">
-        <v>11243431.39456546</v>
+        <v>9444482.371434988</v>
       </c>
       <c r="I90" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="J90" t="n">
         <v>-32000000</v>
       </c>
       <c r="K90" t="n">
-        <v>-62494126.85543452</v>
+        <v>-64347061.41856501</v>
       </c>
       <c r="L90" t="n">
         <v>0.05642057743315654</v>
@@ -9685,10 +9685,10 @@
         <v>-0.01042652380310684</v>
       </c>
       <c r="O90" t="n">
-        <v>108599.4168687611</v>
+        <v>111819.3612567743</v>
       </c>
       <c r="P90" t="n">
-        <v>54299.70843438055</v>
+        <v>55909.68062838717</v>
       </c>
     </row>
     <row r="91">
@@ -9719,19 +9719,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G91" t="n">
-        <v>-105013009.69</v>
+        <v>-105084497.29</v>
       </c>
       <c r="H91" t="n">
-        <v>11307685.82977768</v>
+        <v>9498456.09701325</v>
       </c>
       <c r="I91" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="J91" t="n">
         <v>-32000000</v>
       </c>
       <c r="K91" t="n">
-        <v>-61705323.86022232</v>
+        <v>-63586041.19298677</v>
       </c>
       <c r="L91" t="n">
         <v>0.05625883751011833</v>
@@ -9743,10 +9743,10 @@
         <v>-0.01046759094930644</v>
       </c>
       <c r="O91" t="n">
-        <v>53825.5074636072</v>
+        <v>55466.05577449461</v>
       </c>
       <c r="P91" t="n">
-        <v>26912.7537318036</v>
+        <v>27733.02788724731</v>
       </c>
     </row>
     <row r="92">
@@ -9777,34 +9777,34 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>-86650256.47999999</v>
+        <v>26344865.39000002</v>
       </c>
       <c r="H92" t="n">
-        <v>11236273.29889962</v>
+        <v>9437731.866157647</v>
       </c>
       <c r="I92" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="J92" t="n">
         <v>-32000000</v>
       </c>
       <c r="K92" t="n">
-        <v>-43413983.18110037</v>
+        <v>67782597.25615767</v>
       </c>
       <c r="L92" t="n">
-        <v>0.05612986869467673</v>
+        <v>0.05612125523607059</v>
       </c>
       <c r="M92" t="n">
-        <v>0.04562123316148581</v>
+        <v>0.04561268519858142</v>
       </c>
       <c r="N92" t="n">
-        <v>-0.01050863553319092</v>
+        <v>-0.01050857003748917</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
@@ -9880,22 +9880,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>592799601.3099999</v>
+        <v>568343637.74</v>
       </c>
       <c r="D2" t="n">
-        <v>634633666.41</v>
+        <v>595604777.72</v>
       </c>
       <c r="E2" t="n">
-        <v>41834065.10000002</v>
+        <v>27261139.98000002</v>
       </c>
       <c r="F2" t="n">
-        <v>20917032.55000001</v>
+        <v>13630569.99000001</v>
       </c>
       <c r="G2" t="n">
-        <v>2.324114727777779</v>
+        <v>1.703821248750001</v>
       </c>
       <c r="H2" t="n">
-        <v>1.16205736388889</v>
+        <v>0.8519106243750006</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -9913,22 +9913,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>592799601.3099999</v>
+        <v>568343637.74</v>
       </c>
       <c r="D3" t="n">
-        <v>550757802.72</v>
+        <v>543419870.96</v>
       </c>
       <c r="E3" t="n">
-        <v>-42041798.58999991</v>
+        <v>-24923766.77999997</v>
       </c>
       <c r="F3" t="n">
-        <v>-42041798.58999991</v>
+        <v>-24923766.77999997</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.335655477222217</v>
+        <v>-1.557735423749998</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.335655477222217</v>
+        <v>-1.557735423749998</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -9946,22 +9946,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>592799601.3099999</v>
+        <v>568343637.74</v>
       </c>
       <c r="D4" t="n">
-        <v>593802656.5</v>
+        <v>577077882.63</v>
       </c>
       <c r="E4" t="n">
-        <v>1003055.190000057</v>
+        <v>8734244.889999986</v>
       </c>
       <c r="F4" t="n">
-        <v>501527.5950000286</v>
+        <v>4367122.444999993</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05572528833333652</v>
+        <v>0.5458903056249991</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02786264416666826</v>
+        <v>0.2729451528124995</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -9979,22 +9979,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>592799601.3099999</v>
+        <v>568343637.74</v>
       </c>
       <c r="D5" t="n">
-        <v>597220617.66</v>
+        <v>564941749.88</v>
       </c>
       <c r="E5" t="n">
-        <v>4421016.350000024</v>
+        <v>-3401887.860000014</v>
       </c>
       <c r="F5" t="n">
-        <v>2210508.175000012</v>
+        <v>-3401887.860000014</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2456120194444457</v>
+        <v>-0.2126179912500009</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1228060097222229</v>
+        <v>-0.2126179912500009</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -10012,22 +10012,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>592799601.3099999</v>
+        <v>568343637.74</v>
       </c>
       <c r="D6" t="n">
-        <v>613562440.08</v>
+        <v>575902873.34</v>
       </c>
       <c r="E6" t="n">
-        <v>20762838.7700001</v>
+        <v>7559235.600000024</v>
       </c>
       <c r="F6" t="n">
-        <v>10381419.38500005</v>
+        <v>3779617.800000012</v>
       </c>
       <c r="G6" t="n">
-        <v>1.153491042777783</v>
+        <v>0.4724522250000014</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5767455213888917</v>
+        <v>0.2362261125000007</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -10045,22 +10045,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>592799601.3099999</v>
+        <v>568343637.74</v>
       </c>
       <c r="D7" t="n">
-        <v>571902395.28</v>
+        <v>563205377.86</v>
       </c>
       <c r="E7" t="n">
-        <v>-20897206.02999997</v>
+        <v>-5138259.879999995</v>
       </c>
       <c r="F7" t="n">
-        <v>-20897206.02999997</v>
+        <v>-5138259.879999995</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.160955890555554</v>
+        <v>-0.3211412424999997</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.160955890555554</v>
+        <v>-0.3211412424999997</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -10078,22 +10078,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>592799601.3099999</v>
+        <v>568343637.74</v>
       </c>
       <c r="D8" t="n">
-        <v>575947127.49</v>
+        <v>559119349.5700001</v>
       </c>
       <c r="E8" t="n">
-        <v>-16852473.81999993</v>
+        <v>-9224288.169999957</v>
       </c>
       <c r="F8" t="n">
-        <v>-16852473.81999993</v>
+        <v>-9224288.169999957</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9362485455555519</v>
+        <v>-0.5765180106249973</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9362485455555519</v>
+        <v>-0.5765180106249973</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>

--- a/irrbb_calc/output/eba_sot_results.xlsx
+++ b/irrbb_calc/output/eba_sot_results.xlsx
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-837973082.6800001</v>
+        <v>-1657923918.46</v>
       </c>
       <c r="E2" t="n">
         <v>0.9975215395798449</v>
@@ -495,10 +495,10 @@
         <v>-0.001075339705425948</v>
       </c>
       <c r="H2" t="n">
-        <v>901105.7278839851</v>
+        <v>1782831.418095411</v>
       </c>
       <c r="I2" t="n">
-        <v>450552.8639419926</v>
+        <v>891415.7090477053</v>
       </c>
     </row>
     <row r="3">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19495500.62999999</v>
+        <v>-756411374.3</v>
       </c>
       <c r="E3" t="n">
         <v>0.9903615297882993</v>
@@ -530,10 +530,10 @@
         <v>-0.004118598226101611</v>
       </c>
       <c r="H3" t="n">
-        <v>-80294.1343116808</v>
+        <v>3115354.544395061</v>
       </c>
       <c r="I3" t="n">
-        <v>-80294.1343116808</v>
+        <v>1557677.272197531</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>110748422.65</v>
+        <v>-575289791.02</v>
       </c>
       <c r="E4" t="n">
         <v>0.9786688180301472</v>
@@ -565,10 +565,10 @@
         <v>-0.009135282621367979</v>
       </c>
       <c r="H4" t="n">
-        <v>-1011718.140778461</v>
+        <v>5255434.830155423</v>
       </c>
       <c r="I4" t="n">
-        <v>-1011718.140778461</v>
+        <v>2627717.415077711</v>
       </c>
     </row>
     <row r="5">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28459734.17999999</v>
+        <v>287271212.35</v>
       </c>
       <c r="E5" t="n">
         <v>0.9655145554862491</v>
@@ -600,10 +600,10 @@
         <v>-0.01497137919106994</v>
       </c>
       <c r="H5" t="n">
-        <v>-426081.472085834</v>
+        <v>-4300846.250770225</v>
       </c>
       <c r="I5" t="n">
-        <v>-426081.472085834</v>
+        <v>-4300846.250770225</v>
       </c>
     </row>
     <row r="6">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>120520575.19</v>
+        <v>338026454.7</v>
       </c>
       <c r="E6" t="n">
         <v>0.9530263468310431</v>
@@ -635,10 +635,10 @@
         <v>-0.02062335501537482</v>
       </c>
       <c r="H6" t="n">
-        <v>-2485538.608800545</v>
+        <v>-6971239.579866615</v>
       </c>
       <c r="I6" t="n">
-        <v>-2485538.608800545</v>
+        <v>-6971239.579866615</v>
       </c>
     </row>
     <row r="7">
@@ -658,22 +658,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>41495736.82999998</v>
+        <v>641813154.08</v>
       </c>
       <c r="E7" t="n">
-        <v>0.93726391898459</v>
+        <v>0.9356051227617213</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9084269373918286</v>
+        <v>0.9068191590404275</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.02883698159276149</v>
+        <v>-0.02878596372129372</v>
       </c>
       <c r="H7" t="n">
-        <v>-1196611.799144784</v>
+        <v>-18475210.16919598</v>
       </c>
       <c r="I7" t="n">
-        <v>-1196611.799144784</v>
+        <v>-18475210.16919598</v>
       </c>
     </row>
     <row r="8">
@@ -693,22 +693,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>34519707.57000002</v>
+        <v>514396150.85</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9132428090891569</v>
+        <v>0.9110361496874445</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8741495039644692</v>
+        <v>0.8720372866398278</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.03909330512468767</v>
+        <v>-0.03899886304761668</v>
       </c>
       <c r="H8" t="n">
-        <v>-1349489.460849001</v>
+        <v>-20060865.03922032</v>
       </c>
       <c r="I8" t="n">
-        <v>-1349489.460849001</v>
+        <v>-20060865.03922032</v>
       </c>
     </row>
     <row r="9">
@@ -728,22 +728,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>874279275.16</v>
+        <v>1009792864.15</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8783257731734563</v>
+        <v>0.8754048758167313</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8251101553569301</v>
+        <v>0.8223662072656972</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.05321561781652617</v>
+        <v>-0.05303866855103412</v>
       </c>
       <c r="H9" t="n">
-        <v>-46525311.77182408</v>
+        <v>-53558069.02685127</v>
       </c>
       <c r="I9" t="n">
-        <v>-46525311.77182408</v>
+        <v>-53558069.02685127</v>
       </c>
     </row>
     <row r="10">
@@ -763,22 +763,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>857185142.1</v>
+        <v>794321595.54</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8337865285685646</v>
+        <v>0.8300899355387754</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7639306370293591</v>
+        <v>0.7605437457941407</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.06985589153920546</v>
+        <v>-0.06954618974463467</v>
       </c>
       <c r="H10" t="n">
-        <v>-59879432.31555602</v>
+        <v>-55242040.40168579</v>
       </c>
       <c r="I10" t="n">
-        <v>-59879432.31555602</v>
+        <v>-55242040.40168579</v>
       </c>
     </row>
     <row r="11">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>929236654.11</v>
+        <v>1623369977.36</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7914638140234228</v>
+        <v>0.7871638664957131</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7072498853543311</v>
+        <v>0.7034074629850886</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.08421392866909172</v>
+        <v>-0.08375640351062452</v>
       </c>
       <c r="H11" t="n">
-        <v>-78254669.305925</v>
+        <v>-135967630.8707975</v>
       </c>
       <c r="I11" t="n">
-        <v>-78254669.305925</v>
+        <v>-135967630.8707975</v>
       </c>
     </row>
     <row r="12">
@@ -833,22 +833,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>165783076.62</v>
+        <v>99536703.16000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.751260515961125</v>
+        <v>0.7465017756172543</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6547491807474654</v>
+        <v>0.6506017702139196</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.09651133521365962</v>
+        <v>-0.09590000540333465</v>
       </c>
       <c r="H12" t="n">
-        <v>-15999946.08042464</v>
+        <v>-9545570.370874118</v>
       </c>
       <c r="I12" t="n">
-        <v>-15999946.08042464</v>
+        <v>-9545570.370874118</v>
       </c>
     </row>
     <row r="13">
@@ -868,22 +868,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>347766801.69</v>
+        <v>318521371.88</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7130798016126879</v>
+        <v>0.7079831292590303</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6061289235629088</v>
+        <v>0.6017966661503515</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1069508780497791</v>
+        <v>-0.1061864631086787</v>
       </c>
       <c r="H13" t="n">
-        <v>-37193964.7973089</v>
+        <v>-33822657.90446136</v>
       </c>
       <c r="I13" t="n">
-        <v>-37193964.7973089</v>
+        <v>-33822657.90446136</v>
       </c>
     </row>
     <row r="14">
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>286514959.36</v>
+        <v>306908451.75</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6768263201051378</v>
+        <v>0.6714924005042728</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5611084780344545</v>
+        <v>0.5566864983829313</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1157178420706833</v>
+        <v>-0.1148059021213416</v>
       </c>
       <c r="H14" t="n">
-        <v>-33154892.81810871</v>
+        <v>-35234901.67182298</v>
       </c>
       <c r="I14" t="n">
-        <v>-33154892.81810871</v>
+        <v>-35234901.67182298</v>
       </c>
     </row>
     <row r="15">
@@ -938,22 +938,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>200982460.28</v>
+        <v>223541651.31</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6424083347829114</v>
+        <v>0.6369207605854804</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5194256295822366</v>
+        <v>0.5149885884815573</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1229827052006748</v>
+        <v>-0.1219321721039232</v>
       </c>
       <c r="H15" t="n">
-        <v>-24717366.66312157</v>
+        <v>-27256919.0999261</v>
       </c>
       <c r="I15" t="n">
-        <v>-24717366.66312157</v>
+        <v>-27256919.0999261</v>
       </c>
     </row>
     <row r="16">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8804292.67</v>
+        <v>14469721.94</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6097363477190296</v>
+        <v>0.6041641709026</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4808359175133123</v>
+        <v>0.4764417163072422</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1289004302057173</v>
+        <v>-0.1277224545953578</v>
       </c>
       <c r="H16" t="n">
-        <v>-1134877.112820043</v>
+        <v>-1848108.403489103</v>
       </c>
       <c r="I16" t="n">
-        <v>-1134877.112820043</v>
+        <v>-1848108.403489103</v>
       </c>
     </row>
     <row r="17">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-837973082.6800001</v>
+        <v>-1657923918.46</v>
       </c>
       <c r="E17" t="n">
         <v>0.9975215395798449</v>
@@ -1020,10 +1020,10 @@
         <v>0.001071141156266053</v>
       </c>
       <c r="H17" t="n">
-        <v>-897587.4567016844</v>
+        <v>-1775870.54302039</v>
       </c>
       <c r="I17" t="n">
-        <v>-897587.4567016844</v>
+        <v>-1775870.54302039</v>
       </c>
     </row>
     <row r="18">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>19495500.62999999</v>
+        <v>-756411374.3</v>
       </c>
       <c r="E18" t="n">
         <v>0.9903615297882993</v>
@@ -1055,10 +1055,10 @@
         <v>0.004134433531466697</v>
       </c>
       <c r="H18" t="n">
-        <v>80602.85151740207</v>
+        <v>-3127332.549488726</v>
       </c>
       <c r="I18" t="n">
-        <v>40301.42575870104</v>
+        <v>-3127332.549488726</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>110748422.65</v>
+        <v>-575289791.02</v>
       </c>
       <c r="E19" t="n">
         <v>0.9786688180301472</v>
@@ -1090,10 +1090,10 @@
         <v>0.009214966721668216</v>
       </c>
       <c r="H19" t="n">
-        <v>1020543.029196997</v>
+        <v>-5301276.279564762</v>
       </c>
       <c r="I19" t="n">
-        <v>510271.5145984983</v>
+        <v>-5301276.279564762</v>
       </c>
     </row>
     <row r="20">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28459734.17999999</v>
+        <v>287271212.35</v>
       </c>
       <c r="E20" t="n">
         <v>0.9655145554862491</v>
@@ -1125,10 +1125,10 @@
         <v>0.01520208972261294</v>
       </c>
       <c r="H20" t="n">
-        <v>432647.4324860742</v>
+        <v>4367122.744868496</v>
       </c>
       <c r="I20" t="n">
-        <v>216323.7162430371</v>
+        <v>2183561.372434248</v>
       </c>
     </row>
     <row r="21">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>120520575.19</v>
+        <v>338026454.7</v>
       </c>
       <c r="E21" t="n">
         <v>0.9530263468310431</v>
@@ -1160,10 +1160,10 @@
         <v>0.02107476671306407</v>
       </c>
       <c r="H21" t="n">
-        <v>2539943.006253548</v>
+        <v>7123828.675646621</v>
       </c>
       <c r="I21" t="n">
-        <v>1269971.503126774</v>
+        <v>3561914.33782331</v>
       </c>
     </row>
     <row r="22">
@@ -1183,22 +1183,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>41495736.82999998</v>
+        <v>641813154.08</v>
       </c>
       <c r="E22" t="n">
-        <v>0.93726391898459</v>
+        <v>0.9356051227617213</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9670154398695024</v>
+        <v>0.9653039595636365</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0297515208849124</v>
+        <v>0.02969883680191521</v>
       </c>
       <c r="H22" t="n">
-        <v>1234561.280932573</v>
+        <v>19061104.12034438</v>
       </c>
       <c r="I22" t="n">
-        <v>617280.6404662866</v>
+        <v>9530552.060172191</v>
       </c>
     </row>
     <row r="23">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>34519707.57000002</v>
+        <v>514396150.85</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9132428090891569</v>
+        <v>0.9110361496874445</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9540837026613954</v>
+        <v>0.9517783430676411</v>
       </c>
       <c r="G23" t="n">
-        <v>0.04084089357223852</v>
+        <v>0.04074219338019658</v>
       </c>
       <c r="H23" t="n">
-        <v>1409815.703011167</v>
+        <v>20957627.45195947</v>
       </c>
       <c r="I23" t="n">
-        <v>704907.8515055836</v>
+        <v>10478813.72597974</v>
       </c>
     </row>
     <row r="24">
@@ -1253,22 +1253,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>874279275.16</v>
+        <v>1009792864.15</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8783257731734563</v>
+        <v>0.8754048758167313</v>
       </c>
       <c r="F24" t="n">
-        <v>0.934972302134487</v>
+        <v>0.9318629925800875</v>
       </c>
       <c r="G24" t="n">
-        <v>0.05664652896103073</v>
+        <v>0.05645811676335621</v>
       </c>
       <c r="H24" t="n">
-        <v>49524886.28037989</v>
+        <v>57011003.4309846</v>
       </c>
       <c r="I24" t="n">
-        <v>24762443.14018995</v>
+        <v>28505501.7154923</v>
       </c>
     </row>
     <row r="25">
@@ -1288,22 +1288,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>857185142.1</v>
+        <v>794321595.54</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8337865285685646</v>
+        <v>0.8300899355387754</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9100294844453058</v>
+        <v>0.9059948464314536</v>
       </c>
       <c r="G25" t="n">
-        <v>0.07624295587674124</v>
+        <v>0.07590491089267815</v>
       </c>
       <c r="H25" t="n">
-        <v>65354328.96732847</v>
+        <v>60292909.92959363</v>
       </c>
       <c r="I25" t="n">
-        <v>32677164.48366423</v>
+        <v>30146454.96479682</v>
       </c>
     </row>
     <row r="26">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>929236654.11</v>
+        <v>1623369977.36</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7914638140234228</v>
+        <v>0.7871638664957131</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8857050952684282</v>
+        <v>0.8808931377261134</v>
       </c>
       <c r="G26" t="n">
-        <v>0.09424128124500541</v>
+        <v>0.09372927123040031</v>
       </c>
       <c r="H26" t="n">
-        <v>87572452.86314833</v>
+        <v>152157284.9152642</v>
       </c>
       <c r="I26" t="n">
-        <v>43786226.43157417</v>
+        <v>76078642.45763212</v>
       </c>
     </row>
     <row r="27">
@@ -1358,22 +1358,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>165783076.62</v>
+        <v>99536703.16000001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.751260515961125</v>
+        <v>0.7465017756172543</v>
       </c>
       <c r="F27" t="n">
-        <v>0.861997376412613</v>
+        <v>0.8565371814873228</v>
       </c>
       <c r="G27" t="n">
-        <v>0.110736860451488</v>
+        <v>0.1100354058700685</v>
       </c>
       <c r="H27" t="n">
-        <v>18358297.42088728</v>
+        <v>10952561.53117914</v>
       </c>
       <c r="I27" t="n">
-        <v>9179148.710443642</v>
+        <v>5476280.765589568</v>
       </c>
     </row>
     <row r="28">
@@ -1393,22 +1393,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>347766801.69</v>
+        <v>318521371.88</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7130798016126879</v>
+        <v>0.7079831292590303</v>
       </c>
       <c r="F28" t="n">
-        <v>0.838901007195674</v>
+        <v>0.8329050219133051</v>
       </c>
       <c r="G28" t="n">
-        <v>0.125821205582986</v>
+        <v>0.1249218926542748</v>
       </c>
       <c r="H28" t="n">
-        <v>43756438.25037502</v>
+        <v>39790292.6260857</v>
       </c>
       <c r="I28" t="n">
-        <v>21878219.12518751</v>
+        <v>19895146.31304285</v>
       </c>
     </row>
     <row r="29">
@@ -1428,22 +1428,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>286514959.36</v>
+        <v>306908451.75</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6768263201051378</v>
+        <v>0.6714924005042728</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8164080226826227</v>
+        <v>0.809974080489948</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1395817025774849</v>
+        <v>0.1384816799856752</v>
       </c>
       <c r="H29" t="n">
-        <v>39992245.8413877</v>
+        <v>42501198.00014253</v>
       </c>
       <c r="I29" t="n">
-        <v>19996122.92069385</v>
+        <v>21250599.00007126</v>
       </c>
     </row>
     <row r="30">
@@ -1463,22 +1463,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>200982460.28</v>
+        <v>223541651.31</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6424083347829114</v>
+        <v>0.6369207605854804</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7945084565797302</v>
+        <v>0.7877216066542996</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1521001217968189</v>
+        <v>0.1508008460688192</v>
       </c>
       <c r="H30" t="n">
-        <v>30569456.68761231</v>
+        <v>33710270.14916896</v>
       </c>
       <c r="I30" t="n">
-        <v>15284728.34380616</v>
+        <v>16855135.07458448</v>
       </c>
     </row>
     <row r="31">
@@ -1498,22 +1498,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8804292.67</v>
+        <v>14469721.94</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6097363477190296</v>
+        <v>0.6041641709026</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7731909832372605</v>
+        <v>0.7661250410260293</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1634546355182309</v>
+        <v>0.1619608701234293</v>
       </c>
       <c r="H31" t="n">
-        <v>1439102.449370682</v>
+        <v>2343528.755846475</v>
       </c>
       <c r="I31" t="n">
-        <v>719551.224685341</v>
+        <v>1171764.377923238</v>
       </c>
     </row>
     <row r="32">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-837973082.6800001</v>
+        <v>-1657923918.46</v>
       </c>
       <c r="E32" t="n">
         <v>0.9975215395798449</v>
@@ -1545,10 +1545,10 @@
         <v>0.0008556326727643393</v>
       </c>
       <c r="H32" t="n">
-        <v>-716997.1484380611</v>
+        <v>-1418573.873591856</v>
       </c>
       <c r="I32" t="n">
-        <v>-716997.1484380611</v>
+        <v>-1418573.873591856</v>
       </c>
     </row>
     <row r="33">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>19495500.62999999</v>
+        <v>-756411374.3</v>
       </c>
       <c r="E33" t="n">
         <v>0.9903615297882993</v>
@@ -1580,10 +1580,10 @@
         <v>0.002828930695566667</v>
       </c>
       <c r="H33" t="n">
-        <v>55151.42015764627</v>
+        <v>-2139835.355233037</v>
       </c>
       <c r="I33" t="n">
-        <v>27575.71007882314</v>
+        <v>-2139835.355233037</v>
       </c>
     </row>
     <row r="34">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>110748422.65</v>
+        <v>-575289791.02</v>
       </c>
       <c r="E34" t="n">
         <v>0.9786688180301472</v>
@@ -1615,10 +1615,10 @@
         <v>0.004154192302518012</v>
       </c>
       <c r="H34" t="n">
-        <v>460070.2448886415</v>
+        <v>-2389864.421572479</v>
       </c>
       <c r="I34" t="n">
-        <v>230035.1224443207</v>
+        <v>-2389864.421572479</v>
       </c>
     </row>
     <row r="35">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>28459734.17999999</v>
+        <v>287271212.35</v>
       </c>
       <c r="E35" t="n">
         <v>0.9655145554862491</v>
@@ -1650,10 +1650,10 @@
         <v>0.003541509817362121</v>
       </c>
       <c r="H35" t="n">
-        <v>100790.4279979863</v>
+        <v>1017373.818783044</v>
       </c>
       <c r="I35" t="n">
-        <v>50395.21399899314</v>
+        <v>508686.9093915218</v>
       </c>
     </row>
     <row r="36">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>120520575.19</v>
+        <v>338026454.7</v>
       </c>
       <c r="E36" t="n">
         <v>0.9530263468310431</v>
@@ -1685,10 +1685,10 @@
         <v>0.001327621072548912</v>
       </c>
       <c r="H36" t="n">
-        <v>160005.6552979596</v>
+        <v>448771.0443387203</v>
       </c>
       <c r="I36" t="n">
-        <v>80002.82764897982</v>
+        <v>224385.5221693602</v>
       </c>
     </row>
     <row r="37">
@@ -1708,22 +1708,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>41495736.82999998</v>
+        <v>641813154.08</v>
       </c>
       <c r="E37" t="n">
-        <v>0.93726391898459</v>
+        <v>0.9356051227617213</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9336209204226615</v>
+        <v>0.9319685438064244</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.003642998561928512</v>
+        <v>-0.003636578955296899</v>
       </c>
       <c r="H37" t="n">
-        <v>-151168.9095978539</v>
+        <v>-2334004.209360054</v>
       </c>
       <c r="I37" t="n">
-        <v>-151168.9095978539</v>
+        <v>-2334004.209360054</v>
       </c>
     </row>
     <row r="38">
@@ -1743,22 +1743,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>34519707.57000002</v>
+        <v>514396150.85</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9132428090891569</v>
+        <v>0.9110361496874445</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9018065269889697</v>
+        <v>0.89962748577012</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.01143628210018721</v>
+        <v>-0.01140866391732454</v>
       </c>
       <c r="H38" t="n">
-        <v>-394777.1137864882</v>
+        <v>-5868572.805413024</v>
       </c>
       <c r="I38" t="n">
-        <v>-394777.1137864882</v>
+        <v>-5868572.805413024</v>
       </c>
     </row>
     <row r="39">
@@ -1778,22 +1778,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>874279275.16</v>
+        <v>1009792864.15</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8783257731734563</v>
+        <v>0.8754048758167313</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8555172260785272</v>
+        <v>0.8526721506842372</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.02280854709492908</v>
+        <v>-0.02273272513249414</v>
       </c>
       <c r="H39" t="n">
-        <v>-19941040.02160732</v>
+        <v>-22955343.62147594</v>
       </c>
       <c r="I39" t="n">
-        <v>-19941040.02160732</v>
+        <v>-22955343.62147594</v>
       </c>
     </row>
     <row r="40">
@@ -1813,22 +1813,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>857185142.1</v>
+        <v>794321595.54</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8337865285685646</v>
+        <v>0.8300899355387754</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7983591398693224</v>
+        <v>0.7948195996680136</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.03542738869924222</v>
+        <v>-0.03527033587076178</v>
       </c>
       <c r="H40" t="n">
-        <v>-30367831.21639188</v>
+        <v>-28015989.46409519</v>
       </c>
       <c r="I40" t="n">
-        <v>-30367831.21639188</v>
+        <v>-28015989.46409519</v>
       </c>
     </row>
     <row r="41">
@@ -1848,22 +1848,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>929236654.11</v>
+        <v>1623369977.36</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7914638140234228</v>
+        <v>0.7871638664957131</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7461646182699713</v>
+        <v>0.7421107790921055</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.04529919575345154</v>
+        <v>-0.04505308740360758</v>
       </c>
       <c r="H41" t="n">
-        <v>-42093673.09581123</v>
+        <v>-73137829.47839254</v>
       </c>
       <c r="I41" t="n">
-        <v>-42093673.09581123</v>
+        <v>-73137829.47839254</v>
       </c>
     </row>
     <row r="42">
@@ -1883,22 +1883,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>165783076.62</v>
+        <v>99536703.16000001</v>
       </c>
       <c r="E42" t="n">
-        <v>0.751260515961125</v>
+        <v>0.7465017756172543</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6980683865100574</v>
+        <v>0.6936465830305695</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.05319212945106755</v>
+        <v>-0.05285519258668481</v>
       </c>
       <c r="H42" t="n">
-        <v>-8818354.872367291</v>
+        <v>-5261031.614965479</v>
       </c>
       <c r="I42" t="n">
-        <v>-8818354.872367291</v>
+        <v>-5261031.614965479</v>
       </c>
     </row>
     <row r="43">
@@ -1918,22 +1918,22 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>347766801.69</v>
+        <v>318521371.88</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7130798016126879</v>
+        <v>0.7079831292590303</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6534049109648621</v>
+        <v>0.6487347495892629</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.05967489064782583</v>
+        <v>-0.05924837966976737</v>
       </c>
       <c r="H43" t="n">
-        <v>-20752945.86179488</v>
+        <v>-18871875.1740814</v>
       </c>
       <c r="I43" t="n">
-        <v>-20752945.86179488</v>
+        <v>-18871875.1740814</v>
       </c>
     </row>
     <row r="44">
@@ -1953,22 +1953,22 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>286514959.36</v>
+        <v>306908451.75</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6768263201051378</v>
+        <v>0.6714924005042728</v>
       </c>
       <c r="F44" t="n">
-        <v>0.6117444625408259</v>
+        <v>0.6069234306001043</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.06508185756431184</v>
+        <v>-0.06456896990416849</v>
       </c>
       <c r="H44" t="n">
-        <v>-18646925.77511211</v>
+        <v>-19816762.5843807</v>
       </c>
       <c r="I44" t="n">
-        <v>-18646925.77511211</v>
+        <v>-19816762.5843807</v>
       </c>
     </row>
     <row r="45">
@@ -1988,22 +1988,22 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>200982460.28</v>
+        <v>223541651.31</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6424083347829114</v>
+        <v>0.6369207605854804</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5727998443035995</v>
+        <v>0.5679068720802271</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.06960849047931184</v>
+        <v>-0.06901388850525336</v>
       </c>
       <c r="H45" t="n">
-        <v>-13990085.67290905</v>
+        <v>-15427478.59978857</v>
       </c>
       <c r="I45" t="n">
-        <v>-13990085.67290905</v>
+        <v>-15427478.59978857</v>
       </c>
     </row>
     <row r="46">
@@ -2023,22 +2023,22 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>8804292.67</v>
+        <v>14469721.94</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6097363477190296</v>
+        <v>0.6041641709026</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5363580128366308</v>
+        <v>0.5314564130474985</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.07337833488239887</v>
+        <v>-0.07270775785510153</v>
       </c>
       <c r="H46" t="n">
-        <v>-646044.3359419097</v>
+        <v>-1052061.03904417</v>
       </c>
       <c r="I46" t="n">
-        <v>-646044.3359419097</v>
+        <v>-1052061.03904417</v>
       </c>
     </row>
     <row r="47">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-837973082.6800001</v>
+        <v>-1657923918.46</v>
       </c>
       <c r="E47" t="n">
         <v>0.9975215395798449</v>
@@ -2070,10 +2070,10 @@
         <v>-0.001075593329743385</v>
       </c>
       <c r="H47" t="n">
-        <v>901318.2582351102</v>
+        <v>1783251.907917592</v>
       </c>
       <c r="I47" t="n">
-        <v>450659.1291175551</v>
+        <v>891625.953958796</v>
       </c>
     </row>
     <row r="48">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>19495500.62999999</v>
+        <v>-756411374.3</v>
       </c>
       <c r="E48" t="n">
         <v>0.9903615297882993</v>
@@ -2105,10 +2105,10 @@
         <v>-0.003609302003152015</v>
       </c>
       <c r="H48" t="n">
-        <v>-70365.14947631034</v>
+        <v>2730117.088467958</v>
       </c>
       <c r="I48" t="n">
-        <v>-70365.14947631034</v>
+        <v>1365058.544233979</v>
       </c>
     </row>
     <row r="49">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>110748422.65</v>
+        <v>-575289791.02</v>
       </c>
       <c r="E49" t="n">
         <v>0.9786688180301472</v>
@@ -2140,10 +2140,10 @@
         <v>-0.005714096573316341</v>
       </c>
       <c r="H49" t="n">
-        <v>-632827.1823645548</v>
+        <v>3287261.423531256</v>
       </c>
       <c r="I49" t="n">
-        <v>-632827.1823645548</v>
+        <v>1643630.711765628</v>
       </c>
     </row>
     <row r="50">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>28459734.17999999</v>
+        <v>287271212.35</v>
       </c>
       <c r="E50" t="n">
         <v>0.9655145554862491</v>
@@ -2175,10 +2175,10 @@
         <v>-0.005846989353867849</v>
       </c>
       <c r="H50" t="n">
-        <v>-166403.7627643689</v>
+        <v>-1679671.72028316</v>
       </c>
       <c r="I50" t="n">
-        <v>-166403.7627643689</v>
+        <v>-1679671.72028316</v>
       </c>
     </row>
     <row r="51">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>120520575.19</v>
+        <v>338026454.7</v>
       </c>
       <c r="E51" t="n">
         <v>0.9530263468310431</v>
@@ -2210,10 +2210,10 @@
         <v>-0.004239805017471676</v>
       </c>
       <c r="H51" t="n">
-        <v>-510983.7393991344</v>
+        <v>-1433166.258675222</v>
       </c>
       <c r="I51" t="n">
-        <v>-510983.7393991344</v>
+        <v>-1433166.258675222</v>
       </c>
     </row>
     <row r="52">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>41495736.82999998</v>
+        <v>641813154.08</v>
       </c>
       <c r="E52" t="n">
-        <v>0.93726391898459</v>
+        <v>0.9356051227617213</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9372702303708811</v>
+        <v>0.9356114068714596</v>
       </c>
       <c r="G52" t="n">
-        <v>6.311386291035781e-06</v>
+        <v>6.284109738352583e-06</v>
       </c>
       <c r="H52" t="n">
-        <v>261.8956245652905</v>
+        <v>4033.224291756916</v>
       </c>
       <c r="I52" t="n">
-        <v>130.9478122826452</v>
+        <v>2016.612145878458</v>
       </c>
     </row>
     <row r="53">
@@ -2268,22 +2268,22 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>34519707.57000002</v>
+        <v>514396150.85</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9132428090891569</v>
+        <v>0.9110361496874445</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9203490736599507</v>
+        <v>0.9181252264484042</v>
       </c>
       <c r="G53" t="n">
-        <v>0.007106264570793774</v>
+        <v>0.007089076760959712</v>
       </c>
       <c r="H53" t="n">
-        <v>245306.1748988528</v>
+        <v>3646593.798917861</v>
       </c>
       <c r="I53" t="n">
-        <v>122653.0874494264</v>
+        <v>1823296.899458931</v>
       </c>
     </row>
     <row r="54">
@@ -2303,22 +2303,22 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>874279275.16</v>
+        <v>1009792864.15</v>
       </c>
       <c r="E54" t="n">
-        <v>0.8783257731734563</v>
+        <v>0.8754048758167313</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8961312669792393</v>
+        <v>0.89315112566766</v>
       </c>
       <c r="G54" t="n">
-        <v>0.017805493805783</v>
+        <v>0.01774624985092865</v>
       </c>
       <c r="H54" t="n">
-        <v>15566974.21838583</v>
+        <v>17920036.46489076</v>
       </c>
       <c r="I54" t="n">
-        <v>7783487.109192916</v>
+        <v>8960018.232445378</v>
       </c>
     </row>
     <row r="55">
@@ -2338,22 +2338,22 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>857185142.1</v>
+        <v>794321595.54</v>
       </c>
       <c r="E55" t="n">
-        <v>0.8337865285685646</v>
+        <v>0.8300899355387754</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8636808908085251</v>
+        <v>0.8598517504102717</v>
       </c>
       <c r="G55" t="n">
-        <v>0.02989436223996045</v>
+        <v>0.02976181487149632</v>
       </c>
       <c r="H55" t="n">
-        <v>25625003.14464937</v>
+        <v>23640452.27489305</v>
       </c>
       <c r="I55" t="n">
-        <v>12812501.57232469</v>
+        <v>11820226.13744653</v>
       </c>
     </row>
     <row r="56">
@@ -2373,22 +2373,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>929236654.11</v>
+        <v>1623369977.36</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7914638140234228</v>
+        <v>0.7871638664957131</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8309310899662787</v>
+        <v>0.8264167206253257</v>
       </c>
       <c r="G56" t="n">
-        <v>0.03946727594285593</v>
+        <v>0.03925285412961255</v>
       </c>
       <c r="H56" t="n">
-        <v>36674439.44397554</v>
+        <v>63721904.9197045</v>
       </c>
       <c r="I56" t="n">
-        <v>18337219.72198777</v>
+        <v>31860952.45985225</v>
       </c>
     </row>
     <row r="57">
@@ -2408,22 +2408,22 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>165783076.62</v>
+        <v>99536703.16000001</v>
       </c>
       <c r="E57" t="n">
-        <v>0.751260515961125</v>
+        <v>0.7465017756172543</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7985079617097887</v>
+        <v>0.793449937984499</v>
       </c>
       <c r="G57" t="n">
-        <v>0.04724744574866369</v>
+        <v>0.04694816236724475</v>
       </c>
       <c r="H57" t="n">
-        <v>7832826.918650005</v>
+        <v>4673065.301455924</v>
       </c>
       <c r="I57" t="n">
-        <v>3916413.459325003</v>
+        <v>2336532.650727962</v>
       </c>
     </row>
     <row r="58">
@@ -2443,22 +2443,22 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>347766801.69</v>
+        <v>318521371.88</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7130798016126879</v>
+        <v>0.7079831292590303</v>
       </c>
       <c r="F58" t="n">
-        <v>0.766882878767156</v>
+        <v>0.7614016420153711</v>
       </c>
       <c r="G58" t="n">
-        <v>0.05380307715446808</v>
+        <v>0.0534185127563408</v>
       </c>
       <c r="H58" t="n">
-        <v>18710924.06308967</v>
+        <v>17014937.96693895</v>
       </c>
       <c r="I58" t="n">
-        <v>9355462.031544836</v>
+        <v>8507468.983469475</v>
       </c>
     </row>
     <row r="59">
@@ -2478,22 +2478,22 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>286514959.36</v>
+        <v>306908451.75</v>
       </c>
       <c r="E59" t="n">
-        <v>0.6768263201051378</v>
+        <v>0.6714924005042728</v>
       </c>
       <c r="F59" t="n">
-        <v>0.7362917336347434</v>
+        <v>0.7304891729838603</v>
       </c>
       <c r="G59" t="n">
-        <v>0.05946541352960566</v>
+        <v>0.05899677247958746</v>
       </c>
       <c r="H59" t="n">
-        <v>17037730.54076056</v>
+        <v>18106608.09995719</v>
       </c>
       <c r="I59" t="n">
-        <v>8518865.270380281</v>
+        <v>9053304.049978597</v>
       </c>
     </row>
     <row r="60">
@@ -2513,22 +2513,22 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>200982460.28</v>
+        <v>223541651.31</v>
       </c>
       <c r="E60" t="n">
-        <v>0.6424083347829114</v>
+        <v>0.6369207605854804</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7068233232621161</v>
+        <v>0.7007854946334655</v>
       </c>
       <c r="G60" t="n">
-        <v>0.06441498847920468</v>
+        <v>0.06386473404798509</v>
       </c>
       <c r="H60" t="n">
-        <v>12946282.86345841</v>
+        <v>14276428.10956057</v>
       </c>
       <c r="I60" t="n">
-        <v>6473141.431729207</v>
+        <v>7138214.054780285</v>
       </c>
     </row>
     <row r="61">
@@ -2548,22 +2548,22 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>8804292.67</v>
+        <v>14469721.94</v>
       </c>
       <c r="E61" t="n">
-        <v>0.6097363477190296</v>
+        <v>0.6041641709026</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6784923310968078</v>
+        <v>0.6722918087178391</v>
       </c>
       <c r="G61" t="n">
-        <v>0.06875598337777822</v>
+        <v>0.06812763781523912</v>
       </c>
       <c r="H61" t="n">
-        <v>605347.8004716146</v>
+        <v>985787.9756155391</v>
       </c>
       <c r="I61" t="n">
-        <v>302673.9002358073</v>
+        <v>492893.9878077696</v>
       </c>
     </row>
     <row r="62">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-837973082.6800001</v>
+        <v>-1657923918.46</v>
       </c>
       <c r="E62" t="n">
         <v>0.9975215395798449</v>
@@ -2595,10 +2595,10 @@
         <v>-0.00138963539714354</v>
       </c>
       <c r="H62" t="n">
-        <v>1164477.057545619</v>
+        <v>2303909.762862937</v>
       </c>
       <c r="I62" t="n">
-        <v>582238.5287728094</v>
+        <v>1151954.881431469</v>
       </c>
     </row>
     <row r="63">
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>19495500.62999999</v>
+        <v>-756411374.3</v>
       </c>
       <c r="E63" t="n">
         <v>0.9903615297882993</v>
@@ -2630,10 +2630,10 @@
         <v>-0.004868292240044036</v>
       </c>
       <c r="H63" t="n">
-        <v>-94909.79443280258</v>
+        <v>3682431.623785735</v>
       </c>
       <c r="I63" t="n">
-        <v>-94909.79443280258</v>
+        <v>1841215.811892868</v>
       </c>
     </row>
     <row r="64">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>110748422.65</v>
+        <v>-575289791.02</v>
       </c>
       <c r="E64" t="n">
         <v>0.9786688180301472</v>
@@ -2665,10 +2665,10 @@
         <v>-0.008752967619160001</v>
       </c>
       <c r="H64" t="n">
-        <v>-969377.3573284962</v>
+        <v>5035492.912431384</v>
       </c>
       <c r="I64" t="n">
-        <v>-969377.3573284962</v>
+        <v>2517746.456215692</v>
       </c>
     </row>
     <row r="65">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>28459734.17999999</v>
+        <v>287271212.35</v>
       </c>
       <c r="E65" t="n">
         <v>0.9655145554862491</v>
@@ -2700,10 +2700,10 @@
         <v>-0.01121800353180191</v>
       </c>
       <c r="H65" t="n">
-        <v>-319261.3985453835</v>
+        <v>-3222609.474727317</v>
       </c>
       <c r="I65" t="n">
-        <v>-319261.3985453835</v>
+        <v>-3222609.474727317</v>
       </c>
     </row>
     <row r="66">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>120520575.19</v>
+        <v>338026454.7</v>
       </c>
       <c r="E66" t="n">
         <v>0.9530263468310431</v>
@@ -2735,10 +2735,10 @@
         <v>-0.0120777624290116</v>
       </c>
       <c r="H66" t="n">
-        <v>-1455618.874952649</v>
+        <v>-4082603.21458765</v>
       </c>
       <c r="I66" t="n">
-        <v>-1455618.874952649</v>
+        <v>-4082603.21458765</v>
       </c>
     </row>
     <row r="67">
@@ -2758,22 +2758,22 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>41495736.82999998</v>
+        <v>641813154.08</v>
       </c>
       <c r="E67" t="n">
-        <v>0.93726391898459</v>
+        <v>0.9356051227617213</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9255897136521459</v>
+        <v>0.9239515538524983</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.01167420533244412</v>
+        <v>-0.01165356890922298</v>
       </c>
       <c r="H67" t="n">
-        <v>-484429.7521744837</v>
+        <v>-7479413.817917025</v>
       </c>
       <c r="I67" t="n">
-        <v>-484429.7521744837</v>
+        <v>-7479413.817917025</v>
       </c>
     </row>
     <row r="68">
@@ -2793,22 +2793,22 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>34519707.57000002</v>
+        <v>514396150.85</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9132428090891569</v>
+        <v>0.9110361496874445</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9035739413886649</v>
+        <v>0.9013906216994021</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.009668867700492023</v>
+        <v>-0.009645527988042413</v>
       </c>
       <c r="H68" t="n">
-        <v>-333766.4855540032</v>
+        <v>-4961622.469964962</v>
       </c>
       <c r="I68" t="n">
-        <v>-333766.4855540032</v>
+        <v>-4961622.469964962</v>
       </c>
     </row>
     <row r="69">
@@ -2828,22 +2828,22 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>874279275.16</v>
+        <v>1009792864.15</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8783257731734563</v>
+        <v>0.8754048758167313</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8720389628503553</v>
+        <v>0.8691389452542764</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.006286810323100966</v>
+        <v>-0.006265930562454947</v>
       </c>
       <c r="H69" t="n">
-        <v>-5496427.972349118</v>
+        <v>-6327291.969226401</v>
       </c>
       <c r="I69" t="n">
-        <v>-5496427.972349118</v>
+        <v>-6327291.969226401</v>
       </c>
     </row>
     <row r="70">
@@ -2863,22 +2863,22 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>857185142.1</v>
+        <v>794321595.54</v>
       </c>
       <c r="E70" t="n">
-        <v>0.8337865285685646</v>
+        <v>0.8300899355387754</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8307073618477882</v>
+        <v>0.827024401236104</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.003079166720776461</v>
+        <v>-0.003065534302671424</v>
       </c>
       <c r="H70" t="n">
-        <v>-2639415.963098362</v>
+        <v>-2435020.098480567</v>
       </c>
       <c r="I70" t="n">
-        <v>-2639415.963098362</v>
+        <v>-2435020.098480567</v>
       </c>
     </row>
     <row r="71">
@@ -2898,22 +2898,22 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>929236654.11</v>
+        <v>1623369977.36</v>
       </c>
       <c r="E71" t="n">
-        <v>0.7914638140234228</v>
+        <v>0.7871638664957131</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7900801060240177</v>
+        <v>0.7857876654511835</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.001383707999405126</v>
+        <v>-0.001376201044529624</v>
       </c>
       <c r="H71" t="n">
-        <v>-1285792.191632461</v>
+        <v>-2234083.458500863</v>
       </c>
       <c r="I71" t="n">
-        <v>-1285792.191632461</v>
+        <v>-2234083.458500863</v>
       </c>
     </row>
     <row r="72">
@@ -2933,22 +2933,22 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>165783076.62</v>
+        <v>99536703.16000001</v>
       </c>
       <c r="E72" t="n">
-        <v>0.751260515961125</v>
+        <v>0.7465017756172543</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7506694989807172</v>
+        <v>0.7459144932458476</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.0005910169804077547</v>
+        <v>-0.0005872823714067055</v>
       </c>
       <c r="H72" t="n">
-        <v>-97980.61334665984</v>
+        <v>-58456.15107381012</v>
       </c>
       <c r="I72" t="n">
-        <v>-97980.61334665984</v>
+        <v>-58456.15107381012</v>
       </c>
     </row>
     <row r="73">
@@ -2968,22 +2968,22 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>347766801.69</v>
+        <v>318521371.88</v>
       </c>
       <c r="E73" t="n">
-        <v>0.7130798016126879</v>
+        <v>0.7079831292590303</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7128354683771767</v>
+        <v>0.7077405266571837</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.0002443332355112071</v>
+        <v>-0.0002426026018466088</v>
       </c>
       <c r="H73" t="n">
-        <v>-84970.98786030203</v>
+        <v>-77274.11356183924</v>
       </c>
       <c r="I73" t="n">
-        <v>-84970.98786030203</v>
+        <v>-77274.11356183924</v>
       </c>
     </row>
     <row r="74">
@@ -3003,22 +3003,22 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>286514959.36</v>
+        <v>306908451.75</v>
       </c>
       <c r="E74" t="n">
-        <v>0.6768263201051378</v>
+        <v>0.6714924005042728</v>
       </c>
       <c r="F74" t="n">
-        <v>0.676727750575811</v>
+        <v>0.6713945995447047</v>
       </c>
       <c r="G74" t="n">
-        <v>-9.85695293267419e-05</v>
+        <v>-9.78009595681284e-05</v>
       </c>
       <c r="H74" t="n">
-        <v>-28241.64468918578</v>
+        <v>-30015.94108071864</v>
       </c>
       <c r="I74" t="n">
-        <v>-28241.64468918578</v>
+        <v>-30015.94108071864</v>
       </c>
     </row>
     <row r="75">
@@ -3038,22 +3038,22 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>200982460.28</v>
+        <v>223541651.31</v>
       </c>
       <c r="E75" t="n">
-        <v>0.6424083347829114</v>
+        <v>0.6369207605854804</v>
       </c>
       <c r="F75" t="n">
-        <v>0.642369122932283</v>
+        <v>0.6368818785963716</v>
       </c>
       <c r="G75" t="n">
-        <v>-3.92118506283845e-05</v>
+        <v>-3.8881989108841e-05</v>
       </c>
       <c r="H75" t="n">
-        <v>-7880.894211424582</v>
+        <v>-8691.744051607751</v>
       </c>
       <c r="I75" t="n">
-        <v>-7880.894211424582</v>
+        <v>-8691.744051607751</v>
       </c>
     </row>
     <row r="76">
@@ -3073,22 +3073,22 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>8804292.67</v>
+        <v>14469721.94</v>
       </c>
       <c r="E76" t="n">
-        <v>0.6097363477190296</v>
+        <v>0.6041641709026</v>
       </c>
       <c r="F76" t="n">
-        <v>0.6097208321734507</v>
+        <v>0.6041487887577485</v>
       </c>
       <c r="G76" t="n">
-        <v>-1.551554557888135e-05</v>
+        <v>-1.538214485152789e-05</v>
       </c>
       <c r="H76" t="n">
-        <v>-136.603404211196</v>
+        <v>-222.5753588424111</v>
       </c>
       <c r="I76" t="n">
-        <v>-136.603404211196</v>
+        <v>-222.5753588424111</v>
       </c>
     </row>
     <row r="77">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-837973082.6800001</v>
+        <v>-1657923918.46</v>
       </c>
       <c r="E77" t="n">
         <v>0.9975215395798449</v>
@@ -3120,10 +3120,10 @@
         <v>0.001386210407362531</v>
       </c>
       <c r="H77" t="n">
-        <v>-1161607.008300679</v>
+        <v>-2298231.390384521</v>
       </c>
       <c r="I77" t="n">
-        <v>-1161607.008300679</v>
+        <v>-2298231.390384521</v>
       </c>
     </row>
     <row r="78">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>19495500.62999999</v>
+        <v>-756411374.3</v>
       </c>
       <c r="E78" t="n">
         <v>0.9903615297882993</v>
@@ -3155,10 +3155,10 @@
         <v>0.004890978187868655</v>
       </c>
       <c r="H78" t="n">
-        <v>95352.06834290958</v>
+        <v>-3699591.532757053</v>
       </c>
       <c r="I78" t="n">
-        <v>47676.03417145479</v>
+        <v>-3699591.532757053</v>
       </c>
     </row>
     <row r="79">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>110748422.65</v>
+        <v>-575289791.02</v>
       </c>
       <c r="E79" t="n">
         <v>0.9786688180301472</v>
@@ -3190,10 +3190,10 @@
         <v>0.008825570306637109</v>
       </c>
       <c r="H79" t="n">
-        <v>977417.9904467367</v>
+        <v>-5077260.49733758</v>
       </c>
       <c r="I79" t="n">
-        <v>488708.9952233683</v>
+        <v>-5077260.49733758</v>
       </c>
     </row>
     <row r="80">
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>28459734.17999999</v>
+        <v>287271212.35</v>
       </c>
       <c r="E80" t="n">
         <v>0.9655145554862491</v>
@@ -3225,10 +3225,10 @@
         <v>0.01134479629056684</v>
       </c>
       <c r="H80" t="n">
-        <v>322869.8867557822</v>
+        <v>3259033.384254919</v>
       </c>
       <c r="I80" t="n">
-        <v>161434.9433778911</v>
+        <v>1629516.692127459</v>
       </c>
     </row>
     <row r="81">
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>120520575.19</v>
+        <v>338026454.7</v>
       </c>
       <c r="E81" t="n">
         <v>0.9530263468310431</v>
@@ -3260,10 +3260,10 @@
         <v>0.0122280753910069</v>
       </c>
       <c r="H81" t="n">
-        <v>1473734.679590835</v>
+        <v>4133412.972226378</v>
       </c>
       <c r="I81" t="n">
-        <v>736867.3397954177</v>
+        <v>2066706.486113189</v>
       </c>
     </row>
     <row r="82">
@@ -3283,22 +3283,22 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>41495736.82999998</v>
+        <v>641813154.08</v>
       </c>
       <c r="E82" t="n">
-        <v>0.93726391898459</v>
+        <v>0.9356051227617213</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9490845285066654</v>
+        <v>0.9474047848338234</v>
       </c>
       <c r="G82" t="n">
-        <v>0.01182060952207531</v>
+        <v>0.01179966207210215</v>
       </c>
       <c r="H82" t="n">
-        <v>490504.9018982289</v>
+        <v>7573178.331574027</v>
       </c>
       <c r="I82" t="n">
-        <v>245252.4509491145</v>
+        <v>3786589.165787014</v>
       </c>
     </row>
     <row r="83">
@@ -3318,22 +3318,22 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>34519707.57000002</v>
+        <v>514396150.85</v>
       </c>
       <c r="E83" t="n">
-        <v>0.9132428090891569</v>
+        <v>0.9110361496874445</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9230144382935129</v>
+        <v>0.9207841534302572</v>
       </c>
       <c r="G83" t="n">
-        <v>0.009771629204356036</v>
+        <v>0.009748003742812705</v>
       </c>
       <c r="H83" t="n">
-        <v>337313.7826168423</v>
+        <v>5014335.60377425</v>
       </c>
       <c r="I83" t="n">
-        <v>168656.8913084212</v>
+        <v>2507167.801887125</v>
       </c>
     </row>
     <row r="84">
@@ -3353,22 +3353,22 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>874279275.16</v>
+        <v>1009792864.15</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8783257731734563</v>
+        <v>0.8754048758167313</v>
       </c>
       <c r="F84" t="n">
-        <v>0.8846567405439828</v>
+        <v>0.8817147543300172</v>
       </c>
       <c r="G84" t="n">
-        <v>0.006330967370526519</v>
+        <v>0.006309878513285905</v>
       </c>
       <c r="H84" t="n">
-        <v>5535033.563765536</v>
+        <v>6371670.296369517</v>
       </c>
       <c r="I84" t="n">
-        <v>2767516.781882768</v>
+        <v>3185835.148184759</v>
       </c>
     </row>
     <row r="85">
@@ -3388,22 +3388,22 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>857185142.1</v>
+        <v>794321595.54</v>
       </c>
       <c r="E85" t="n">
-        <v>0.8337865285685646</v>
+        <v>0.8300899355387754</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8368764237722052</v>
+        <v>0.8331661161197905</v>
       </c>
       <c r="G85" t="n">
-        <v>0.003089895203640558</v>
+        <v>0.003076180581015109</v>
       </c>
       <c r="H85" t="n">
-        <v>2648612.25920674</v>
+        <v>2443476.667281085</v>
       </c>
       <c r="I85" t="n">
-        <v>1324306.12960337</v>
+        <v>1221738.333640543</v>
       </c>
     </row>
     <row r="86">
@@ -3423,22 +3423,22 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>929236654.11</v>
+        <v>1623369977.36</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7914638140234228</v>
+        <v>0.7871638664957131</v>
       </c>
       <c r="F86" t="n">
-        <v>0.7928497625860698</v>
+        <v>0.7885422913538858</v>
       </c>
       <c r="G86" t="n">
-        <v>0.001385948562646955</v>
+        <v>0.001378424858172633</v>
       </c>
       <c r="H86" t="n">
-        <v>1287874.20512262</v>
+        <v>2237693.530804169</v>
       </c>
       <c r="I86" t="n">
-        <v>643937.1025613101</v>
+        <v>1118846.765402084</v>
       </c>
     </row>
     <row r="87">
@@ -3458,22 +3458,22 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>165783076.62</v>
+        <v>99536703.16000001</v>
       </c>
       <c r="E87" t="n">
-        <v>0.751260515961125</v>
+        <v>0.7465017756172543</v>
       </c>
       <c r="F87" t="n">
-        <v>0.7518516126765387</v>
+        <v>0.7470891193811869</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0005910967154136859</v>
+        <v>0.0005873437639326573</v>
       </c>
       <c r="H87" t="n">
-        <v>97993.83206125743</v>
+        <v>58462.26188344203</v>
       </c>
       <c r="I87" t="n">
-        <v>48996.91603062872</v>
+        <v>29231.13094172101</v>
       </c>
     </row>
     <row r="88">
@@ -3493,22 +3493,22 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>347766801.69</v>
+        <v>318521371.88</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7130798016126879</v>
+        <v>0.7079831292590303</v>
       </c>
       <c r="F88" t="n">
-        <v>0.7133233293846294</v>
+        <v>0.7082249026637973</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0002435277719414763</v>
+        <v>0.0002417734047670539</v>
       </c>
       <c r="H88" t="n">
-        <v>84690.87437077895</v>
+        <v>77009.99657050053</v>
       </c>
       <c r="I88" t="n">
-        <v>42345.43718538948</v>
+        <v>38504.99828525027</v>
       </c>
     </row>
     <row r="89">
@@ -3528,22 +3528,22 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>286514959.36</v>
+        <v>306908451.75</v>
       </c>
       <c r="E89" t="n">
-        <v>0.6768263201051378</v>
+        <v>0.6714924005042728</v>
       </c>
       <c r="F89" t="n">
-        <v>0.6769243027127022</v>
+        <v>0.6715896062479044</v>
       </c>
       <c r="G89" t="n">
-        <v>9.798260756443966e-05</v>
+        <v>9.720574363158985e-05</v>
       </c>
       <c r="H89" t="n">
-        <v>28073.48282431226</v>
+        <v>29833.26427917866</v>
       </c>
       <c r="I89" t="n">
-        <v>14036.74141215613</v>
+        <v>14916.63213958933</v>
       </c>
     </row>
     <row r="90">
@@ -3563,22 +3563,22 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>200982460.28</v>
+        <v>223541651.31</v>
       </c>
       <c r="E90" t="n">
-        <v>0.6424083347829114</v>
+        <v>0.6369207605854804</v>
       </c>
       <c r="F90" t="n">
-        <v>0.6424469098247421</v>
+        <v>0.6369589980232822</v>
       </c>
       <c r="G90" t="n">
-        <v>3.857504183069072e-05</v>
+        <v>3.823743780173583e-05</v>
       </c>
       <c r="H90" t="n">
-        <v>7752.906812536135</v>
+        <v>8547.659988063444</v>
       </c>
       <c r="I90" t="n">
-        <v>3876.453406268068</v>
+        <v>4273.829994031722</v>
       </c>
     </row>
     <row r="91">
@@ -3598,22 +3598,22 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>8804292.67</v>
+        <v>14469721.94</v>
       </c>
       <c r="E91" t="n">
-        <v>0.6097363477190296</v>
+        <v>0.6041641709026</v>
       </c>
       <c r="F91" t="n">
-        <v>0.6097511888543204</v>
+        <v>0.6041788672544907</v>
       </c>
       <c r="G91" t="n">
-        <v>1.484113529082176e-05</v>
+        <v>1.469635189066398e-05</v>
       </c>
       <c r="H91" t="n">
-        <v>130.6656986554603</v>
+        <v>212.6521253903011</v>
       </c>
       <c r="I91" t="n">
-        <v>65.33284932773017</v>
+        <v>106.3260626951506</v>
       </c>
     </row>
     <row r="92">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-837973082.6800001</v>
+        <v>-1657923918.46</v>
       </c>
       <c r="E92" t="n">
         <v>0.9975215395798449</v>
@@ -3645,10 +3645,10 @@
         <v>0.0004267113511314813</v>
       </c>
       <c r="H92" t="n">
-        <v>-357572.6263221953</v>
+        <v>-707454.9553192664</v>
       </c>
       <c r="I92" t="n">
-        <v>-357572.6263221953</v>
+        <v>-707454.9553192664</v>
       </c>
     </row>
     <row r="93">
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>19495500.62999999</v>
+        <v>-756411374.3</v>
       </c>
       <c r="E93" t="n">
         <v>0.9903615297882993</v>
@@ -3680,10 +3680,10 @@
         <v>0.001651293781163021</v>
       </c>
       <c r="H93" t="n">
-        <v>32192.79895097875</v>
+        <v>-1249057.398382564</v>
       </c>
       <c r="I93" t="n">
-        <v>16096.39947548938</v>
+        <v>-1249057.398382564</v>
       </c>
     </row>
     <row r="94">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>110748422.65</v>
+        <v>-575289791.02</v>
       </c>
       <c r="E94" t="n">
         <v>0.9786688180301472</v>
@@ -3715,10 +3715,10 @@
         <v>0.003673721028352284</v>
       </c>
       <c r="H94" t="n">
-        <v>406858.8091461514</v>
+        <v>-2113454.202666565</v>
       </c>
       <c r="I94" t="n">
-        <v>203429.4045730757</v>
+        <v>-2113454.202666565</v>
       </c>
     </row>
     <row r="95">
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>28459734.17999999</v>
+        <v>287271212.35</v>
       </c>
       <c r="E95" t="n">
         <v>0.9655145554862491</v>
@@ -3750,10 +3750,10 @@
         <v>0.006050833538578271</v>
       </c>
       <c r="H95" t="n">
-        <v>172205.1140753663</v>
+        <v>1738230.28635542</v>
       </c>
       <c r="I95" t="n">
-        <v>86102.55703768316</v>
+        <v>869115.1431777102</v>
       </c>
     </row>
     <row r="96">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>120520575.19</v>
+        <v>338026454.7</v>
       </c>
       <c r="E96" t="n">
         <v>0.9530263468310431</v>
@@ -3785,10 +3785,10 @@
         <v>0.008373224807978752</v>
       </c>
       <c r="H96" t="n">
-        <v>1009145.870052776</v>
+        <v>2830371.496247146</v>
       </c>
       <c r="I96" t="n">
-        <v>504572.9350263882</v>
+        <v>1415185.748123573</v>
       </c>
     </row>
     <row r="97">
@@ -3808,22 +3808,22 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>41495736.82999998</v>
+        <v>641813154.08</v>
       </c>
       <c r="E97" t="n">
-        <v>0.93726391898459</v>
+        <v>0.9356051227617213</v>
       </c>
       <c r="F97" t="n">
-        <v>0.9490528208351157</v>
+        <v>0.9473731452282037</v>
       </c>
       <c r="G97" t="n">
-        <v>0.01178890185052561</v>
+        <v>0.01176802246648245</v>
       </c>
       <c r="H97" t="n">
-        <v>489189.1687041106</v>
+        <v>7552871.616497405</v>
       </c>
       <c r="I97" t="n">
-        <v>244594.5843520553</v>
+        <v>3776435.808248702</v>
       </c>
     </row>
     <row r="98">
@@ -3843,22 +3843,22 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>34519707.57000002</v>
+        <v>514396150.85</v>
       </c>
       <c r="E98" t="n">
-        <v>0.9132428090891569</v>
+        <v>0.9110361496874445</v>
       </c>
       <c r="F98" t="n">
-        <v>0.9293648610540347</v>
+        <v>0.9271192361753671</v>
       </c>
       <c r="G98" t="n">
-        <v>0.01612205196487781</v>
+        <v>0.01608308648792256</v>
       </c>
       <c r="H98" t="n">
-        <v>556528.5192559264</v>
+        <v>8273077.78317501</v>
       </c>
       <c r="I98" t="n">
-        <v>278264.2596279632</v>
+        <v>4136538.891587505</v>
       </c>
     </row>
     <row r="99">
@@ -3878,22 +3878,22 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>874279275.16</v>
+        <v>1009792864.15</v>
       </c>
       <c r="E99" t="n">
-        <v>0.8783257731734563</v>
+        <v>0.8754048758167313</v>
       </c>
       <c r="F99" t="n">
-        <v>0.9005600940055343</v>
+        <v>0.8975652297165327</v>
       </c>
       <c r="G99" t="n">
-        <v>0.02223432083207799</v>
+        <v>0.02216035389980142</v>
       </c>
       <c r="H99" t="n">
-        <v>19439005.90074403</v>
+        <v>22377367.2350581</v>
       </c>
       <c r="I99" t="n">
-        <v>9719502.950372016</v>
+        <v>11188683.61752905</v>
       </c>
     </row>
     <row r="100">
@@ -3913,22 +3913,22 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>857185142.1</v>
+        <v>794321595.54</v>
       </c>
       <c r="E100" t="n">
-        <v>0.8337865285685646</v>
+        <v>0.8300899355387754</v>
       </c>
       <c r="F100" t="n">
-        <v>0.863485402981736</v>
+        <v>0.8596571328525812</v>
       </c>
       <c r="G100" t="n">
-        <v>0.02969887441317143</v>
+        <v>0.02956719731380575</v>
       </c>
       <c r="H100" t="n">
-        <v>25457433.88406441</v>
+        <v>23485863.34594818</v>
       </c>
       <c r="I100" t="n">
-        <v>12728716.9420322</v>
+        <v>11742931.67297409</v>
       </c>
     </row>
     <row r="101">
@@ -3948,22 +3948,22 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>929236654.11</v>
+        <v>1623369977.36</v>
       </c>
       <c r="E101" t="n">
-        <v>0.7914638140234228</v>
+        <v>0.7871638664957131</v>
       </c>
       <c r="F101" t="n">
-        <v>0.8278931061235369</v>
+        <v>0.8233952316458175</v>
       </c>
       <c r="G101" t="n">
-        <v>0.03642929210011414</v>
+        <v>0.03623136515010439</v>
       </c>
       <c r="H101" t="n">
-        <v>33851433.50270592</v>
+        <v>58816910.42344685</v>
       </c>
       <c r="I101" t="n">
-        <v>16925716.75135296</v>
+        <v>29408455.21172342</v>
       </c>
     </row>
     <row r="102">
@@ -3983,22 +3983,22 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>165783076.62</v>
+        <v>99536703.16000001</v>
       </c>
       <c r="E102" t="n">
-        <v>0.751260515961125</v>
+        <v>0.7465017756172543</v>
       </c>
       <c r="F102" t="n">
-        <v>0.7937370416694218</v>
+        <v>0.7887092384228424</v>
       </c>
       <c r="G102" t="n">
-        <v>0.04247652570829685</v>
+        <v>0.04220746280558807</v>
       </c>
       <c r="H102" t="n">
-        <v>7041889.116049977</v>
+        <v>4201191.696416561</v>
       </c>
       <c r="I102" t="n">
-        <v>3520944.558024989</v>
+        <v>2100595.84820828</v>
       </c>
     </row>
     <row r="103">
@@ -4018,22 +4018,22 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>347766801.69</v>
+        <v>318521371.88</v>
       </c>
       <c r="E103" t="n">
-        <v>0.7130798016126879</v>
+        <v>0.7079831292590303</v>
       </c>
       <c r="F103" t="n">
-        <v>0.7609690657464063</v>
+        <v>0.7555300952994544</v>
       </c>
       <c r="G103" t="n">
-        <v>0.04788926413371841</v>
+        <v>0.04754696604042408</v>
       </c>
       <c r="H103" t="n">
-        <v>16654296.22307088</v>
+        <v>15144724.85192765</v>
       </c>
       <c r="I103" t="n">
-        <v>8327148.11153544</v>
+        <v>7572362.425963824</v>
       </c>
     </row>
     <row r="104">
@@ -4053,22 +4053,22 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>286514959.36</v>
+        <v>306908451.75</v>
       </c>
       <c r="E104" t="n">
-        <v>0.6768263201051378</v>
+        <v>0.6714924005042728</v>
       </c>
       <c r="F104" t="n">
-        <v>0.7295400427060942</v>
+        <v>0.7237906915672608</v>
       </c>
       <c r="G104" t="n">
-        <v>0.05271372260095641</v>
+        <v>0.052298291062988</v>
       </c>
       <c r="H104" t="n">
-        <v>15103270.08872734</v>
+        <v>16050787.53931251</v>
       </c>
       <c r="I104" t="n">
-        <v>7551635.044363671</v>
+        <v>8025393.769656255</v>
       </c>
     </row>
     <row r="105">
@@ -4088,22 +4088,22 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>200982460.28</v>
+        <v>223541651.31</v>
       </c>
       <c r="E105" t="n">
-        <v>0.6424083347829114</v>
+        <v>0.6369207605854804</v>
       </c>
       <c r="F105" t="n">
-        <v>0.6994005629016571</v>
+        <v>0.6934261484137834</v>
       </c>
       <c r="G105" t="n">
-        <v>0.05699222811874571</v>
+        <v>0.05650538782830294</v>
       </c>
       <c r="H105" t="n">
-        <v>11454438.22414451</v>
+        <v>12631307.70305081</v>
       </c>
       <c r="I105" t="n">
-        <v>5727219.112072255</v>
+        <v>6315653.851525407</v>
       </c>
     </row>
     <row r="106">
@@ -4123,22 +4123,22 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>8804292.67</v>
+        <v>14469721.94</v>
       </c>
       <c r="E106" t="n">
-        <v>0.6097363477190296</v>
+        <v>0.6041641709026</v>
       </c>
       <c r="F106" t="n">
-        <v>0.6705016035786937</v>
+        <v>0.664374099575429</v>
       </c>
       <c r="G106" t="n">
-        <v>0.06076525585966408</v>
+        <v>0.06020992867282904</v>
       </c>
       <c r="H106" t="n">
-        <v>534995.096755915</v>
+        <v>871220.9259230694</v>
       </c>
       <c r="I106" t="n">
-        <v>267497.5483779575</v>
+        <v>435610.4629615347</v>
       </c>
     </row>
   </sheetData>
@@ -4214,22 +4214,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="D2" t="n">
-        <v>2289576861.54</v>
+        <v>2088879685.01</v>
       </c>
       <c r="E2" t="n">
-        <v>-134741169.5100002</v>
+        <v>-85376944.77999997</v>
       </c>
       <c r="F2" t="n">
-        <v>-134741169.5100002</v>
+        <v>-85376944.77999997</v>
       </c>
       <c r="G2" t="n">
-        <v>-8.421323094375015</v>
+        <v>-7.11474539833333</v>
       </c>
       <c r="H2" t="n">
-        <v>-8.421323094375015</v>
+        <v>-7.11474539833333</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -4247,22 +4247,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="D3" t="n">
-        <v>2570934764.39</v>
+        <v>2267212933.25</v>
       </c>
       <c r="E3" t="n">
-        <v>146616733.3399997</v>
+        <v>92956303.46000004</v>
       </c>
       <c r="F3" t="n">
-        <v>73308366.66999984</v>
+        <v>46478151.73000002</v>
       </c>
       <c r="G3" t="n">
-        <v>9.16354583374998</v>
+        <v>7.74635862166667</v>
       </c>
       <c r="H3" t="n">
-        <v>4.58177291687499</v>
+        <v>3.873179310833335</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -4280,22 +4280,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="D4" t="n">
-        <v>2378544175.29</v>
+        <v>2158367069.35</v>
       </c>
       <c r="E4" t="n">
-        <v>-45773855.76000023</v>
+        <v>-15889560.44000006</v>
       </c>
       <c r="F4" t="n">
-        <v>-45773855.76000023</v>
+        <v>-15889560.44000006</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.860865985000014</v>
+        <v>-1.324130036666671</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.860865985000014</v>
+        <v>-1.324130036666671</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -4313,22 +4313,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="D5" t="n">
-        <v>2458096736.1</v>
+        <v>2181936002.53</v>
       </c>
       <c r="E5" t="n">
-        <v>33778705.04999971</v>
+        <v>7679372.740000248</v>
       </c>
       <c r="F5" t="n">
-        <v>16889352.52499986</v>
+        <v>3839686.370000124</v>
       </c>
       <c r="G5" t="n">
-        <v>2.111169065624982</v>
+        <v>0.639947728333354</v>
       </c>
       <c r="H5" t="n">
-        <v>1.055584532812491</v>
+        <v>0.319973864166677</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -4346,22 +4346,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="D6" t="n">
-        <v>2397400495.19</v>
+        <v>2145100116.98</v>
       </c>
       <c r="E6" t="n">
-        <v>-26917535.86000013</v>
+        <v>-29156512.80999994</v>
       </c>
       <c r="F6" t="n">
-        <v>-26917535.86000013</v>
+        <v>-29156512.80999994</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.682345991250008</v>
+        <v>-2.429709400833329</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.682345991250008</v>
+        <v>-2.429709400833329</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -4379,22 +4379,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="D7" t="n">
-        <v>2452319419.53</v>
+        <v>2204808001.51</v>
       </c>
       <c r="E7" t="n">
-        <v>28001388.48000002</v>
+        <v>30551371.72000027</v>
       </c>
       <c r="F7" t="n">
-        <v>14000694.24000001</v>
+        <v>15275685.86000013</v>
       </c>
       <c r="G7" t="n">
-        <v>1.750086780000001</v>
+        <v>2.545947643333355</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8750433900000005</v>
+        <v>1.272973821666678</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -4412,22 +4412,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="D8" t="n">
-        <v>2481860090.69</v>
+        <v>2210930152.52</v>
       </c>
       <c r="E8" t="n">
-        <v>57542059.63999987</v>
+        <v>36673522.73000002</v>
       </c>
       <c r="F8" t="n">
-        <v>28771029.81999993</v>
+        <v>18336761.36500001</v>
       </c>
       <c r="G8" t="n">
-        <v>3.596378727499991</v>
+        <v>3.056126894166668</v>
       </c>
       <c r="H8" t="n">
-        <v>1.798189363749996</v>
+        <v>1.528063447083334</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -4557,19 +4557,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G2" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="J2" t="n">
-        <v>-640000000</v>
+        <v>-680000000</v>
       </c>
       <c r="K2" t="n">
-        <v>-303055643.3100001</v>
+        <v>-655362070.4300001</v>
       </c>
       <c r="L2" t="n">
         <v>0.1050151041880321</v>
@@ -4581,10 +4581,10 @@
         <v>-0.02747158338321065</v>
       </c>
       <c r="O2" t="n">
-        <v>8302609.009532409</v>
+        <v>17954508.19205512</v>
       </c>
       <c r="P2" t="n">
-        <v>4151304.504766204</v>
+        <v>8977254.096027562</v>
       </c>
     </row>
     <row r="3">
@@ -4615,19 +4615,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G3" t="n">
-        <v>548709791.53</v>
+        <v>133911619.36</v>
       </c>
       <c r="H3" t="n">
-        <v>-484035602.7846395</v>
+        <v>-90269181.22613968</v>
       </c>
       <c r="I3" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="J3" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K3" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="L3" t="n">
         <v>0.05822765833026367</v>
@@ -4639,10 +4639,10 @@
         <v>0.02514989940008316</v>
       </c>
       <c r="O3" t="n">
-        <v>1491003.562333822</v>
+        <v>1006136.017920862</v>
       </c>
       <c r="P3" t="n">
-        <v>745501.7811669109</v>
+        <v>503068.0089604312</v>
       </c>
     </row>
     <row r="4">
@@ -4673,19 +4673,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>1990072267.9</v>
+        <v>2364336920.83</v>
       </c>
       <c r="H4" t="n">
-        <v>-446135269.4812486</v>
+        <v>-51490547.94520548</v>
       </c>
       <c r="I4" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="J4" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K4" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="L4" t="n">
         <v>0.05839364669442126</v>
@@ -4697,10 +4697,10 @@
         <v>0.02530014515467949</v>
       </c>
       <c r="O4" t="n">
-        <v>32551525.14139548</v>
+        <v>48762790.79538272</v>
       </c>
       <c r="P4" t="n">
-        <v>16275762.57069774</v>
+        <v>24381395.39769136</v>
       </c>
     </row>
     <row r="5">
@@ -4731,19 +4731,19 @@
         <v>0.75</v>
       </c>
       <c r="G5" t="n">
-        <v>321318332.1300001</v>
+        <v>-157998693</v>
       </c>
       <c r="H5" t="n">
-        <v>-496658630.361554</v>
+        <v>-92049904.10958904</v>
       </c>
       <c r="I5" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="J5" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K5" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="L5" t="n">
         <v>0.05851824187679444</v>
@@ -4755,10 +4755,10 @@
         <v>0.02544697899977066</v>
       </c>
       <c r="O5" t="n">
-        <v>-3346410.665183908</v>
+        <v>-4772236.049677371</v>
       </c>
       <c r="P5" t="n">
-        <v>-3346410.665183908</v>
+        <v>-4772236.049677371</v>
       </c>
     </row>
     <row r="6">
@@ -4789,19 +4789,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>82481230.3</v>
+        <v>-194599255.21</v>
       </c>
       <c r="H6" t="n">
-        <v>-119458296.2048057</v>
+        <v>-51458493.15068493</v>
       </c>
       <c r="I6" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="J6" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K6" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="L6" t="n">
         <v>0.05821004393128892</v>
@@ -4813,10 +4813,10 @@
         <v>0.02559354982454409</v>
       </c>
       <c r="O6" t="n">
-        <v>-630916.2524000645</v>
+        <v>-4198327.494922882</v>
       </c>
       <c r="P6" t="n">
-        <v>-630916.2524000645</v>
+        <v>-4198327.494922882</v>
       </c>
     </row>
     <row r="7">
@@ -4847,19 +4847,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>518697858.84</v>
+        <v>398501812.66</v>
       </c>
       <c r="H7" t="n">
-        <v>-119426252.4590164</v>
+        <v>-51445520.54794521</v>
       </c>
       <c r="I7" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="J7" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K7" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="L7" t="n">
         <v>0.05808035784574397</v>
@@ -4871,10 +4871,10 @@
         <v>0.02573959809769572</v>
       </c>
       <c r="O7" t="n">
-        <v>5994969.563372931</v>
+        <v>5210968.861140452</v>
       </c>
       <c r="P7" t="n">
-        <v>2997484.781686465</v>
+        <v>2605484.430570226</v>
       </c>
     </row>
     <row r="8">
@@ -4905,19 +4905,19 @@
         <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>669118580.01</v>
+        <v>772422393.1500001</v>
       </c>
       <c r="H8" t="n">
-        <v>-207983441.3653717</v>
+        <v>-90799555.08645856</v>
       </c>
       <c r="I8" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="J8" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K8" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="L8" t="n">
         <v>0.0579990267461179</v>
@@ -4929,10 +4929,10 @@
         <v>0.02588744766971374</v>
       </c>
       <c r="O8" t="n">
-        <v>5968805.885164502</v>
+        <v>8822737.775425846</v>
       </c>
       <c r="P8" t="n">
-        <v>2984402.942582251</v>
+        <v>4411368.887712923</v>
       </c>
     </row>
     <row r="9">
@@ -4963,19 +4963,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G9" t="n">
-        <v>-153952841.84</v>
+        <v>-35157733.02</v>
       </c>
       <c r="H9" t="n">
-        <v>61685111.16101505</v>
+        <v>2247136.761733663</v>
       </c>
       <c r="I9" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="J9" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K9" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="L9" t="n">
         <v>0.05738520780446178</v>
@@ -4987,10 +4987,10 @@
         <v>0.02602676969992171</v>
       </c>
       <c r="O9" t="n">
-        <v>-1000596.240465143</v>
+        <v>-356898.545625418</v>
       </c>
       <c r="P9" t="n">
-        <v>-1000596.240465143</v>
+        <v>-356898.545625418</v>
       </c>
     </row>
     <row r="10">
@@ -5021,19 +5021,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G10" t="n">
-        <v>-105287618.79</v>
+        <v>-35284909.43000001</v>
       </c>
       <c r="H10" t="n">
-        <v>9506772.962048057</v>
+        <v>2266152.03233775</v>
       </c>
       <c r="I10" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="J10" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K10" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="L10" t="n">
         <v>0.05695407285841891</v>
@@ -5045,10 +5045,10 @@
         <v>0.02616692125524978</v>
       </c>
       <c r="O10" t="n">
-        <v>-835429.9501804125</v>
+        <v>-287999.7415902748</v>
       </c>
       <c r="P10" t="n">
-        <v>-835429.9501804125</v>
+        <v>-287999.7415902748</v>
       </c>
     </row>
     <row r="11">
@@ -5079,19 +5079,19 @@
         <v>0.25</v>
       </c>
       <c r="G11" t="n">
-        <v>-8670744.480000019</v>
+        <v>-35779408.35</v>
       </c>
       <c r="H11" t="n">
-        <v>61673328.09342016</v>
+        <v>2248181.001571974</v>
       </c>
       <c r="I11" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="J11" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K11" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="L11" t="n">
         <v>0.05664439372837885</v>
@@ -5103,10 +5103,10 @@
         <v>0.02630835803903212</v>
       </c>
       <c r="O11" t="n">
-        <v>348602.7366738985</v>
+        <v>-220537.8836426575</v>
       </c>
       <c r="P11" t="n">
-        <v>174301.3683369493</v>
+        <v>-220537.8836426575</v>
       </c>
     </row>
     <row r="12">
@@ -5137,19 +5137,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G12" t="n">
-        <v>-105791543.79</v>
+        <v>-35814156.50999999</v>
       </c>
       <c r="H12" t="n">
-        <v>9444482.371434988</v>
+        <v>2248686.278913092</v>
       </c>
       <c r="I12" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="J12" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K12" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="L12" t="n">
         <v>0.05642057743315654</v>
@@ -5161,10 +5161,10 @@
         <v>0.02645013495868191</v>
       </c>
       <c r="O12" t="n">
-        <v>-424732.1295655764</v>
+        <v>-147968.5362606447</v>
       </c>
       <c r="P12" t="n">
-        <v>-424732.1295655764</v>
+        <v>-147968.5362606447</v>
       </c>
     </row>
     <row r="13">
@@ -5195,19 +5195,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G13" t="n">
-        <v>-105084497.29</v>
+        <v>-35845139.96</v>
       </c>
       <c r="H13" t="n">
-        <v>9498456.09701325</v>
+        <v>2261537.165955536</v>
       </c>
       <c r="I13" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="J13" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K13" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="L13" t="n">
         <v>0.05625883751011833</v>
@@ -5219,10 +5219,10 @@
         <v>0.02659286987606641</v>
       </c>
       <c r="O13" t="n">
-        <v>-211825.5962844518</v>
+        <v>-74423.69825596042</v>
       </c>
       <c r="P13" t="n">
-        <v>-211825.5962844518</v>
+        <v>-74423.69825596042</v>
       </c>
     </row>
     <row r="14">
@@ -5253,34 +5253,34 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>26344865.39000002</v>
+        <v>-36463708.53000001</v>
       </c>
       <c r="H14" t="n">
-        <v>9437731.866157647</v>
+        <v>4044566.584325174</v>
       </c>
       <c r="I14" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="J14" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K14" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05612125523607059</v>
+        <v>0.05613367690325632</v>
       </c>
       <c r="M14" t="n">
-        <v>0.08285710130558432</v>
+        <v>0.08286986959442011</v>
       </c>
       <c r="N14" t="n">
-        <v>0.02673584606951374</v>
+        <v>0.02673619269116378</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -5311,19 +5311,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G15" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="J15" t="n">
-        <v>-640000000</v>
+        <v>-680000000</v>
       </c>
       <c r="K15" t="n">
-        <v>-303055643.3100001</v>
+        <v>-655362070.4300001</v>
       </c>
       <c r="L15" t="n">
         <v>0.1050151041880321</v>
@@ -5335,10 +5335,10 @@
         <v>-0.07747761902794248</v>
       </c>
       <c r="O15" t="n">
-        <v>23415700.82821106</v>
+        <v>50636780.78302096</v>
       </c>
       <c r="P15" t="n">
-        <v>11707850.41410553</v>
+        <v>25318390.39151048</v>
       </c>
     </row>
     <row r="16">
@@ -5369,19 +5369,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G16" t="n">
-        <v>548709791.53</v>
+        <v>133911619.36</v>
       </c>
       <c r="H16" t="n">
-        <v>-484035602.7846395</v>
+        <v>-90269181.22613968</v>
       </c>
       <c r="I16" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="J16" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K16" t="n">
-        <v>128674188.7453604</v>
+        <v>111642438.1338603</v>
       </c>
       <c r="L16" t="n">
         <v>0.05822765833026367</v>
@@ -5393,10 +5393,10 @@
         <v>-0.02509271293939896</v>
       </c>
       <c r="O16" t="n">
-        <v>-2959719.107489256</v>
+        <v>-2567960.680951935</v>
       </c>
       <c r="P16" t="n">
-        <v>-2959719.107489256</v>
+        <v>-2567960.680951935</v>
       </c>
     </row>
     <row r="17">
@@ -5427,19 +5427,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G17" t="n">
-        <v>1990072267.9</v>
+        <v>2364336920.83</v>
       </c>
       <c r="H17" t="n">
-        <v>-446135269.4812486</v>
+        <v>-51490547.94520548</v>
       </c>
       <c r="I17" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="J17" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K17" t="n">
-        <v>1607936998.418751</v>
+        <v>2380846372.884794</v>
       </c>
       <c r="L17" t="n">
         <v>0.05839364669442126</v>
@@ -5451,10 +5451,10 @@
         <v>-0.02518665410778054</v>
       </c>
       <c r="O17" t="n">
-        <v>-33748794.17189663</v>
+        <v>-49971295.06467766</v>
       </c>
       <c r="P17" t="n">
-        <v>-33748794.17189663</v>
+        <v>-49971295.06467766</v>
       </c>
     </row>
     <row r="18">
@@ -5485,19 +5485,19 @@
         <v>0.75</v>
       </c>
       <c r="G18" t="n">
-        <v>321318332.1300001</v>
+        <v>-157998693</v>
       </c>
       <c r="H18" t="n">
-        <v>-496658630.361554</v>
+        <v>-92049904.10958904</v>
       </c>
       <c r="I18" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="J18" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K18" t="n">
-        <v>-111340298.2315539</v>
+        <v>-182048597.109589</v>
       </c>
       <c r="L18" t="n">
         <v>0.05851824187679444</v>
@@ -5509,10 +5509,10 @@
         <v>-0.02528484926412755</v>
       </c>
       <c r="O18" t="n">
-        <v>2111416.993355886</v>
+        <v>3452303.502496384</v>
       </c>
       <c r="P18" t="n">
-        <v>1055708.496677943</v>
+        <v>1726151.751248192</v>
       </c>
     </row>
     <row r="19">
@@ -5543,19 +5543,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>82481230.3</v>
+        <v>-194599255.21</v>
       </c>
       <c r="H19" t="n">
-        <v>-119458296.2048057</v>
+        <v>-51458493.15068493</v>
       </c>
       <c r="I19" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="J19" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K19" t="n">
-        <v>27022934.09519425</v>
+        <v>-178057748.3606849</v>
       </c>
       <c r="L19" t="n">
         <v>0.05821004393128892</v>
@@ -5567,10 +5567,10 @@
         <v>-0.02537722477452231</v>
       </c>
       <c r="O19" t="n">
-        <v>-457178.0484005649</v>
+        <v>3012407.668662956</v>
       </c>
       <c r="P19" t="n">
-        <v>-457178.0484005649</v>
+        <v>1506203.834331478</v>
       </c>
     </row>
     <row r="20">
@@ -5601,19 +5601,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>518697858.84</v>
+        <v>398501812.66</v>
       </c>
       <c r="H20" t="n">
-        <v>-119426252.4590164</v>
+        <v>-51445520.54794521</v>
       </c>
       <c r="I20" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="J20" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K20" t="n">
-        <v>463271606.3809837</v>
+        <v>415056292.1120548</v>
       </c>
       <c r="L20" t="n">
         <v>0.05808035784574397</v>
@@ -5625,10 +5625,10 @@
         <v>-0.02547134730704866</v>
       </c>
       <c r="O20" t="n">
-        <v>-6883421.99044755</v>
+        <v>-6167025.064877826</v>
       </c>
       <c r="P20" t="n">
-        <v>-6883421.99044755</v>
+        <v>-6167025.064877826</v>
       </c>
     </row>
     <row r="21">
@@ -5659,19 +5659,19 @@
         <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>669118580.01</v>
+        <v>772422393.1500001</v>
       </c>
       <c r="H21" t="n">
-        <v>-207983441.3653717</v>
+        <v>-90799555.08645856</v>
       </c>
       <c r="I21" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="J21" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K21" t="n">
-        <v>493135138.6446283</v>
+        <v>715622838.0635415</v>
       </c>
       <c r="L21" t="n">
         <v>0.0579990267461179</v>
@@ -5683,10 +5683,10 @@
         <v>-0.02556388968728518</v>
       </c>
       <c r="O21" t="n">
-        <v>-6303226.14261768</v>
+        <v>-9147051.64497916</v>
       </c>
       <c r="P21" t="n">
-        <v>-6303226.14261768</v>
+        <v>-9147051.64497916</v>
       </c>
     </row>
     <row r="22">
@@ -5717,19 +5717,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G22" t="n">
-        <v>-153952841.84</v>
+        <v>-35157733.02</v>
       </c>
       <c r="H22" t="n">
-        <v>61685111.16101505</v>
+        <v>2247136.761733663</v>
       </c>
       <c r="I22" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="J22" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K22" t="n">
-        <v>-60267730.67898495</v>
+        <v>1089403.741733659</v>
       </c>
       <c r="L22" t="n">
         <v>0.05738520780446178</v>
@@ -5741,10 +5741,10 @@
         <v>-0.02564879692438105</v>
       </c>
       <c r="O22" t="n">
-        <v>644081.1605327394</v>
+        <v>-11642.45639182811</v>
       </c>
       <c r="P22" t="n">
-        <v>322040.5802663697</v>
+        <v>-11642.45639182811</v>
       </c>
     </row>
     <row r="23">
@@ -5775,19 +5775,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>-105287618.79</v>
+        <v>-35284909.43000001</v>
       </c>
       <c r="H23" t="n">
-        <v>9506772.962048057</v>
+        <v>2266152.03233775</v>
       </c>
       <c r="I23" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="J23" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K23" t="n">
-        <v>-63780845.82795194</v>
+        <v>981242.6023377441</v>
       </c>
       <c r="L23" t="n">
         <v>0.05695407285841891</v>
@@ -5799,10 +5799,10 @@
         <v>-0.02573394353653935</v>
       </c>
       <c r="O23" t="n">
-        <v>547110.895083079</v>
+        <v>-8417.080574735481</v>
       </c>
       <c r="P23" t="n">
-        <v>273555.4475415395</v>
+        <v>-8417.080574735481</v>
       </c>
     </row>
     <row r="24">
@@ -5833,19 +5833,19 @@
         <v>0.25</v>
       </c>
       <c r="G24" t="n">
-        <v>-8670744.480000019</v>
+        <v>-35779408.35</v>
       </c>
       <c r="H24" t="n">
-        <v>61673328.09342016</v>
+        <v>2248181.001571974</v>
       </c>
       <c r="I24" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="J24" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K24" t="n">
-        <v>85002583.61342014</v>
+        <v>468772.6515719742</v>
       </c>
       <c r="L24" t="n">
         <v>0.05664439372837885</v>
@@ -5857,10 +5857,10 @@
         <v>-0.02581887365352179</v>
       </c>
       <c r="O24" t="n">
-        <v>-548667.7416344541</v>
+        <v>-3025.795465790799</v>
       </c>
       <c r="P24" t="n">
-        <v>-548667.7416344541</v>
+        <v>-3025.795465790799</v>
       </c>
     </row>
     <row r="25">
@@ -5891,19 +5891,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G25" t="n">
-        <v>-105791543.79</v>
+        <v>-35814156.50999999</v>
       </c>
       <c r="H25" t="n">
-        <v>9444482.371434988</v>
+        <v>2248686.278913092</v>
       </c>
       <c r="I25" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="J25" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K25" t="n">
-        <v>-64347061.41856501</v>
+        <v>434529.7689131051</v>
       </c>
       <c r="L25" t="n">
         <v>0.05642057743315654</v>
@@ -5915,10 +5915,10 @@
         <v>-0.02590450870981425</v>
       </c>
       <c r="O25" t="n">
-        <v>277813.1688280281</v>
+        <v>-1876.046697247183</v>
       </c>
       <c r="P25" t="n">
-        <v>138906.5844140141</v>
+        <v>-1876.046697247183</v>
       </c>
     </row>
     <row r="26">
@@ -5949,19 +5949,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G26" t="n">
-        <v>-105084497.29</v>
+        <v>-35845139.96</v>
       </c>
       <c r="H26" t="n">
-        <v>9498456.09701325</v>
+        <v>2261537.165955536</v>
       </c>
       <c r="I26" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="J26" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K26" t="n">
-        <v>-63586041.19298677</v>
+        <v>416397.2059555352</v>
       </c>
       <c r="L26" t="n">
         <v>0.05625883751011833</v>
@@ -5973,10 +5973,10 @@
         <v>-0.025990262065432</v>
       </c>
       <c r="O26" t="n">
-        <v>137718.1561924235</v>
+        <v>-901.8560421748355</v>
       </c>
       <c r="P26" t="n">
-        <v>68859.07809621173</v>
+        <v>-901.8560421748355</v>
       </c>
     </row>
     <row r="27">
@@ -6007,28 +6007,28 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>26344865.39000002</v>
+        <v>-36463708.53000001</v>
       </c>
       <c r="H27" t="n">
-        <v>9437731.866157647</v>
+        <v>4044566.584325174</v>
       </c>
       <c r="I27" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="J27" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K27" t="n">
-        <v>67782597.25615767</v>
+        <v>1580858.054325163</v>
       </c>
       <c r="L27" t="n">
-        <v>0.05612125523607059</v>
+        <v>0.05613367690325632</v>
       </c>
       <c r="M27" t="n">
-        <v>0.030045538435584</v>
+        <v>0.03005768533093844</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.02607571680048659</v>
+        <v>-0.02607599157231788</v>
       </c>
       <c r="O27" t="n">
         <v>-0</v>
@@ -6065,19 +6065,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G28" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="J28" t="n">
-        <v>-640000000</v>
+        <v>-680000000</v>
       </c>
       <c r="K28" t="n">
-        <v>-303055643.3100001</v>
+        <v>-655362070.4300001</v>
       </c>
       <c r="L28" t="n">
         <v>0.1050151041880321</v>
@@ -6089,10 +6089,10 @@
         <v>-0.07502986587896165</v>
       </c>
       <c r="O28" t="n">
-        <v>22675927.76655857</v>
+        <v>49037011.18283243</v>
       </c>
       <c r="P28" t="n">
-        <v>11337963.88327928</v>
+        <v>24518505.59141621</v>
       </c>
     </row>
     <row r="29">
@@ -6123,19 +6123,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G29" t="n">
-        <v>548709791.53</v>
+        <v>133911619.36</v>
       </c>
       <c r="H29" t="n">
-        <v>-484035602.7846395</v>
+        <v>-90269181.22613968</v>
       </c>
       <c r="I29" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="J29" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K29" t="n">
-        <v>128674188.7453604</v>
+        <v>111642438.1338603</v>
       </c>
       <c r="L29" t="n">
         <v>0.05822765833026367</v>
@@ -6147,10 +6147,10 @@
         <v>-0.01988106139069767</v>
       </c>
       <c r="O29" t="n">
-        <v>-2344997.825357669</v>
+        <v>-2034605.985817574</v>
       </c>
       <c r="P29" t="n">
-        <v>-2344997.825357669</v>
+        <v>-2034605.985817574</v>
       </c>
     </row>
     <row r="30">
@@ -6181,19 +6181,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G30" t="n">
-        <v>1990072267.9</v>
+        <v>2364336920.83</v>
       </c>
       <c r="H30" t="n">
-        <v>-446135269.4812486</v>
+        <v>-51490547.94520548</v>
       </c>
       <c r="I30" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="J30" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K30" t="n">
-        <v>1607936998.418751</v>
+        <v>2380846372.884794</v>
       </c>
       <c r="L30" t="n">
         <v>0.05839364669442126</v>
@@ -6205,10 +6205,10 @@
         <v>-0.01725628309459371</v>
       </c>
       <c r="O30" t="n">
-        <v>-23122513.36915437</v>
+        <v>-34237132.51269718</v>
       </c>
       <c r="P30" t="n">
-        <v>-23122513.36915437</v>
+        <v>-34237132.51269718</v>
       </c>
     </row>
     <row r="31">
@@ -6239,19 +6239,19 @@
         <v>0.75</v>
       </c>
       <c r="G31" t="n">
-        <v>321318332.1300001</v>
+        <v>-157998693</v>
       </c>
       <c r="H31" t="n">
-        <v>-496658630.361554</v>
+        <v>-92049904.10958904</v>
       </c>
       <c r="I31" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="J31" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K31" t="n">
-        <v>-111340298.2315539</v>
+        <v>-182048597.109589</v>
       </c>
       <c r="L31" t="n">
         <v>0.05851824187679444</v>
@@ -6263,10 +6263,10 @@
         <v>-0.01489062910622074</v>
       </c>
       <c r="O31" t="n">
-        <v>1243445.314156556</v>
+        <v>2033113.604150025</v>
       </c>
       <c r="P31" t="n">
-        <v>621722.657078278</v>
+        <v>1016556.802075012</v>
       </c>
     </row>
     <row r="32">
@@ -6297,19 +6297,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G32" t="n">
-        <v>82481230.3</v>
+        <v>-194599255.21</v>
       </c>
       <c r="H32" t="n">
-        <v>-119458296.2048057</v>
+        <v>-51458493.15068493</v>
       </c>
       <c r="I32" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="J32" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K32" t="n">
-        <v>27022934.09519425</v>
+        <v>-178057748.3606849</v>
       </c>
       <c r="L32" t="n">
         <v>0.05821004393128892</v>
@@ -6321,10 +6321,10 @@
         <v>-0.01266202848122933</v>
       </c>
       <c r="O32" t="n">
-        <v>-228110.1074398218</v>
+        <v>1503048.187364371</v>
       </c>
       <c r="P32" t="n">
-        <v>-228110.1074398218</v>
+        <v>751524.0936821856</v>
       </c>
     </row>
     <row r="33">
@@ -6355,19 +6355,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G33" t="n">
-        <v>518697858.84</v>
+        <v>398501812.66</v>
       </c>
       <c r="H33" t="n">
-        <v>-119426252.4590164</v>
+        <v>-51445520.54794521</v>
       </c>
       <c r="I33" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="J33" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K33" t="n">
-        <v>463271606.3809837</v>
+        <v>415056292.1120548</v>
       </c>
       <c r="L33" t="n">
         <v>0.05808035784574397</v>
@@ -6379,10 +6379,10 @@
         <v>-0.01061579379409725</v>
       </c>
       <c r="O33" t="n">
-        <v>-2868830.909000414</v>
+        <v>-2570255.339169097</v>
       </c>
       <c r="P33" t="n">
-        <v>-2868830.909000414</v>
+        <v>-2570255.339169097</v>
       </c>
     </row>
     <row r="34">
@@ -6413,19 +6413,19 @@
         <v>0.5</v>
       </c>
       <c r="G34" t="n">
-        <v>669118580.01</v>
+        <v>772422393.1500001</v>
       </c>
       <c r="H34" t="n">
-        <v>-207983441.3653717</v>
+        <v>-90799555.08645856</v>
       </c>
       <c r="I34" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="J34" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K34" t="n">
-        <v>493135138.6446283</v>
+        <v>715622838.0635415</v>
       </c>
       <c r="L34" t="n">
         <v>0.0579990267461179</v>
@@ -6437,10 +6437,10 @@
         <v>-0.008701770963537303</v>
       </c>
       <c r="O34" t="n">
-        <v>-2145574.515278884</v>
+        <v>-3113593.016552742</v>
       </c>
       <c r="P34" t="n">
-        <v>-2145574.515278884</v>
+        <v>-3113593.016552742</v>
       </c>
     </row>
     <row r="35">
@@ -6471,19 +6471,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G35" t="n">
-        <v>-153952841.84</v>
+        <v>-35157733.02</v>
       </c>
       <c r="H35" t="n">
-        <v>61685111.16101505</v>
+        <v>2247136.761733663</v>
       </c>
       <c r="I35" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="J35" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K35" t="n">
-        <v>-60267730.67898495</v>
+        <v>1089403.741733659</v>
       </c>
       <c r="L35" t="n">
         <v>0.05738520780446178</v>
@@ -6495,10 +6495,10 @@
         <v>-0.006933843412663093</v>
       </c>
       <c r="O35" t="n">
-        <v>174119.5864019305</v>
+        <v>-3147.397899312691</v>
       </c>
       <c r="P35" t="n">
-        <v>87059.79320096526</v>
+        <v>-3147.397899312691</v>
       </c>
     </row>
     <row r="36">
@@ -6529,19 +6529,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G36" t="n">
-        <v>-105287618.79</v>
+        <v>-35284909.43000001</v>
       </c>
       <c r="H36" t="n">
-        <v>9506772.962048057</v>
+        <v>2266152.03233775</v>
       </c>
       <c r="I36" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="J36" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K36" t="n">
-        <v>-63780845.82795194</v>
+        <v>981242.6023377441</v>
       </c>
       <c r="L36" t="n">
         <v>0.05695407285841891</v>
@@ -6553,10 +6553,10 @@
         <v>-0.005293779960104272</v>
       </c>
       <c r="O36" t="n">
-        <v>112547.2544941707</v>
+        <v>-1731.494141418705</v>
       </c>
       <c r="P36" t="n">
-        <v>56273.62724708537</v>
+        <v>-1731.494141418705</v>
       </c>
     </row>
     <row r="37">
@@ -6587,19 +6587,19 @@
         <v>0.25</v>
       </c>
       <c r="G37" t="n">
-        <v>-8670744.480000019</v>
+        <v>-35779408.35</v>
       </c>
       <c r="H37" t="n">
-        <v>61673328.09342016</v>
+        <v>2248181.001571974</v>
       </c>
       <c r="I37" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="J37" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K37" t="n">
-        <v>85002583.61342014</v>
+        <v>468772.6515719742</v>
       </c>
       <c r="L37" t="n">
         <v>0.05664439372837885</v>
@@ -6611,10 +6611,10 @@
         <v>-0.003768699327115023</v>
       </c>
       <c r="O37" t="n">
-        <v>-80087.29491673374</v>
+        <v>-441.665794137306</v>
       </c>
       <c r="P37" t="n">
-        <v>-80087.29491673374</v>
+        <v>-441.665794137306</v>
       </c>
     </row>
     <row r="38">
@@ -6645,19 +6645,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G38" t="n">
-        <v>-105791543.79</v>
+        <v>-35814156.50999999</v>
       </c>
       <c r="H38" t="n">
-        <v>9444482.371434988</v>
+        <v>2248686.278913092</v>
       </c>
       <c r="I38" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="J38" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K38" t="n">
-        <v>-64347061.41856501</v>
+        <v>434529.7689131051</v>
       </c>
       <c r="L38" t="n">
         <v>0.05642057743315654</v>
@@ -6669,10 +6669,10 @@
         <v>-0.002356874069323035</v>
       </c>
       <c r="O38" t="n">
-        <v>25276.32008242542</v>
+        <v>-170.688657450038</v>
       </c>
       <c r="P38" t="n">
-        <v>12638.16004121271</v>
+        <v>-170.688657450038</v>
       </c>
     </row>
     <row r="39">
@@ -6703,19 +6703,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G39" t="n">
-        <v>-105084497.29</v>
+        <v>-35845139.96</v>
       </c>
       <c r="H39" t="n">
-        <v>9498456.09701325</v>
+        <v>2261537.165955536</v>
       </c>
       <c r="I39" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="J39" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K39" t="n">
-        <v>-63586041.19298677</v>
+        <v>416397.2059555352</v>
       </c>
       <c r="L39" t="n">
         <v>0.05625883751011833</v>
@@ -6727,10 +6727,10 @@
         <v>-0.001044890098674874</v>
       </c>
       <c r="O39" t="n">
-        <v>5536.702071373712</v>
+        <v>-36.25744313490175</v>
       </c>
       <c r="P39" t="n">
-        <v>2768.351035686856</v>
+        <v>-36.25744313490175</v>
       </c>
     </row>
     <row r="40">
@@ -6761,34 +6761,34 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>26344865.39000002</v>
+        <v>-36463708.53000001</v>
       </c>
       <c r="H40" t="n">
-        <v>9437731.866157647</v>
+        <v>4044566.584325174</v>
       </c>
       <c r="I40" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="J40" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K40" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="L40" t="n">
-        <v>0.05612125523607059</v>
+        <v>0.05613367690325632</v>
       </c>
       <c r="M40" t="n">
-        <v>0.05629528248589444</v>
+        <v>0.05630773793266308</v>
       </c>
       <c r="N40" t="n">
-        <v>0.0001740272498238493</v>
+        <v>0.0001740610294067579</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="41">
@@ -6819,19 +6819,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G41" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="J41" t="n">
-        <v>-640000000</v>
+        <v>-680000000</v>
       </c>
       <c r="K41" t="n">
-        <v>-303055643.3100001</v>
+        <v>-655362070.4300001</v>
       </c>
       <c r="L41" t="n">
         <v>0.1050151041880321</v>
@@ -6843,10 +6843,10 @@
         <v>-0.02468474605999638</v>
       </c>
       <c r="O41" t="n">
-        <v>7460356.113328367</v>
+        <v>16133124.51527166</v>
       </c>
       <c r="P41" t="n">
-        <v>3730178.056664183</v>
+        <v>8066562.257635831</v>
       </c>
     </row>
     <row r="42">
@@ -6877,19 +6877,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G42" t="n">
-        <v>548709791.53</v>
+        <v>133911619.36</v>
       </c>
       <c r="H42" t="n">
-        <v>-484035602.7846395</v>
+        <v>-90269181.22613968</v>
       </c>
       <c r="I42" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="J42" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K42" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="L42" t="n">
         <v>0.05822765833026367</v>
@@ -6901,10 +6901,10 @@
         <v>0.02495849603761435</v>
       </c>
       <c r="O42" t="n">
-        <v>1479656.276575584</v>
+        <v>998478.8176328007</v>
       </c>
       <c r="P42" t="n">
-        <v>739828.1382877921</v>
+        <v>499239.4088164003</v>
       </c>
     </row>
     <row r="43">
@@ -6935,19 +6935,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G43" t="n">
-        <v>1990072267.9</v>
+        <v>2364336920.83</v>
       </c>
       <c r="H43" t="n">
-        <v>-446135269.4812486</v>
+        <v>-51490547.94520548</v>
       </c>
       <c r="I43" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="J43" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K43" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="L43" t="n">
         <v>0.05839364669442126</v>
@@ -6959,10 +6959,10 @@
         <v>0.02216014487646945</v>
       </c>
       <c r="O43" t="n">
-        <v>28511556.30425076</v>
+        <v>42710842.25011992</v>
       </c>
       <c r="P43" t="n">
-        <v>14255778.15212538</v>
+        <v>21355421.12505996</v>
       </c>
     </row>
     <row r="44">
@@ -6993,19 +6993,19 @@
         <v>0.75</v>
       </c>
       <c r="G44" t="n">
-        <v>321318332.1300001</v>
+        <v>-157998693</v>
       </c>
       <c r="H44" t="n">
-        <v>-496658630.361554</v>
+        <v>-92049904.10958904</v>
       </c>
       <c r="I44" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="J44" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K44" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="L44" t="n">
         <v>0.05851824187679444</v>
@@ -7017,10 +7017,10 @@
         <v>0.01962016480210327</v>
       </c>
       <c r="O44" t="n">
-        <v>-2580154.160814768</v>
+        <v>-3679496.012868645</v>
       </c>
       <c r="P44" t="n">
-        <v>-2580154.160814768</v>
+        <v>-3679496.012868645</v>
       </c>
     </row>
     <row r="45">
@@ -7051,19 +7051,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G45" t="n">
-        <v>82481230.3</v>
+        <v>-194599255.21</v>
       </c>
       <c r="H45" t="n">
-        <v>-119458296.2048057</v>
+        <v>-51458493.15068493</v>
       </c>
       <c r="I45" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="J45" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K45" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="L45" t="n">
         <v>0.05821004393128892</v>
@@ -7075,10 +7075,10 @@
         <v>0.01722340313955706</v>
       </c>
       <c r="O45" t="n">
-        <v>-424580.6086642931</v>
+        <v>-2825301.197085175</v>
       </c>
       <c r="P45" t="n">
-        <v>-424580.6086642931</v>
+        <v>-2825301.197085175</v>
       </c>
     </row>
     <row r="46">
@@ -7109,19 +7109,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G46" t="n">
-        <v>518697858.84</v>
+        <v>398501812.66</v>
       </c>
       <c r="H46" t="n">
-        <v>-119426252.4590164</v>
+        <v>-51445520.54794521</v>
       </c>
       <c r="I46" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="J46" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K46" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="L46" t="n">
         <v>0.05808035784574397</v>
@@ -7133,10 +7133,10 @@
         <v>0.01501522413586098</v>
       </c>
       <c r="O46" t="n">
-        <v>3497172.385522508</v>
+        <v>3039824.674730283</v>
       </c>
       <c r="P46" t="n">
-        <v>1748586.192761254</v>
+        <v>1519912.337365141</v>
       </c>
     </row>
     <row r="47">
@@ -7167,19 +7167,19 @@
         <v>0.5</v>
       </c>
       <c r="G47" t="n">
-        <v>669118580.01</v>
+        <v>772422393.1500001</v>
       </c>
       <c r="H47" t="n">
-        <v>-207983441.3653717</v>
+        <v>-90799555.08645856</v>
       </c>
       <c r="I47" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="J47" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K47" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="L47" t="n">
         <v>0.0579990267461179</v>
@@ -7191,10 +7191,10 @@
         <v>0.01294941997535037</v>
       </c>
       <c r="O47" t="n">
-        <v>2985716.287850357</v>
+        <v>4413310.197437519</v>
       </c>
       <c r="P47" t="n">
-        <v>1492858.143925178</v>
+        <v>2206655.09871876</v>
       </c>
     </row>
     <row r="48">
@@ -7225,19 +7225,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G48" t="n">
-        <v>-153952841.84</v>
+        <v>-35157733.02</v>
       </c>
       <c r="H48" t="n">
-        <v>61685111.16101505</v>
+        <v>2247136.761733663</v>
       </c>
       <c r="I48" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="J48" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K48" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="L48" t="n">
         <v>0.05738520780446178</v>
@@ -7249,10 +7249,10 @@
         <v>0.01103784963125674</v>
       </c>
       <c r="O48" t="n">
-        <v>-424348.8904383044</v>
+        <v>-151359.2553223936</v>
       </c>
       <c r="P48" t="n">
-        <v>-424348.8904383044</v>
+        <v>-151359.2553223936</v>
       </c>
     </row>
     <row r="49">
@@ -7283,19 +7283,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G49" t="n">
-        <v>-105287618.79</v>
+        <v>-35284909.43000001</v>
       </c>
       <c r="H49" t="n">
-        <v>9506772.962048057</v>
+        <v>2266152.03233775</v>
       </c>
       <c r="I49" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="J49" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K49" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="L49" t="n">
         <v>0.05695407285841891</v>
@@ -7307,10 +7307,10 @@
         <v>0.009264716116377802</v>
       </c>
       <c r="O49" t="n">
-        <v>-295794.115327508</v>
+        <v>-101969.8046016301</v>
       </c>
       <c r="P49" t="n">
-        <v>-295794.115327508</v>
+        <v>-101969.8046016301</v>
       </c>
     </row>
     <row r="50">
@@ -7341,19 +7341,19 @@
         <v>0.25</v>
       </c>
       <c r="G50" t="n">
-        <v>-8670744.480000019</v>
+        <v>-35779408.35</v>
       </c>
       <c r="H50" t="n">
-        <v>61673328.09342016</v>
+        <v>2248181.001571974</v>
       </c>
       <c r="I50" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="J50" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K50" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="L50" t="n">
         <v>0.05664439372837885</v>
@@ -7365,10 +7365,10 @@
         <v>0.007618063727031256</v>
       </c>
       <c r="O50" t="n">
-        <v>100944.2649160843</v>
+        <v>-63860.7566964745</v>
       </c>
       <c r="P50" t="n">
-        <v>50472.13245804216</v>
+        <v>-63860.7566964745</v>
       </c>
     </row>
     <row r="51">
@@ -7399,19 +7399,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G51" t="n">
-        <v>-105791543.79</v>
+        <v>-35814156.50999999</v>
       </c>
       <c r="H51" t="n">
-        <v>9444482.371434988</v>
+        <v>2248686.278913092</v>
       </c>
       <c r="I51" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="J51" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K51" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="L51" t="n">
         <v>0.05642057743315654</v>
@@ -7423,10 +7423,10 @@
         <v>0.006094907231449384</v>
       </c>
       <c r="O51" t="n">
-        <v>-97871.06689481827</v>
+        <v>-34096.40453974175</v>
       </c>
       <c r="P51" t="n">
-        <v>-97871.06689481827</v>
+        <v>-34096.40453974175</v>
       </c>
     </row>
     <row r="52">
@@ -7457,19 +7457,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G52" t="n">
-        <v>-105084497.29</v>
+        <v>-35845139.96</v>
       </c>
       <c r="H52" t="n">
-        <v>9498456.09701325</v>
+        <v>2261537.165955536</v>
       </c>
       <c r="I52" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="J52" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K52" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="L52" t="n">
         <v>0.05625883751011833</v>
@@ -7481,10 +7481,10 @@
         <v>0.004682431355023151</v>
       </c>
       <c r="O52" t="n">
-        <v>-37297.923032048</v>
+        <v>-13104.40956145641</v>
       </c>
       <c r="P52" t="n">
-        <v>-37297.923032048</v>
+        <v>-13104.40956145641</v>
       </c>
     </row>
     <row r="53">
@@ -7515,34 +7515,34 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>26344865.39000002</v>
+        <v>-36463708.53000001</v>
       </c>
       <c r="H53" t="n">
-        <v>9437731.866157647</v>
+        <v>4044566.584325174</v>
       </c>
       <c r="I53" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="J53" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K53" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="L53" t="n">
-        <v>0.05612125523607059</v>
+        <v>0.05613367690325632</v>
       </c>
       <c r="M53" t="n">
-        <v>0.05949445427920219</v>
+        <v>0.05950694809658197</v>
       </c>
       <c r="N53" t="n">
-        <v>0.003373199043131603</v>
+        <v>0.003373271193325644</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="54">
@@ -7573,19 +7573,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G54" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="J54" t="n">
-        <v>-640000000</v>
+        <v>-680000000</v>
       </c>
       <c r="K54" t="n">
-        <v>-303055643.3100001</v>
+        <v>-655362070.4300001</v>
       </c>
       <c r="L54" t="n">
         <v>0.1050151041880321</v>
@@ -7597,10 +7597,10 @@
         <v>-0.01765980557248192</v>
       </c>
       <c r="O54" t="n">
-        <v>5337240.988529545</v>
+        <v>11541858.34133637</v>
       </c>
       <c r="P54" t="n">
-        <v>2668620.494264773</v>
+        <v>5770929.170668184</v>
       </c>
     </row>
     <row r="55">
@@ -7631,19 +7631,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G55" t="n">
-        <v>548709791.53</v>
+        <v>133911619.36</v>
       </c>
       <c r="H55" t="n">
-        <v>-484035602.7846395</v>
+        <v>-90269181.22613968</v>
       </c>
       <c r="I55" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="J55" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K55" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="L55" t="n">
         <v>0.05822765833026367</v>
@@ -7655,10 +7655,10 @@
         <v>0.03235719235381929</v>
       </c>
       <c r="O55" t="n">
-        <v>1918285.568430772</v>
+        <v>1294467.868363062</v>
       </c>
       <c r="P55" t="n">
-        <v>959142.7842153859</v>
+        <v>647233.9341815311</v>
       </c>
     </row>
     <row r="56">
@@ -7689,19 +7689,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G56" t="n">
-        <v>1990072267.9</v>
+        <v>2364336920.83</v>
       </c>
       <c r="H56" t="n">
-        <v>-446135269.4812486</v>
+        <v>-51490547.94520548</v>
       </c>
       <c r="I56" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="J56" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K56" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="L56" t="n">
         <v>0.05839364669442126</v>
@@ -7713,10 +7713,10 @@
         <v>0.02992819194854235</v>
       </c>
       <c r="O56" t="n">
-        <v>38506035.70427726</v>
+        <v>57682758.4959884</v>
       </c>
       <c r="P56" t="n">
-        <v>19253017.85213863</v>
+        <v>28841379.2479942</v>
       </c>
     </row>
     <row r="57">
@@ -7747,19 +7747,19 @@
         <v>0.75</v>
       </c>
       <c r="G57" t="n">
-        <v>321318332.1300001</v>
+        <v>-157998693</v>
       </c>
       <c r="H57" t="n">
-        <v>-496658630.361554</v>
+        <v>-92049904.10958904</v>
       </c>
       <c r="I57" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="J57" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K57" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="L57" t="n">
         <v>0.05851824187679444</v>
@@ -7771,10 +7771,10 @@
         <v>0.02772661859587089</v>
       </c>
       <c r="O57" t="n">
-        <v>-3646195.180164413</v>
+        <v>-5199751.561867619</v>
       </c>
       <c r="P57" t="n">
-        <v>-3646195.180164413</v>
+        <v>-5199751.561867619</v>
       </c>
     </row>
     <row r="58">
@@ -7805,19 +7805,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G58" t="n">
-        <v>82481230.3</v>
+        <v>-194599255.21</v>
       </c>
       <c r="H58" t="n">
-        <v>-119458296.2048057</v>
+        <v>-51458493.15068493</v>
       </c>
       <c r="I58" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="J58" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K58" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="L58" t="n">
         <v>0.05821004393128892</v>
@@ -7829,10 +7829,10 @@
         <v>0.02564903369930005</v>
       </c>
       <c r="O58" t="n">
-        <v>-632284.0063290679</v>
+        <v>-4207428.9864514</v>
       </c>
       <c r="P58" t="n">
-        <v>-632284.0063290679</v>
+        <v>-4207428.9864514</v>
       </c>
     </row>
     <row r="59">
@@ -7863,19 +7863,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G59" t="n">
-        <v>518697858.84</v>
+        <v>398501812.66</v>
       </c>
       <c r="H59" t="n">
-        <v>-119426252.4590164</v>
+        <v>-51445520.54794521</v>
       </c>
       <c r="I59" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="J59" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K59" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="L59" t="n">
         <v>0.05808035784574397</v>
@@ -7887,10 +7887,10 @@
         <v>0.02373722363569292</v>
       </c>
       <c r="O59" t="n">
-        <v>5528599.657027863</v>
+        <v>4805589.145022292</v>
       </c>
       <c r="P59" t="n">
-        <v>2764299.828513931</v>
+        <v>2402794.572511146</v>
       </c>
     </row>
     <row r="60">
@@ -7921,19 +7921,19 @@
         <v>0.5</v>
       </c>
       <c r="G60" t="n">
-        <v>669118580.01</v>
+        <v>772422393.1500001</v>
       </c>
       <c r="H60" t="n">
-        <v>-207983441.3653717</v>
+        <v>-90799555.08645856</v>
       </c>
       <c r="I60" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="J60" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K60" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="L60" t="n">
         <v>0.0579990267461179</v>
@@ -7945,10 +7945,10 @@
         <v>0.02195017150422629</v>
       </c>
       <c r="O60" t="n">
-        <v>5060997.689937379</v>
+        <v>7480869.0983461</v>
       </c>
       <c r="P60" t="n">
-        <v>2530498.84496869</v>
+        <v>3740434.54917305</v>
       </c>
     </row>
     <row r="61">
@@ -7979,19 +7979,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G61" t="n">
-        <v>-153952841.84</v>
+        <v>-35157733.02</v>
       </c>
       <c r="H61" t="n">
-        <v>61685111.16101505</v>
+        <v>2247136.761733663</v>
       </c>
       <c r="I61" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="J61" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K61" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="L61" t="n">
         <v>0.05738520780446178</v>
@@ -8003,10 +8003,10 @@
         <v>0.02029522229252897</v>
       </c>
       <c r="O61" t="n">
-        <v>-780247.5435654979</v>
+        <v>-278303.2778504948</v>
       </c>
       <c r="P61" t="n">
-        <v>-780247.5435654979</v>
+        <v>-278303.2778504948</v>
       </c>
     </row>
     <row r="62">
@@ -8037,19 +8037,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G62" t="n">
-        <v>-105287618.79</v>
+        <v>-35284909.43000001</v>
       </c>
       <c r="H62" t="n">
-        <v>9506772.962048057</v>
+        <v>2266152.03233775</v>
       </c>
       <c r="I62" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="J62" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K62" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="L62" t="n">
         <v>0.05695407285841891</v>
@@ -8061,10 +8061,10 @@
         <v>0.01876196760334525</v>
       </c>
       <c r="O62" t="n">
-        <v>-599012.3754816803</v>
+        <v>-206498.9521992186</v>
       </c>
       <c r="P62" t="n">
-        <v>-599012.3754816803</v>
+        <v>-206498.9521992186</v>
       </c>
     </row>
     <row r="63">
@@ -8095,19 +8095,19 @@
         <v>0.25</v>
       </c>
       <c r="G63" t="n">
-        <v>-8670744.480000019</v>
+        <v>-35779408.35</v>
       </c>
       <c r="H63" t="n">
-        <v>61673328.09342016</v>
+        <v>2248181.001571974</v>
       </c>
       <c r="I63" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="J63" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K63" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="L63" t="n">
         <v>0.05664439372837885</v>
@@ -8119,10 +8119,10 @@
         <v>0.01733996627504109</v>
       </c>
       <c r="O63" t="n">
-        <v>229765.7530866877</v>
+        <v>-145357.5878456194</v>
       </c>
       <c r="P63" t="n">
-        <v>114882.8765433439</v>
+        <v>-145357.5878456194</v>
       </c>
     </row>
     <row r="64">
@@ -8153,19 +8153,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G64" t="n">
-        <v>-105791543.79</v>
+        <v>-35814156.50999999</v>
       </c>
       <c r="H64" t="n">
-        <v>9444482.371434988</v>
+        <v>2248686.278913092</v>
       </c>
       <c r="I64" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="J64" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K64" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="L64" t="n">
         <v>0.05642057743315654</v>
@@ -8177,10 +8177,10 @@
         <v>0.01602670204966161</v>
       </c>
       <c r="O64" t="n">
-        <v>-257354.2744526314</v>
+        <v>-89657.29842506933</v>
       </c>
       <c r="P64" t="n">
-        <v>-257354.2744526314</v>
+        <v>-89657.29842506933</v>
       </c>
     </row>
     <row r="65">
@@ -8211,19 +8211,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G65" t="n">
-        <v>-105084497.29</v>
+        <v>-35845139.96</v>
       </c>
       <c r="H65" t="n">
-        <v>9498456.09701325</v>
+        <v>2261537.165955536</v>
       </c>
       <c r="I65" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="J65" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K65" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="L65" t="n">
         <v>0.05625883751011833</v>
@@ -8235,10 +8235,10 @@
         <v>0.01481092208165177</v>
       </c>
       <c r="O65" t="n">
-        <v>-117976.4506835737</v>
+        <v>-41450.34368364463</v>
       </c>
       <c r="P65" t="n">
-        <v>-117976.4506835737</v>
+        <v>-41450.34368364463</v>
       </c>
     </row>
     <row r="66">
@@ -8269,34 +8269,34 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>26344865.39000002</v>
+        <v>-36463708.53000001</v>
       </c>
       <c r="H66" t="n">
-        <v>9437731.866157647</v>
+        <v>4044566.584325174</v>
       </c>
       <c r="I66" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="J66" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K66" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="L66" t="n">
-        <v>0.05612125523607059</v>
+        <v>0.05613367690325632</v>
       </c>
       <c r="M66" t="n">
-        <v>0.06980717394620273</v>
+        <v>0.06981978911298969</v>
       </c>
       <c r="N66" t="n">
-        <v>0.01368591871013214</v>
+        <v>0.01368611220973337</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="67">
@@ -8327,19 +8327,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G67" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="J67" t="n">
-        <v>-640000000</v>
+        <v>-680000000</v>
       </c>
       <c r="K67" t="n">
-        <v>-303055643.3100001</v>
+        <v>-655362070.4300001</v>
       </c>
       <c r="L67" t="n">
         <v>0.1050151041880321</v>
@@ -8351,10 +8351,10 @@
         <v>-0.08728823124945828</v>
       </c>
       <c r="O67" t="n">
-        <v>26380716.57860157</v>
+        <v>57048668.84360989</v>
       </c>
       <c r="P67" t="n">
-        <v>13190358.28930079</v>
+        <v>28524334.42180495</v>
       </c>
     </row>
     <row r="68">
@@ -8385,19 +8385,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G68" t="n">
-        <v>548709791.53</v>
+        <v>133911619.36</v>
       </c>
       <c r="H68" t="n">
-        <v>-484035602.7846395</v>
+        <v>-90269181.22613968</v>
       </c>
       <c r="I68" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="J68" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K68" t="n">
-        <v>128674188.7453604</v>
+        <v>111642438.1338603</v>
       </c>
       <c r="L68" t="n">
         <v>0.05822765833026367</v>
@@ -8409,10 +8409,10 @@
         <v>-0.03226565096877909</v>
       </c>
       <c r="O68" t="n">
-        <v>-3805776.757519552</v>
+        <v>-3302031.280286429</v>
       </c>
       <c r="P68" t="n">
-        <v>-3805776.757519552</v>
+        <v>-3302031.280286429</v>
       </c>
     </row>
     <row r="69">
@@ -8443,19 +8443,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G69" t="n">
-        <v>1990072267.9</v>
+        <v>2364336920.83</v>
       </c>
       <c r="H69" t="n">
-        <v>-446135269.4812486</v>
+        <v>-51490547.94520548</v>
       </c>
       <c r="I69" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="J69" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K69" t="n">
-        <v>1607936998.418751</v>
+        <v>2380846372.884794</v>
       </c>
       <c r="L69" t="n">
         <v>0.05839364669442126</v>
@@ -8467,10 +8467,10 @@
         <v>-0.0297728173926024</v>
       </c>
       <c r="O69" t="n">
-        <v>-39894012.19394226</v>
+        <v>-59070420.24978229</v>
       </c>
       <c r="P69" t="n">
-        <v>-39894012.19394226</v>
+        <v>-59070420.24978229</v>
       </c>
     </row>
     <row r="70">
@@ -8501,19 +8501,19 @@
         <v>0.75</v>
       </c>
       <c r="G70" t="n">
-        <v>321318332.1300001</v>
+        <v>-157998693</v>
       </c>
       <c r="H70" t="n">
-        <v>-496658630.361554</v>
+        <v>-92049904.10958904</v>
       </c>
       <c r="I70" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="J70" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K70" t="n">
-        <v>-111340298.2315539</v>
+        <v>-182048597.109589</v>
       </c>
       <c r="L70" t="n">
         <v>0.05851824187679444</v>
@@ -8525,10 +8525,10 @@
         <v>-0.02753489969717293</v>
       </c>
       <c r="O70" t="n">
-        <v>2299307.958044368</v>
+        <v>3759517.396067685</v>
       </c>
       <c r="P70" t="n">
-        <v>1149653.979022184</v>
+        <v>1879758.698033842</v>
       </c>
     </row>
     <row r="71">
@@ -8559,19 +8559,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G71" t="n">
-        <v>82481230.3</v>
+        <v>-194599255.21</v>
       </c>
       <c r="H71" t="n">
-        <v>-119458296.2048057</v>
+        <v>-51458493.15068493</v>
       </c>
       <c r="I71" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="J71" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K71" t="n">
-        <v>27022934.09519425</v>
+        <v>-178057748.3606849</v>
       </c>
       <c r="L71" t="n">
         <v>0.05821004393128892</v>
@@ -8583,10 +8583,10 @@
         <v>-0.02543179398870032</v>
       </c>
       <c r="O71" t="n">
-        <v>-458161.1285861375</v>
+        <v>3018885.316267188</v>
       </c>
       <c r="P71" t="n">
-        <v>-458161.1285861375</v>
+        <v>1509442.658133594</v>
       </c>
     </row>
     <row r="72">
@@ -8617,19 +8617,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G72" t="n">
-        <v>518697858.84</v>
+        <v>398501812.66</v>
       </c>
       <c r="H72" t="n">
-        <v>-119426252.4590164</v>
+        <v>-51445520.54794521</v>
       </c>
       <c r="I72" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="J72" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K72" t="n">
-        <v>463271606.3809837</v>
+        <v>415056292.1120548</v>
       </c>
       <c r="L72" t="n">
         <v>0.05808035784574397</v>
@@ -8641,10 +8641,10 @@
         <v>-0.02350867571892774</v>
       </c>
       <c r="O72" t="n">
-        <v>-6353026.145781747</v>
+        <v>-5691830.536211658</v>
       </c>
       <c r="P72" t="n">
-        <v>-6353026.145781747</v>
+        <v>-5691830.536211658</v>
       </c>
     </row>
     <row r="73">
@@ -8675,19 +8675,19 @@
         <v>0.5</v>
       </c>
       <c r="G73" t="n">
-        <v>669118580.01</v>
+        <v>772422393.1500001</v>
       </c>
       <c r="H73" t="n">
-        <v>-207983441.3653717</v>
+        <v>-90799555.08645856</v>
       </c>
       <c r="I73" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="J73" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K73" t="n">
-        <v>493135138.6446283</v>
+        <v>715622838.0635415</v>
       </c>
       <c r="L73" t="n">
         <v>0.0579990267461179</v>
@@ -8699,10 +8699,10 @@
         <v>-0.02171656780992581</v>
       </c>
       <c r="O73" t="n">
-        <v>-5354601.338916618</v>
+        <v>-7770435.944569229</v>
       </c>
       <c r="P73" t="n">
-        <v>-5354601.338916618</v>
+        <v>-7770435.944569229</v>
       </c>
     </row>
     <row r="74">
@@ -8733,19 +8733,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G74" t="n">
-        <v>-153952841.84</v>
+        <v>-35157733.02</v>
       </c>
       <c r="H74" t="n">
-        <v>61685111.16101505</v>
+        <v>2247136.761733663</v>
       </c>
       <c r="I74" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="J74" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K74" t="n">
-        <v>-60267730.67898495</v>
+        <v>1089403.741733659</v>
       </c>
       <c r="L74" t="n">
         <v>0.05738520780446178</v>
@@ -8757,10 +8757,10 @@
         <v>-0.02006419037968943</v>
       </c>
       <c r="O74" t="n">
-        <v>503843.0092062514</v>
+        <v>-9107.501697704229</v>
       </c>
       <c r="P74" t="n">
-        <v>251921.5046031257</v>
+        <v>-9107.501697704229</v>
       </c>
     </row>
     <row r="75">
@@ -8791,19 +8791,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G75" t="n">
-        <v>-105287618.79</v>
+        <v>-35284909.43000001</v>
       </c>
       <c r="H75" t="n">
-        <v>9506772.962048057</v>
+        <v>2266152.03233775</v>
       </c>
       <c r="I75" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="J75" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K75" t="n">
-        <v>-63780845.82795194</v>
+        <v>981242.6023377441</v>
       </c>
       <c r="L75" t="n">
         <v>0.05695407285841891</v>
@@ -8815,10 +8815,10 @@
         <v>-0.01853809135614659</v>
       </c>
       <c r="O75" t="n">
-        <v>394125.0489102915</v>
+        <v>-6063.455001560041</v>
       </c>
       <c r="P75" t="n">
-        <v>197062.5244551457</v>
+        <v>-6063.455001560041</v>
       </c>
     </row>
     <row r="76">
@@ -8849,19 +8849,19 @@
         <v>0.25</v>
       </c>
       <c r="G76" t="n">
-        <v>-8670744.480000019</v>
+        <v>-35779408.35</v>
       </c>
       <c r="H76" t="n">
-        <v>61673328.09342016</v>
+        <v>2248181.001571974</v>
       </c>
       <c r="I76" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="J76" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K76" t="n">
-        <v>85002583.61342014</v>
+        <v>468772.6515719742</v>
       </c>
       <c r="L76" t="n">
         <v>0.05664439372837885</v>
@@ -8873,10 +8873,10 @@
         <v>-0.01712553721773909</v>
       </c>
       <c r="O76" t="n">
-        <v>-363928.7273189013</v>
+        <v>-2006.99587278852</v>
       </c>
       <c r="P76" t="n">
-        <v>-363928.7273189013</v>
+        <v>-2006.99587278852</v>
       </c>
     </row>
     <row r="77">
@@ -8907,19 +8907,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G77" t="n">
-        <v>-105791543.79</v>
+        <v>-35814156.50999999</v>
       </c>
       <c r="H77" t="n">
-        <v>9444482.371434988</v>
+        <v>2248686.278913092</v>
       </c>
       <c r="I77" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="J77" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K77" t="n">
-        <v>-64347061.41856501</v>
+        <v>434529.7689131051</v>
       </c>
       <c r="L77" t="n">
         <v>0.05642057743315654</v>
@@ -8931,10 +8931,10 @@
         <v>-0.01582455504283544</v>
       </c>
       <c r="O77" t="n">
-        <v>169710.6025437991</v>
+        <v>-1146.040040985999</v>
       </c>
       <c r="P77" t="n">
-        <v>84855.30127189953</v>
+        <v>-1146.040040985999</v>
       </c>
     </row>
     <row r="78">
@@ -8965,19 +8965,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G78" t="n">
-        <v>-105084497.29</v>
+        <v>-35845139.96</v>
       </c>
       <c r="H78" t="n">
-        <v>9498456.09701325</v>
+        <v>2261537.165955536</v>
       </c>
       <c r="I78" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="J78" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K78" t="n">
-        <v>-63586041.19298677</v>
+        <v>416397.2059555352</v>
       </c>
       <c r="L78" t="n">
         <v>0.05625883751011833</v>
@@ -8989,10 +8989,10 @@
         <v>-0.01462200030522725</v>
       </c>
       <c r="O78" t="n">
-        <v>77479.59281100379</v>
+        <v>-507.3800060481344</v>
       </c>
       <c r="P78" t="n">
-        <v>38739.7964055019</v>
+        <v>-507.3800060481344</v>
       </c>
     </row>
     <row r="79">
@@ -9023,28 +9023,28 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>26344865.39000002</v>
+        <v>-36463708.53000001</v>
       </c>
       <c r="H79" t="n">
-        <v>9437731.866157647</v>
+        <v>4044566.584325174</v>
       </c>
       <c r="I79" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="J79" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K79" t="n">
-        <v>67782597.25615767</v>
+        <v>1580858.054325163</v>
       </c>
       <c r="L79" t="n">
-        <v>0.05612125523607059</v>
+        <v>0.05613367690325632</v>
       </c>
       <c r="M79" t="n">
-        <v>0.04261044181554507</v>
+        <v>0.0426227362277094</v>
       </c>
       <c r="N79" t="n">
-        <v>-0.01351081342052551</v>
+        <v>-0.01351094067554692</v>
       </c>
       <c r="O79" t="n">
         <v>-0</v>
@@ -9081,19 +9081,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G80" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="J80" t="n">
-        <v>-640000000</v>
+        <v>-680000000</v>
       </c>
       <c r="K80" t="n">
-        <v>-303055643.3100001</v>
+        <v>-655362070.4300001</v>
       </c>
       <c r="L80" t="n">
         <v>0.1050151041880321</v>
@@ -9105,10 +9105,10 @@
         <v>-0.06247613761654947</v>
       </c>
       <c r="O80" t="n">
-        <v>18881872.79998446</v>
+        <v>40832314.21345187</v>
       </c>
       <c r="P80" t="n">
-        <v>9440936.399992229</v>
+        <v>20416157.10672593</v>
       </c>
     </row>
     <row r="81">
@@ -9139,19 +9139,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G81" t="n">
-        <v>548709791.53</v>
+        <v>133911619.36</v>
       </c>
       <c r="H81" t="n">
-        <v>-484035602.7846395</v>
+        <v>-90269181.22613968</v>
       </c>
       <c r="I81" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="J81" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K81" t="n">
-        <v>128674188.7453604</v>
+        <v>111642438.1338603</v>
       </c>
       <c r="L81" t="n">
         <v>0.05822765833026367</v>
@@ -9163,10 +9163,10 @@
         <v>-0.01004192341464538</v>
       </c>
       <c r="O81" t="n">
-        <v>-1184458.31975399</v>
+        <v>-1027679.412434135</v>
       </c>
       <c r="P81" t="n">
-        <v>-1184458.31975399</v>
+        <v>-1027679.412434135</v>
       </c>
     </row>
     <row r="82">
@@ -9197,19 +9197,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G82" t="n">
-        <v>1990072267.9</v>
+        <v>2364336920.83</v>
       </c>
       <c r="H82" t="n">
-        <v>-446135269.4812486</v>
+        <v>-51490547.94520548</v>
       </c>
       <c r="I82" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="J82" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K82" t="n">
-        <v>1607936998.418751</v>
+        <v>2380846372.884794</v>
       </c>
       <c r="L82" t="n">
         <v>0.05839364669442126</v>
@@ -9221,10 +9221,10 @@
         <v>-0.01008473632087492</v>
       </c>
       <c r="O82" t="n">
-        <v>-13513017.20802682</v>
+        <v>-20008506.57587884</v>
       </c>
       <c r="P82" t="n">
-        <v>-13513017.20802682</v>
+        <v>-20008506.57587884</v>
       </c>
     </row>
     <row r="83">
@@ -9255,19 +9255,19 @@
         <v>0.75</v>
       </c>
       <c r="G83" t="n">
-        <v>321318332.1300001</v>
+        <v>-157998693</v>
       </c>
       <c r="H83" t="n">
-        <v>-496658630.361554</v>
+        <v>-92049904.10958904</v>
       </c>
       <c r="I83" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="J83" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K83" t="n">
-        <v>-111340298.2315539</v>
+        <v>-182048597.109589</v>
       </c>
       <c r="L83" t="n">
         <v>0.05851824187679444</v>
@@ -9279,10 +9279,10 @@
         <v>-0.01013182991584927</v>
       </c>
       <c r="O83" t="n">
-        <v>846060.7233465279</v>
+        <v>1383364.066749993</v>
       </c>
       <c r="P83" t="n">
-        <v>423030.3616732639</v>
+        <v>691682.0333749967</v>
       </c>
     </row>
     <row r="84">
@@ -9313,19 +9313,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G84" t="n">
-        <v>82481230.3</v>
+        <v>-194599255.21</v>
       </c>
       <c r="H84" t="n">
-        <v>-119458296.2048057</v>
+        <v>-51458493.15068493</v>
       </c>
       <c r="I84" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="J84" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K84" t="n">
-        <v>27022934.09519425</v>
+        <v>-178057748.3606849</v>
       </c>
       <c r="L84" t="n">
         <v>0.05821004393128892</v>
@@ -9337,10 +9337,10 @@
         <v>-0.01017508542911516</v>
       </c>
       <c r="O84" t="n">
-        <v>-183307.1086426336</v>
+        <v>1207835.200590573</v>
       </c>
       <c r="P84" t="n">
-        <v>-183307.1086426336</v>
+        <v>603917.6002952865</v>
       </c>
     </row>
     <row r="85">
@@ -9371,19 +9371,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G85" t="n">
-        <v>518697858.84</v>
+        <v>398501812.66</v>
       </c>
       <c r="H85" t="n">
-        <v>-119426252.4590164</v>
+        <v>-51445520.54794521</v>
       </c>
       <c r="I85" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="J85" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K85" t="n">
-        <v>463271606.3809837</v>
+        <v>415056292.1120548</v>
       </c>
       <c r="L85" t="n">
         <v>0.05808035784574397</v>
@@ -9395,10 +9395,10 @@
         <v>-0.01021994033044944</v>
       </c>
       <c r="O85" t="n">
-        <v>-2761854.76816965</v>
+        <v>-2474412.81451163</v>
       </c>
       <c r="P85" t="n">
-        <v>-2761854.76816965</v>
+        <v>-2474412.81451163</v>
       </c>
     </row>
     <row r="86">
@@ -9429,19 +9429,19 @@
         <v>0.5</v>
       </c>
       <c r="G86" t="n">
-        <v>669118580.01</v>
+        <v>772422393.1500001</v>
       </c>
       <c r="H86" t="n">
-        <v>-207983441.3653717</v>
+        <v>-90799555.08645856</v>
       </c>
       <c r="I86" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="J86" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K86" t="n">
-        <v>493135138.6446283</v>
+        <v>715622838.0635415</v>
       </c>
       <c r="L86" t="n">
         <v>0.0579990267461179</v>
@@ -9453,10 +9453,10 @@
         <v>-0.01026331977023442</v>
       </c>
       <c r="O86" t="n">
-        <v>-2530601.808924354</v>
+        <v>-3672333.010964407</v>
       </c>
       <c r="P86" t="n">
-        <v>-2530601.808924354</v>
+        <v>-3672333.010964407</v>
       </c>
     </row>
     <row r="87">
@@ -9487,19 +9487,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G87" t="n">
-        <v>-153952841.84</v>
+        <v>-35157733.02</v>
       </c>
       <c r="H87" t="n">
-        <v>61685111.16101505</v>
+        <v>2247136.761733663</v>
       </c>
       <c r="I87" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="J87" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K87" t="n">
-        <v>-60267730.67898495</v>
+        <v>1089403.741733659</v>
       </c>
       <c r="L87" t="n">
         <v>0.05738520780446178</v>
@@ -9511,10 +9511,10 @@
         <v>-0.01030407096516736</v>
       </c>
       <c r="O87" t="n">
-        <v>258751.2390941062</v>
+        <v>-4677.205610226033</v>
       </c>
       <c r="P87" t="n">
-        <v>129375.6195470531</v>
+        <v>-4677.205610226033</v>
       </c>
     </row>
     <row r="88">
@@ -9545,19 +9545,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G88" t="n">
-        <v>-105287618.79</v>
+        <v>-35284909.43000001</v>
       </c>
       <c r="H88" t="n">
-        <v>9506772.962048057</v>
+        <v>2266152.03233775</v>
       </c>
       <c r="I88" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="J88" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K88" t="n">
-        <v>-63780845.82795194</v>
+        <v>981242.6023377441</v>
       </c>
       <c r="L88" t="n">
         <v>0.05695407285841891</v>
@@ -9569,10 +9569,10 @@
         <v>-0.01034491853166675</v>
       </c>
       <c r="O88" t="n">
-        <v>219935.8846569866</v>
+        <v>-3383.624926994878</v>
       </c>
       <c r="P88" t="n">
-        <v>109967.9423284933</v>
+        <v>-3383.624926994878</v>
       </c>
     </row>
     <row r="89">
@@ -9603,19 +9603,19 @@
         <v>0.25</v>
       </c>
       <c r="G89" t="n">
-        <v>-8670744.480000019</v>
+        <v>-35779408.35</v>
       </c>
       <c r="H89" t="n">
-        <v>61673328.09342016</v>
+        <v>2248181.001571974</v>
       </c>
       <c r="I89" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="J89" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K89" t="n">
-        <v>85002583.61342014</v>
+        <v>468772.6515719742</v>
       </c>
       <c r="L89" t="n">
         <v>0.05664439372837885</v>
@@ -9627,10 +9627,10 @@
         <v>-0.01038544122264451</v>
       </c>
       <c r="O89" t="n">
-        <v>-220697.3339725251</v>
+        <v>-1217.102704920988</v>
       </c>
       <c r="P89" t="n">
-        <v>-220697.3339725251</v>
+        <v>-1217.102704920988</v>
       </c>
     </row>
     <row r="90">
@@ -9661,19 +9661,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>-105791543.79</v>
+        <v>-35814156.50999999</v>
       </c>
       <c r="H90" t="n">
-        <v>9444482.371434988</v>
+        <v>2248686.278913092</v>
       </c>
       <c r="I90" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="J90" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K90" t="n">
-        <v>-64347061.41856501</v>
+        <v>434529.7689131051</v>
       </c>
       <c r="L90" t="n">
         <v>0.05642057743315654</v>
@@ -9685,10 +9685,10 @@
         <v>-0.01042652380310684</v>
       </c>
       <c r="O90" t="n">
-        <v>111819.3612567743</v>
+        <v>-755.1058297885011</v>
       </c>
       <c r="P90" t="n">
-        <v>55909.68062838717</v>
+        <v>-755.1058297885011</v>
       </c>
     </row>
     <row r="91">
@@ -9719,19 +9719,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G91" t="n">
-        <v>-105084497.29</v>
+        <v>-35845139.96</v>
       </c>
       <c r="H91" t="n">
-        <v>9498456.09701325</v>
+        <v>2261537.165955536</v>
       </c>
       <c r="I91" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="J91" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K91" t="n">
-        <v>-63586041.19298677</v>
+        <v>416397.2059555352</v>
       </c>
       <c r="L91" t="n">
         <v>0.05625883751011833</v>
@@ -9743,10 +9743,10 @@
         <v>-0.01046759094930644</v>
       </c>
       <c r="O91" t="n">
-        <v>55466.05577449461</v>
+        <v>-363.2229686980544</v>
       </c>
       <c r="P91" t="n">
-        <v>27733.02788724731</v>
+        <v>-363.2229686980544</v>
       </c>
     </row>
     <row r="92">
@@ -9777,28 +9777,28 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>26344865.39000002</v>
+        <v>-36463708.53000001</v>
       </c>
       <c r="H92" t="n">
-        <v>9437731.866157647</v>
+        <v>4044566.584325174</v>
       </c>
       <c r="I92" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="J92" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="K92" t="n">
-        <v>67782597.25615767</v>
+        <v>1580858.054325163</v>
       </c>
       <c r="L92" t="n">
-        <v>0.05612125523607059</v>
+        <v>0.05613367690325632</v>
       </c>
       <c r="M92" t="n">
-        <v>0.04561268519858142</v>
+        <v>0.04562501529258145</v>
       </c>
       <c r="N92" t="n">
-        <v>-0.01050857003748917</v>
+        <v>-0.01050866161067487</v>
       </c>
       <c r="O92" t="n">
         <v>-0</v>
@@ -9880,22 +9880,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="D2" t="n">
-        <v>595604777.72</v>
+        <v>657013128.1</v>
       </c>
       <c r="E2" t="n">
-        <v>27261139.98000002</v>
+        <v>42626950.92000008</v>
       </c>
       <c r="F2" t="n">
-        <v>13630569.99000001</v>
+        <v>21313475.46000004</v>
       </c>
       <c r="G2" t="n">
-        <v>1.703821248750001</v>
+        <v>3.552245910000006</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8519106243750006</v>
+        <v>1.776122955000003</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -9913,22 +9913,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="D3" t="n">
-        <v>543419870.96</v>
+        <v>571846923.42</v>
       </c>
       <c r="E3" t="n">
-        <v>-24923766.77999997</v>
+        <v>-42539253.75999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-24923766.77999997</v>
+        <v>-42539253.75999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.557735423749998</v>
+        <v>-3.544937813333333</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.557735423749998</v>
+        <v>-3.544937813333333</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -9946,22 +9946,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="D4" t="n">
-        <v>577077882.63</v>
+        <v>647366157.4400001</v>
       </c>
       <c r="E4" t="n">
-        <v>8734244.889999986</v>
+        <v>32979980.26000011</v>
       </c>
       <c r="F4" t="n">
-        <v>4367122.444999993</v>
+        <v>16489990.13000005</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5458903056249991</v>
+        <v>2.748331688333343</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2729451528124995</v>
+        <v>1.374165844166671</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -9979,22 +9979,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="D5" t="n">
-        <v>564941749.88</v>
+        <v>584447213.12</v>
       </c>
       <c r="E5" t="n">
-        <v>-3401887.860000014</v>
+        <v>-29938964.05999994</v>
       </c>
       <c r="F5" t="n">
-        <v>-3401887.860000014</v>
+        <v>-29938964.05999994</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2126179912500009</v>
+        <v>-2.494913671666662</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2126179912500009</v>
+        <v>-2.494913671666662</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -10012,22 +10012,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="D6" t="n">
-        <v>575902873.34</v>
+        <v>604742509.74</v>
       </c>
       <c r="E6" t="n">
-        <v>7559235.600000024</v>
+        <v>-9643667.439999938</v>
       </c>
       <c r="F6" t="n">
-        <v>3779617.800000012</v>
+        <v>-9643667.439999938</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4724522250000014</v>
+        <v>-0.8036389533333281</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2362261125000007</v>
+        <v>-0.8036389533333281</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -10045,22 +10045,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="D7" t="n">
-        <v>563205377.86</v>
+        <v>623974966.02</v>
       </c>
       <c r="E7" t="n">
-        <v>-5138259.879999995</v>
+        <v>9588788.840000033</v>
       </c>
       <c r="F7" t="n">
-        <v>-5138259.879999995</v>
+        <v>4794394.420000017</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3211412424999997</v>
+        <v>0.7990657366666696</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3211412424999997</v>
+        <v>0.3995328683333348</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -10078,22 +10078,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="D8" t="n">
-        <v>559119349.5700001</v>
+        <v>597394594.91</v>
       </c>
       <c r="E8" t="n">
-        <v>-9224288.169999957</v>
+        <v>-16991582.26999998</v>
       </c>
       <c r="F8" t="n">
-        <v>-9224288.169999957</v>
+        <v>-16991582.26999998</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5765180106249973</v>
+        <v>-1.415965189166665</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5765180106249973</v>
+        <v>-1.415965189166665</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>

--- a/irrbb_calc/output/eba_sot_results.xlsx
+++ b/irrbb_calc/output/eba_sot_results.xlsx
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1657923918.46</v>
+        <v>-1323380873.66</v>
       </c>
       <c r="E2" t="n">
         <v>0.9975215395798449</v>
@@ -495,10 +495,10 @@
         <v>-0.001075339705425948</v>
       </c>
       <c r="H2" t="n">
-        <v>1782831.418095411</v>
+        <v>1423083.998847879</v>
       </c>
       <c r="I2" t="n">
-        <v>891415.7090477053</v>
+        <v>711541.9994239394</v>
       </c>
     </row>
     <row r="3">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-756411374.3</v>
+        <v>-563607788.72</v>
       </c>
       <c r="E3" t="n">
         <v>0.9903615297882993</v>
@@ -530,10 +530,10 @@
         <v>-0.004118598226101611</v>
       </c>
       <c r="H3" t="n">
-        <v>3115354.544395061</v>
+        <v>2321274.038839243</v>
       </c>
       <c r="I3" t="n">
-        <v>1557677.272197531</v>
+        <v>1160637.019419622</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-575289791.02</v>
+        <v>-639535554.92</v>
       </c>
       <c r="E4" t="n">
         <v>0.9786688180301472</v>
@@ -565,10 +565,10 @@
         <v>-0.009135282621367979</v>
       </c>
       <c r="H4" t="n">
-        <v>5255434.830155423</v>
+        <v>5842338.040607602</v>
       </c>
       <c r="I4" t="n">
-        <v>2627717.415077711</v>
+        <v>2921169.020303801</v>
       </c>
     </row>
     <row r="5">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>287271212.35</v>
+        <v>282089586.14</v>
       </c>
       <c r="E5" t="n">
         <v>0.9655145554862491</v>
@@ -600,10 +600,10 @@
         <v>-0.01497137919106994</v>
       </c>
       <c r="H5" t="n">
-        <v>-4300846.250770225</v>
+        <v>-4223270.159953929</v>
       </c>
       <c r="I5" t="n">
-        <v>-4300846.250770225</v>
+        <v>-4223270.159953929</v>
       </c>
     </row>
     <row r="6">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>338026454.7</v>
+        <v>319161024.12</v>
       </c>
       <c r="E6" t="n">
         <v>0.9530263468310431</v>
@@ -635,10 +635,10 @@
         <v>-0.02062335501537482</v>
       </c>
       <c r="H6" t="n">
-        <v>-6971239.579866615</v>
+        <v>-6582171.107497367</v>
       </c>
       <c r="I6" t="n">
-        <v>-6971239.579866615</v>
+        <v>-6582171.107497367</v>
       </c>
     </row>
     <row r="7">
@@ -658,22 +658,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>641813154.08</v>
+        <v>533754600.58</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9356051227617213</v>
+        <v>0.9378479178638877</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9068191590404275</v>
+        <v>0.9089929721392235</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.02878596372129372</v>
+        <v>-0.02885494572466418</v>
       </c>
       <c r="H7" t="n">
-        <v>-18475210.16919598</v>
+        <v>-15401460.03002571</v>
       </c>
       <c r="I7" t="n">
-        <v>-18475210.16919598</v>
+        <v>-15401460.03002571</v>
       </c>
     </row>
     <row r="8">
@@ -693,22 +693,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>514396150.85</v>
+        <v>725837405.03</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9110361496874445</v>
+        <v>0.914020029743317</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8720372866398278</v>
+        <v>0.874893456123076</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.03899886304761668</v>
+        <v>-0.03912657362024097</v>
       </c>
       <c r="H8" t="n">
-        <v>-20060865.03922032</v>
+        <v>-28399530.66423095</v>
       </c>
       <c r="I8" t="n">
-        <v>-20060865.03922032</v>
+        <v>-28399530.66423095</v>
       </c>
     </row>
     <row r="9">
@@ -728,22 +728,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1009792864.15</v>
+        <v>1456815524.71</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8754048758167313</v>
+        <v>0.8793551938327786</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8223662072656972</v>
+        <v>0.8260772215220972</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.05303866855103412</v>
+        <v>-0.05327797231068143</v>
       </c>
       <c r="H9" t="n">
-        <v>-53558069.02685127</v>
+        <v>-77616177.18727022</v>
       </c>
       <c r="I9" t="n">
-        <v>-53558069.02685127</v>
+        <v>-77616177.18727022</v>
       </c>
     </row>
     <row r="10">
@@ -763,22 +763,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>794321595.54</v>
+        <v>436647272.55</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8300899355387754</v>
+        <v>0.8350903091634028</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7605437457941407</v>
+        <v>0.7651251962107317</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.06954618974463467</v>
+        <v>-0.06996511295267105</v>
       </c>
       <c r="H10" t="n">
-        <v>-55242040.40168579</v>
+        <v>-30550075.74443649</v>
       </c>
       <c r="I10" t="n">
-        <v>-55242040.40168579</v>
+        <v>-30550075.74443649</v>
       </c>
     </row>
     <row r="11">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1623369977.36</v>
+        <v>857024694.1899999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7871638664957131</v>
+        <v>0.7929814256230181</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7034074629850886</v>
+        <v>0.7086060176961181</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.08375640351062452</v>
+        <v>-0.08437540792690001</v>
       </c>
       <c r="H11" t="n">
-        <v>-135967630.8707975</v>
+        <v>-72311808.17570798</v>
       </c>
       <c r="I11" t="n">
-        <v>-135967630.8707975</v>
+        <v>-72311808.17570798</v>
       </c>
     </row>
     <row r="12">
@@ -833,22 +833,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>99536703.16000001</v>
+        <v>98149543.74000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7465017756172543</v>
+        <v>0.7529410815413444</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6506017702139196</v>
+        <v>0.6562138446458032</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.09590000540333465</v>
+        <v>-0.09672723689554119</v>
       </c>
       <c r="H12" t="n">
-        <v>-9545570.370874118</v>
+        <v>-9493734.168528263</v>
       </c>
       <c r="I12" t="n">
-        <v>-9545570.370874118</v>
+        <v>-9493734.168528263</v>
       </c>
     </row>
     <row r="13">
@@ -868,22 +868,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>318521371.88</v>
+        <v>317275857.88</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7079831292590303</v>
+        <v>0.7148807043542068</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6017966661503515</v>
+        <v>0.6076597287586817</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1061864631086787</v>
+        <v>-0.1072209755955251</v>
       </c>
       <c r="H13" t="n">
-        <v>-33822657.90446136</v>
+        <v>-34018627.01480078</v>
       </c>
       <c r="I13" t="n">
-        <v>-33822657.90446136</v>
+        <v>-34018627.01480078</v>
       </c>
     </row>
     <row r="14">
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>306908451.75</v>
+        <v>305998789.65</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6714924005042728</v>
+        <v>0.6787119945050498</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5566864983829313</v>
+        <v>0.5626717641363838</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1148059021213416</v>
+        <v>-0.1160402303686661</v>
       </c>
       <c r="H14" t="n">
-        <v>-35234901.67182298</v>
+        <v>-35508170.04351898</v>
       </c>
       <c r="I14" t="n">
-        <v>-35234901.67182298</v>
+        <v>-35508170.04351898</v>
       </c>
     </row>
     <row r="15">
@@ -938,22 +938,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>223541651.31</v>
+        <v>213878647.01</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6369207605854804</v>
+        <v>0.6443492036977719</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5149885884815573</v>
+        <v>0.5209949352383458</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1219321721039232</v>
+        <v>-0.1233542684594261</v>
       </c>
       <c r="H15" t="n">
-        <v>-27256919.0999261</v>
+        <v>-26382844.04101037</v>
       </c>
       <c r="I15" t="n">
-        <v>-27256919.0999261</v>
+        <v>-26382844.04101037</v>
       </c>
     </row>
     <row r="16">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14469721.94</v>
+        <v>6012265.48</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6041641709026</v>
+        <v>0.6117079401756688</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4764417163072422</v>
+        <v>0.4823907164755455</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1277224545953578</v>
+        <v>-0.1293172237001232</v>
       </c>
       <c r="H16" t="n">
-        <v>-1848108.403489103</v>
+        <v>-777489.4800216887</v>
       </c>
       <c r="I16" t="n">
-        <v>-1848108.403489103</v>
+        <v>-777489.4800216887</v>
       </c>
     </row>
     <row r="17">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1657923918.46</v>
+        <v>-1323380873.66</v>
       </c>
       <c r="E17" t="n">
         <v>0.9975215395798449</v>
@@ -1020,10 +1020,10 @@
         <v>0.001071141156266053</v>
       </c>
       <c r="H17" t="n">
-        <v>-1775870.54302039</v>
+        <v>-1417527.719192552</v>
       </c>
       <c r="I17" t="n">
-        <v>-1775870.54302039</v>
+        <v>-1417527.719192552</v>
       </c>
     </row>
     <row r="18">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-756411374.3</v>
+        <v>-563607788.72</v>
       </c>
       <c r="E18" t="n">
         <v>0.9903615297882993</v>
@@ -1055,10 +1055,10 @@
         <v>0.004134433531466697</v>
       </c>
       <c r="H18" t="n">
-        <v>-3127332.549488726</v>
+        <v>-2330198.940279766</v>
       </c>
       <c r="I18" t="n">
-        <v>-3127332.549488726</v>
+        <v>-2330198.940279766</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-575289791.02</v>
+        <v>-639535554.92</v>
       </c>
       <c r="E19" t="n">
         <v>0.9786688180301472</v>
@@ -1090,10 +1090,10 @@
         <v>0.009214966721668216</v>
       </c>
       <c r="H19" t="n">
-        <v>-5301276.279564762</v>
+        <v>-5893298.855911415</v>
       </c>
       <c r="I19" t="n">
-        <v>-5301276.279564762</v>
+        <v>-5893298.855911415</v>
       </c>
     </row>
     <row r="20">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>287271212.35</v>
+        <v>282089586.14</v>
       </c>
       <c r="E20" t="n">
         <v>0.9655145554862491</v>
@@ -1125,10 +1125,10 @@
         <v>0.01520208972261294</v>
       </c>
       <c r="H20" t="n">
-        <v>4367122.744868496</v>
+        <v>4288351.198315033</v>
       </c>
       <c r="I20" t="n">
-        <v>2183561.372434248</v>
+        <v>2144175.599157516</v>
       </c>
     </row>
     <row r="21">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>338026454.7</v>
+        <v>319161024.12</v>
       </c>
       <c r="E21" t="n">
         <v>0.9530263468310431</v>
@@ -1160,10 +1160,10 @@
         <v>0.02107476671306407</v>
       </c>
       <c r="H21" t="n">
-        <v>7123828.675646621</v>
+        <v>6726244.127231617</v>
       </c>
       <c r="I21" t="n">
-        <v>3561914.33782331</v>
+        <v>3363122.063615808</v>
       </c>
     </row>
     <row r="22">
@@ -1183,22 +1183,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>641813154.08</v>
+        <v>533754600.58</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9356051227617213</v>
+        <v>0.9378479178638877</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9653039595636365</v>
+        <v>0.9676179779401868</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02969883680191521</v>
+        <v>0.02977006007629912</v>
       </c>
       <c r="H22" t="n">
-        <v>19061104.12034438</v>
+        <v>15889906.52526764</v>
       </c>
       <c r="I22" t="n">
-        <v>9530552.060172191</v>
+        <v>7944953.26263382</v>
       </c>
     </row>
     <row r="23">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>514396150.85</v>
+        <v>725837405.03</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9110361496874445</v>
+        <v>0.914020029743317</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9517783430676411</v>
+        <v>0.9548956940906148</v>
       </c>
       <c r="G23" t="n">
-        <v>0.04074219338019658</v>
+        <v>0.04087566434729784</v>
       </c>
       <c r="H23" t="n">
-        <v>20957627.45195947</v>
+        <v>29669086.13871995</v>
       </c>
       <c r="I23" t="n">
-        <v>10478813.72597974</v>
+        <v>14834543.06935997</v>
       </c>
     </row>
     <row r="24">
@@ -1253,22 +1253,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1009792864.15</v>
+        <v>1456815524.71</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8754048758167313</v>
+        <v>0.8793551938327786</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9318629925800875</v>
+        <v>0.936068121791669</v>
       </c>
       <c r="G24" t="n">
-        <v>0.05645811676335621</v>
+        <v>0.05671292795889038</v>
       </c>
       <c r="H24" t="n">
-        <v>57011003.4309846</v>
+        <v>82620273.90227132</v>
       </c>
       <c r="I24" t="n">
-        <v>28505501.7154923</v>
+        <v>41310136.95113566</v>
       </c>
     </row>
     <row r="25">
@@ -1288,22 +1288,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>794321595.54</v>
+        <v>436647272.55</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8300899355387754</v>
+        <v>0.8350903091634028</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9059948464314536</v>
+        <v>0.9114524892145283</v>
       </c>
       <c r="G25" t="n">
-        <v>0.07590491089267815</v>
+        <v>0.07636218005112549</v>
       </c>
       <c r="H25" t="n">
-        <v>60292909.92959363</v>
+        <v>33343337.64529597</v>
       </c>
       <c r="I25" t="n">
-        <v>30146454.96479682</v>
+        <v>16671668.82264798</v>
       </c>
     </row>
     <row r="26">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1623369977.36</v>
+        <v>857024694.1899999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7871638664957131</v>
+        <v>0.7929814256230181</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8808931377261134</v>
+        <v>0.8874034155732852</v>
       </c>
       <c r="G26" t="n">
-        <v>0.09372927123040031</v>
+        <v>0.09442198995026707</v>
       </c>
       <c r="H26" t="n">
-        <v>152157284.9152642</v>
+        <v>80921977.06193888</v>
       </c>
       <c r="I26" t="n">
-        <v>76078642.45763212</v>
+        <v>40460988.53096944</v>
       </c>
     </row>
     <row r="27">
@@ -1358,22 +1358,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>99536703.16000001</v>
+        <v>98149543.74000001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7465017756172543</v>
+        <v>0.7529410815413444</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8565371814873228</v>
+        <v>0.8639256557819821</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1100354058700685</v>
+        <v>0.1109845742406377</v>
       </c>
       <c r="H27" t="n">
-        <v>10952561.53117914</v>
+        <v>10893085.32389675</v>
       </c>
       <c r="I27" t="n">
-        <v>5476280.765589568</v>
+        <v>5446542.661948374</v>
       </c>
     </row>
     <row r="28">
@@ -1393,22 +1393,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>318521371.88</v>
+        <v>317275857.88</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7079831292590303</v>
+        <v>0.7148807043542068</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8329050219133051</v>
+        <v>0.8410196849995127</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1249218926542748</v>
+        <v>0.1261389806453059</v>
       </c>
       <c r="H28" t="n">
-        <v>39790292.6260857</v>
+        <v>40020853.29634815</v>
       </c>
       <c r="I28" t="n">
-        <v>19895146.31304285</v>
+        <v>20010426.64817408</v>
       </c>
     </row>
     <row r="29">
@@ -1428,22 +1428,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>306908451.75</v>
+        <v>305998789.65</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6714924005042728</v>
+        <v>0.6787119945050498</v>
       </c>
       <c r="F29" t="n">
-        <v>0.809974080489948</v>
+        <v>0.8186825770896045</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1384816799856752</v>
+        <v>0.1399705825845546</v>
       </c>
       <c r="H29" t="n">
-        <v>42501198.00014253</v>
+        <v>42830828.85747909</v>
       </c>
       <c r="I29" t="n">
-        <v>21250599.00007126</v>
+        <v>21415414.42873954</v>
       </c>
     </row>
     <row r="30">
@@ -1463,22 +1463,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>223541651.31</v>
+        <v>213878647.01</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6369207605854804</v>
+        <v>0.6443492036977719</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7877216066542996</v>
+        <v>0.796908862114506</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1508008460688192</v>
+        <v>0.152559658416734</v>
       </c>
       <c r="H30" t="n">
-        <v>33710270.14916896</v>
+        <v>32629253.33047883</v>
       </c>
       <c r="I30" t="n">
-        <v>16855135.07458448</v>
+        <v>16314626.66523941</v>
       </c>
     </row>
     <row r="31">
@@ -1498,22 +1498,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14469721.94</v>
+        <v>6012265.48</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6041641709026</v>
+        <v>0.6117079401756688</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7661250410260293</v>
+        <v>0.775691111553262</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1619608701234293</v>
+        <v>0.1639831713775932</v>
       </c>
       <c r="H31" t="n">
-        <v>2343528.755846475</v>
+        <v>985910.3605744279</v>
       </c>
       <c r="I31" t="n">
-        <v>1171764.377923238</v>
+        <v>492955.1802872139</v>
       </c>
     </row>
     <row r="32">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-1657923918.46</v>
+        <v>-1323380873.66</v>
       </c>
       <c r="E32" t="n">
         <v>0.9975215395798449</v>
@@ -1545,10 +1545,10 @@
         <v>0.0008556326727643393</v>
       </c>
       <c r="H32" t="n">
-        <v>-1418573.873591856</v>
+        <v>-1132327.914014912</v>
       </c>
       <c r="I32" t="n">
-        <v>-1418573.873591856</v>
+        <v>-1132327.914014912</v>
       </c>
     </row>
     <row r="33">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-756411374.3</v>
+        <v>-563607788.72</v>
       </c>
       <c r="E33" t="n">
         <v>0.9903615297882993</v>
@@ -1580,10 +1580,10 @@
         <v>0.002828930695566667</v>
       </c>
       <c r="H33" t="n">
-        <v>-2139835.355233037</v>
+        <v>-1594407.373770461</v>
       </c>
       <c r="I33" t="n">
-        <v>-2139835.355233037</v>
+        <v>-1594407.373770461</v>
       </c>
     </row>
     <row r="34">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-575289791.02</v>
+        <v>-639535554.92</v>
       </c>
       <c r="E34" t="n">
         <v>0.9786688180301472</v>
@@ -1615,10 +1615,10 @@
         <v>0.004154192302518012</v>
       </c>
       <c r="H34" t="n">
-        <v>-2389864.421572479</v>
+        <v>-2656753.679435249</v>
       </c>
       <c r="I34" t="n">
-        <v>-2389864.421572479</v>
+        <v>-2656753.679435249</v>
       </c>
     </row>
     <row r="35">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>287271212.35</v>
+        <v>282089586.14</v>
       </c>
       <c r="E35" t="n">
         <v>0.9655145554862491</v>
@@ -1650,10 +1650,10 @@
         <v>0.003541509817362121</v>
       </c>
       <c r="H35" t="n">
-        <v>1017373.818783044</v>
+        <v>999023.0386904276</v>
       </c>
       <c r="I35" t="n">
-        <v>508686.9093915218</v>
+        <v>499511.5193452138</v>
       </c>
     </row>
     <row r="36">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>338026454.7</v>
+        <v>319161024.12</v>
       </c>
       <c r="E36" t="n">
         <v>0.9530263468310431</v>
@@ -1685,10 +1685,10 @@
         <v>0.001327621072548912</v>
       </c>
       <c r="H36" t="n">
-        <v>448771.0443387203</v>
+        <v>423724.9011580037</v>
       </c>
       <c r="I36" t="n">
-        <v>224385.5221693602</v>
+        <v>211862.4505790019</v>
       </c>
     </row>
     <row r="37">
@@ -1708,22 +1708,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>641813154.08</v>
+        <v>533754600.58</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9356051227617213</v>
+        <v>0.9378479178638877</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9319685438064244</v>
+        <v>0.9342026515219396</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.003636578955296899</v>
+        <v>-0.003645266341948061</v>
       </c>
       <c r="H37" t="n">
-        <v>-2334004.209360054</v>
+        <v>-1945677.680354205</v>
       </c>
       <c r="I37" t="n">
-        <v>-2334004.209360054</v>
+        <v>-1945677.680354205</v>
       </c>
     </row>
     <row r="38">
@@ -1743,22 +1743,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>514396150.85</v>
+        <v>725837405.03</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9110361496874445</v>
+        <v>0.914020029743317</v>
       </c>
       <c r="F38" t="n">
-        <v>0.89962748577012</v>
+        <v>0.9025740198456692</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.01140866391732454</v>
+        <v>-0.01144600989764777</v>
       </c>
       <c r="H38" t="n">
-        <v>-5868572.805413024</v>
+        <v>-8307942.122056352</v>
       </c>
       <c r="I38" t="n">
-        <v>-5868572.805413024</v>
+        <v>-8307942.122056352</v>
       </c>
     </row>
     <row r="39">
@@ -1778,22 +1778,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1009792864.15</v>
+        <v>1456815524.71</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8754048758167313</v>
+        <v>0.8793551938327786</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8526721506842372</v>
+        <v>0.8565199208718595</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.02273272513249414</v>
+        <v>-0.02283527296091914</v>
       </c>
       <c r="H39" t="n">
-        <v>-22955343.62147594</v>
+        <v>-33266780.16045749</v>
       </c>
       <c r="I39" t="n">
-        <v>-22955343.62147594</v>
+        <v>-33266780.16045749</v>
       </c>
     </row>
     <row r="40">
@@ -1813,22 +1813,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>794321595.54</v>
+        <v>436647272.55</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8300899355387754</v>
+        <v>0.8350903091634028</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7948195996680136</v>
+        <v>0.7996075232713666</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.03527033587076178</v>
+        <v>-0.03548278589203613</v>
       </c>
       <c r="H40" t="n">
-        <v>-28015989.46409519</v>
+        <v>-15493461.68223319</v>
       </c>
       <c r="I40" t="n">
-        <v>-28015989.46409519</v>
+        <v>-15493461.68223319</v>
       </c>
     </row>
     <row r="41">
@@ -1848,22 +1848,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1623369977.36</v>
+        <v>857024694.1899999</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7871638664957131</v>
+        <v>0.7929814256230181</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7421107790921055</v>
+        <v>0.7475953682933623</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.04505308740360758</v>
+        <v>-0.04538605732965584</v>
       </c>
       <c r="H41" t="n">
-        <v>-73137829.47839254</v>
+        <v>-38896971.9034381</v>
       </c>
       <c r="I41" t="n">
-        <v>-73137829.47839254</v>
+        <v>-38896971.9034381</v>
       </c>
     </row>
     <row r="42">
@@ -1883,22 +1883,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>99536703.16000001</v>
+        <v>98149543.74000001</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7465017756172543</v>
+        <v>0.7529410815413444</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6936465830305695</v>
+        <v>0.699629964006139</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.05285519258668481</v>
+        <v>-0.05331111753520545</v>
       </c>
       <c r="H42" t="n">
-        <v>-5261031.614965479</v>
+        <v>-5232461.862349929</v>
       </c>
       <c r="I42" t="n">
-        <v>-5261031.614965479</v>
+        <v>-5232461.862349929</v>
       </c>
     </row>
     <row r="43">
@@ -1918,22 +1918,22 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>318521371.88</v>
+        <v>317275857.88</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7079831292590303</v>
+        <v>0.7148807043542068</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6487347495892629</v>
+        <v>0.655055106394129</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.05924837966976737</v>
+        <v>-0.0598255979600778</v>
       </c>
       <c r="H43" t="n">
-        <v>-18871875.1740814</v>
+        <v>-18981217.91596766</v>
       </c>
       <c r="I43" t="n">
-        <v>-18871875.1740814</v>
+        <v>-18981217.91596766</v>
       </c>
     </row>
     <row r="44">
@@ -1953,22 +1953,22 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>306908451.75</v>
+        <v>305998789.65</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6714924005042728</v>
+        <v>0.6787119945050498</v>
       </c>
       <c r="F44" t="n">
-        <v>0.6069234306001043</v>
+        <v>0.6134488178814577</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.06456896990416849</v>
+        <v>-0.06526317662359216</v>
       </c>
       <c r="H44" t="n">
-        <v>-19816762.5843807</v>
+        <v>-19970453.05553337</v>
       </c>
       <c r="I44" t="n">
-        <v>-19816762.5843807</v>
+        <v>-19970453.05553337</v>
       </c>
     </row>
     <row r="45">
@@ -1988,22 +1988,22 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>223541651.31</v>
+        <v>213878647.01</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6369207605854804</v>
+        <v>0.6443492036977719</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5679068720802271</v>
+        <v>0.5745304054163424</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.06901388850525336</v>
+        <v>-0.06981879828142956</v>
       </c>
       <c r="H45" t="n">
-        <v>-15427478.59978857</v>
+        <v>-14932750.11229627</v>
       </c>
       <c r="I45" t="n">
-        <v>-15427478.59978857</v>
+        <v>-14932750.11229627</v>
       </c>
     </row>
     <row r="46">
@@ -2023,22 +2023,22 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>14469721.94</v>
+        <v>6012265.48</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6041641709026</v>
+        <v>0.6117079401756688</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5314564130474985</v>
+        <v>0.538092340316341</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.07270775785510153</v>
+        <v>-0.07361559985932775</v>
       </c>
       <c r="H46" t="n">
-        <v>-1052061.03904417</v>
+        <v>-442596.5298237291</v>
       </c>
       <c r="I46" t="n">
-        <v>-1052061.03904417</v>
+        <v>-442596.5298237291</v>
       </c>
     </row>
     <row r="47">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-1657923918.46</v>
+        <v>-1323380873.66</v>
       </c>
       <c r="E47" t="n">
         <v>0.9975215395798449</v>
@@ -2070,10 +2070,10 @@
         <v>-0.001075593329743385</v>
       </c>
       <c r="H47" t="n">
-        <v>1783251.907917592</v>
+        <v>1423419.640418669</v>
       </c>
       <c r="I47" t="n">
-        <v>891625.953958796</v>
+        <v>711709.8202093347</v>
       </c>
     </row>
     <row r="48">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-756411374.3</v>
+        <v>-563607788.72</v>
       </c>
       <c r="E48" t="n">
         <v>0.9903615297882993</v>
@@ -2105,10 +2105,10 @@
         <v>-0.003609302003152015</v>
       </c>
       <c r="H48" t="n">
-        <v>2730117.088467958</v>
+        <v>2034230.720819174</v>
       </c>
       <c r="I48" t="n">
-        <v>1365058.544233979</v>
+        <v>1017115.360409587</v>
       </c>
     </row>
     <row r="49">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-575289791.02</v>
+        <v>-639535554.92</v>
       </c>
       <c r="E49" t="n">
         <v>0.9786688180301472</v>
@@ -2140,10 +2140,10 @@
         <v>-0.005714096573316341</v>
       </c>
       <c r="H49" t="n">
-        <v>3287261.423531256</v>
+        <v>3654367.922882336</v>
       </c>
       <c r="I49" t="n">
-        <v>1643630.711765628</v>
+        <v>1827183.961441168</v>
       </c>
     </row>
     <row r="50">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>287271212.35</v>
+        <v>282089586.14</v>
       </c>
       <c r="E50" t="n">
         <v>0.9655145554862491</v>
@@ -2175,10 +2175,10 @@
         <v>-0.005846989353867849</v>
       </c>
       <c r="H50" t="n">
-        <v>-1679671.72028316</v>
+        <v>-1649374.806997567</v>
       </c>
       <c r="I50" t="n">
-        <v>-1679671.72028316</v>
+        <v>-1649374.806997567</v>
       </c>
     </row>
     <row r="51">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>338026454.7</v>
+        <v>319161024.12</v>
       </c>
       <c r="E51" t="n">
         <v>0.9530263468310431</v>
@@ -2210,10 +2210,10 @@
         <v>-0.004239805017471676</v>
       </c>
       <c r="H51" t="n">
-        <v>-1433166.258675222</v>
+        <v>-1353180.511445375</v>
       </c>
       <c r="I51" t="n">
-        <v>-1433166.258675222</v>
+        <v>-1353180.511445375</v>
       </c>
     </row>
     <row r="52">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>641813154.08</v>
+        <v>533754600.58</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9356051227617213</v>
+        <v>0.9378479178638877</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9356114068714596</v>
+        <v>0.9378542448959014</v>
       </c>
       <c r="G52" t="n">
-        <v>6.284109738352583e-06</v>
+        <v>6.327032013753175e-06</v>
       </c>
       <c r="H52" t="n">
-        <v>4033.224291756916</v>
+        <v>3377.082445357699</v>
       </c>
       <c r="I52" t="n">
-        <v>2016.612145878458</v>
+        <v>1688.54122267885</v>
       </c>
     </row>
     <row r="53">
@@ -2268,22 +2268,22 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>514396150.85</v>
+        <v>725837405.03</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9110361496874445</v>
+        <v>0.914020029743317</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9181252264484042</v>
+        <v>0.9211323475322419</v>
       </c>
       <c r="G53" t="n">
-        <v>0.007089076760959712</v>
+        <v>0.00711231778892496</v>
       </c>
       <c r="H53" t="n">
-        <v>3646593.798917861</v>
+        <v>5162386.287662</v>
       </c>
       <c r="I53" t="n">
-        <v>1823296.899458931</v>
+        <v>2581193.143831</v>
       </c>
     </row>
     <row r="54">
@@ -2303,22 +2303,22 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1009792864.15</v>
+        <v>1456815524.71</v>
       </c>
       <c r="E54" t="n">
-        <v>0.8754048758167313</v>
+        <v>0.8793551938327786</v>
       </c>
       <c r="F54" t="n">
-        <v>0.89315112566766</v>
+        <v>0.8971815662398448</v>
       </c>
       <c r="G54" t="n">
-        <v>0.01774624985092865</v>
+        <v>0.01782637240706619</v>
       </c>
       <c r="H54" t="n">
-        <v>17920036.46489076</v>
+        <v>25969736.071876</v>
       </c>
       <c r="I54" t="n">
-        <v>8960018.232445378</v>
+        <v>12984868.035938</v>
       </c>
     </row>
     <row r="55">
@@ -2338,22 +2338,22 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>794321595.54</v>
+        <v>436647272.55</v>
       </c>
       <c r="E55" t="n">
-        <v>0.8300899355387754</v>
+        <v>0.8350903091634028</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8598517504102717</v>
+        <v>0.8650314228040723</v>
       </c>
       <c r="G55" t="n">
-        <v>0.02976181487149632</v>
+        <v>0.02994111364066954</v>
       </c>
       <c r="H55" t="n">
-        <v>23640452.27489305</v>
+        <v>13073705.60830795</v>
       </c>
       <c r="I55" t="n">
-        <v>11820226.13744653</v>
+        <v>6536852.804153977</v>
       </c>
     </row>
     <row r="56">
@@ -2373,22 +2373,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1623369977.36</v>
+        <v>857024694.1899999</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7871638664957131</v>
+        <v>0.7929814256230181</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8264167206253257</v>
+        <v>0.8325243862731679</v>
       </c>
       <c r="G56" t="n">
-        <v>0.03925285412961255</v>
+        <v>0.03954296065014984</v>
       </c>
       <c r="H56" t="n">
-        <v>63721904.9197045</v>
+        <v>33889293.75856186</v>
       </c>
       <c r="I56" t="n">
-        <v>31860952.45985225</v>
+        <v>16944646.87928093</v>
       </c>
     </row>
     <row r="57">
@@ -2408,22 +2408,22 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>99536703.16000001</v>
+        <v>98149543.74000001</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7465017756172543</v>
+        <v>0.7529410815413444</v>
       </c>
       <c r="F57" t="n">
-        <v>0.793449937984499</v>
+        <v>0.800294227812458</v>
       </c>
       <c r="G57" t="n">
-        <v>0.04694816236724475</v>
+        <v>0.04735314627111353</v>
       </c>
       <c r="H57" t="n">
-        <v>4673065.301455924</v>
+        <v>4647689.701163276</v>
       </c>
       <c r="I57" t="n">
-        <v>2336532.650727962</v>
+        <v>2323844.850581638</v>
       </c>
     </row>
     <row r="58">
@@ -2443,22 +2443,22 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>318521371.88</v>
+        <v>317275857.88</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7079831292590303</v>
+        <v>0.7148807043542068</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7614016420153711</v>
+        <v>0.7688196693783695</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0534185127563408</v>
+        <v>0.05393896502416273</v>
       </c>
       <c r="H58" t="n">
-        <v>17014937.96693895</v>
+        <v>17113531.40120054</v>
       </c>
       <c r="I58" t="n">
-        <v>8507468.983469475</v>
+        <v>8556765.700600272</v>
       </c>
     </row>
     <row r="59">
@@ -2478,22 +2478,22 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>306908451.75</v>
+        <v>305998789.65</v>
       </c>
       <c r="E59" t="n">
-        <v>0.6714924005042728</v>
+        <v>0.6787119945050498</v>
       </c>
       <c r="F59" t="n">
-        <v>0.7304891729838603</v>
+        <v>0.7383430913025396</v>
       </c>
       <c r="G59" t="n">
-        <v>0.05899677247958746</v>
+        <v>0.05963109679748979</v>
       </c>
       <c r="H59" t="n">
-        <v>18106608.09995719</v>
+        <v>18247043.44553386</v>
       </c>
       <c r="I59" t="n">
-        <v>9053304.049978597</v>
+        <v>9123521.722766932</v>
       </c>
     </row>
     <row r="60">
@@ -2513,22 +2513,22 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>223541651.31</v>
+        <v>213878647.01</v>
       </c>
       <c r="E60" t="n">
-        <v>0.6369207605854804</v>
+        <v>0.6443492036977719</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7007854946334655</v>
+        <v>0.7089588137102256</v>
       </c>
       <c r="G60" t="n">
-        <v>0.06386473404798509</v>
+        <v>0.06460961001245369</v>
       </c>
       <c r="H60" t="n">
-        <v>14276428.10956057</v>
+        <v>13818615.97330734</v>
       </c>
       <c r="I60" t="n">
-        <v>7138214.054780285</v>
+        <v>6909307.986653672</v>
       </c>
     </row>
     <row r="61">
@@ -2548,22 +2548,22 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14469721.94</v>
+        <v>6012265.48</v>
       </c>
       <c r="E61" t="n">
-        <v>0.6041641709026</v>
+        <v>0.6117079401756688</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6722918087178391</v>
+        <v>0.6806862497127172</v>
       </c>
       <c r="G61" t="n">
-        <v>0.06812763781523912</v>
+        <v>0.06897830953704842</v>
       </c>
       <c r="H61" t="n">
-        <v>985787.9756155391</v>
+        <v>414715.909298351</v>
       </c>
       <c r="I61" t="n">
-        <v>492893.9878077696</v>
+        <v>207357.9546491755</v>
       </c>
     </row>
     <row r="62">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-1657923918.46</v>
+        <v>-1323380873.66</v>
       </c>
       <c r="E62" t="n">
         <v>0.9975215395798449</v>
@@ -2595,10 +2595,10 @@
         <v>-0.00138963539714354</v>
       </c>
       <c r="H62" t="n">
-        <v>2303909.762862937</v>
+        <v>1839016.90594068</v>
       </c>
       <c r="I62" t="n">
-        <v>1151954.881431469</v>
+        <v>919508.4529703399</v>
       </c>
     </row>
     <row r="63">
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-756411374.3</v>
+        <v>-563607788.72</v>
       </c>
       <c r="E63" t="n">
         <v>0.9903615297882993</v>
@@ -2630,10 +2630,10 @@
         <v>-0.004868292240044036</v>
       </c>
       <c r="H63" t="n">
-        <v>3682431.623785735</v>
+        <v>2743807.424253955</v>
       </c>
       <c r="I63" t="n">
-        <v>1841215.811892868</v>
+        <v>1371903.712126978</v>
       </c>
     </row>
     <row r="64">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-575289791.02</v>
+        <v>-639535554.92</v>
       </c>
       <c r="E64" t="n">
         <v>0.9786688180301472</v>
@@ -2665,10 +2665,10 @@
         <v>-0.008752967619160001</v>
       </c>
       <c r="H64" t="n">
-        <v>5035492.912431384</v>
+        <v>5597834.003516282</v>
       </c>
       <c r="I64" t="n">
-        <v>2517746.456215692</v>
+        <v>2798917.001758141</v>
       </c>
     </row>
     <row r="65">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>287271212.35</v>
+        <v>282089586.14</v>
       </c>
       <c r="E65" t="n">
         <v>0.9655145554862491</v>
@@ -2700,10 +2700,10 @@
         <v>-0.01121800353180191</v>
       </c>
       <c r="H65" t="n">
-        <v>-3222609.474727317</v>
+        <v>-3164481.97360306</v>
       </c>
       <c r="I65" t="n">
-        <v>-3222609.474727317</v>
+        <v>-3164481.97360306</v>
       </c>
     </row>
     <row r="66">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>338026454.7</v>
+        <v>319161024.12</v>
       </c>
       <c r="E66" t="n">
         <v>0.9530263468310431</v>
@@ -2735,10 +2735,10 @@
         <v>-0.0120777624290116</v>
       </c>
       <c r="H66" t="n">
-        <v>-4082603.21458765</v>
+        <v>-3854751.0259214</v>
       </c>
       <c r="I66" t="n">
-        <v>-4082603.21458765</v>
+        <v>-3854751.0259214</v>
       </c>
     </row>
     <row r="67">
@@ -2758,22 +2758,22 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>641813154.08</v>
+        <v>533754600.58</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9356051227617213</v>
+        <v>0.9378479178638877</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9239515538524983</v>
+        <v>0.9261664375823063</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.01165356890922298</v>
+        <v>-0.01168148028158134</v>
       </c>
       <c r="H67" t="n">
-        <v>-7479413.817917025</v>
+        <v>-6235043.841878591</v>
       </c>
       <c r="I67" t="n">
-        <v>-7479413.817917025</v>
+        <v>-6235043.841878591</v>
       </c>
     </row>
     <row r="68">
@@ -2793,22 +2793,22 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>514396150.85</v>
+        <v>725837405.03</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9110361496874445</v>
+        <v>0.914020029743317</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9013906216994021</v>
+        <v>0.904342933514297</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.009645527988042413</v>
+        <v>-0.009677096229020021</v>
       </c>
       <c r="H68" t="n">
-        <v>-4961622.469964962</v>
+        <v>-7023998.415097491</v>
       </c>
       <c r="I68" t="n">
-        <v>-4961622.469964962</v>
+        <v>-7023998.415097491</v>
       </c>
     </row>
     <row r="69">
@@ -2828,22 +2828,22 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1009792864.15</v>
+        <v>1456815524.71</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8754048758167313</v>
+        <v>0.8793551938327786</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8691389452542764</v>
+        <v>0.8730610207674812</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.006265930562454947</v>
+        <v>-0.006294173065297448</v>
       </c>
       <c r="H69" t="n">
-        <v>-6327291.969226401</v>
+        <v>-9169449.036736852</v>
       </c>
       <c r="I69" t="n">
-        <v>-6327291.969226401</v>
+        <v>-9169449.036736852</v>
       </c>
     </row>
     <row r="70">
@@ -2863,22 +2863,22 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>794321595.54</v>
+        <v>436647272.55</v>
       </c>
       <c r="E70" t="n">
-        <v>0.8300899355387754</v>
+        <v>0.8350903091634028</v>
       </c>
       <c r="F70" t="n">
-        <v>0.827024401236104</v>
+        <v>0.8320063292318809</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.003065534302671424</v>
+        <v>-0.003083979931521874</v>
       </c>
       <c r="H70" t="n">
-        <v>-2435020.098480567</v>
+        <v>-1346611.425697962</v>
       </c>
       <c r="I70" t="n">
-        <v>-2435020.098480567</v>
+        <v>-1346611.425697962</v>
       </c>
     </row>
     <row r="71">
@@ -2898,22 +2898,22 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1623369977.36</v>
+        <v>857024694.1899999</v>
       </c>
       <c r="E71" t="n">
-        <v>0.7871638664957131</v>
+        <v>0.7929814256230181</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7857876654511835</v>
+        <v>0.7915950611515638</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.001376201044529624</v>
+        <v>-0.001386364471454349</v>
       </c>
       <c r="H71" t="n">
-        <v>-2234083.458500863</v>
+        <v>-1188148.587184044</v>
       </c>
       <c r="I71" t="n">
-        <v>-2234083.458500863</v>
+        <v>-1188148.587184044</v>
       </c>
     </row>
     <row r="72">
@@ -2933,22 +2933,22 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>99536703.16000001</v>
+        <v>98149543.74000001</v>
       </c>
       <c r="E72" t="n">
-        <v>0.7465017756172543</v>
+        <v>0.7529410815413444</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7459144932458476</v>
+        <v>0.7523487456045337</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.0005872823714067055</v>
+        <v>-0.0005923359368107395</v>
       </c>
       <c r="H72" t="n">
-        <v>-58456.15107381012</v>
+        <v>-58137.50193877955</v>
       </c>
       <c r="I72" t="n">
-        <v>-58456.15107381012</v>
+        <v>-58137.50193877955</v>
       </c>
     </row>
     <row r="73">
@@ -2968,22 +2968,22 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>318521371.88</v>
+        <v>317275857.88</v>
       </c>
       <c r="E73" t="n">
-        <v>0.7079831292590303</v>
+        <v>0.7148807043542068</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7077405266571837</v>
+        <v>0.7146357572841225</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.0002426026018466088</v>
+        <v>-0.0002449470700842671</v>
       </c>
       <c r="H73" t="n">
-        <v>-77274.11356183924</v>
+        <v>-77715.79179617832</v>
       </c>
       <c r="I73" t="n">
-        <v>-77274.11356183924</v>
+        <v>-77715.79179617832</v>
       </c>
     </row>
     <row r="74">
@@ -3003,22 +3003,22 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>306908451.75</v>
+        <v>305998789.65</v>
       </c>
       <c r="E74" t="n">
-        <v>0.6714924005042728</v>
+        <v>0.6787119945050498</v>
       </c>
       <c r="F74" t="n">
-        <v>0.6713945995447047</v>
+        <v>0.6786131588002061</v>
       </c>
       <c r="G74" t="n">
-        <v>-9.78009595681284e-05</v>
+        <v>-9.883570484370274e-05</v>
       </c>
       <c r="H74" t="n">
-        <v>-30015.94108071864</v>
+        <v>-30243.60605637768</v>
       </c>
       <c r="I74" t="n">
-        <v>-30015.94108071864</v>
+        <v>-30243.60605637768</v>
       </c>
     </row>
     <row r="75">
@@ -3038,22 +3038,22 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>223541651.31</v>
+        <v>213878647.01</v>
       </c>
       <c r="E75" t="n">
-        <v>0.6369207605854804</v>
+        <v>0.6443492036977719</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6368818785963716</v>
+        <v>0.6443098785224229</v>
       </c>
       <c r="G75" t="n">
-        <v>-3.8881989108841e-05</v>
+        <v>-3.932517534899205e-05</v>
       </c>
       <c r="H75" t="n">
-        <v>-8691.744051607751</v>
+        <v>-8410.815297073423</v>
       </c>
       <c r="I75" t="n">
-        <v>-8691.744051607751</v>
+        <v>-8410.815297073423</v>
       </c>
     </row>
     <row r="76">
@@ -3073,22 +3073,22 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>14469721.94</v>
+        <v>6012265.48</v>
       </c>
       <c r="E76" t="n">
-        <v>0.6041641709026</v>
+        <v>0.6117079401756688</v>
       </c>
       <c r="F76" t="n">
-        <v>0.6041487887577485</v>
+        <v>0.6116923728724937</v>
       </c>
       <c r="G76" t="n">
-        <v>-1.538214485152789e-05</v>
+        <v>-1.556730317509025e-05</v>
       </c>
       <c r="H76" t="n">
-        <v>-222.5753588424111</v>
+        <v>-93.59475949628953</v>
       </c>
       <c r="I76" t="n">
-        <v>-222.5753588424111</v>
+        <v>-93.59475949628953</v>
       </c>
     </row>
     <row r="77">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-1657923918.46</v>
+        <v>-1323380873.66</v>
       </c>
       <c r="E77" t="n">
         <v>0.9975215395798449</v>
@@ -3120,10 +3120,10 @@
         <v>0.001386210407362531</v>
       </c>
       <c r="H77" t="n">
-        <v>-2298231.390384521</v>
+        <v>-1834484.339972012</v>
       </c>
       <c r="I77" t="n">
-        <v>-2298231.390384521</v>
+        <v>-1834484.339972012</v>
       </c>
     </row>
     <row r="78">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-756411374.3</v>
+        <v>-563607788.72</v>
       </c>
       <c r="E78" t="n">
         <v>0.9903615297882993</v>
@@ -3155,10 +3155,10 @@
         <v>0.004890978187868655</v>
       </c>
       <c r="H78" t="n">
-        <v>-3699591.532757053</v>
+        <v>-2756593.401142406</v>
       </c>
       <c r="I78" t="n">
-        <v>-3699591.532757053</v>
+        <v>-2756593.401142406</v>
       </c>
     </row>
     <row r="79">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>-575289791.02</v>
+        <v>-639535554.92</v>
       </c>
       <c r="E79" t="n">
         <v>0.9786688180301472</v>
@@ -3190,10 +3190,10 @@
         <v>0.008825570306637109</v>
       </c>
       <c r="H79" t="n">
-        <v>-5077260.49733758</v>
+        <v>-5644266.003540638</v>
       </c>
       <c r="I79" t="n">
-        <v>-5077260.49733758</v>
+        <v>-5644266.003540638</v>
       </c>
     </row>
     <row r="80">
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>287271212.35</v>
+        <v>282089586.14</v>
       </c>
       <c r="E80" t="n">
         <v>0.9655145554862491</v>
@@ -3225,10 +3225,10 @@
         <v>0.01134479629056684</v>
       </c>
       <c r="H80" t="n">
-        <v>3259033.384254919</v>
+        <v>3200248.890448607</v>
       </c>
       <c r="I80" t="n">
-        <v>1629516.692127459</v>
+        <v>1600124.445224303</v>
       </c>
     </row>
     <row r="81">
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>338026454.7</v>
+        <v>319161024.12</v>
       </c>
       <c r="E81" t="n">
         <v>0.9530263468310431</v>
@@ -3260,10 +3260,10 @@
         <v>0.0122280753910069</v>
       </c>
       <c r="H81" t="n">
-        <v>4133412.972226378</v>
+        <v>3902725.064810331</v>
       </c>
       <c r="I81" t="n">
-        <v>2066706.486113189</v>
+        <v>1951362.532405165</v>
       </c>
     </row>
     <row r="82">
@@ -3283,22 +3283,22 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>641813154.08</v>
+        <v>533754600.58</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9356051227617213</v>
+        <v>0.9378479178638877</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9474047848338234</v>
+        <v>0.949675902004242</v>
       </c>
       <c r="G82" t="n">
-        <v>0.01179966207210215</v>
+        <v>0.01182798414035435</v>
       </c>
       <c r="H82" t="n">
-        <v>7573178.331574027</v>
+        <v>6313240.950501412</v>
       </c>
       <c r="I82" t="n">
-        <v>3786589.165787014</v>
+        <v>3156620.475250706</v>
       </c>
     </row>
     <row r="83">
@@ -3318,22 +3318,22 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>514396150.85</v>
+        <v>725837405.03</v>
       </c>
       <c r="E83" t="n">
-        <v>0.9110361496874445</v>
+        <v>0.914020029743317</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9207841534302572</v>
+        <v>0.9237999822004164</v>
       </c>
       <c r="G83" t="n">
-        <v>0.009748003742812705</v>
+        <v>0.009779952457099395</v>
       </c>
       <c r="H83" t="n">
-        <v>5014335.60377425</v>
+        <v>7098655.312777797</v>
       </c>
       <c r="I83" t="n">
-        <v>2507167.801887125</v>
+        <v>3549327.656388898</v>
       </c>
     </row>
     <row r="84">
@@ -3353,22 +3353,22 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1009792864.15</v>
+        <v>1456815524.71</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8754048758167313</v>
+        <v>0.8793551938327786</v>
       </c>
       <c r="F84" t="n">
-        <v>0.8817147543300172</v>
+        <v>0.8856935834571039</v>
       </c>
       <c r="G84" t="n">
-        <v>0.006309878513285905</v>
+        <v>0.006338389624325313</v>
       </c>
       <c r="H84" t="n">
-        <v>6371670.296369517</v>
+        <v>9233864.406377902</v>
       </c>
       <c r="I84" t="n">
-        <v>3185835.148184759</v>
+        <v>4616932.203188951</v>
       </c>
     </row>
     <row r="85">
@@ -3388,22 +3388,22 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>794321595.54</v>
+        <v>436647272.55</v>
       </c>
       <c r="E85" t="n">
-        <v>0.8300899355387754</v>
+        <v>0.8350903091634028</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8331661161197905</v>
+        <v>0.83818504204624</v>
       </c>
       <c r="G85" t="n">
-        <v>0.003076180581015109</v>
+        <v>0.003094732882837237</v>
       </c>
       <c r="H85" t="n">
-        <v>2443476.667281085</v>
+        <v>1351306.672561678</v>
       </c>
       <c r="I85" t="n">
-        <v>1221738.333640543</v>
+        <v>675653.3362808391</v>
       </c>
     </row>
     <row r="86">
@@ -3423,22 +3423,22 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1623369977.36</v>
+        <v>857024694.1899999</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7871638664957131</v>
+        <v>0.7929814256230181</v>
       </c>
       <c r="F86" t="n">
-        <v>0.7885422913538858</v>
+        <v>0.7943700412704571</v>
       </c>
       <c r="G86" t="n">
-        <v>0.001378424858172633</v>
+        <v>0.001388615647438973</v>
       </c>
       <c r="H86" t="n">
-        <v>2237693.530804169</v>
+        <v>1190077.900593835</v>
       </c>
       <c r="I86" t="n">
-        <v>1118846.765402084</v>
+        <v>595038.9502969175</v>
       </c>
     </row>
     <row r="87">
@@ -3458,22 +3458,22 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>99536703.16000001</v>
+        <v>98149543.74000001</v>
       </c>
       <c r="E87" t="n">
-        <v>0.7465017756172543</v>
+        <v>0.7529410815413444</v>
       </c>
       <c r="F87" t="n">
-        <v>0.7470891193811869</v>
+        <v>0.7535334946689828</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0005873437639326573</v>
+        <v>0.0005924131276383582</v>
       </c>
       <c r="H87" t="n">
-        <v>58462.26188344203</v>
+        <v>58145.07818329125</v>
       </c>
       <c r="I87" t="n">
-        <v>29231.13094172101</v>
+        <v>29072.53909164562</v>
       </c>
     </row>
     <row r="88">
@@ -3493,22 +3493,22 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>318521371.88</v>
+        <v>317275857.88</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7079831292590303</v>
+        <v>0.7148807043542068</v>
       </c>
       <c r="F88" t="n">
-        <v>0.7082249026637973</v>
+        <v>0.7151248528360472</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0002417734047670539</v>
+        <v>0.0002441484818404005</v>
       </c>
       <c r="H88" t="n">
-        <v>77009.99657050053</v>
+        <v>77462.41902601266</v>
       </c>
       <c r="I88" t="n">
-        <v>38504.99828525027</v>
+        <v>38731.20951300633</v>
       </c>
     </row>
     <row r="89">
@@ -3528,22 +3528,22 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>306908451.75</v>
+        <v>305998789.65</v>
       </c>
       <c r="E89" t="n">
-        <v>0.6714924005042728</v>
+        <v>0.6787119945050498</v>
       </c>
       <c r="F89" t="n">
-        <v>0.6715896062479044</v>
+        <v>0.6788102588577627</v>
       </c>
       <c r="G89" t="n">
-        <v>9.720574363158985e-05</v>
+        <v>9.826435271287348e-05</v>
       </c>
       <c r="H89" t="n">
-        <v>29833.26427917866</v>
+        <v>30068.77299587998</v>
       </c>
       <c r="I89" t="n">
-        <v>14916.63213958933</v>
+        <v>15034.38649793999</v>
       </c>
     </row>
     <row r="90">
@@ -3563,22 +3563,22 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>223541651.31</v>
+        <v>213878647.01</v>
       </c>
       <c r="E90" t="n">
-        <v>0.6369207605854804</v>
+        <v>0.6443492036977719</v>
       </c>
       <c r="F90" t="n">
-        <v>0.6369589980232822</v>
+        <v>0.6443878944004078</v>
       </c>
       <c r="G90" t="n">
-        <v>3.823743780173583e-05</v>
+        <v>3.869070263584629e-05</v>
       </c>
       <c r="H90" t="n">
-        <v>8547.659988063444</v>
+        <v>8275.115131621043</v>
       </c>
       <c r="I90" t="n">
-        <v>4273.829994031722</v>
+        <v>4137.557565810522</v>
       </c>
     </row>
     <row r="91">
@@ -3598,22 +3598,22 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>14469721.94</v>
+        <v>6012265.48</v>
       </c>
       <c r="E91" t="n">
-        <v>0.6041641709026</v>
+        <v>0.6117079401756688</v>
       </c>
       <c r="F91" t="n">
-        <v>0.6041788672544907</v>
+        <v>0.6117228289482252</v>
       </c>
       <c r="G91" t="n">
-        <v>1.469635189066398e-05</v>
+        <v>1.488877255639842e-05</v>
       </c>
       <c r="H91" t="n">
-        <v>212.6521253903011</v>
+        <v>89.51525328040559</v>
       </c>
       <c r="I91" t="n">
-        <v>106.3260626951506</v>
+        <v>44.75762664020279</v>
       </c>
     </row>
     <row r="92">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-1657923918.46</v>
+        <v>-1323380873.66</v>
       </c>
       <c r="E92" t="n">
         <v>0.9975215395798449</v>
@@ -3645,10 +3645,10 @@
         <v>0.0004267113511314813</v>
       </c>
       <c r="H92" t="n">
-        <v>-707454.9553192664</v>
+        <v>-564701.6406610188</v>
       </c>
       <c r="I92" t="n">
-        <v>-707454.9553192664</v>
+        <v>-564701.6406610188</v>
       </c>
     </row>
     <row r="93">
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-756411374.3</v>
+        <v>-563607788.72</v>
       </c>
       <c r="E93" t="n">
         <v>0.9903615297882993</v>
@@ -3680,10 +3680,10 @@
         <v>0.001651293781163021</v>
       </c>
       <c r="H93" t="n">
-        <v>-1249057.398382564</v>
+        <v>-930682.036528378</v>
       </c>
       <c r="I93" t="n">
-        <v>-1249057.398382564</v>
+        <v>-930682.036528378</v>
       </c>
     </row>
     <row r="94">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-575289791.02</v>
+        <v>-639535554.92</v>
       </c>
       <c r="E94" t="n">
         <v>0.9786688180301472</v>
@@ -3715,10 +3715,10 @@
         <v>0.003673721028352284</v>
       </c>
       <c r="H94" t="n">
-        <v>-2113454.202666565</v>
+        <v>-2349475.21648855</v>
       </c>
       <c r="I94" t="n">
-        <v>-2113454.202666565</v>
+        <v>-2349475.21648855</v>
       </c>
     </row>
     <row r="95">
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>287271212.35</v>
+        <v>282089586.14</v>
       </c>
       <c r="E95" t="n">
         <v>0.9655145554862491</v>
@@ -3750,10 +3750,10 @@
         <v>0.006050833538578271</v>
       </c>
       <c r="H95" t="n">
-        <v>1738230.28635542</v>
+        <v>1706877.128699576</v>
       </c>
       <c r="I95" t="n">
-        <v>869115.1431777102</v>
+        <v>853438.564349788</v>
       </c>
     </row>
     <row r="96">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>338026454.7</v>
+        <v>319161024.12</v>
       </c>
       <c r="E96" t="n">
         <v>0.9530263468310431</v>
@@ -3785,10 +3785,10 @@
         <v>0.008373224807978752</v>
       </c>
       <c r="H96" t="n">
-        <v>2830371.496247146</v>
+        <v>2672407.004901489</v>
       </c>
       <c r="I96" t="n">
-        <v>1415185.748123573</v>
+        <v>1336203.502450744</v>
       </c>
     </row>
     <row r="97">
@@ -3808,22 +3808,22 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>641813154.08</v>
+        <v>533754600.58</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9356051227617213</v>
+        <v>0.9378479178638877</v>
       </c>
       <c r="F97" t="n">
-        <v>0.9473731452282037</v>
+        <v>0.9496441759214491</v>
       </c>
       <c r="G97" t="n">
-        <v>0.01176802246648245</v>
+        <v>0.01179625805756146</v>
       </c>
       <c r="H97" t="n">
-        <v>7552871.616497405</v>
+        <v>6296307.007852323</v>
       </c>
       <c r="I97" t="n">
-        <v>3776435.808248702</v>
+        <v>3148153.503926162</v>
       </c>
     </row>
     <row r="98">
@@ -3843,22 +3843,22 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>514396150.85</v>
+        <v>725837405.03</v>
       </c>
       <c r="E98" t="n">
-        <v>0.9110361496874445</v>
+        <v>0.914020029743317</v>
       </c>
       <c r="F98" t="n">
-        <v>0.9271192361753671</v>
+        <v>0.9301558102536122</v>
       </c>
       <c r="G98" t="n">
-        <v>0.01608308648792256</v>
+        <v>0.01613578051029518</v>
       </c>
       <c r="H98" t="n">
-        <v>8273077.78317501</v>
+        <v>11711953.0537263</v>
       </c>
       <c r="I98" t="n">
-        <v>4136538.891587505</v>
+        <v>5855976.526863152</v>
       </c>
     </row>
     <row r="99">
@@ -3878,22 +3878,22 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1009792864.15</v>
+        <v>1456815524.71</v>
       </c>
       <c r="E99" t="n">
-        <v>0.8754048758167313</v>
+        <v>0.8793551938327786</v>
       </c>
       <c r="F99" t="n">
-        <v>0.8975652297165327</v>
+        <v>0.9016155859299932</v>
       </c>
       <c r="G99" t="n">
-        <v>0.02216035389980142</v>
+        <v>0.02226039209721464</v>
       </c>
       <c r="H99" t="n">
-        <v>22377367.2350581</v>
+        <v>32429284.79335409</v>
       </c>
       <c r="I99" t="n">
-        <v>11188683.61752905</v>
+        <v>16214642.39667704</v>
       </c>
     </row>
     <row r="100">
@@ -3913,22 +3913,22 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>794321595.54</v>
+        <v>436647272.55</v>
       </c>
       <c r="E100" t="n">
-        <v>0.8300899355387754</v>
+        <v>0.8350903091634028</v>
       </c>
       <c r="F100" t="n">
-        <v>0.8596571328525812</v>
+        <v>0.864835634020792</v>
       </c>
       <c r="G100" t="n">
-        <v>0.02956719731380575</v>
+        <v>0.02974532485738923</v>
       </c>
       <c r="H100" t="n">
-        <v>23485863.34594818</v>
+        <v>12988214.97009273</v>
       </c>
       <c r="I100" t="n">
-        <v>11742931.67297409</v>
+        <v>6494107.485046363</v>
       </c>
     </row>
     <row r="101">
@@ -3948,22 +3948,22 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1623369977.36</v>
+        <v>857024694.1899999</v>
       </c>
       <c r="E101" t="n">
-        <v>0.7871638664957131</v>
+        <v>0.7929814256230181</v>
       </c>
       <c r="F101" t="n">
-        <v>0.8233952316458175</v>
+        <v>0.8294805679220334</v>
       </c>
       <c r="G101" t="n">
-        <v>0.03623136515010439</v>
+        <v>0.0364991422990153</v>
       </c>
       <c r="H101" t="n">
-        <v>58816910.42344685</v>
+        <v>31280666.26701088</v>
       </c>
       <c r="I101" t="n">
-        <v>29408455.21172342</v>
+        <v>15640333.13350544</v>
       </c>
     </row>
     <row r="102">
@@ -3983,22 +3983,22 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>99536703.16000001</v>
+        <v>98149543.74000001</v>
       </c>
       <c r="E102" t="n">
-        <v>0.7465017756172543</v>
+        <v>0.7529410815413444</v>
       </c>
       <c r="F102" t="n">
-        <v>0.7887092384228424</v>
+        <v>0.7955126273253091</v>
       </c>
       <c r="G102" t="n">
-        <v>0.04220746280558807</v>
+        <v>0.04257154578396471</v>
       </c>
       <c r="H102" t="n">
-        <v>4201191.696416561</v>
+        <v>4178377.795002658</v>
       </c>
       <c r="I102" t="n">
-        <v>2100595.84820828</v>
+        <v>2089188.897501329</v>
       </c>
     </row>
     <row r="103">
@@ -4018,22 +4018,22 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>318521371.88</v>
+        <v>317275857.88</v>
       </c>
       <c r="E103" t="n">
-        <v>0.7079831292590303</v>
+        <v>0.7148807043542068</v>
       </c>
       <c r="F103" t="n">
-        <v>0.7555300952994544</v>
+        <v>0.762890923118997</v>
       </c>
       <c r="G103" t="n">
-        <v>0.04754696604042408</v>
+        <v>0.04801021876479017</v>
       </c>
       <c r="H103" t="n">
-        <v>15144724.85192765</v>
+        <v>15232483.34560527</v>
       </c>
       <c r="I103" t="n">
-        <v>7572362.425963824</v>
+        <v>7616241.672802637</v>
       </c>
     </row>
     <row r="104">
@@ -4053,22 +4053,22 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>306908451.75</v>
+        <v>305998789.65</v>
       </c>
       <c r="E104" t="n">
-        <v>0.6714924005042728</v>
+        <v>0.6787119945050498</v>
       </c>
       <c r="F104" t="n">
-        <v>0.7237906915672608</v>
+        <v>0.7315725866506247</v>
       </c>
       <c r="G104" t="n">
-        <v>0.052298291062988</v>
+        <v>0.05286059214557493</v>
       </c>
       <c r="H104" t="n">
-        <v>16050787.53931251</v>
+        <v>16175277.21672822</v>
       </c>
       <c r="I104" t="n">
-        <v>8025393.769656255</v>
+        <v>8087638.608364111</v>
       </c>
     </row>
     <row r="105">
@@ -4088,22 +4088,22 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>223541651.31</v>
+        <v>213878647.01</v>
       </c>
       <c r="E105" t="n">
-        <v>0.6369207605854804</v>
+        <v>0.6443492036977719</v>
       </c>
       <c r="F105" t="n">
-        <v>0.6934261484137834</v>
+        <v>0.7015136281311324</v>
       </c>
       <c r="G105" t="n">
-        <v>0.05650538782830294</v>
+        <v>0.05716442443336045</v>
       </c>
       <c r="H105" t="n">
-        <v>12631307.70305081</v>
+        <v>12226249.75491252</v>
       </c>
       <c r="I105" t="n">
-        <v>6315653.851525407</v>
+        <v>6113124.877456259</v>
       </c>
     </row>
     <row r="106">
@@ -4123,22 +4123,22 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>14469721.94</v>
+        <v>6012265.48</v>
       </c>
       <c r="E106" t="n">
-        <v>0.6041641709026</v>
+        <v>0.6117079401756688</v>
       </c>
       <c r="F106" t="n">
-        <v>0.664374099575429</v>
+        <v>0.6726696846576002</v>
       </c>
       <c r="G106" t="n">
-        <v>0.06020992867282904</v>
+        <v>0.06096174448193148</v>
       </c>
       <c r="H106" t="n">
-        <v>871220.9259230694</v>
+        <v>366518.1919492972</v>
       </c>
       <c r="I106" t="n">
-        <v>435610.4629615347</v>
+        <v>183259.0959746486</v>
       </c>
     </row>
   </sheetData>
@@ -4214,22 +4214,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="D2" t="n">
-        <v>2088879685.01</v>
+        <v>2135795552.07</v>
       </c>
       <c r="E2" t="n">
-        <v>-85376944.77999997</v>
+        <v>-56451590.77999997</v>
       </c>
       <c r="F2" t="n">
-        <v>-85376944.77999997</v>
+        <v>-56451590.77999997</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.11474539833333</v>
+        <v>-4.704299231666664</v>
       </c>
       <c r="H2" t="n">
-        <v>-7.11474539833333</v>
+        <v>-4.704299231666664</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -4247,22 +4247,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="D3" t="n">
-        <v>2267212933.25</v>
+        <v>2253653018.34</v>
       </c>
       <c r="E3" t="n">
-        <v>92956303.46000004</v>
+        <v>61405875.49000025</v>
       </c>
       <c r="F3" t="n">
-        <v>46478151.73000002</v>
+        <v>30702937.74500012</v>
       </c>
       <c r="G3" t="n">
-        <v>7.74635862166667</v>
+        <v>5.117156290833353</v>
       </c>
       <c r="H3" t="n">
-        <v>3.873179310833335</v>
+        <v>2.558578145416677</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -4280,22 +4280,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="D4" t="n">
-        <v>2158367069.35</v>
+        <v>2188335533.43</v>
       </c>
       <c r="E4" t="n">
-        <v>-15889560.44000006</v>
+        <v>-3911609.420000076</v>
       </c>
       <c r="F4" t="n">
-        <v>-15889560.44000006</v>
+        <v>-3911609.420000076</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.324130036666671</v>
+        <v>-0.325967451666673</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.324130036666671</v>
+        <v>-0.325967451666673</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -4313,22 +4313,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="D5" t="n">
-        <v>2181936002.53</v>
+        <v>2190935799.46</v>
       </c>
       <c r="E5" t="n">
-        <v>7679372.740000248</v>
+        <v>-1311343.389999866</v>
       </c>
       <c r="F5" t="n">
-        <v>3839686.370000124</v>
+        <v>-1311343.389999866</v>
       </c>
       <c r="G5" t="n">
-        <v>0.639947728333354</v>
+        <v>-0.1092786158333222</v>
       </c>
       <c r="H5" t="n">
-        <v>0.319973864166677</v>
+        <v>-0.1092786158333222</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -4346,22 +4346,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="D6" t="n">
-        <v>2145100116.98</v>
+        <v>2167308510.39</v>
       </c>
       <c r="E6" t="n">
-        <v>-29156512.80999994</v>
+        <v>-24938632.46000004</v>
       </c>
       <c r="F6" t="n">
-        <v>-29156512.80999994</v>
+        <v>-24938632.46000004</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.429709400833329</v>
+        <v>-2.07821937166667</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.429709400833329</v>
+        <v>-2.07821937166667</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -4379,22 +4379,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="D7" t="n">
-        <v>2204808001.51</v>
+        <v>2219037258.94</v>
       </c>
       <c r="E7" t="n">
-        <v>30551371.72000027</v>
+        <v>26790116.09000015</v>
       </c>
       <c r="F7" t="n">
-        <v>15275685.86000013</v>
+        <v>13395058.04500008</v>
       </c>
       <c r="G7" t="n">
-        <v>2.545947643333355</v>
+        <v>2.232509674166679</v>
       </c>
       <c r="H7" t="n">
-        <v>1.272973821666678</v>
+        <v>1.11625483708334</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -4412,22 +4412,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="D8" t="n">
-        <v>2210930152.52</v>
+        <v>2216973654.4</v>
       </c>
       <c r="E8" t="n">
-        <v>36673522.73000002</v>
+        <v>24726511.55000019</v>
       </c>
       <c r="F8" t="n">
-        <v>18336761.36500001</v>
+        <v>12363255.7750001</v>
       </c>
       <c r="G8" t="n">
-        <v>3.056126894166668</v>
+        <v>2.060542629166683</v>
       </c>
       <c r="H8" t="n">
-        <v>1.528063447083334</v>
+        <v>1.030271314583341</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -4557,19 +4557,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G2" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="J2" t="n">
         <v>-680000000</v>
       </c>
       <c r="K2" t="n">
-        <v>-655362070.4300001</v>
+        <v>-750323402.3400002</v>
       </c>
       <c r="L2" t="n">
         <v>0.1050151041880321</v>
@@ -4581,10 +4581,10 @@
         <v>-0.02747158338321065</v>
       </c>
       <c r="O2" t="n">
-        <v>17954508.19205512</v>
+        <v>20556099.11199939</v>
       </c>
       <c r="P2" t="n">
-        <v>8977254.096027562</v>
+        <v>10278049.55599969</v>
       </c>
     </row>
     <row r="3">
@@ -4615,19 +4615,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G3" t="n">
-        <v>133911619.36</v>
+        <v>425995266.0600001</v>
       </c>
       <c r="H3" t="n">
         <v>-90269181.22613968</v>
       </c>
       <c r="I3" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="J3" t="n">
         <v>-68000000</v>
       </c>
       <c r="K3" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="L3" t="n">
         <v>0.05822765833026367</v>
@@ -4639,10 +4639,10 @@
         <v>0.02514989940008316</v>
       </c>
       <c r="O3" t="n">
-        <v>1006136.017920862</v>
+        <v>7739854.154592426</v>
       </c>
       <c r="P3" t="n">
-        <v>503068.0089604312</v>
+        <v>3869927.077296213</v>
       </c>
     </row>
     <row r="4">
@@ -4673,19 +4673,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>2364336920.83</v>
+        <v>2339361769.16</v>
       </c>
       <c r="H4" t="n">
         <v>-51490547.94520548</v>
       </c>
       <c r="I4" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="J4" t="n">
         <v>-68000000</v>
       </c>
       <c r="K4" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="L4" t="n">
         <v>0.05839364669442126</v>
@@ -4697,10 +4697,10 @@
         <v>0.02530014515467949</v>
       </c>
       <c r="O4" t="n">
-        <v>48762790.79538272</v>
+        <v>48236228.32662344</v>
       </c>
       <c r="P4" t="n">
-        <v>24381395.39769136</v>
+        <v>24118114.16331172</v>
       </c>
     </row>
     <row r="5">
@@ -4731,19 +4731,19 @@
         <v>0.75</v>
       </c>
       <c r="G5" t="n">
-        <v>-157998693</v>
+        <v>368810148.66</v>
       </c>
       <c r="H5" t="n">
         <v>-92049904.10958904</v>
       </c>
       <c r="I5" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="J5" t="n">
         <v>-68000000</v>
       </c>
       <c r="K5" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="L5" t="n">
         <v>0.05851824187679444</v>
@@ -4755,10 +4755,10 @@
         <v>0.02544697899977066</v>
       </c>
       <c r="O5" t="n">
-        <v>-4772236.049677371</v>
+        <v>5282034.098284275</v>
       </c>
       <c r="P5" t="n">
-        <v>-4772236.049677371</v>
+        <v>2641017.049142138</v>
       </c>
     </row>
     <row r="6">
@@ -4789,19 +4789,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>-194599255.21</v>
+        <v>-180822610.01</v>
       </c>
       <c r="H6" t="n">
         <v>-51458493.15068493</v>
       </c>
       <c r="I6" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="J6" t="n">
         <v>-68000000</v>
       </c>
       <c r="K6" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="L6" t="n">
         <v>0.05821004393128892</v>
@@ -4813,10 +4813,10 @@
         <v>0.02559354982454409</v>
       </c>
       <c r="O6" t="n">
-        <v>-4198327.494922882</v>
+        <v>-3963265.324695371</v>
       </c>
       <c r="P6" t="n">
-        <v>-4198327.494922882</v>
+        <v>-3963265.324695371</v>
       </c>
     </row>
     <row r="7">
@@ -4847,19 +4847,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>398501812.66</v>
+        <v>396368601.78</v>
       </c>
       <c r="H7" t="n">
         <v>-51445520.54794521</v>
       </c>
       <c r="I7" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="J7" t="n">
         <v>-68000000</v>
       </c>
       <c r="K7" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="L7" t="n">
         <v>0.05808035784574397</v>
@@ -4871,10 +4871,10 @@
         <v>0.02573959809769572</v>
       </c>
       <c r="O7" t="n">
-        <v>5210968.861140452</v>
+        <v>5178939.199893634</v>
       </c>
       <c r="P7" t="n">
-        <v>2605484.430570226</v>
+        <v>2589469.599946817</v>
       </c>
     </row>
     <row r="8">
@@ -4905,19 +4905,19 @@
         <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>772422393.1500001</v>
+        <v>270725457.28</v>
       </c>
       <c r="H8" t="n">
         <v>-90799555.08645856</v>
       </c>
       <c r="I8" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="J8" t="n">
         <v>-34000000</v>
       </c>
       <c r="K8" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="L8" t="n">
         <v>0.0579990267461179</v>
@@ -4929,10 +4929,10 @@
         <v>0.02588744766971374</v>
       </c>
       <c r="O8" t="n">
-        <v>8822737.775425846</v>
+        <v>2328911.188730668</v>
       </c>
       <c r="P8" t="n">
-        <v>4411368.887712923</v>
+        <v>1164455.594365334</v>
       </c>
     </row>
     <row r="9">
@@ -4963,19 +4963,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G9" t="n">
-        <v>-35157733.02</v>
+        <v>-35174959.2</v>
       </c>
       <c r="H9" t="n">
         <v>2247136.761733663</v>
       </c>
       <c r="I9" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="J9" t="n">
         <v>-34000000</v>
       </c>
       <c r="K9" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="L9" t="n">
         <v>0.05738520780446178</v>
@@ -4987,10 +4987,10 @@
         <v>0.02602676969992171</v>
       </c>
       <c r="O9" t="n">
-        <v>-356898.545625418</v>
+        <v>-357085.3547169468</v>
       </c>
       <c r="P9" t="n">
-        <v>-356898.545625418</v>
+        <v>-357085.3547169468</v>
       </c>
     </row>
     <row r="10">
@@ -5021,19 +5021,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G10" t="n">
-        <v>-35284909.43000001</v>
+        <v>-35427280.72000001</v>
       </c>
       <c r="H10" t="n">
         <v>2266152.03233775</v>
       </c>
       <c r="I10" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="J10" t="n">
         <v>-34000000</v>
       </c>
       <c r="K10" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="L10" t="n">
         <v>0.05695407285841891</v>
@@ -5045,10 +5045,10 @@
         <v>0.02616692125524978</v>
       </c>
       <c r="O10" t="n">
-        <v>-287999.7415902748</v>
+        <v>-289241.5477017542</v>
       </c>
       <c r="P10" t="n">
-        <v>-287999.7415902748</v>
+        <v>-289241.5477017542</v>
       </c>
     </row>
     <row r="11">
@@ -5079,19 +5079,19 @@
         <v>0.25</v>
       </c>
       <c r="G11" t="n">
-        <v>-35779408.35</v>
+        <v>-35839034.46</v>
       </c>
       <c r="H11" t="n">
         <v>2248181.001571974</v>
       </c>
       <c r="I11" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="J11" t="n">
         <v>-34000000</v>
       </c>
       <c r="K11" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="L11" t="n">
         <v>0.05664439372837885</v>
@@ -5103,10 +5103,10 @@
         <v>0.02630835803903212</v>
       </c>
       <c r="O11" t="n">
-        <v>-220537.8836426575</v>
+        <v>-220930.0499052462</v>
       </c>
       <c r="P11" t="n">
-        <v>-220537.8836426575</v>
+        <v>-220930.0499052462</v>
       </c>
     </row>
     <row r="12">
@@ -5137,19 +5137,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G12" t="n">
-        <v>-35814156.50999999</v>
+        <v>-35777615.53999999</v>
       </c>
       <c r="H12" t="n">
         <v>2248686.278913092</v>
       </c>
       <c r="I12" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="J12" t="n">
         <v>-34000000</v>
       </c>
       <c r="K12" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="L12" t="n">
         <v>0.05642057743315654</v>
@@ -5161,10 +5161,10 @@
         <v>0.02645013495868191</v>
       </c>
       <c r="O12" t="n">
-        <v>-147968.5362606447</v>
+        <v>-147807.4506626412</v>
       </c>
       <c r="P12" t="n">
-        <v>-147968.5362606447</v>
+        <v>-147807.4506626412</v>
       </c>
     </row>
     <row r="13">
@@ -5195,19 +5195,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G13" t="n">
-        <v>-35845139.96</v>
+        <v>-35715304.73</v>
       </c>
       <c r="H13" t="n">
         <v>2261537.165955536</v>
       </c>
       <c r="I13" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="J13" t="n">
         <v>-34000000</v>
       </c>
       <c r="K13" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="L13" t="n">
         <v>0.05625883751011833</v>
@@ -5219,10 +5219,10 @@
         <v>0.02659286987606641</v>
       </c>
       <c r="O13" t="n">
-        <v>-74423.69825596042</v>
+        <v>-74135.97397456717</v>
       </c>
       <c r="P13" t="n">
-        <v>-74423.69825596042</v>
+        <v>-74135.97397456717</v>
       </c>
     </row>
     <row r="14">
@@ -5253,28 +5253,28 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-36463708.53000001</v>
+        <v>-36430105.95000001</v>
       </c>
       <c r="H14" t="n">
         <v>4044566.584325174</v>
       </c>
       <c r="I14" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="J14" t="n">
         <v>-34000000</v>
       </c>
       <c r="K14" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05613367690325632</v>
+        <v>0.05611688274594639</v>
       </c>
       <c r="M14" t="n">
-        <v>0.08286986959442011</v>
+        <v>0.08285261130760024</v>
       </c>
       <c r="N14" t="n">
-        <v>0.02673619269116378</v>
+        <v>0.02673572856165385</v>
       </c>
       <c r="O14" t="n">
         <v>-0</v>
@@ -5311,19 +5311,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G15" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="J15" t="n">
         <v>-680000000</v>
       </c>
       <c r="K15" t="n">
-        <v>-655362070.4300001</v>
+        <v>-750323402.3400002</v>
       </c>
       <c r="L15" t="n">
         <v>0.1050151041880321</v>
@@ -5335,10 +5335,10 @@
         <v>-0.07747761902794248</v>
       </c>
       <c r="O15" t="n">
-        <v>50636780.78302096</v>
+        <v>57974001.47941458</v>
       </c>
       <c r="P15" t="n">
-        <v>25318390.39151048</v>
+        <v>28987000.73970729</v>
       </c>
     </row>
     <row r="16">
@@ -5369,19 +5369,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G16" t="n">
-        <v>133911619.36</v>
+        <v>425995266.0600001</v>
       </c>
       <c r="H16" t="n">
         <v>-90269181.22613968</v>
       </c>
       <c r="I16" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="J16" t="n">
         <v>-68000000</v>
       </c>
       <c r="K16" t="n">
-        <v>111642438.1338603</v>
+        <v>403726084.8338604</v>
       </c>
       <c r="L16" t="n">
         <v>0.05822765833026367</v>
@@ -5393,10 +5393,10 @@
         <v>-0.02509271293939896</v>
       </c>
       <c r="O16" t="n">
-        <v>-2567960.680951935</v>
+        <v>-9286367.523476534</v>
       </c>
       <c r="P16" t="n">
-        <v>-2567960.680951935</v>
+        <v>-9286367.523476534</v>
       </c>
     </row>
     <row r="17">
@@ -5427,19 +5427,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G17" t="n">
-        <v>2364336920.83</v>
+        <v>2339361769.16</v>
       </c>
       <c r="H17" t="n">
         <v>-51490547.94520548</v>
       </c>
       <c r="I17" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="J17" t="n">
         <v>-68000000</v>
       </c>
       <c r="K17" t="n">
-        <v>2380846372.884794</v>
+        <v>2355871221.214795</v>
       </c>
       <c r="L17" t="n">
         <v>0.05839364669442126</v>
@@ -5451,10 +5451,10 @@
         <v>-0.02518665410778054</v>
       </c>
       <c r="O17" t="n">
-        <v>-49971295.06467766</v>
+        <v>-49447094.6426763</v>
       </c>
       <c r="P17" t="n">
-        <v>-49971295.06467766</v>
+        <v>-49447094.6426763</v>
       </c>
     </row>
     <row r="18">
@@ -5485,19 +5485,19 @@
         <v>0.75</v>
       </c>
       <c r="G18" t="n">
-        <v>-157998693</v>
+        <v>368810148.66</v>
       </c>
       <c r="H18" t="n">
         <v>-92049904.10958904</v>
       </c>
       <c r="I18" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="J18" t="n">
         <v>-68000000</v>
       </c>
       <c r="K18" t="n">
-        <v>-182048597.109589</v>
+        <v>344760244.5504109</v>
       </c>
       <c r="L18" t="n">
         <v>0.05851824187679444</v>
@@ -5509,10 +5509,10 @@
         <v>-0.02528484926412755</v>
       </c>
       <c r="O18" t="n">
-        <v>3452303.502496384</v>
+        <v>-6537908.111790668</v>
       </c>
       <c r="P18" t="n">
-        <v>1726151.751248192</v>
+        <v>-6537908.111790668</v>
       </c>
     </row>
     <row r="19">
@@ -5543,19 +5543,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>-194599255.21</v>
+        <v>-180822610.01</v>
       </c>
       <c r="H19" t="n">
         <v>-51458493.15068493</v>
       </c>
       <c r="I19" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="J19" t="n">
         <v>-68000000</v>
       </c>
       <c r="K19" t="n">
-        <v>-178057748.3606849</v>
+        <v>-164281103.1606849</v>
       </c>
       <c r="L19" t="n">
         <v>0.05821004393128892</v>
@@ -5567,10 +5567,10 @@
         <v>-0.02537722477452231</v>
       </c>
       <c r="O19" t="n">
-        <v>3012407.668662956</v>
+        <v>2779332.32074346</v>
       </c>
       <c r="P19" t="n">
-        <v>1506203.834331478</v>
+        <v>1389666.16037173</v>
       </c>
     </row>
     <row r="20">
@@ -5601,19 +5601,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>398501812.66</v>
+        <v>396368601.78</v>
       </c>
       <c r="H20" t="n">
         <v>-51445520.54794521</v>
       </c>
       <c r="I20" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="J20" t="n">
         <v>-68000000</v>
       </c>
       <c r="K20" t="n">
-        <v>415056292.1120548</v>
+        <v>412923081.2320548</v>
       </c>
       <c r="L20" t="n">
         <v>0.05808035784574397</v>
@@ -5625,10 +5625,10 @@
         <v>-0.02547134730704866</v>
       </c>
       <c r="O20" t="n">
-        <v>-6167025.064877826</v>
+        <v>-6135329.207675694</v>
       </c>
       <c r="P20" t="n">
-        <v>-6167025.064877826</v>
+        <v>-6135329.207675694</v>
       </c>
     </row>
     <row r="21">
@@ -5659,19 +5659,19 @@
         <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>772422393.1500001</v>
+        <v>270725457.28</v>
       </c>
       <c r="H21" t="n">
         <v>-90799555.08645856</v>
       </c>
       <c r="I21" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="J21" t="n">
         <v>-34000000</v>
       </c>
       <c r="K21" t="n">
-        <v>715622838.0635415</v>
+        <v>213925902.1935414</v>
       </c>
       <c r="L21" t="n">
         <v>0.0579990267461179</v>
@@ -5683,10 +5683,10 @@
         <v>-0.02556388968728518</v>
       </c>
       <c r="O21" t="n">
-        <v>-9147051.64497916</v>
+        <v>-2734389.082464326</v>
       </c>
       <c r="P21" t="n">
-        <v>-9147051.64497916</v>
+        <v>-2734389.082464326</v>
       </c>
     </row>
     <row r="22">
@@ -5717,19 +5717,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G22" t="n">
-        <v>-35157733.02</v>
+        <v>-35174959.2</v>
       </c>
       <c r="H22" t="n">
         <v>2247136.761733663</v>
       </c>
       <c r="I22" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="J22" t="n">
         <v>-34000000</v>
       </c>
       <c r="K22" t="n">
-        <v>1089403.741733659</v>
+        <v>1072177.561733659</v>
       </c>
       <c r="L22" t="n">
         <v>0.05738520780446178</v>
@@ -5741,10 +5741,10 @@
         <v>-0.02564879692438105</v>
       </c>
       <c r="O22" t="n">
-        <v>-11642.45639182811</v>
+        <v>-11458.3602282436</v>
       </c>
       <c r="P22" t="n">
-        <v>-11642.45639182811</v>
+        <v>-11458.3602282436</v>
       </c>
     </row>
     <row r="23">
@@ -5775,19 +5775,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>-35284909.43000001</v>
+        <v>-35427280.72000001</v>
       </c>
       <c r="H23" t="n">
         <v>2266152.03233775</v>
       </c>
       <c r="I23" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="J23" t="n">
         <v>-34000000</v>
       </c>
       <c r="K23" t="n">
-        <v>981242.6023377441</v>
+        <v>838871.312337745</v>
       </c>
       <c r="L23" t="n">
         <v>0.05695407285841891</v>
@@ -5799,10 +5799,10 @@
         <v>-0.02573394353653935</v>
       </c>
       <c r="O23" t="n">
-        <v>-8417.080574735481</v>
+        <v>-7195.8223287074</v>
       </c>
       <c r="P23" t="n">
-        <v>-8417.080574735481</v>
+        <v>-7195.8223287074</v>
       </c>
     </row>
     <row r="24">
@@ -5833,19 +5833,19 @@
         <v>0.25</v>
       </c>
       <c r="G24" t="n">
-        <v>-35779408.35</v>
+        <v>-35839034.46</v>
       </c>
       <c r="H24" t="n">
         <v>2248181.001571974</v>
       </c>
       <c r="I24" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="J24" t="n">
         <v>-34000000</v>
       </c>
       <c r="K24" t="n">
-        <v>468772.6515719742</v>
+        <v>409146.5415719748</v>
       </c>
       <c r="L24" t="n">
         <v>0.05664439372837885</v>
@@ -5857,10 +5857,10 @@
         <v>-0.02581887365352179</v>
       </c>
       <c r="O24" t="n">
-        <v>-3025.795465790799</v>
+        <v>-2640.925715655555</v>
       </c>
       <c r="P24" t="n">
-        <v>-3025.795465790799</v>
+        <v>-2640.925715655555</v>
       </c>
     </row>
     <row r="25">
@@ -5891,19 +5891,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G25" t="n">
-        <v>-35814156.50999999</v>
+        <v>-35777615.53999999</v>
       </c>
       <c r="H25" t="n">
         <v>2248686.278913092</v>
       </c>
       <c r="I25" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="J25" t="n">
         <v>-34000000</v>
       </c>
       <c r="K25" t="n">
-        <v>434529.7689131051</v>
+        <v>471070.7389131002</v>
       </c>
       <c r="L25" t="n">
         <v>0.05642057743315654</v>
@@ -5915,10 +5915,10 @@
         <v>-0.02590450870981425</v>
       </c>
       <c r="O25" t="n">
-        <v>-1876.046697247183</v>
+        <v>-2033.809343185506</v>
       </c>
       <c r="P25" t="n">
-        <v>-1876.046697247183</v>
+        <v>-2033.809343185506</v>
       </c>
     </row>
     <row r="26">
@@ -5949,19 +5949,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G26" t="n">
-        <v>-35845139.96</v>
+        <v>-35715304.73</v>
       </c>
       <c r="H26" t="n">
         <v>2261537.165955536</v>
       </c>
       <c r="I26" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="J26" t="n">
         <v>-34000000</v>
       </c>
       <c r="K26" t="n">
-        <v>416397.2059555352</v>
+        <v>546232.4359555319</v>
       </c>
       <c r="L26" t="n">
         <v>0.05625883751011833</v>
@@ -5973,10 +5973,10 @@
         <v>-0.025990262065432</v>
       </c>
       <c r="O26" t="n">
-        <v>-901.8560421748355</v>
+        <v>-1183.060346593632</v>
       </c>
       <c r="P26" t="n">
-        <v>-901.8560421748355</v>
+        <v>-1183.060346593632</v>
       </c>
     </row>
     <row r="27">
@@ -6007,28 +6007,28 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-36463708.53000001</v>
+        <v>-36430105.95000001</v>
       </c>
       <c r="H27" t="n">
         <v>4044566.584325174</v>
       </c>
       <c r="I27" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="J27" t="n">
         <v>-34000000</v>
       </c>
       <c r="K27" t="n">
-        <v>1580858.054325163</v>
+        <v>1614460.634325162</v>
       </c>
       <c r="L27" t="n">
-        <v>0.05613367690325632</v>
+        <v>0.05611688274594639</v>
       </c>
       <c r="M27" t="n">
-        <v>0.03005768533093844</v>
+        <v>0.030041267032894</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.02607599157231788</v>
+        <v>-0.02607561571305239</v>
       </c>
       <c r="O27" t="n">
         <v>-0</v>
@@ -6065,19 +6065,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G28" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="J28" t="n">
         <v>-680000000</v>
       </c>
       <c r="K28" t="n">
-        <v>-655362070.4300001</v>
+        <v>-750323402.3400002</v>
       </c>
       <c r="L28" t="n">
         <v>0.1050151041880321</v>
@@ -6089,10 +6089,10 @@
         <v>-0.07502986587896165</v>
       </c>
       <c r="O28" t="n">
-        <v>49037011.18283243</v>
+        <v>56142426.80713306</v>
       </c>
       <c r="P28" t="n">
-        <v>24518505.59141621</v>
+        <v>28071213.40356653</v>
       </c>
     </row>
     <row r="29">
@@ -6123,19 +6123,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G29" t="n">
-        <v>133911619.36</v>
+        <v>425995266.0600001</v>
       </c>
       <c r="H29" t="n">
         <v>-90269181.22613968</v>
       </c>
       <c r="I29" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="J29" t="n">
         <v>-68000000</v>
       </c>
       <c r="K29" t="n">
-        <v>111642438.1338603</v>
+        <v>403726084.8338604</v>
       </c>
       <c r="L29" t="n">
         <v>0.05822765833026367</v>
@@ -6147,10 +6147,10 @@
         <v>-0.01988106139069767</v>
       </c>
       <c r="O29" t="n">
-        <v>-2034605.985817574</v>
+        <v>-7357627.821140663</v>
       </c>
       <c r="P29" t="n">
-        <v>-2034605.985817574</v>
+        <v>-7357627.821140663</v>
       </c>
     </row>
     <row r="30">
@@ -6181,19 +6181,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G30" t="n">
-        <v>2364336920.83</v>
+        <v>2339361769.16</v>
       </c>
       <c r="H30" t="n">
         <v>-51490547.94520548</v>
       </c>
       <c r="I30" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="J30" t="n">
         <v>-68000000</v>
       </c>
       <c r="K30" t="n">
-        <v>2380846372.884794</v>
+        <v>2355871221.214795</v>
       </c>
       <c r="L30" t="n">
         <v>0.05839364669442126</v>
@@ -6205,10 +6205,10 @@
         <v>-0.01725628309459371</v>
       </c>
       <c r="O30" t="n">
-        <v>-34237132.51269718</v>
+        <v>-33877983.93974058</v>
       </c>
       <c r="P30" t="n">
-        <v>-34237132.51269718</v>
+        <v>-33877983.93974058</v>
       </c>
     </row>
     <row r="31">
@@ -6239,19 +6239,19 @@
         <v>0.75</v>
       </c>
       <c r="G31" t="n">
-        <v>-157998693</v>
+        <v>368810148.66</v>
       </c>
       <c r="H31" t="n">
         <v>-92049904.10958904</v>
       </c>
       <c r="I31" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="J31" t="n">
         <v>-68000000</v>
       </c>
       <c r="K31" t="n">
-        <v>-182048597.109589</v>
+        <v>344760244.5504109</v>
       </c>
       <c r="L31" t="n">
         <v>0.05851824187679444</v>
@@ -6263,10 +6263,10 @@
         <v>-0.01489062910622074</v>
       </c>
       <c r="O31" t="n">
-        <v>2033113.604150025</v>
+        <v>-3850272.699127598</v>
       </c>
       <c r="P31" t="n">
-        <v>1016556.802075012</v>
+        <v>-3850272.699127598</v>
       </c>
     </row>
     <row r="32">
@@ -6297,19 +6297,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G32" t="n">
-        <v>-194599255.21</v>
+        <v>-180822610.01</v>
       </c>
       <c r="H32" t="n">
         <v>-51458493.15068493</v>
       </c>
       <c r="I32" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="J32" t="n">
         <v>-68000000</v>
       </c>
       <c r="K32" t="n">
-        <v>-178057748.3606849</v>
+        <v>-164281103.1606849</v>
       </c>
       <c r="L32" t="n">
         <v>0.05821004393128892</v>
@@ -6321,10 +6321,10 @@
         <v>-0.01266202848122933</v>
       </c>
       <c r="O32" t="n">
-        <v>1503048.187364371</v>
+        <v>1386754.671432244</v>
       </c>
       <c r="P32" t="n">
-        <v>751524.0936821856</v>
+        <v>693377.3357161219</v>
       </c>
     </row>
     <row r="33">
@@ -6355,19 +6355,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G33" t="n">
-        <v>398501812.66</v>
+        <v>396368601.78</v>
       </c>
       <c r="H33" t="n">
         <v>-51445520.54794521</v>
       </c>
       <c r="I33" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="J33" t="n">
         <v>-68000000</v>
       </c>
       <c r="K33" t="n">
-        <v>415056292.1120548</v>
+        <v>412923081.2320548</v>
       </c>
       <c r="L33" t="n">
         <v>0.05808035784574397</v>
@@ -6379,10 +6379,10 @@
         <v>-0.01061579379409725</v>
       </c>
       <c r="O33" t="n">
-        <v>-2570255.339169097</v>
+        <v>-2557045.331856611</v>
       </c>
       <c r="P33" t="n">
-        <v>-2570255.339169097</v>
+        <v>-2557045.331856611</v>
       </c>
     </row>
     <row r="34">
@@ -6413,19 +6413,19 @@
         <v>0.5</v>
       </c>
       <c r="G34" t="n">
-        <v>772422393.1500001</v>
+        <v>270725457.28</v>
       </c>
       <c r="H34" t="n">
         <v>-90799555.08645856</v>
       </c>
       <c r="I34" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="J34" t="n">
         <v>-34000000</v>
       </c>
       <c r="K34" t="n">
-        <v>715622838.0635415</v>
+        <v>213925902.1935414</v>
       </c>
       <c r="L34" t="n">
         <v>0.0579990267461179</v>
@@ -6437,10 +6437,10 @@
         <v>-0.008701770963537303</v>
       </c>
       <c r="O34" t="n">
-        <v>-3113593.016552742</v>
+        <v>-930767.1020281399</v>
       </c>
       <c r="P34" t="n">
-        <v>-3113593.016552742</v>
+        <v>-930767.1020281399</v>
       </c>
     </row>
     <row r="35">
@@ -6471,19 +6471,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G35" t="n">
-        <v>-35157733.02</v>
+        <v>-35174959.2</v>
       </c>
       <c r="H35" t="n">
         <v>2247136.761733663</v>
       </c>
       <c r="I35" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="J35" t="n">
         <v>-34000000</v>
       </c>
       <c r="K35" t="n">
-        <v>1089403.741733659</v>
+        <v>1072177.561733659</v>
       </c>
       <c r="L35" t="n">
         <v>0.05738520780446178</v>
@@ -6495,10 +6495,10 @@
         <v>-0.006933843412663093</v>
       </c>
       <c r="O35" t="n">
-        <v>-3147.397899312691</v>
+        <v>-3097.629718180046</v>
       </c>
       <c r="P35" t="n">
-        <v>-3147.397899312691</v>
+        <v>-3097.629718180046</v>
       </c>
     </row>
     <row r="36">
@@ -6529,19 +6529,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G36" t="n">
-        <v>-35284909.43000001</v>
+        <v>-35427280.72000001</v>
       </c>
       <c r="H36" t="n">
         <v>2266152.03233775</v>
       </c>
       <c r="I36" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="J36" t="n">
         <v>-34000000</v>
       </c>
       <c r="K36" t="n">
-        <v>981242.6023377441</v>
+        <v>838871.312337745</v>
       </c>
       <c r="L36" t="n">
         <v>0.05695407285841891</v>
@@ -6553,10 +6553,10 @@
         <v>-0.005293779960104272</v>
       </c>
       <c r="O36" t="n">
-        <v>-1731.494141418705</v>
+        <v>-1480.266714119976</v>
       </c>
       <c r="P36" t="n">
-        <v>-1731.494141418705</v>
+        <v>-1480.266714119976</v>
       </c>
     </row>
     <row r="37">
@@ -6587,19 +6587,19 @@
         <v>0.25</v>
       </c>
       <c r="G37" t="n">
-        <v>-35779408.35</v>
+        <v>-35839034.46</v>
       </c>
       <c r="H37" t="n">
         <v>2248181.001571974</v>
       </c>
       <c r="I37" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="J37" t="n">
         <v>-34000000</v>
       </c>
       <c r="K37" t="n">
-        <v>468772.6515719742</v>
+        <v>409146.5415719748</v>
       </c>
       <c r="L37" t="n">
         <v>0.05664439372837885</v>
@@ -6611,10 +6611,10 @@
         <v>-0.003768699327115023</v>
       </c>
       <c r="O37" t="n">
-        <v>-441.665794137306</v>
+        <v>-385.487573978435</v>
       </c>
       <c r="P37" t="n">
-        <v>-441.665794137306</v>
+        <v>-385.487573978435</v>
       </c>
     </row>
     <row r="38">
@@ -6645,19 +6645,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G38" t="n">
-        <v>-35814156.50999999</v>
+        <v>-35777615.53999999</v>
       </c>
       <c r="H38" t="n">
         <v>2248686.278913092</v>
       </c>
       <c r="I38" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="J38" t="n">
         <v>-34000000</v>
       </c>
       <c r="K38" t="n">
-        <v>434529.7689131051</v>
+        <v>471070.7389131002</v>
       </c>
       <c r="L38" t="n">
         <v>0.05642057743315654</v>
@@ -6669,10 +6669,10 @@
         <v>-0.002356874069323035</v>
       </c>
       <c r="O38" t="n">
-        <v>-170.688657450038</v>
+        <v>-185.0424015601879</v>
       </c>
       <c r="P38" t="n">
-        <v>-170.688657450038</v>
+        <v>-185.0424015601879</v>
       </c>
     </row>
     <row r="39">
@@ -6703,19 +6703,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G39" t="n">
-        <v>-35845139.96</v>
+        <v>-35715304.73</v>
       </c>
       <c r="H39" t="n">
         <v>2261537.165955536</v>
       </c>
       <c r="I39" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="J39" t="n">
         <v>-34000000</v>
       </c>
       <c r="K39" t="n">
-        <v>416397.2059555352</v>
+        <v>546232.4359555319</v>
       </c>
       <c r="L39" t="n">
         <v>0.05625883751011833</v>
@@ -6727,10 +6727,10 @@
         <v>-0.001044890098674874</v>
       </c>
       <c r="O39" t="n">
-        <v>-36.25744313490175</v>
+        <v>-47.56273865874938</v>
       </c>
       <c r="P39" t="n">
-        <v>-36.25744313490175</v>
+        <v>-47.56273865874938</v>
       </c>
     </row>
     <row r="40">
@@ -6761,28 +6761,28 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-36463708.53000001</v>
+        <v>-36430105.95000001</v>
       </c>
       <c r="H40" t="n">
         <v>4044566.584325174</v>
       </c>
       <c r="I40" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="J40" t="n">
         <v>-34000000</v>
       </c>
       <c r="K40" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="L40" t="n">
-        <v>0.05613367690325632</v>
+        <v>0.05611688274594639</v>
       </c>
       <c r="M40" t="n">
-        <v>0.05630773793266308</v>
+        <v>0.05629090260522096</v>
       </c>
       <c r="N40" t="n">
-        <v>0.0001740610294067579</v>
+        <v>0.0001740198592745656</v>
       </c>
       <c r="O40" t="n">
         <v>-0</v>
@@ -6819,19 +6819,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G41" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="J41" t="n">
         <v>-680000000</v>
       </c>
       <c r="K41" t="n">
-        <v>-655362070.4300001</v>
+        <v>-750323402.3400002</v>
       </c>
       <c r="L41" t="n">
         <v>0.1050151041880321</v>
@@ -6843,10 +6843,10 @@
         <v>-0.02468474605999638</v>
       </c>
       <c r="O41" t="n">
-        <v>16133124.51527166</v>
+        <v>18470798.69717064</v>
       </c>
       <c r="P41" t="n">
-        <v>8066562.257635831</v>
+        <v>9235399.348585319</v>
       </c>
     </row>
     <row r="42">
@@ -6877,19 +6877,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G42" t="n">
-        <v>133911619.36</v>
+        <v>425995266.0600001</v>
       </c>
       <c r="H42" t="n">
         <v>-90269181.22613968</v>
       </c>
       <c r="I42" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="J42" t="n">
         <v>-68000000</v>
       </c>
       <c r="K42" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="L42" t="n">
         <v>0.05822765833026367</v>
@@ -6901,10 +6901,10 @@
         <v>0.02495849603761435</v>
       </c>
       <c r="O42" t="n">
-        <v>998478.8176328007</v>
+        <v>7680949.978212211</v>
       </c>
       <c r="P42" t="n">
-        <v>499239.4088164003</v>
+        <v>3840474.989106106</v>
       </c>
     </row>
     <row r="43">
@@ -6935,19 +6935,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G43" t="n">
-        <v>2364336920.83</v>
+        <v>2339361769.16</v>
       </c>
       <c r="H43" t="n">
         <v>-51490547.94520548</v>
       </c>
       <c r="I43" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="J43" t="n">
         <v>-68000000</v>
       </c>
       <c r="K43" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="L43" t="n">
         <v>0.05839364669442126</v>
@@ -6959,10 +6959,10 @@
         <v>0.02216014487646945</v>
       </c>
       <c r="O43" t="n">
-        <v>42710842.25011992</v>
+        <v>42249631.43402077</v>
       </c>
       <c r="P43" t="n">
-        <v>21355421.12505996</v>
+        <v>21124815.71701039</v>
       </c>
     </row>
     <row r="44">
@@ -6993,19 +6993,19 @@
         <v>0.75</v>
       </c>
       <c r="G44" t="n">
-        <v>-157998693</v>
+        <v>368810148.66</v>
       </c>
       <c r="H44" t="n">
         <v>-92049904.10958904</v>
       </c>
       <c r="I44" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="J44" t="n">
         <v>-68000000</v>
       </c>
       <c r="K44" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="L44" t="n">
         <v>0.05851824187679444</v>
@@ -7017,10 +7017,10 @@
         <v>0.01962016480210327</v>
       </c>
       <c r="O44" t="n">
-        <v>-3679496.012868645</v>
+        <v>4072561.206562099</v>
       </c>
       <c r="P44" t="n">
-        <v>-3679496.012868645</v>
+        <v>2036280.60328105</v>
       </c>
     </row>
     <row r="45">
@@ -7051,19 +7051,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G45" t="n">
-        <v>-194599255.21</v>
+        <v>-180822610.01</v>
       </c>
       <c r="H45" t="n">
         <v>-51458493.15068493</v>
       </c>
       <c r="I45" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="J45" t="n">
         <v>-68000000</v>
       </c>
       <c r="K45" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="L45" t="n">
         <v>0.05821004393128892</v>
@@ -7075,10 +7075,10 @@
         <v>0.01722340313955706</v>
       </c>
       <c r="O45" t="n">
-        <v>-2825301.197085175</v>
+        <v>-2667114.054291679</v>
       </c>
       <c r="P45" t="n">
-        <v>-2825301.197085175</v>
+        <v>-2667114.054291679</v>
       </c>
     </row>
     <row r="46">
@@ -7109,19 +7109,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G46" t="n">
-        <v>398501812.66</v>
+        <v>396368601.78</v>
       </c>
       <c r="H46" t="n">
         <v>-51445520.54794521</v>
       </c>
       <c r="I46" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="J46" t="n">
         <v>-68000000</v>
       </c>
       <c r="K46" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="L46" t="n">
         <v>0.05808035784574397</v>
@@ -7133,10 +7133,10 @@
         <v>0.01501522413586098</v>
       </c>
       <c r="O46" t="n">
-        <v>3039824.674730283</v>
+        <v>3021140.135026467</v>
       </c>
       <c r="P46" t="n">
-        <v>1519912.337365141</v>
+        <v>1510570.067513233</v>
       </c>
     </row>
     <row r="47">
@@ -7167,19 +7167,19 @@
         <v>0.5</v>
       </c>
       <c r="G47" t="n">
-        <v>772422393.1500001</v>
+        <v>270725457.28</v>
       </c>
       <c r="H47" t="n">
         <v>-90799555.08645856</v>
       </c>
       <c r="I47" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="J47" t="n">
         <v>-34000000</v>
       </c>
       <c r="K47" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="L47" t="n">
         <v>0.0579990267461179</v>
@@ -7191,10 +7191,10 @@
         <v>0.01294941997535037</v>
       </c>
       <c r="O47" t="n">
-        <v>4413310.197437519</v>
+        <v>1164968.035973991</v>
       </c>
       <c r="P47" t="n">
-        <v>2206655.09871876</v>
+        <v>582484.0179869956</v>
       </c>
     </row>
     <row r="48">
@@ -7225,19 +7225,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G48" t="n">
-        <v>-35157733.02</v>
+        <v>-35174959.2</v>
       </c>
       <c r="H48" t="n">
         <v>2247136.761733663</v>
       </c>
       <c r="I48" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="J48" t="n">
         <v>-34000000</v>
       </c>
       <c r="K48" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="L48" t="n">
         <v>0.05738520780446178</v>
@@ -7249,10 +7249,10 @@
         <v>0.01103784963125674</v>
       </c>
       <c r="O48" t="n">
-        <v>-151359.2553223936</v>
+        <v>-151438.4803159607</v>
       </c>
       <c r="P48" t="n">
-        <v>-151359.2553223936</v>
+        <v>-151438.4803159607</v>
       </c>
     </row>
     <row r="49">
@@ -7283,19 +7283,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G49" t="n">
-        <v>-35284909.43000001</v>
+        <v>-35427280.72000001</v>
       </c>
       <c r="H49" t="n">
         <v>2266152.03233775</v>
       </c>
       <c r="I49" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="J49" t="n">
         <v>-34000000</v>
       </c>
       <c r="K49" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="L49" t="n">
         <v>0.05695407285841891</v>
@@ -7307,10 +7307,10 @@
         <v>0.009264716116377802</v>
       </c>
       <c r="O49" t="n">
-        <v>-101969.8046016301</v>
+        <v>-102409.4811299543</v>
       </c>
       <c r="P49" t="n">
-        <v>-101969.8046016301</v>
+        <v>-102409.4811299543</v>
       </c>
     </row>
     <row r="50">
@@ -7341,19 +7341,19 @@
         <v>0.25</v>
       </c>
       <c r="G50" t="n">
-        <v>-35779408.35</v>
+        <v>-35839034.46</v>
       </c>
       <c r="H50" t="n">
         <v>2248181.001571974</v>
       </c>
       <c r="I50" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="J50" t="n">
         <v>-34000000</v>
       </c>
       <c r="K50" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="L50" t="n">
         <v>0.05664439372837885</v>
@@ -7365,10 +7365,10 @@
         <v>0.007618063727031256</v>
       </c>
       <c r="O50" t="n">
-        <v>-63860.7566964745</v>
+        <v>-63974.31557291824</v>
       </c>
       <c r="P50" t="n">
-        <v>-63860.7566964745</v>
+        <v>-63974.31557291824</v>
       </c>
     </row>
     <row r="51">
@@ -7399,19 +7399,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G51" t="n">
-        <v>-35814156.50999999</v>
+        <v>-35777615.53999999</v>
       </c>
       <c r="H51" t="n">
         <v>2248686.278913092</v>
       </c>
       <c r="I51" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="J51" t="n">
         <v>-34000000</v>
       </c>
       <c r="K51" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="L51" t="n">
         <v>0.05642057743315654</v>
@@ -7423,10 +7423,10 @@
         <v>0.006094907231449384</v>
       </c>
       <c r="O51" t="n">
-        <v>-34096.40453974175</v>
+        <v>-34059.28556935889</v>
       </c>
       <c r="P51" t="n">
-        <v>-34096.40453974175</v>
+        <v>-34059.28556935889</v>
       </c>
     </row>
     <row r="52">
@@ -7457,19 +7457,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G52" t="n">
-        <v>-35845139.96</v>
+        <v>-35715304.73</v>
       </c>
       <c r="H52" t="n">
         <v>2261537.165955536</v>
       </c>
       <c r="I52" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="J52" t="n">
         <v>-34000000</v>
       </c>
       <c r="K52" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="L52" t="n">
         <v>0.05625883751011833</v>
@@ -7481,10 +7481,10 @@
         <v>0.004682431355023151</v>
       </c>
       <c r="O52" t="n">
-        <v>-13104.40956145641</v>
+        <v>-13053.74751546153</v>
       </c>
       <c r="P52" t="n">
-        <v>-13104.40956145641</v>
+        <v>-13053.74751546153</v>
       </c>
     </row>
     <row r="53">
@@ -7515,28 +7515,28 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>-36463708.53000001</v>
+        <v>-36430105.95000001</v>
       </c>
       <c r="H53" t="n">
         <v>4044566.584325174</v>
       </c>
       <c r="I53" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="J53" t="n">
         <v>-34000000</v>
       </c>
       <c r="K53" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="L53" t="n">
-        <v>0.05613367690325632</v>
+        <v>0.05611688274594639</v>
       </c>
       <c r="M53" t="n">
-        <v>0.05950694809658197</v>
+        <v>0.05949006088389019</v>
       </c>
       <c r="N53" t="n">
-        <v>0.003373271193325644</v>
+        <v>0.0033731781379438</v>
       </c>
       <c r="O53" t="n">
         <v>-0</v>
@@ -7573,19 +7573,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G54" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="J54" t="n">
         <v>-680000000</v>
       </c>
       <c r="K54" t="n">
-        <v>-655362070.4300001</v>
+        <v>-750323402.3400002</v>
       </c>
       <c r="L54" t="n">
         <v>0.1050151041880321</v>
@@ -7597,10 +7597,10 @@
         <v>-0.01765980557248192</v>
       </c>
       <c r="O54" t="n">
-        <v>11541858.34133637</v>
+        <v>13214262.48289847</v>
       </c>
       <c r="P54" t="n">
-        <v>5770929.170668184</v>
+        <v>6607131.241449235</v>
       </c>
     </row>
     <row r="55">
@@ -7631,19 +7631,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G55" t="n">
-        <v>133911619.36</v>
+        <v>425995266.0600001</v>
       </c>
       <c r="H55" t="n">
         <v>-90269181.22613968</v>
       </c>
       <c r="I55" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="J55" t="n">
         <v>-68000000</v>
       </c>
       <c r="K55" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="L55" t="n">
         <v>0.05822765833026367</v>
@@ -7655,10 +7655,10 @@
         <v>0.03235719235381929</v>
       </c>
       <c r="O55" t="n">
-        <v>1294467.868363062</v>
+        <v>9957890.713066883</v>
       </c>
       <c r="P55" t="n">
-        <v>647233.9341815311</v>
+        <v>4978945.356533442</v>
       </c>
     </row>
     <row r="56">
@@ -7689,19 +7689,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G56" t="n">
-        <v>2364336920.83</v>
+        <v>2339361769.16</v>
       </c>
       <c r="H56" t="n">
         <v>-51490547.94520548</v>
       </c>
       <c r="I56" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="J56" t="n">
         <v>-68000000</v>
       </c>
       <c r="K56" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="L56" t="n">
         <v>0.05839364669442126</v>
@@ -7713,10 +7713,10 @@
         <v>0.02992819194854235</v>
       </c>
       <c r="O56" t="n">
-        <v>57682758.4959884</v>
+        <v>57059874.21838531</v>
       </c>
       <c r="P56" t="n">
-        <v>28841379.2479942</v>
+        <v>28529937.10919265</v>
       </c>
     </row>
     <row r="57">
@@ -7747,19 +7747,19 @@
         <v>0.75</v>
       </c>
       <c r="G57" t="n">
-        <v>-157998693</v>
+        <v>368810148.66</v>
       </c>
       <c r="H57" t="n">
         <v>-92049904.10958904</v>
       </c>
       <c r="I57" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="J57" t="n">
         <v>-68000000</v>
       </c>
       <c r="K57" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="L57" t="n">
         <v>0.05851824187679444</v>
@@ -7771,10 +7771,10 @@
         <v>0.02772661859587089</v>
       </c>
       <c r="O57" t="n">
-        <v>-5199751.561867619</v>
+        <v>5755219.307361899</v>
       </c>
       <c r="P57" t="n">
-        <v>-5199751.561867619</v>
+        <v>2877609.653680949</v>
       </c>
     </row>
     <row r="58">
@@ -7805,19 +7805,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G58" t="n">
-        <v>-194599255.21</v>
+        <v>-180822610.01</v>
       </c>
       <c r="H58" t="n">
         <v>-51458493.15068493</v>
       </c>
       <c r="I58" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="J58" t="n">
         <v>-68000000</v>
       </c>
       <c r="K58" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="L58" t="n">
         <v>0.05821004393128892</v>
@@ -7829,10 +7829,10 @@
         <v>0.02564903369930005</v>
       </c>
       <c r="O58" t="n">
-        <v>-4207428.9864514</v>
+        <v>-3971857.228452666</v>
       </c>
       <c r="P58" t="n">
-        <v>-4207428.9864514</v>
+        <v>-3971857.228452666</v>
       </c>
     </row>
     <row r="59">
@@ -7863,19 +7863,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G59" t="n">
-        <v>398501812.66</v>
+        <v>396368601.78</v>
       </c>
       <c r="H59" t="n">
         <v>-51445520.54794521</v>
       </c>
       <c r="I59" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="J59" t="n">
         <v>-68000000</v>
       </c>
       <c r="K59" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="L59" t="n">
         <v>0.05808035784574397</v>
@@ -7887,10 +7887,10 @@
         <v>0.02373722363569292</v>
       </c>
       <c r="O59" t="n">
-        <v>4805589.145022292</v>
+        <v>4776051.184518578</v>
       </c>
       <c r="P59" t="n">
-        <v>2402794.572511146</v>
+        <v>2388025.592259289</v>
       </c>
     </row>
     <row r="60">
@@ -7921,19 +7921,19 @@
         <v>0.5</v>
       </c>
       <c r="G60" t="n">
-        <v>772422393.1500001</v>
+        <v>270725457.28</v>
       </c>
       <c r="H60" t="n">
         <v>-90799555.08645856</v>
       </c>
       <c r="I60" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="J60" t="n">
         <v>-34000000</v>
       </c>
       <c r="K60" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="L60" t="n">
         <v>0.0579990267461179</v>
@@ -7945,10 +7945,10 @@
         <v>0.02195017150422629</v>
       </c>
       <c r="O60" t="n">
-        <v>7480869.0983461</v>
+        <v>1974702.20560044</v>
       </c>
       <c r="P60" t="n">
-        <v>3740434.54917305</v>
+        <v>987351.1028002198</v>
       </c>
     </row>
     <row r="61">
@@ -7979,19 +7979,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G61" t="n">
-        <v>-35157733.02</v>
+        <v>-35174959.2</v>
       </c>
       <c r="H61" t="n">
         <v>2247136.761733663</v>
       </c>
       <c r="I61" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="J61" t="n">
         <v>-34000000</v>
       </c>
       <c r="K61" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="L61" t="n">
         <v>0.05738520780446178</v>
@@ -8003,10 +8003,10 @@
         <v>0.02029522229252897</v>
       </c>
       <c r="O61" t="n">
-        <v>-278303.2778504948</v>
+        <v>-278448.9483306411</v>
       </c>
       <c r="P61" t="n">
-        <v>-278303.2778504948</v>
+        <v>-278448.9483306411</v>
       </c>
     </row>
     <row r="62">
@@ -8037,19 +8037,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G62" t="n">
-        <v>-35284909.43000001</v>
+        <v>-35427280.72000001</v>
       </c>
       <c r="H62" t="n">
         <v>2266152.03233775</v>
       </c>
       <c r="I62" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="J62" t="n">
         <v>-34000000</v>
       </c>
       <c r="K62" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="L62" t="n">
         <v>0.05695407285841891</v>
@@ -8061,10 +8061,10 @@
         <v>0.01876196760334525</v>
       </c>
       <c r="O62" t="n">
-        <v>-206498.9521992186</v>
+        <v>-207389.3407094274</v>
       </c>
       <c r="P62" t="n">
-        <v>-206498.9521992186</v>
+        <v>-207389.3407094274</v>
       </c>
     </row>
     <row r="63">
@@ -8095,19 +8095,19 @@
         <v>0.25</v>
       </c>
       <c r="G63" t="n">
-        <v>-35779408.35</v>
+        <v>-35839034.46</v>
       </c>
       <c r="H63" t="n">
         <v>2248181.001571974</v>
       </c>
       <c r="I63" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="J63" t="n">
         <v>-34000000</v>
       </c>
       <c r="K63" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="L63" t="n">
         <v>0.05664439372837885</v>
@@ -8119,10 +8119,10 @@
         <v>0.01733996627504109</v>
       </c>
       <c r="O63" t="n">
-        <v>-145357.5878456194</v>
+        <v>-145616.0665297474</v>
       </c>
       <c r="P63" t="n">
-        <v>-145357.5878456194</v>
+        <v>-145616.0665297474</v>
       </c>
     </row>
     <row r="64">
@@ -8153,19 +8153,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G64" t="n">
-        <v>-35814156.50999999</v>
+        <v>-35777615.53999999</v>
       </c>
       <c r="H64" t="n">
         <v>2248686.278913092</v>
       </c>
       <c r="I64" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="J64" t="n">
         <v>-34000000</v>
       </c>
       <c r="K64" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="L64" t="n">
         <v>0.05642057743315654</v>
@@ -8177,10 +8177,10 @@
         <v>0.01602670204966161</v>
       </c>
       <c r="O64" t="n">
-        <v>-89657.29842506933</v>
+        <v>-89559.69321860342</v>
       </c>
       <c r="P64" t="n">
-        <v>-89657.29842506933</v>
+        <v>-89559.69321860342</v>
       </c>
     </row>
     <row r="65">
@@ -8211,19 +8211,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G65" t="n">
-        <v>-35845139.96</v>
+        <v>-35715304.73</v>
       </c>
       <c r="H65" t="n">
         <v>2261537.165955536</v>
       </c>
       <c r="I65" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="J65" t="n">
         <v>-34000000</v>
       </c>
       <c r="K65" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="L65" t="n">
         <v>0.05625883751011833</v>
@@ -8235,10 +8235,10 @@
         <v>0.01481092208165177</v>
       </c>
       <c r="O65" t="n">
-        <v>-41450.34368364463</v>
+        <v>-41290.09539406269</v>
       </c>
       <c r="P65" t="n">
-        <v>-41450.34368364463</v>
+        <v>-41290.09539406269</v>
       </c>
     </row>
     <row r="66">
@@ -8269,28 +8269,28 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>-36463708.53000001</v>
+        <v>-36430105.95000001</v>
       </c>
       <c r="H66" t="n">
         <v>4044566.584325174</v>
       </c>
       <c r="I66" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="J66" t="n">
         <v>-34000000</v>
       </c>
       <c r="K66" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="L66" t="n">
-        <v>0.05613367690325632</v>
+        <v>0.05611688274594639</v>
       </c>
       <c r="M66" t="n">
-        <v>0.06981978911298969</v>
+        <v>0.06980273792339808</v>
       </c>
       <c r="N66" t="n">
-        <v>0.01368611220973337</v>
+        <v>0.01368585517745169</v>
       </c>
       <c r="O66" t="n">
         <v>-0</v>
@@ -8327,19 +8327,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G67" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="J67" t="n">
         <v>-680000000</v>
       </c>
       <c r="K67" t="n">
-        <v>-655362070.4300001</v>
+        <v>-750323402.3400002</v>
       </c>
       <c r="L67" t="n">
         <v>0.1050151041880321</v>
@@ -8351,10 +8351,10 @@
         <v>-0.08728823124945828</v>
       </c>
       <c r="O67" t="n">
-        <v>57048668.84360989</v>
+        <v>65314965.9357306</v>
       </c>
       <c r="P67" t="n">
-        <v>28524334.42180495</v>
+        <v>32657482.9678653</v>
       </c>
     </row>
     <row r="68">
@@ -8385,19 +8385,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G68" t="n">
-        <v>133911619.36</v>
+        <v>425995266.0600001</v>
       </c>
       <c r="H68" t="n">
         <v>-90269181.22613968</v>
       </c>
       <c r="I68" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="J68" t="n">
         <v>-68000000</v>
       </c>
       <c r="K68" t="n">
-        <v>111642438.1338603</v>
+        <v>403726084.8338604</v>
       </c>
       <c r="L68" t="n">
         <v>0.05822765833026367</v>
@@ -8409,10 +8409,10 @@
         <v>-0.03226565096877909</v>
       </c>
       <c r="O68" t="n">
-        <v>-3302031.280286429</v>
+        <v>-11940944.52855428</v>
       </c>
       <c r="P68" t="n">
-        <v>-3302031.280286429</v>
+        <v>-11940944.52855428</v>
       </c>
     </row>
     <row r="69">
@@ -8443,19 +8443,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G69" t="n">
-        <v>2364336920.83</v>
+        <v>2339361769.16</v>
       </c>
       <c r="H69" t="n">
         <v>-51490547.94520548</v>
       </c>
       <c r="I69" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="J69" t="n">
         <v>-68000000</v>
       </c>
       <c r="K69" t="n">
-        <v>2380846372.884794</v>
+        <v>2355871221.214795</v>
       </c>
       <c r="L69" t="n">
         <v>0.05839364669442126</v>
@@ -8467,10 +8467,10 @@
         <v>-0.0297728173926024</v>
       </c>
       <c r="O69" t="n">
-        <v>-59070420.24978229</v>
+        <v>-58450769.72476275</v>
       </c>
       <c r="P69" t="n">
-        <v>-59070420.24978229</v>
+        <v>-58450769.72476275</v>
       </c>
     </row>
     <row r="70">
@@ -8501,19 +8501,19 @@
         <v>0.75</v>
       </c>
       <c r="G70" t="n">
-        <v>-157998693</v>
+        <v>368810148.66</v>
       </c>
       <c r="H70" t="n">
         <v>-92049904.10958904</v>
       </c>
       <c r="I70" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="J70" t="n">
         <v>-68000000</v>
       </c>
       <c r="K70" t="n">
-        <v>-182048597.109589</v>
+        <v>344760244.5504109</v>
       </c>
       <c r="L70" t="n">
         <v>0.05851824187679444</v>
@@ -8525,10 +8525,10 @@
         <v>-0.02753489969717293</v>
       </c>
       <c r="O70" t="n">
-        <v>3759517.396067685</v>
+        <v>-7119704.064951282</v>
       </c>
       <c r="P70" t="n">
-        <v>1879758.698033842</v>
+        <v>-7119704.064951282</v>
       </c>
     </row>
     <row r="71">
@@ -8559,19 +8559,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G71" t="n">
-        <v>-194599255.21</v>
+        <v>-180822610.01</v>
       </c>
       <c r="H71" t="n">
         <v>-51458493.15068493</v>
       </c>
       <c r="I71" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="J71" t="n">
         <v>-68000000</v>
       </c>
       <c r="K71" t="n">
-        <v>-178057748.3606849</v>
+        <v>-164281103.1606849</v>
       </c>
       <c r="L71" t="n">
         <v>0.05821004393128892</v>
@@ -8583,10 +8583,10 @@
         <v>-0.02543179398870032</v>
       </c>
       <c r="O71" t="n">
-        <v>3018885.316267188</v>
+        <v>2785308.781212643</v>
       </c>
       <c r="P71" t="n">
-        <v>1509442.658133594</v>
+        <v>1392654.390606322</v>
       </c>
     </row>
     <row r="72">
@@ -8617,19 +8617,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G72" t="n">
-        <v>398501812.66</v>
+        <v>396368601.78</v>
       </c>
       <c r="H72" t="n">
         <v>-51445520.54794521</v>
       </c>
       <c r="I72" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="J72" t="n">
         <v>-68000000</v>
       </c>
       <c r="K72" t="n">
-        <v>415056292.1120548</v>
+        <v>412923081.2320548</v>
       </c>
       <c r="L72" t="n">
         <v>0.05808035784574397</v>
@@ -8641,10 +8641,10 @@
         <v>-0.02350867571892774</v>
       </c>
       <c r="O72" t="n">
-        <v>-5691830.536211658</v>
+        <v>-5662576.97456782</v>
       </c>
       <c r="P72" t="n">
-        <v>-5691830.536211658</v>
+        <v>-5662576.97456782</v>
       </c>
     </row>
     <row r="73">
@@ -8675,19 +8675,19 @@
         <v>0.5</v>
       </c>
       <c r="G73" t="n">
-        <v>772422393.1500001</v>
+        <v>270725457.28</v>
       </c>
       <c r="H73" t="n">
         <v>-90799555.08645856</v>
       </c>
       <c r="I73" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="J73" t="n">
         <v>-34000000</v>
       </c>
       <c r="K73" t="n">
-        <v>715622838.0635415</v>
+        <v>213925902.1935414</v>
       </c>
       <c r="L73" t="n">
         <v>0.0579990267461179</v>
@@ -8699,10 +8699,10 @@
         <v>-0.02171656780992581</v>
       </c>
       <c r="O73" t="n">
-        <v>-7770435.944569229</v>
+        <v>-2322868.180642799</v>
       </c>
       <c r="P73" t="n">
-        <v>-7770435.944569229</v>
+        <v>-2322868.180642799</v>
       </c>
     </row>
     <row r="74">
@@ -8733,19 +8733,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G74" t="n">
-        <v>-35157733.02</v>
+        <v>-35174959.2</v>
       </c>
       <c r="H74" t="n">
         <v>2247136.761733663</v>
       </c>
       <c r="I74" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="J74" t="n">
         <v>-34000000</v>
       </c>
       <c r="K74" t="n">
-        <v>1089403.741733659</v>
+        <v>1072177.561733659</v>
       </c>
       <c r="L74" t="n">
         <v>0.05738520780446178</v>
@@ -8757,10 +8757,10 @@
         <v>-0.02006419037968943</v>
       </c>
       <c r="O74" t="n">
-        <v>-9107.501697704229</v>
+        <v>-8963.489466439732</v>
       </c>
       <c r="P74" t="n">
-        <v>-9107.501697704229</v>
+        <v>-8963.489466439732</v>
       </c>
     </row>
     <row r="75">
@@ -8791,19 +8791,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G75" t="n">
-        <v>-35284909.43000001</v>
+        <v>-35427280.72000001</v>
       </c>
       <c r="H75" t="n">
         <v>2266152.03233775</v>
       </c>
       <c r="I75" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="J75" t="n">
         <v>-34000000</v>
       </c>
       <c r="K75" t="n">
-        <v>981242.6023377441</v>
+        <v>838871.312337745</v>
       </c>
       <c r="L75" t="n">
         <v>0.05695407285841891</v>
@@ -8815,10 +8815,10 @@
         <v>-0.01853809135614659</v>
       </c>
       <c r="O75" t="n">
-        <v>-6063.455001560041</v>
+        <v>-5183.6910080559</v>
       </c>
       <c r="P75" t="n">
-        <v>-6063.455001560041</v>
+        <v>-5183.6910080559</v>
       </c>
     </row>
     <row r="76">
@@ -8849,19 +8849,19 @@
         <v>0.25</v>
       </c>
       <c r="G76" t="n">
-        <v>-35779408.35</v>
+        <v>-35839034.46</v>
       </c>
       <c r="H76" t="n">
         <v>2248181.001571974</v>
       </c>
       <c r="I76" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="J76" t="n">
         <v>-34000000</v>
       </c>
       <c r="K76" t="n">
-        <v>468772.6515719742</v>
+        <v>409146.5415719748</v>
       </c>
       <c r="L76" t="n">
         <v>0.05664439372837885</v>
@@ -8873,10 +8873,10 @@
         <v>-0.01712553721773909</v>
       </c>
       <c r="O76" t="n">
-        <v>-2006.99587278852</v>
+        <v>-1751.713581300022</v>
       </c>
       <c r="P76" t="n">
-        <v>-2006.99587278852</v>
+        <v>-1751.713581300022</v>
       </c>
     </row>
     <row r="77">
@@ -8907,19 +8907,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G77" t="n">
-        <v>-35814156.50999999</v>
+        <v>-35777615.53999999</v>
       </c>
       <c r="H77" t="n">
         <v>2248686.278913092</v>
       </c>
       <c r="I77" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="J77" t="n">
         <v>-34000000</v>
       </c>
       <c r="K77" t="n">
-        <v>434529.7689131051</v>
+        <v>471070.7389131002</v>
       </c>
       <c r="L77" t="n">
         <v>0.05642057743315654</v>
@@ -8931,10 +8931,10 @@
         <v>-0.01582455504283544</v>
       </c>
       <c r="O77" t="n">
-        <v>-1146.040040985999</v>
+        <v>-1242.414139499919</v>
       </c>
       <c r="P77" t="n">
-        <v>-1146.040040985999</v>
+        <v>-1242.414139499919</v>
       </c>
     </row>
     <row r="78">
@@ -8965,19 +8965,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G78" t="n">
-        <v>-35845139.96</v>
+        <v>-35715304.73</v>
       </c>
       <c r="H78" t="n">
         <v>2261537.165955536</v>
       </c>
       <c r="I78" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="J78" t="n">
         <v>-34000000</v>
       </c>
       <c r="K78" t="n">
-        <v>416397.2059555352</v>
+        <v>546232.4359555319</v>
       </c>
       <c r="L78" t="n">
         <v>0.05625883751011833</v>
@@ -8989,10 +8989,10 @@
         <v>-0.01462200030522725</v>
       </c>
       <c r="O78" t="n">
-        <v>-507.3800060481344</v>
+        <v>-665.5842371055679</v>
       </c>
       <c r="P78" t="n">
-        <v>-507.3800060481344</v>
+        <v>-665.5842371055679</v>
       </c>
     </row>
     <row r="79">
@@ -9023,28 +9023,28 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>-36463708.53000001</v>
+        <v>-36430105.95000001</v>
       </c>
       <c r="H79" t="n">
         <v>4044566.584325174</v>
       </c>
       <c r="I79" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="J79" t="n">
         <v>-34000000</v>
       </c>
       <c r="K79" t="n">
-        <v>1580858.054325163</v>
+        <v>1614460.634325162</v>
       </c>
       <c r="L79" t="n">
-        <v>0.05613367690325632</v>
+        <v>0.05611688274594639</v>
       </c>
       <c r="M79" t="n">
-        <v>0.0426227362277094</v>
+        <v>0.04260611853542318</v>
       </c>
       <c r="N79" t="n">
-        <v>-0.01351094067554692</v>
+        <v>-0.01351076421052322</v>
       </c>
       <c r="O79" t="n">
         <v>-0</v>
@@ -9081,19 +9081,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G80" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="J80" t="n">
         <v>-680000000</v>
       </c>
       <c r="K80" t="n">
-        <v>-655362070.4300001</v>
+        <v>-750323402.3400002</v>
       </c>
       <c r="L80" t="n">
         <v>0.1050151041880321</v>
@@ -9105,10 +9105,10 @@
         <v>-0.06247613761654947</v>
       </c>
       <c r="O80" t="n">
-        <v>40832314.21345187</v>
+        <v>46748877.16030184</v>
       </c>
       <c r="P80" t="n">
-        <v>20416157.10672593</v>
+        <v>23374438.58015092</v>
       </c>
     </row>
     <row r="81">
@@ -9139,19 +9139,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G81" t="n">
-        <v>133911619.36</v>
+        <v>425995266.0600001</v>
       </c>
       <c r="H81" t="n">
         <v>-90269181.22613968</v>
       </c>
       <c r="I81" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="J81" t="n">
         <v>-68000000</v>
       </c>
       <c r="K81" t="n">
-        <v>111642438.1338603</v>
+        <v>403726084.8338604</v>
       </c>
       <c r="L81" t="n">
         <v>0.05822765833026367</v>
@@ -9163,10 +9163,10 @@
         <v>-0.01004192341464538</v>
       </c>
       <c r="O81" t="n">
-        <v>-1027679.412434135</v>
+        <v>-3716337.555696563</v>
       </c>
       <c r="P81" t="n">
-        <v>-1027679.412434135</v>
+        <v>-3716337.555696563</v>
       </c>
     </row>
     <row r="82">
@@ -9197,19 +9197,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G82" t="n">
-        <v>2364336920.83</v>
+        <v>2339361769.16</v>
       </c>
       <c r="H82" t="n">
         <v>-51490547.94520548</v>
       </c>
       <c r="I82" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="J82" t="n">
         <v>-68000000</v>
       </c>
       <c r="K82" t="n">
-        <v>2380846372.884794</v>
+        <v>2355871221.214795</v>
       </c>
       <c r="L82" t="n">
         <v>0.05839364669442126</v>
@@ -9221,10 +9221,10 @@
         <v>-0.01008473632087492</v>
       </c>
       <c r="O82" t="n">
-        <v>-20008506.57587884</v>
+        <v>-19798616.726574</v>
       </c>
       <c r="P82" t="n">
-        <v>-20008506.57587884</v>
+        <v>-19798616.726574</v>
       </c>
     </row>
     <row r="83">
@@ -9255,19 +9255,19 @@
         <v>0.75</v>
       </c>
       <c r="G83" t="n">
-        <v>-157998693</v>
+        <v>368810148.66</v>
       </c>
       <c r="H83" t="n">
         <v>-92049904.10958904</v>
       </c>
       <c r="I83" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="J83" t="n">
         <v>-68000000</v>
       </c>
       <c r="K83" t="n">
-        <v>-182048597.109589</v>
+        <v>344760244.5504109</v>
       </c>
       <c r="L83" t="n">
         <v>0.05851824187679444</v>
@@ -9279,10 +9279,10 @@
         <v>-0.01013182991584927</v>
       </c>
       <c r="O83" t="n">
-        <v>1383364.066749993</v>
+        <v>-2619789.119648522</v>
       </c>
       <c r="P83" t="n">
-        <v>691682.0333749967</v>
+        <v>-2619789.119648522</v>
       </c>
     </row>
     <row r="84">
@@ -9313,19 +9313,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G84" t="n">
-        <v>-194599255.21</v>
+        <v>-180822610.01</v>
       </c>
       <c r="H84" t="n">
         <v>-51458493.15068493</v>
       </c>
       <c r="I84" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="J84" t="n">
         <v>-68000000</v>
       </c>
       <c r="K84" t="n">
-        <v>-178057748.3606849</v>
+        <v>-164281103.1606849</v>
       </c>
       <c r="L84" t="n">
         <v>0.05821004393128892</v>
@@ -9337,10 +9337,10 @@
         <v>-0.01017508542911516</v>
       </c>
       <c r="O84" t="n">
-        <v>1207835.200590573</v>
+        <v>1114382.839366167</v>
       </c>
       <c r="P84" t="n">
-        <v>603917.6002952865</v>
+        <v>557191.4196830833</v>
       </c>
     </row>
     <row r="85">
@@ -9371,19 +9371,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G85" t="n">
-        <v>398501812.66</v>
+        <v>396368601.78</v>
       </c>
       <c r="H85" t="n">
         <v>-51445520.54794521</v>
       </c>
       <c r="I85" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="J85" t="n">
         <v>-68000000</v>
       </c>
       <c r="K85" t="n">
-        <v>415056292.1120548</v>
+        <v>412923081.2320548</v>
       </c>
       <c r="L85" t="n">
         <v>0.05808035784574397</v>
@@ -9395,10 +9395,10 @@
         <v>-0.01021994033044944</v>
       </c>
       <c r="O85" t="n">
-        <v>-2474412.81451163</v>
+        <v>-2461695.396566541</v>
       </c>
       <c r="P85" t="n">
-        <v>-2474412.81451163</v>
+        <v>-2461695.396566541</v>
       </c>
     </row>
     <row r="86">
@@ -9429,19 +9429,19 @@
         <v>0.5</v>
       </c>
       <c r="G86" t="n">
-        <v>772422393.1500001</v>
+        <v>270725457.28</v>
       </c>
       <c r="H86" t="n">
         <v>-90799555.08645856</v>
       </c>
       <c r="I86" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="J86" t="n">
         <v>-34000000</v>
       </c>
       <c r="K86" t="n">
-        <v>715622838.0635415</v>
+        <v>213925902.1935414</v>
       </c>
       <c r="L86" t="n">
         <v>0.0579990267461179</v>
@@ -9453,10 +9453,10 @@
         <v>-0.01026331977023442</v>
       </c>
       <c r="O86" t="n">
-        <v>-3672333.010964407</v>
+        <v>-1097794.970674105</v>
       </c>
       <c r="P86" t="n">
-        <v>-3672333.010964407</v>
+        <v>-1097794.970674105</v>
       </c>
     </row>
     <row r="87">
@@ -9487,19 +9487,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G87" t="n">
-        <v>-35157733.02</v>
+        <v>-35174959.2</v>
       </c>
       <c r="H87" t="n">
         <v>2247136.761733663</v>
       </c>
       <c r="I87" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="J87" t="n">
         <v>-34000000</v>
       </c>
       <c r="K87" t="n">
-        <v>1089403.741733659</v>
+        <v>1072177.561733659</v>
       </c>
       <c r="L87" t="n">
         <v>0.05738520780446178</v>
@@ -9511,10 +9511,10 @@
         <v>-0.01030407096516736</v>
       </c>
       <c r="O87" t="n">
-        <v>-4677.205610226033</v>
+        <v>-4603.247368068223</v>
       </c>
       <c r="P87" t="n">
-        <v>-4677.205610226033</v>
+        <v>-4603.247368068223</v>
       </c>
     </row>
     <row r="88">
@@ -9545,19 +9545,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G88" t="n">
-        <v>-35284909.43000001</v>
+        <v>-35427280.72000001</v>
       </c>
       <c r="H88" t="n">
         <v>2266152.03233775</v>
       </c>
       <c r="I88" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="J88" t="n">
         <v>-34000000</v>
       </c>
       <c r="K88" t="n">
-        <v>981242.6023377441</v>
+        <v>838871.312337745</v>
       </c>
       <c r="L88" t="n">
         <v>0.05695407285841891</v>
@@ -9569,10 +9569,10 @@
         <v>-0.01034491853166675</v>
       </c>
       <c r="O88" t="n">
-        <v>-3383.624926994878</v>
+        <v>-2892.685128228781</v>
       </c>
       <c r="P88" t="n">
-        <v>-3383.624926994878</v>
+        <v>-2892.685128228781</v>
       </c>
     </row>
     <row r="89">
@@ -9603,19 +9603,19 @@
         <v>0.25</v>
       </c>
       <c r="G89" t="n">
-        <v>-35779408.35</v>
+        <v>-35839034.46</v>
       </c>
       <c r="H89" t="n">
         <v>2248181.001571974</v>
       </c>
       <c r="I89" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="J89" t="n">
         <v>-34000000</v>
       </c>
       <c r="K89" t="n">
-        <v>468772.6515719742</v>
+        <v>409146.5415719748</v>
       </c>
       <c r="L89" t="n">
         <v>0.05664439372837885</v>
@@ -9627,10 +9627,10 @@
         <v>-0.01038544122264451</v>
       </c>
       <c r="O89" t="n">
-        <v>-1217.102704920988</v>
+        <v>-1062.291839736006</v>
       </c>
       <c r="P89" t="n">
-        <v>-1217.102704920988</v>
+        <v>-1062.291839736006</v>
       </c>
     </row>
     <row r="90">
@@ -9661,19 +9661,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>-35814156.50999999</v>
+        <v>-35777615.53999999</v>
       </c>
       <c r="H90" t="n">
         <v>2248686.278913092</v>
       </c>
       <c r="I90" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="J90" t="n">
         <v>-34000000</v>
       </c>
       <c r="K90" t="n">
-        <v>434529.7689131051</v>
+        <v>471070.7389131002</v>
       </c>
       <c r="L90" t="n">
         <v>0.05642057743315654</v>
@@ -9685,10 +9685,10 @@
         <v>-0.01042652380310684</v>
       </c>
       <c r="O90" t="n">
-        <v>-755.1058297885011</v>
+        <v>-818.6050453707613</v>
       </c>
       <c r="P90" t="n">
-        <v>-755.1058297885011</v>
+        <v>-818.6050453707613</v>
       </c>
     </row>
     <row r="91">
@@ -9719,19 +9719,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G91" t="n">
-        <v>-35845139.96</v>
+        <v>-35715304.73</v>
       </c>
       <c r="H91" t="n">
         <v>2261537.165955536</v>
       </c>
       <c r="I91" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="J91" t="n">
         <v>-34000000</v>
       </c>
       <c r="K91" t="n">
-        <v>416397.2059555352</v>
+        <v>546232.4359555319</v>
       </c>
       <c r="L91" t="n">
         <v>0.05625883751011833</v>
@@ -9743,10 +9743,10 @@
         <v>-0.01046759094930644</v>
       </c>
       <c r="O91" t="n">
-        <v>-363.2229686980544</v>
+        <v>-476.478141902145</v>
       </c>
       <c r="P91" t="n">
-        <v>-363.2229686980544</v>
+        <v>-476.478141902145</v>
       </c>
     </row>
     <row r="92">
@@ -9777,28 +9777,28 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>-36463708.53000001</v>
+        <v>-36430105.95000001</v>
       </c>
       <c r="H92" t="n">
         <v>4044566.584325174</v>
       </c>
       <c r="I92" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="J92" t="n">
         <v>-34000000</v>
       </c>
       <c r="K92" t="n">
-        <v>1580858.054325163</v>
+        <v>1614460.634325162</v>
       </c>
       <c r="L92" t="n">
-        <v>0.05613367690325632</v>
+        <v>0.05611688274594639</v>
       </c>
       <c r="M92" t="n">
-        <v>0.04562501529258145</v>
+        <v>0.04560834936885638</v>
       </c>
       <c r="N92" t="n">
-        <v>-0.01050866161067487</v>
+        <v>-0.01050853337709001</v>
       </c>
       <c r="O92" t="n">
         <v>-0</v>
@@ -9880,22 +9880,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="D2" t="n">
-        <v>657013128.1</v>
+        <v>673143847.5700001</v>
       </c>
       <c r="E2" t="n">
-        <v>42626950.92000008</v>
+        <v>61073262.91000009</v>
       </c>
       <c r="F2" t="n">
-        <v>21313475.46000004</v>
+        <v>30536631.45500004</v>
       </c>
       <c r="G2" t="n">
-        <v>3.552245910000006</v>
+        <v>5.08943857583334</v>
       </c>
       <c r="H2" t="n">
-        <v>1.776122955000003</v>
+        <v>2.54471928791667</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -9913,22 +9913,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="D3" t="n">
-        <v>571846923.42</v>
+        <v>555254424.24</v>
       </c>
       <c r="E3" t="n">
-        <v>-42539253.75999999</v>
+        <v>-56816160.41999996</v>
       </c>
       <c r="F3" t="n">
-        <v>-42539253.75999999</v>
+        <v>-56816160.41999996</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.544937813333333</v>
+        <v>-4.734680034999996</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.544937813333333</v>
+        <v>-4.734680034999996</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -9946,22 +9946,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="D4" t="n">
-        <v>647366157.4400001</v>
+        <v>638606894.7</v>
       </c>
       <c r="E4" t="n">
-        <v>32979980.26000011</v>
+        <v>26536310.04000008</v>
       </c>
       <c r="F4" t="n">
-        <v>16489990.13000005</v>
+        <v>13268155.02000004</v>
       </c>
       <c r="G4" t="n">
-        <v>2.748331688333343</v>
+        <v>2.211359170000007</v>
       </c>
       <c r="H4" t="n">
-        <v>1.374165844166671</v>
+        <v>1.105679585000003</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -9979,22 +9979,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="D5" t="n">
-        <v>584447213.12</v>
+        <v>595587989.5599999</v>
       </c>
       <c r="E5" t="n">
-        <v>-29938964.05999994</v>
+        <v>-16482595.10000002</v>
       </c>
       <c r="F5" t="n">
-        <v>-29938964.05999994</v>
+        <v>-16482595.10000002</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.494913671666662</v>
+        <v>-1.373549591666669</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.494913671666662</v>
+        <v>-1.373549591666669</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -10012,22 +10012,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="D6" t="n">
-        <v>604742509.74</v>
+        <v>621226231.51</v>
       </c>
       <c r="E6" t="n">
-        <v>-9643667.439999938</v>
+        <v>9155646.850000024</v>
       </c>
       <c r="F6" t="n">
-        <v>-9643667.439999938</v>
+        <v>4577823.425000012</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8036389533333281</v>
+        <v>0.7629705708333353</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8036389533333281</v>
+        <v>0.3814852854166677</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -10045,22 +10045,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="D7" t="n">
-        <v>623974966.02</v>
+        <v>606993370.22</v>
       </c>
       <c r="E7" t="n">
-        <v>9588788.840000033</v>
+        <v>-5077214.439999938</v>
       </c>
       <c r="F7" t="n">
-        <v>4794394.420000017</v>
+        <v>-5077214.439999938</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7990657366666696</v>
+        <v>-0.4231012033333282</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3995328683333348</v>
+        <v>-0.4231012033333282</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -10078,22 +10078,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="D8" t="n">
-        <v>597394594.91</v>
+        <v>590585952.03</v>
       </c>
       <c r="E8" t="n">
-        <v>-16991582.26999998</v>
+        <v>-21484632.63</v>
       </c>
       <c r="F8" t="n">
-        <v>-16991582.26999998</v>
+        <v>-21484632.63</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.415965189166665</v>
+        <v>-1.790386052499999</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.415965189166665</v>
+        <v>-1.790386052499999</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>

--- a/irrbb_calc/output/eba_sot_results.xlsx
+++ b/irrbb_calc/output/eba_sot_results.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,26 +479,26 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>Overnight</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1323380873.66</v>
+        <v>-1357868945.18</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9975215395798449</v>
+        <v>0.999906031812547</v>
       </c>
       <c r="F2" t="n">
-        <v>0.996446199874419</v>
+        <v>0.999918739380137</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.001075339705425948</v>
+        <v>1.270756758997571e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1423083.998847879</v>
+        <v>-17255.21139920387</v>
       </c>
       <c r="I2" t="n">
-        <v>711541.9994239394</v>
+        <v>-17255.21139920387</v>
       </c>
     </row>
     <row r="3">
@@ -514,26 +514,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-563607788.72</v>
+        <v>-273538406.96</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9903615297882993</v>
+        <v>0.9983821828874917</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9862429315621977</v>
+        <v>0.9973074623585604</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.004118598226101611</v>
+        <v>-0.001074720528931317</v>
       </c>
       <c r="H3" t="n">
-        <v>2321274.038839243</v>
+        <v>293977.3414110809</v>
       </c>
       <c r="I3" t="n">
-        <v>1160637.019419622</v>
+        <v>146988.6707055405</v>
       </c>
     </row>
     <row r="4">
@@ -549,26 +549,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6M</t>
+          <t>3M</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-639535554.92</v>
+        <v>-391346094.59</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9786688180301472</v>
+        <v>0.9936563817038003</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9695335354087792</v>
+        <v>0.9895245741287695</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.009135282621367979</v>
+        <v>-0.004131807575030844</v>
       </c>
       <c r="H4" t="n">
-        <v>5842338.040607602</v>
+        <v>1616966.758085699</v>
       </c>
       <c r="I4" t="n">
-        <v>2921169.020303801</v>
+        <v>808483.3790428495</v>
       </c>
     </row>
     <row r="5">
@@ -584,26 +584,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9M</t>
+          <t>6M</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>282089586.14</v>
+        <v>-784700756.36</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9655145554862491</v>
+        <v>0.9856536327098718</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9505431762951791</v>
+        <v>0.9764549779987347</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.01497137919106994</v>
+        <v>-0.009198654711137122</v>
       </c>
       <c r="H5" t="n">
-        <v>-4223270.159953929</v>
+        <v>7218191.309323777</v>
       </c>
       <c r="I5" t="n">
-        <v>-4223270.159953929</v>
+        <v>3609095.654661889</v>
       </c>
     </row>
     <row r="6">
@@ -619,26 +619,26 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>9M</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>319161024.12</v>
+        <v>106194068.06</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9530263468310431</v>
+        <v>0.9761318955535195</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9324029918156683</v>
+        <v>0.9609973342866598</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.02062335501537482</v>
+        <v>-0.01513456126685975</v>
       </c>
       <c r="H6" t="n">
-        <v>-6582171.107497367</v>
+        <v>-1607200.629231144</v>
       </c>
       <c r="I6" t="n">
-        <v>-6582171.107497367</v>
+        <v>-1607200.629231144</v>
       </c>
     </row>
     <row r="7">
@@ -654,26 +654,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.5Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>533754600.58</v>
+        <v>327029241.36</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9378479178638877</v>
+        <v>0.9667342819189046</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9089929721392235</v>
+        <v>0.9458153193868882</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.02885494572466418</v>
+        <v>-0.02091896253201642</v>
       </c>
       <c r="H7" t="n">
-        <v>-15401460.03002571</v>
+        <v>-6841112.446883594</v>
       </c>
       <c r="I7" t="n">
-        <v>-15401460.03002571</v>
+        <v>-6841112.446883594</v>
       </c>
     </row>
     <row r="8">
@@ -689,26 +689,26 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>1.5Y</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>725837405.03</v>
+        <v>453172829.04</v>
       </c>
       <c r="E8" t="n">
-        <v>0.914020029743317</v>
+        <v>0.9524015829683793</v>
       </c>
       <c r="F8" t="n">
-        <v>0.874893456123076</v>
+        <v>0.9230991916369015</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.03912657362024097</v>
+        <v>-0.02930239133147783</v>
       </c>
       <c r="H8" t="n">
-        <v>-28399530.66423095</v>
+        <v>-13279047.57732298</v>
       </c>
       <c r="I8" t="n">
-        <v>-28399530.66423095</v>
+        <v>-13279047.57732298</v>
       </c>
     </row>
     <row r="9">
@@ -724,26 +724,26 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1456815524.71</v>
+        <v>706989755.74</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8793551938327786</v>
+        <v>0.9333610479054046</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8260772215220972</v>
+        <v>0.893406842337341</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.05327797231068143</v>
+        <v>-0.03995420556806362</v>
       </c>
       <c r="H9" t="n">
-        <v>-77616177.18727022</v>
+        <v>-28247214.03535105</v>
       </c>
       <c r="I9" t="n">
-        <v>-77616177.18727022</v>
+        <v>-28247214.03535105</v>
       </c>
     </row>
     <row r="10">
@@ -759,26 +759,26 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>436647272.55</v>
+        <v>950082301.61</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8350903091634028</v>
+        <v>0.9066754799235061</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7651251962107317</v>
+        <v>0.8517422733959322</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.06996511295267105</v>
+        <v>-0.05493320652757383</v>
       </c>
       <c r="H10" t="n">
-        <v>-30550075.74443649</v>
+        <v>-52191067.29253482</v>
       </c>
       <c r="I10" t="n">
-        <v>-30550075.74443649</v>
+        <v>-52191067.29253482</v>
       </c>
     </row>
     <row r="11">
@@ -794,26 +794,26 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>857024694.1899999</v>
+        <v>1131433784.31</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7929814256230181</v>
+        <v>0.8730418834956067</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7086060176961181</v>
+        <v>0.7998972452094898</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.08437540792690001</v>
+        <v>-0.07314463828611695</v>
       </c>
       <c r="H11" t="n">
-        <v>-72311808.17570798</v>
+        <v>-82758314.8980474</v>
       </c>
       <c r="I11" t="n">
-        <v>-72311808.17570798</v>
+        <v>-82758314.8980474</v>
       </c>
     </row>
     <row r="12">
@@ -829,26 +829,26 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>98149543.74000001</v>
+        <v>725856199.14</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7529410815413444</v>
+        <v>0.839886760163754</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6562138446458032</v>
+        <v>0.7505205332452695</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.09672723689554119</v>
+        <v>-0.0893662269184845</v>
       </c>
       <c r="H12" t="n">
-        <v>-9493734.168528263</v>
+        <v>-64867029.80253392</v>
       </c>
       <c r="I12" t="n">
-        <v>-9493734.168528263</v>
+        <v>-64867029.80253392</v>
       </c>
     </row>
     <row r="13">
@@ -864,26 +864,26 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>317275857.88</v>
+        <v>135257246.09</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7148807043542068</v>
+        <v>0.8060794216350962</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6076597287586817</v>
+        <v>0.7025258881080018</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1072209755955251</v>
+        <v>-0.1035535335270944</v>
       </c>
       <c r="H13" t="n">
-        <v>-34018627.01480078</v>
+        <v>-14006365.76776327</v>
       </c>
       <c r="I13" t="n">
-        <v>-34018627.01480078</v>
+        <v>-14006365.76776327</v>
       </c>
     </row>
     <row r="14">
@@ -899,26 +899,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>305998789.65</v>
+        <v>290934368.76</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6787119945050498</v>
+        <v>0.7725125366488534</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5626717641363838</v>
+        <v>0.6566479693024505</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1160402303686661</v>
+        <v>-0.1158645673464029</v>
       </c>
       <c r="H14" t="n">
-        <v>-35508170.04351898</v>
+        <v>-33708984.76257624</v>
       </c>
       <c r="I14" t="n">
-        <v>-35508170.04351898</v>
+        <v>-33708984.76257624</v>
       </c>
     </row>
     <row r="15">
@@ -934,26 +934,26 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9Y</t>
+          <t>8Y</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>213878647.01</v>
+        <v>293928244.15</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6443492036977719</v>
+        <v>0.7390723504327896</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5209949352383458</v>
+        <v>0.6127124119984428</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1233542684594261</v>
+        <v>-0.1263599384343468</v>
       </c>
       <c r="H15" t="n">
-        <v>-26382844.04101037</v>
+        <v>-37140754.83490965</v>
       </c>
       <c r="I15" t="n">
-        <v>-26382844.04101037</v>
+        <v>-37140754.83490965</v>
       </c>
     </row>
     <row r="16">
@@ -969,32 +969,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>9Y</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6012265.48</v>
+        <v>240687365.15</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6117079401756688</v>
+        <v>0.7058360643204235</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4823907164755455</v>
+        <v>0.5707105794672964</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1293172237001232</v>
+        <v>-0.135125484853127</v>
       </c>
       <c r="H16" t="n">
-        <v>-777489.4800216887</v>
+        <v>-32522996.91391538</v>
       </c>
       <c r="I16" t="n">
-        <v>-777489.4800216887</v>
+        <v>-32522996.91391538</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>par_dn</t>
+          <t>par_up</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1004,32 +1004,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1323380873.66</v>
+        <v>152144703.2</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9975215395798449</v>
+        <v>0.6740936305925465</v>
       </c>
       <c r="F17" t="n">
-        <v>0.998592680736111</v>
+        <v>0.5315880010548585</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001071141156266053</v>
+        <v>-0.142505629537688</v>
       </c>
       <c r="H17" t="n">
-        <v>-1417527.719192552</v>
+        <v>-21681476.71034069</v>
       </c>
       <c r="I17" t="n">
-        <v>-1417527.719192552</v>
+        <v>-21681476.71034069</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>par_dn</t>
+          <t>par_up</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1039,26 +1039,26 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3M</t>
+          <t>15Y</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-563607788.72</v>
+        <v>11282921.34</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9903615297882993</v>
+        <v>0.5835756277426192</v>
       </c>
       <c r="F18" t="n">
-        <v>0.994495963319766</v>
+        <v>0.4269530095095613</v>
       </c>
       <c r="G18" t="n">
-        <v>0.004134433531466697</v>
+        <v>-0.1566226182330579</v>
       </c>
       <c r="H18" t="n">
-        <v>-2330198.940279766</v>
+        <v>-1767160.681588442</v>
       </c>
       <c r="I18" t="n">
-        <v>-2330198.940279766</v>
+        <v>-1767160.681588442</v>
       </c>
     </row>
     <row r="19">
@@ -1074,26 +1074,26 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6M</t>
+          <t>Overnight</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-639535554.92</v>
+        <v>-1357868945.18</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9786688180301472</v>
+        <v>0.999906031812547</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9878837847518154</v>
+        <v>0.9999872262568493</v>
       </c>
       <c r="G19" t="n">
-        <v>0.009214966721668216</v>
+        <v>8.119444430232381e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>-5893298.855911415</v>
+        <v>-110251.4144392727</v>
       </c>
       <c r="I19" t="n">
-        <v>-5893298.855911415</v>
+        <v>-110251.4144392727</v>
       </c>
     </row>
     <row r="20">
@@ -1109,26 +1109,26 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>282089586.14</v>
+        <v>-273538406.96</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9655145554862491</v>
+        <v>0.9983821828874917</v>
       </c>
       <c r="F20" t="n">
-        <v>0.980716645208862</v>
+        <v>0.9994558012160737</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01520208972261294</v>
+        <v>0.001073618328581993</v>
       </c>
       <c r="H20" t="n">
-        <v>4288351.198315033</v>
+        <v>-293675.8472833763</v>
       </c>
       <c r="I20" t="n">
-        <v>2144175.599157516</v>
+        <v>-293675.8472833763</v>
       </c>
     </row>
     <row r="21">
@@ -1144,26 +1144,26 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>3M</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>319161024.12</v>
+        <v>-391346094.59</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9530263468310431</v>
+        <v>0.9936563817038003</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9741011135441072</v>
+        <v>0.9978050568610267</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02107476671306407</v>
+        <v>0.004148675157226389</v>
       </c>
       <c r="H21" t="n">
-        <v>6726244.127231617</v>
+        <v>-1623567.820503101</v>
       </c>
       <c r="I21" t="n">
-        <v>3363122.063615808</v>
+        <v>-1623567.820503101</v>
       </c>
     </row>
     <row r="22">
@@ -1179,26 +1179,26 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.5Y</t>
+          <t>6M</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>533754600.58</v>
+        <v>-784700756.36</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9378479178638877</v>
+        <v>0.9856536327098718</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9676179779401868</v>
+        <v>0.9949362247370691</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02977006007629912</v>
+        <v>0.009282592027197278</v>
       </c>
       <c r="H22" t="n">
-        <v>15889906.52526764</v>
+        <v>-7284056.98472301</v>
       </c>
       <c r="I22" t="n">
-        <v>7944953.26263382</v>
+        <v>-7284056.98472301</v>
       </c>
     </row>
     <row r="23">
@@ -1214,26 +1214,26 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>9M</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>725837405.03</v>
+        <v>106194068.06</v>
       </c>
       <c r="E23" t="n">
-        <v>0.914020029743317</v>
+        <v>0.9761318955535195</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9548956940906148</v>
+        <v>0.9915026586821418</v>
       </c>
       <c r="G23" t="n">
-        <v>0.04087566434729784</v>
+        <v>0.01537076312862229</v>
       </c>
       <c r="H23" t="n">
-        <v>29669086.13871995</v>
+        <v>1632283.865815054</v>
       </c>
       <c r="I23" t="n">
-        <v>14834543.06935997</v>
+        <v>816141.932907527</v>
       </c>
     </row>
     <row r="24">
@@ -1249,26 +1249,26 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1456815524.71</v>
+        <v>327029241.36</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8793551938327786</v>
+        <v>0.9667342819189046</v>
       </c>
       <c r="F24" t="n">
-        <v>0.936068121791669</v>
+        <v>0.9881132592939402</v>
       </c>
       <c r="G24" t="n">
-        <v>0.05671292795889038</v>
+        <v>0.02137897737503558</v>
       </c>
       <c r="H24" t="n">
-        <v>82620273.90227132</v>
+        <v>6991550.75201049</v>
       </c>
       <c r="I24" t="n">
-        <v>41310136.95113566</v>
+        <v>3495775.376005245</v>
       </c>
     </row>
     <row r="25">
@@ -1284,26 +1284,26 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>1.5Y</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>436647272.55</v>
+        <v>453172829.04</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8350903091634028</v>
+        <v>0.9524015829683793</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9114524892145283</v>
+        <v>0.9826339733256618</v>
       </c>
       <c r="G25" t="n">
-        <v>0.07636218005112549</v>
+        <v>0.03023239035728253</v>
       </c>
       <c r="H25" t="n">
-        <v>33343337.64529597</v>
+        <v>13700497.86685134</v>
       </c>
       <c r="I25" t="n">
-        <v>16671668.82264798</v>
+        <v>6850248.933425671</v>
       </c>
     </row>
     <row r="26">
@@ -1319,26 +1319,26 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>857024694.1899999</v>
+        <v>706989755.74</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7929814256230181</v>
+        <v>0.9333610479054046</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8874034155732852</v>
+        <v>0.9751019867411274</v>
       </c>
       <c r="G26" t="n">
-        <v>0.09442198995026707</v>
+        <v>0.04174093883572272</v>
       </c>
       <c r="H26" t="n">
-        <v>80921977.06193888</v>
+        <v>29510416.15182589</v>
       </c>
       <c r="I26" t="n">
-        <v>40460988.53096944</v>
+        <v>14755208.07591294</v>
       </c>
     </row>
     <row r="27">
@@ -1354,26 +1354,26 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>98149543.74000001</v>
+        <v>950082301.61</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7529410815413444</v>
+        <v>0.9066754799235061</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8639256557819821</v>
+        <v>0.96515043845863</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1109845742406377</v>
+        <v>0.05847495853512397</v>
       </c>
       <c r="H27" t="n">
-        <v>10893085.32389675</v>
+        <v>55556023.19159989</v>
       </c>
       <c r="I27" t="n">
-        <v>5446542.661948374</v>
+        <v>27778011.59579995</v>
       </c>
     </row>
     <row r="28">
@@ -1389,26 +1389,26 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>317275857.88</v>
+        <v>1131433784.31</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7148807043542068</v>
+        <v>0.8730418834956067</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8410196849995127</v>
+        <v>0.952874567112068</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1261389806453059</v>
+        <v>0.07983268361646123</v>
       </c>
       <c r="H28" t="n">
-        <v>40020853.29634815</v>
+        <v>90325395.33579566</v>
       </c>
       <c r="I28" t="n">
-        <v>20010426.64817408</v>
+        <v>45162697.66789783</v>
       </c>
     </row>
     <row r="29">
@@ -1424,26 +1424,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>8Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>305998789.65</v>
+        <v>725856199.14</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6787119945050498</v>
+        <v>0.839886760163754</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8186825770896045</v>
+        <v>0.9398939190136093</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1399705825845546</v>
+        <v>0.1000071588498553</v>
       </c>
       <c r="H29" t="n">
-        <v>42830828.85747909</v>
+        <v>72590816.20954621</v>
       </c>
       <c r="I29" t="n">
-        <v>21415414.42873954</v>
+        <v>36295408.1047731</v>
       </c>
     </row>
     <row r="30">
@@ -1459,26 +1459,26 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>213878647.01</v>
+        <v>135257246.09</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6443492036977719</v>
+        <v>0.8060794216350962</v>
       </c>
       <c r="F30" t="n">
-        <v>0.796908862114506</v>
+        <v>0.9248968801905073</v>
       </c>
       <c r="G30" t="n">
-        <v>0.152559658416734</v>
+        <v>0.1188174585554111</v>
       </c>
       <c r="H30" t="n">
-        <v>32629253.33047883</v>
+        <v>16070922.23161762</v>
       </c>
       <c r="I30" t="n">
-        <v>16314626.66523941</v>
+        <v>8035461.115808811</v>
       </c>
     </row>
     <row r="31">
@@ -1494,32 +1494,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6012265.48</v>
+        <v>290934368.76</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6117079401756688</v>
+        <v>0.7725125366488534</v>
       </c>
       <c r="F31" t="n">
-        <v>0.775691111553262</v>
+        <v>0.9088209147477103</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1639831713775932</v>
+        <v>0.1363083780988569</v>
       </c>
       <c r="H31" t="n">
-        <v>985910.3605744279</v>
+        <v>39656791.93889033</v>
       </c>
       <c r="I31" t="n">
-        <v>492955.1802872139</v>
+        <v>19828395.96944517</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>steep</t>
+          <t>par_dn</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1529,32 +1529,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>8Y</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-1323380873.66</v>
+        <v>293928244.15</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9975215395798449</v>
+        <v>0.7390723504327896</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9983771722526092</v>
+        <v>0.8914912953273965</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0008556326727643393</v>
+        <v>0.1524189448946068</v>
       </c>
       <c r="H32" t="n">
-        <v>-1132327.914014912</v>
+        <v>44800232.84806739</v>
       </c>
       <c r="I32" t="n">
-        <v>-1132327.914014912</v>
+        <v>22400116.42403369</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>steep</t>
+          <t>par_dn</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1564,32 +1564,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3M</t>
+          <t>9Y</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-563607788.72</v>
+        <v>240687365.15</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9903615297882993</v>
+        <v>0.7058360643204235</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9931904604838659</v>
+        <v>0.872953434342666</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002828930695566667</v>
+        <v>0.1671173700222426</v>
       </c>
       <c r="H33" t="n">
-        <v>-1594407.373770461</v>
+        <v>40223039.46145117</v>
       </c>
       <c r="I33" t="n">
-        <v>-1594407.373770461</v>
+        <v>20111519.73072558</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>steep</t>
+          <t>par_dn</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1599,32 +1599,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>6M</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-639535554.92</v>
+        <v>152144703.2</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9786688180301472</v>
+        <v>0.6740936305925465</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9828230103326652</v>
+        <v>0.8548010536316132</v>
       </c>
       <c r="G34" t="n">
-        <v>0.004154192302518012</v>
+        <v>0.1807074230390667</v>
       </c>
       <c r="H34" t="n">
-        <v>-2656753.679435249</v>
+        <v>27493677.24431565</v>
       </c>
       <c r="I34" t="n">
-        <v>-2656753.679435249</v>
+        <v>13746838.62215782</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>steep</t>
+          <t>par_dn</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1634,26 +1634,26 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>9M</t>
+          <t>15Y</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>282089586.14</v>
+        <v>11282921.34</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9655145554862491</v>
+        <v>0.5835756277426192</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9690560653036112</v>
+        <v>0.7976532262586258</v>
       </c>
       <c r="G35" t="n">
-        <v>0.003541509817362121</v>
+        <v>0.2140775985160066</v>
       </c>
       <c r="H35" t="n">
-        <v>999023.0386904276</v>
+        <v>2415420.704712203</v>
       </c>
       <c r="I35" t="n">
-        <v>499511.5193452138</v>
+        <v>1207710.352356102</v>
       </c>
     </row>
     <row r="36">
@@ -1669,26 +1669,26 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>Overnight</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>319161024.12</v>
+        <v>-1357868945.18</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9530263468310431</v>
+        <v>0.999906031812547</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9543539679035921</v>
+        <v>0.9999840090547945</v>
       </c>
       <c r="G36" t="n">
-        <v>0.001327621072548912</v>
+        <v>7.797724224745117e-05</v>
       </c>
       <c r="H36" t="n">
-        <v>423724.9011580037</v>
+        <v>-105882.8756785919</v>
       </c>
       <c r="I36" t="n">
-        <v>211862.4505790019</v>
+        <v>-105882.8756785919</v>
       </c>
     </row>
     <row r="37">
@@ -1704,26 +1704,26 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.5Y</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>533754600.58</v>
+        <v>-273538406.96</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9378479178638877</v>
+        <v>0.9983821828874917</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9342026515219396</v>
+        <v>0.9992398172674322</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.003645266341948061</v>
+        <v>0.000857634379940464</v>
       </c>
       <c r="H37" t="n">
-        <v>-1945677.680354205</v>
+        <v>-234595.9420430419</v>
       </c>
       <c r="I37" t="n">
-        <v>-1945677.680354205</v>
+        <v>-234595.9420430419</v>
       </c>
     </row>
     <row r="38">
@@ -1739,26 +1739,26 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3M</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>725837405.03</v>
+        <v>-391346094.59</v>
       </c>
       <c r="E38" t="n">
-        <v>0.914020029743317</v>
+        <v>0.9936563817038003</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9025740198456692</v>
+        <v>0.9964986465343718</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.01144600989764777</v>
+        <v>0.002842264830571484</v>
       </c>
       <c r="H38" t="n">
-        <v>-8307942.122056352</v>
+        <v>-1112309.241234658</v>
       </c>
       <c r="I38" t="n">
-        <v>-8307942.122056352</v>
+        <v>-1112309.241234658</v>
       </c>
     </row>
     <row r="39">
@@ -1774,26 +1774,26 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>6M</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1456815524.71</v>
+        <v>-784700756.36</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8793551938327786</v>
+        <v>0.9856536327098718</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8565199208718595</v>
+        <v>0.9898442575672471</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.02283527296091914</v>
+        <v>0.004190624857375314</v>
       </c>
       <c r="H39" t="n">
-        <v>-33266780.16045749</v>
+        <v>-3288386.495203426</v>
       </c>
       <c r="I39" t="n">
-        <v>-33266780.16045749</v>
+        <v>-3288386.495203426</v>
       </c>
     </row>
     <row r="40">
@@ -1809,26 +1809,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>9M</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>436647272.55</v>
+        <v>106194068.06</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8350903091634028</v>
+        <v>0.9761318955535195</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7996075232713666</v>
+        <v>0.9797201268086021</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.03548278589203613</v>
+        <v>0.003588231255082563</v>
       </c>
       <c r="H40" t="n">
-        <v>-15493461.68223319</v>
+        <v>381048.874117257</v>
       </c>
       <c r="I40" t="n">
-        <v>-15493461.68223319</v>
+        <v>190524.4370586285</v>
       </c>
     </row>
     <row r="41">
@@ -1844,26 +1844,26 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>857024694.1899999</v>
+        <v>327029241.36</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7929814256230181</v>
+        <v>0.9667342819189046</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7475953682933623</v>
+        <v>0.9680820499427143</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.04538605732965584</v>
+        <v>0.001347768023809648</v>
       </c>
       <c r="H41" t="n">
-        <v>-38896971.9034381</v>
+        <v>440759.5543557356</v>
       </c>
       <c r="I41" t="n">
-        <v>-38896971.9034381</v>
+        <v>220379.7771778678</v>
       </c>
     </row>
     <row r="42">
@@ -1879,26 +1879,26 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>1.5Y</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>98149543.74000001</v>
+        <v>453172829.04</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7529410815413444</v>
+        <v>0.9524015829683793</v>
       </c>
       <c r="F42" t="n">
-        <v>0.699629964006139</v>
+        <v>0.9487008592230047</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.05331111753520545</v>
+        <v>-0.003700723745374557</v>
       </c>
       <c r="H42" t="n">
-        <v>-5232461.862349929</v>
+        <v>-1677067.449186892</v>
       </c>
       <c r="I42" t="n">
-        <v>-5232461.862349929</v>
+        <v>-1677067.449186892</v>
       </c>
     </row>
     <row r="43">
@@ -1914,26 +1914,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>317275857.88</v>
+        <v>706989755.74</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7148807043542068</v>
+        <v>0.9333610479054046</v>
       </c>
       <c r="F43" t="n">
-        <v>0.655055106394129</v>
+        <v>0.9216733004796271</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.0598255979600778</v>
+        <v>-0.01168774742577749</v>
       </c>
       <c r="H43" t="n">
-        <v>-18981217.91596766</v>
+        <v>-8263117.697701245</v>
       </c>
       <c r="I43" t="n">
-        <v>-18981217.91596766</v>
+        <v>-8263117.697701245</v>
       </c>
     </row>
     <row r="44">
@@ -1949,26 +1949,26 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>8Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>305998789.65</v>
+        <v>950082301.61</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6787119945050498</v>
+        <v>0.9066754799235061</v>
       </c>
       <c r="F44" t="n">
-        <v>0.6134488178814577</v>
+        <v>0.8831310094023822</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.06526317662359216</v>
+        <v>-0.02354447052112385</v>
       </c>
       <c r="H44" t="n">
-        <v>-19970453.05553337</v>
+        <v>-22369184.74289814</v>
       </c>
       <c r="I44" t="n">
-        <v>-19970453.05553337</v>
+        <v>-22369184.74289814</v>
       </c>
     </row>
     <row r="45">
@@ -1984,26 +1984,26 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9Y</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>213878647.01</v>
+        <v>1131433784.31</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6443492036977719</v>
+        <v>0.8730418834956067</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5745304054163424</v>
+        <v>0.8359467059557391</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.06981879828142956</v>
+        <v>-0.03709517753986769</v>
       </c>
       <c r="H45" t="n">
-        <v>-14932750.11229627</v>
+        <v>-41970737.10358381</v>
       </c>
       <c r="I45" t="n">
-        <v>-14932750.11229627</v>
+        <v>-41970737.10358381</v>
       </c>
     </row>
     <row r="46">
@@ -2019,32 +2019,32 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6012265.48</v>
+        <v>725856199.14</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6117079401756688</v>
+        <v>0.839886760163754</v>
       </c>
       <c r="F46" t="n">
-        <v>0.538092340316341</v>
+        <v>0.791816130904004</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.07361559985932775</v>
+        <v>-0.04807062925974992</v>
       </c>
       <c r="H46" t="n">
-        <v>-442596.5298237291</v>
+        <v>-34892364.24475015</v>
       </c>
       <c r="I46" t="n">
-        <v>-442596.5298237291</v>
+        <v>-34892364.24475015</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2054,32 +2054,32 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-1323380873.66</v>
+        <v>135257246.09</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9975215395798449</v>
+        <v>0.8060794216350962</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9964459462501015</v>
+        <v>0.7490060504954742</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.001075593329743385</v>
+        <v>-0.05707337113962196</v>
       </c>
       <c r="H47" t="n">
-        <v>1423419.640418669</v>
+        <v>-7719587.005417752</v>
       </c>
       <c r="I47" t="n">
-        <v>711709.8202093347</v>
+        <v>-7719587.005417752</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3M</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-563607788.72</v>
+        <v>290934368.76</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9903615297882993</v>
+        <v>0.7725125366488534</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9867522277851473</v>
+        <v>0.7078642504313568</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.003609302003152015</v>
+        <v>-0.06464828621749663</v>
       </c>
       <c r="H48" t="n">
-        <v>2034230.720819174</v>
+        <v>-18808408.34210319</v>
       </c>
       <c r="I48" t="n">
-        <v>1017115.360409587</v>
+        <v>-18808408.34210319</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>6M</t>
+          <t>8Y</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-639535554.92</v>
+        <v>293928244.15</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9786688180301472</v>
+        <v>0.7390723504327896</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9729547214568308</v>
+        <v>0.6680052603746156</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.005714096573316341</v>
+        <v>-0.07106709005817402</v>
       </c>
       <c r="H49" t="n">
-        <v>3654367.922882336</v>
+        <v>-20888624.99764901</v>
       </c>
       <c r="I49" t="n">
-        <v>1827183.961441168</v>
+        <v>-20888624.99764901</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>9M</t>
+          <t>9Y</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>282089586.14</v>
+        <v>240687365.15</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9655145554862491</v>
+        <v>0.7058360643204235</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9596675661323812</v>
+        <v>0.6293546527166931</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.005846989353867849</v>
+        <v>-0.07648141160373034</v>
       </c>
       <c r="H50" t="n">
-        <v>-1649374.806997567</v>
+        <v>-18408109.44185449</v>
       </c>
       <c r="I50" t="n">
-        <v>-1649374.806997567</v>
+        <v>-18408109.44185449</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2194,32 +2194,32 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>319161024.12</v>
+        <v>152144703.2</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9530263468310431</v>
+        <v>0.6740936305925465</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9487865418135715</v>
+        <v>0.5929704296740601</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.004239805017471676</v>
+        <v>-0.08112320091848635</v>
       </c>
       <c r="H51" t="n">
-        <v>-1353180.511445375</v>
+        <v>-12342465.32637707</v>
       </c>
       <c r="I51" t="n">
-        <v>-1353180.511445375</v>
+        <v>-12342465.32637707</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2229,26 +2229,26 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.5Y</t>
+          <t>15Y</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>533754600.58</v>
+        <v>11282921.34</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9378479178638877</v>
+        <v>0.5835756277426192</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9378542448959014</v>
+        <v>0.4929588247471065</v>
       </c>
       <c r="G52" t="n">
-        <v>6.327032013753175e-06</v>
+        <v>-0.09061680299551267</v>
       </c>
       <c r="H52" t="n">
-        <v>3377.082445357699</v>
+        <v>-1022422.260280646</v>
       </c>
       <c r="I52" t="n">
-        <v>1688.54122267885</v>
+        <v>-1022422.260280646</v>
       </c>
     </row>
     <row r="53">
@@ -2264,26 +2264,26 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>Overnight</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>725837405.03</v>
+        <v>-1357868945.18</v>
       </c>
       <c r="E53" t="n">
-        <v>0.914020029743317</v>
+        <v>0.999906031812547</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9211323475322419</v>
+        <v>0.9999147816712329</v>
       </c>
       <c r="G53" t="n">
-        <v>0.00711231778892496</v>
+        <v>8.749858685930256e-06</v>
       </c>
       <c r="H53" t="n">
-        <v>5162386.287662</v>
+        <v>-11881.16138433818</v>
       </c>
       <c r="I53" t="n">
-        <v>2581193.143831</v>
+        <v>-11881.16138433818</v>
       </c>
     </row>
     <row r="54">
@@ -2299,26 +2299,26 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1456815524.71</v>
+        <v>-273538406.96</v>
       </c>
       <c r="E54" t="n">
-        <v>0.8793551938327786</v>
+        <v>0.9983821828874917</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8971815662398448</v>
+        <v>0.9973075252458976</v>
       </c>
       <c r="G54" t="n">
-        <v>0.01782637240706619</v>
+        <v>-0.00107465764159409</v>
       </c>
       <c r="H54" t="n">
-        <v>25969736.071876</v>
+        <v>293960.139309038</v>
       </c>
       <c r="I54" t="n">
-        <v>12984868.035938</v>
+        <v>146980.069654519</v>
       </c>
     </row>
     <row r="55">
@@ -2334,26 +2334,26 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>3M</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>436647272.55</v>
+        <v>-391346094.59</v>
       </c>
       <c r="E55" t="n">
-        <v>0.8350903091634028</v>
+        <v>0.9936563817038003</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8650314228040723</v>
+        <v>0.9900318688113408</v>
       </c>
       <c r="G55" t="n">
-        <v>0.02994111364066954</v>
+        <v>-0.003624512892459575</v>
       </c>
       <c r="H55" t="n">
-        <v>13073705.60830795</v>
+        <v>1418438.965255159</v>
       </c>
       <c r="I55" t="n">
-        <v>6536852.804153977</v>
+        <v>709219.4826275796</v>
       </c>
     </row>
     <row r="56">
@@ -2369,26 +2369,26 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>6M</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>857024694.1899999</v>
+        <v>-784700756.36</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7929814256230181</v>
+        <v>0.9856536327098718</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8325243862731679</v>
+        <v>0.9798953056923163</v>
       </c>
       <c r="G56" t="n">
-        <v>0.03954296065014984</v>
+        <v>-0.00575832701755552</v>
       </c>
       <c r="H56" t="n">
-        <v>33889293.75856186</v>
+        <v>4518563.56604404</v>
       </c>
       <c r="I56" t="n">
-        <v>16944646.87928093</v>
+        <v>2259281.78302202</v>
       </c>
     </row>
     <row r="57">
@@ -2404,26 +2404,26 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>9M</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>98149543.74000001</v>
+        <v>106194068.06</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7529410815413444</v>
+        <v>0.9761318955535195</v>
       </c>
       <c r="F57" t="n">
-        <v>0.800294227812458</v>
+        <v>0.9702153419678559</v>
       </c>
       <c r="G57" t="n">
-        <v>0.04735314627111353</v>
+        <v>-0.005916553585663675</v>
       </c>
       <c r="H57" t="n">
-        <v>4647689.701163276</v>
+        <v>-628302.8941566054</v>
       </c>
       <c r="I57" t="n">
-        <v>2323844.850581638</v>
+        <v>-628302.8941566054</v>
       </c>
     </row>
     <row r="58">
@@ -2439,26 +2439,26 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>317275857.88</v>
+        <v>327029241.36</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7148807043542068</v>
+        <v>0.9667342819189046</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7688196693783695</v>
+        <v>0.9624345418590539</v>
       </c>
       <c r="G58" t="n">
-        <v>0.05393896502416273</v>
+        <v>-0.004299740059850787</v>
       </c>
       <c r="H58" t="n">
-        <v>17113531.40120054</v>
+        <v>-1406140.729818204</v>
       </c>
       <c r="I58" t="n">
-        <v>8556765.700600272</v>
+        <v>-1406140.729818204</v>
       </c>
     </row>
     <row r="59">
@@ -2474,26 +2474,26 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>8Y</t>
+          <t>1.5Y</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>305998789.65</v>
+        <v>453172829.04</v>
       </c>
       <c r="E59" t="n">
-        <v>0.6787119945050498</v>
+        <v>0.9524015829683793</v>
       </c>
       <c r="F59" t="n">
-        <v>0.7383430913025396</v>
+        <v>0.9524075184936596</v>
       </c>
       <c r="G59" t="n">
-        <v>0.05963109679748979</v>
+        <v>5.935525280276188e-06</v>
       </c>
       <c r="H59" t="n">
-        <v>18247043.44553386</v>
+        <v>2689.818783101199</v>
       </c>
       <c r="I59" t="n">
-        <v>9123521.722766932</v>
+        <v>1344.9093915506</v>
       </c>
     </row>
     <row r="60">
@@ -2509,26 +2509,26 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>9Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>213878647.01</v>
+        <v>706989755.74</v>
       </c>
       <c r="E60" t="n">
-        <v>0.6443492036977719</v>
+        <v>0.9333610479054046</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7089588137102256</v>
+        <v>0.940624011446744</v>
       </c>
       <c r="G60" t="n">
-        <v>0.06460961001245369</v>
+        <v>0.007262963541339373</v>
       </c>
       <c r="H60" t="n">
-        <v>13818615.97330734</v>
+        <v>5134840.820040049</v>
       </c>
       <c r="I60" t="n">
-        <v>6909307.986653672</v>
+        <v>2567420.410020025</v>
       </c>
     </row>
     <row r="61">
@@ -2544,32 +2544,32 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6012265.48</v>
+        <v>950082301.61</v>
       </c>
       <c r="E61" t="n">
-        <v>0.6117079401756688</v>
+        <v>0.9066754799235061</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6806862497127172</v>
+        <v>0.9250554921357728</v>
       </c>
       <c r="G61" t="n">
-        <v>0.06897830953704842</v>
+        <v>0.01838001221226671</v>
       </c>
       <c r="H61" t="n">
-        <v>414715.909298351</v>
+        <v>17462524.30625026</v>
       </c>
       <c r="I61" t="n">
-        <v>207357.9546491755</v>
+        <v>8731262.15312513</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>sr_up</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2579,32 +2579,32 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-1323380873.66</v>
+        <v>1131433784.31</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9975215395798449</v>
+        <v>0.8730418834956067</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9961319041827014</v>
+        <v>0.9043437958460138</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.00138963539714354</v>
+        <v>0.03130191235040702</v>
       </c>
       <c r="H62" t="n">
-        <v>1839016.90594068</v>
+        <v>35416041.14676094</v>
       </c>
       <c r="I62" t="n">
-        <v>919508.4529703399</v>
+        <v>17708020.57338047</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>sr_up</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2614,32 +2614,32 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>3M</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-563607788.72</v>
+        <v>725856199.14</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9903615297882993</v>
+        <v>0.839886760163754</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9854932375482552</v>
+        <v>0.8817687551218356</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.004868292240044036</v>
+        <v>0.04188199495808165</v>
       </c>
       <c r="H63" t="n">
-        <v>2743807.424253955</v>
+        <v>30400305.67267379</v>
       </c>
       <c r="I63" t="n">
-        <v>1371903.712126978</v>
+        <v>15200152.83633689</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>sr_up</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2649,32 +2649,32 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>6M</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-639535554.92</v>
+        <v>135257246.09</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9786688180301472</v>
+        <v>0.8060794216350962</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9699158504109872</v>
+        <v>0.85677471502625</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.008752967619160001</v>
+        <v>0.05069529339115386</v>
       </c>
       <c r="H64" t="n">
-        <v>5597834.003516282</v>
+        <v>6856905.773812049</v>
       </c>
       <c r="I64" t="n">
-        <v>2798917.001758141</v>
+        <v>3428452.886906025</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>sr_up</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2684,32 +2684,32 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>9M</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>282089586.14</v>
+        <v>290934368.76</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9655145554862491</v>
+        <v>0.7725125366488534</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9542965519544472</v>
+        <v>0.8308003157157615</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.01121800353180191</v>
+        <v>0.05828777906690807</v>
       </c>
       <c r="H65" t="n">
-        <v>-3164481.97360306</v>
+        <v>16957918.20925324</v>
       </c>
       <c r="I65" t="n">
-        <v>-3164481.97360306</v>
+        <v>8478959.10462662</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>sr_up</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2719,32 +2719,32 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>8Y</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>319161024.12</v>
+        <v>293928244.15</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9530263468310431</v>
+        <v>0.7390723504327896</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9409485844020316</v>
+        <v>0.804006895737882</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.0120777624290116</v>
+        <v>0.06493454530509235</v>
       </c>
       <c r="H66" t="n">
-        <v>-3854751.0259214</v>
+        <v>19086096.88620442</v>
       </c>
       <c r="I66" t="n">
-        <v>-3854751.0259214</v>
+        <v>9543048.443102209</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>sr_up</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2754,32 +2754,32 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1.5Y</t>
+          <t>9Y</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>533754600.58</v>
+        <v>240687365.15</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9378479178638877</v>
+        <v>0.7058360643204235</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9261664375823063</v>
+        <v>0.7766107928070644</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.01168148028158134</v>
+        <v>0.0707747284866409</v>
       </c>
       <c r="H67" t="n">
-        <v>-6235043.841878591</v>
+        <v>17034582.91865624</v>
       </c>
       <c r="I67" t="n">
-        <v>-6235043.841878591</v>
+        <v>8517291.459328122</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>sr_up</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2789,32 +2789,32 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>725837405.03</v>
+        <v>152144703.2</v>
       </c>
       <c r="E68" t="n">
-        <v>0.914020029743317</v>
+        <v>0.6740936305925465</v>
       </c>
       <c r="F68" t="n">
-        <v>0.904342933514297</v>
+        <v>0.7501069833464871</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.009677096229020021</v>
+        <v>0.07601335275394061</v>
       </c>
       <c r="H68" t="n">
-        <v>-7023998.415097491</v>
+        <v>11565028.9939852</v>
       </c>
       <c r="I68" t="n">
-        <v>-7023998.415097491</v>
+        <v>5782514.496992598</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>sr_up</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2824,26 +2824,26 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>15Y</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1456815524.71</v>
+        <v>11282921.34</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8793551938327786</v>
+        <v>0.5835756277426192</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8730610207674812</v>
+        <v>0.6716901334458708</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.006294173065297448</v>
+        <v>0.08811450570325163</v>
       </c>
       <c r="H69" t="n">
-        <v>-9169449.036736852</v>
+        <v>994189.0367627696</v>
       </c>
       <c r="I69" t="n">
-        <v>-9169449.036736852</v>
+        <v>497094.5183813848</v>
       </c>
     </row>
     <row r="70">
@@ -2859,26 +2859,26 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>Overnight</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>436647272.55</v>
+        <v>-1357868945.18</v>
       </c>
       <c r="E70" t="n">
-        <v>0.8350903091634028</v>
+        <v>0.999906031812547</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8320063292318809</v>
+        <v>0.9999051750958904</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.003083979931521874</v>
+        <v>-8.56716656616463e-07</v>
       </c>
       <c r="H70" t="n">
-        <v>-1346611.425697962</v>
+        <v>1163.308942837933</v>
       </c>
       <c r="I70" t="n">
-        <v>-1346611.425697962</v>
+        <v>581.6544714189665</v>
       </c>
     </row>
     <row r="71">
@@ -2894,26 +2894,26 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>857024694.1899999</v>
+        <v>-273538406.96</v>
       </c>
       <c r="E71" t="n">
-        <v>0.7929814256230181</v>
+        <v>0.9983821828874917</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7915950611515638</v>
+        <v>0.9969931793923301</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.001386364471454349</v>
+        <v>-0.001389003495161578</v>
       </c>
       <c r="H71" t="n">
-        <v>-1188148.587184044</v>
+        <v>379945.8033283702</v>
       </c>
       <c r="I71" t="n">
-        <v>-1188148.587184044</v>
+        <v>189972.9016641851</v>
       </c>
     </row>
     <row r="72">
@@ -2929,26 +2929,26 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>3M</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>98149543.74000001</v>
+        <v>-391346094.59</v>
       </c>
       <c r="E72" t="n">
-        <v>0.7529410815413444</v>
+        <v>0.9936563817038003</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7523487456045337</v>
+        <v>0.9887690874847765</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.0005923359368107395</v>
+        <v>-0.004887294219023786</v>
       </c>
       <c r="H72" t="n">
-        <v>-58137.50193877955</v>
+        <v>1912623.505727242</v>
       </c>
       <c r="I72" t="n">
-        <v>-58137.50193877955</v>
+        <v>956311.7528636212</v>
       </c>
     </row>
     <row r="73">
@@ -2964,26 +2964,26 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>6M</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>317275857.88</v>
+        <v>-784700756.36</v>
       </c>
       <c r="E73" t="n">
-        <v>0.7148807043542068</v>
+        <v>0.9856536327098718</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7146357572841225</v>
+        <v>0.9768353223953496</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.0002449470700842671</v>
+        <v>-0.008818310314522182</v>
       </c>
       <c r="H73" t="n">
-        <v>-77715.79179617832</v>
+        <v>6919734.773622746</v>
       </c>
       <c r="I73" t="n">
-        <v>-77715.79179617832</v>
+        <v>3459867.386811373</v>
       </c>
     </row>
     <row r="74">
@@ -2999,26 +2999,26 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>8Y</t>
+          <t>9M</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>305998789.65</v>
+        <v>106194068.06</v>
       </c>
       <c r="E74" t="n">
-        <v>0.6787119945050498</v>
+        <v>0.9761318955535195</v>
       </c>
       <c r="F74" t="n">
-        <v>0.6786131588002061</v>
+        <v>0.9647860151613262</v>
       </c>
       <c r="G74" t="n">
-        <v>-9.883570484370274e-05</v>
+        <v>-0.01134588039219331</v>
       </c>
       <c r="H74" t="n">
-        <v>-30243.60605637768</v>
+        <v>-1204865.194569196</v>
       </c>
       <c r="I74" t="n">
-        <v>-30243.60605637768</v>
+        <v>-1204865.194569196</v>
       </c>
     </row>
     <row r="75">
@@ -3034,26 +3034,26 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>9Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>213878647.01</v>
+        <v>327029241.36</v>
       </c>
       <c r="E75" t="n">
-        <v>0.6443492036977719</v>
+        <v>0.9667342819189046</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6443098785224229</v>
+        <v>0.9544838436419948</v>
       </c>
       <c r="G75" t="n">
-        <v>-3.932517534899205e-05</v>
+        <v>-0.01225043827690986</v>
       </c>
       <c r="H75" t="n">
-        <v>-8410.815297073423</v>
+        <v>-4006251.536025337</v>
       </c>
       <c r="I75" t="n">
-        <v>-8410.815297073423</v>
+        <v>-4006251.536025337</v>
       </c>
     </row>
     <row r="76">
@@ -3069,32 +3069,32 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>1.5Y</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6012265.48</v>
+        <v>453172829.04</v>
       </c>
       <c r="E76" t="n">
-        <v>0.6117079401756688</v>
+        <v>0.9524015829683793</v>
       </c>
       <c r="F76" t="n">
-        <v>0.6116923728724937</v>
+        <v>0.9405384309552712</v>
       </c>
       <c r="G76" t="n">
-        <v>-1.556730317509025e-05</v>
+        <v>-0.01186315201310806</v>
       </c>
       <c r="H76" t="n">
-        <v>-93.59475949628953</v>
+        <v>-5376058.15911175</v>
       </c>
       <c r="I76" t="n">
-        <v>-93.59475949628953</v>
+        <v>-5376058.15911175</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>sr_dn</t>
+          <t>sr_up</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3104,32 +3104,32 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-1323380873.66</v>
+        <v>706989755.74</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9975215395798449</v>
+        <v>0.9333610479054046</v>
       </c>
       <c r="F77" t="n">
-        <v>0.9989077499872074</v>
+        <v>0.923479353401916</v>
       </c>
       <c r="G77" t="n">
-        <v>0.001386210407362531</v>
+        <v>-0.009881694503488636</v>
       </c>
       <c r="H77" t="n">
-        <v>-1834484.339972012</v>
+        <v>-6986256.783318732</v>
       </c>
       <c r="I77" t="n">
-        <v>-1834484.339972012</v>
+        <v>-6986256.783318732</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>sr_dn</t>
+          <t>sr_up</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3139,32 +3139,32 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>3M</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-563607788.72</v>
+        <v>950082301.61</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9903615297882993</v>
+        <v>0.9066754799235061</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9952525079761679</v>
+        <v>0.9001855974907953</v>
       </c>
       <c r="G78" t="n">
-        <v>0.004890978187868655</v>
+        <v>-0.006489882432710758</v>
       </c>
       <c r="H78" t="n">
-        <v>-2756593.401142406</v>
+        <v>-6165922.438848143</v>
       </c>
       <c r="I78" t="n">
-        <v>-2756593.401142406</v>
+        <v>-6165922.438848143</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>sr_dn</t>
+          <t>sr_up</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3174,32 +3174,32 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>6M</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>-639535554.92</v>
+        <v>1131433784.31</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9786688180301472</v>
+        <v>0.8730418834956067</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9874943883367843</v>
+        <v>0.8698178437108439</v>
       </c>
       <c r="G79" t="n">
-        <v>0.008825570306637109</v>
+        <v>-0.003224039784762822</v>
       </c>
       <c r="H79" t="n">
-        <v>-5644266.003540638</v>
+        <v>-3647787.534440198</v>
       </c>
       <c r="I79" t="n">
-        <v>-5644266.003540638</v>
+        <v>-3647787.534440198</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>sr_dn</t>
+          <t>sr_up</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3209,32 +3209,32 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9M</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>282089586.14</v>
+        <v>725856199.14</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9655145554862491</v>
+        <v>0.839886760163754</v>
       </c>
       <c r="F80" t="n">
-        <v>0.9768593517768159</v>
+        <v>0.8384184419278786</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01134479629056684</v>
+        <v>-0.001468318235875343</v>
       </c>
       <c r="H80" t="n">
-        <v>3200248.890448607</v>
+        <v>-1065787.893820427</v>
       </c>
       <c r="I80" t="n">
-        <v>1600124.445224303</v>
+        <v>-1065787.893820427</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>sr_dn</t>
+          <t>sr_up</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3244,32 +3244,32 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>319161024.12</v>
+        <v>135257246.09</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9530263468310431</v>
+        <v>0.8060794216350962</v>
       </c>
       <c r="F81" t="n">
-        <v>0.96525442222205</v>
+        <v>0.8054455020165052</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0122280753910069</v>
+        <v>-0.000633919618590939</v>
       </c>
       <c r="H81" t="n">
-        <v>3902725.064810331</v>
+        <v>-85742.22185303358</v>
       </c>
       <c r="I81" t="n">
-        <v>1951362.532405165</v>
+        <v>-85742.22185303358</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>sr_dn</t>
+          <t>sr_up</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3279,32 +3279,32 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1.5Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>533754600.58</v>
+        <v>290934368.76</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9378479178638877</v>
+        <v>0.7725125366488534</v>
       </c>
       <c r="F82" t="n">
-        <v>0.949675902004242</v>
+        <v>0.7722482029285767</v>
       </c>
       <c r="G82" t="n">
-        <v>0.01182798414035435</v>
+        <v>-0.0002643337202767881</v>
       </c>
       <c r="H82" t="n">
-        <v>6313240.950501412</v>
+        <v>-76903.76405070977</v>
       </c>
       <c r="I82" t="n">
-        <v>3156620.475250706</v>
+        <v>-76903.76405070977</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>sr_dn</t>
+          <t>sr_up</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3314,32 +3314,32 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>8Y</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>725837405.03</v>
+        <v>293928244.15</v>
       </c>
       <c r="E83" t="n">
-        <v>0.914020029743317</v>
+        <v>0.7390723504327896</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9237999822004164</v>
+        <v>0.7389649477310883</v>
       </c>
       <c r="G83" t="n">
-        <v>0.009779952457099395</v>
+        <v>-0.0001074027017012869</v>
       </c>
       <c r="H83" t="n">
-        <v>7098655.312777797</v>
+        <v>-31568.68752802546</v>
       </c>
       <c r="I83" t="n">
-        <v>3549327.656388898</v>
+        <v>-31568.68752802546</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>sr_dn</t>
+          <t>sr_up</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3349,32 +3349,32 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>9Y</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1456815524.71</v>
+        <v>240687365.15</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8793551938327786</v>
+        <v>0.7058360643204235</v>
       </c>
       <c r="F84" t="n">
-        <v>0.8856935834571039</v>
+        <v>0.7057927646712869</v>
       </c>
       <c r="G84" t="n">
-        <v>0.006338389624325313</v>
+        <v>-4.329964913651896e-05</v>
       </c>
       <c r="H84" t="n">
-        <v>9233864.406377902</v>
+        <v>-10421.67846258822</v>
       </c>
       <c r="I84" t="n">
-        <v>4616932.203188951</v>
+        <v>-10421.67846258822</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>sr_dn</t>
+          <t>sr_up</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3384,32 +3384,32 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>436647272.55</v>
+        <v>152144703.2</v>
       </c>
       <c r="E85" t="n">
-        <v>0.8350903091634028</v>
+        <v>0.6740936305925465</v>
       </c>
       <c r="F85" t="n">
-        <v>0.83818504204624</v>
+        <v>0.6740766698847023</v>
       </c>
       <c r="G85" t="n">
-        <v>0.003094732882837237</v>
+        <v>-1.696070784418247e-05</v>
       </c>
       <c r="H85" t="n">
-        <v>1351306.672561678</v>
+        <v>-2580.481861015053</v>
       </c>
       <c r="I85" t="n">
-        <v>675653.3362808391</v>
+        <v>-2580.481861015053</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>sr_dn</t>
+          <t>sr_up</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3419,26 +3419,26 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>15Y</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>857024694.1899999</v>
+        <v>11282921.34</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7929814256230181</v>
+        <v>0.5835756277426192</v>
       </c>
       <c r="F86" t="n">
-        <v>0.7943700412704571</v>
+        <v>0.5835746190638877</v>
       </c>
       <c r="G86" t="n">
-        <v>0.001388615647438973</v>
+        <v>-1.008678731428958e-06</v>
       </c>
       <c r="H86" t="n">
-        <v>1190077.900593835</v>
+        <v>-11.38084278404392</v>
       </c>
       <c r="I86" t="n">
-        <v>595038.9502969175</v>
+        <v>-11.38084278404392</v>
       </c>
     </row>
     <row r="87">
@@ -3454,26 +3454,26 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>Overnight</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>98149543.74000001</v>
+        <v>-1357868945.18</v>
       </c>
       <c r="E87" t="n">
-        <v>0.7529410815413444</v>
+        <v>0.999906031812547</v>
       </c>
       <c r="F87" t="n">
-        <v>0.7535334946689828</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0005924131276383582</v>
+        <v>9.39681874529974e-05</v>
       </c>
       <c r="H87" t="n">
-        <v>58145.07818329125</v>
+        <v>-127596.4835772781</v>
       </c>
       <c r="I87" t="n">
-        <v>29072.53909164562</v>
+        <v>-127596.4835772781</v>
       </c>
     </row>
     <row r="88">
@@ -3489,26 +3489,26 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>317275857.88</v>
+        <v>-273538406.96</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7148807043542068</v>
+        <v>0.9983821828874917</v>
       </c>
       <c r="F88" t="n">
-        <v>0.7151248528360472</v>
+        <v>0.9997700824582705</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0002441484818404005</v>
+        <v>0.001387899570778783</v>
       </c>
       <c r="H88" t="n">
-        <v>77462.41902601266</v>
+        <v>-379643.8376112962</v>
       </c>
       <c r="I88" t="n">
-        <v>38731.20951300633</v>
+        <v>-379643.8376112962</v>
       </c>
     </row>
     <row r="89">
@@ -3524,26 +3524,26 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>8Y</t>
+          <t>3M</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>305998789.65</v>
+        <v>-391346094.59</v>
       </c>
       <c r="E89" t="n">
-        <v>0.6787119945050498</v>
+        <v>0.9936563817038003</v>
       </c>
       <c r="F89" t="n">
-        <v>0.6788102588577627</v>
+        <v>0.9985674463473354</v>
       </c>
       <c r="G89" t="n">
-        <v>9.826435271287348e-05</v>
+        <v>0.004911064643535079</v>
       </c>
       <c r="H89" t="n">
-        <v>30068.77299587998</v>
+        <v>-1921925.968526484</v>
       </c>
       <c r="I89" t="n">
-        <v>15034.38649793999</v>
+        <v>-1921925.968526484</v>
       </c>
     </row>
     <row r="90">
@@ -3559,26 +3559,26 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>9Y</t>
+          <t>6M</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>213878647.01</v>
+        <v>-784700756.36</v>
       </c>
       <c r="E90" t="n">
-        <v>0.6443492036977719</v>
+        <v>0.9856536327098718</v>
       </c>
       <c r="F90" t="n">
-        <v>0.6443878944004078</v>
+        <v>0.9945488326935176</v>
       </c>
       <c r="G90" t="n">
-        <v>3.869070263584629e-05</v>
+        <v>0.008895199983645741</v>
       </c>
       <c r="H90" t="n">
-        <v>8275.115131621043</v>
+        <v>-6980070.155140272</v>
       </c>
       <c r="I90" t="n">
-        <v>4137.557565810522</v>
+        <v>-6980070.155140272</v>
       </c>
     </row>
     <row r="91">
@@ -3594,32 +3594,32 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>9M</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>6012265.48</v>
+        <v>106194068.06</v>
       </c>
       <c r="E91" t="n">
-        <v>0.6117079401756688</v>
+        <v>0.9761318955535195</v>
       </c>
       <c r="F91" t="n">
-        <v>0.6117228289482252</v>
+        <v>0.9876090645865213</v>
       </c>
       <c r="G91" t="n">
-        <v>1.488877255639842e-05</v>
+        <v>0.01147716903300178</v>
       </c>
       <c r="H91" t="n">
-        <v>89.51525328040559</v>
+        <v>1218807.269426715</v>
       </c>
       <c r="I91" t="n">
-        <v>44.75762664020279</v>
+        <v>609403.6347133575</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>sr_dn</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3629,32 +3629,32 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-1323380873.66</v>
+        <v>327029241.36</v>
       </c>
       <c r="E92" t="n">
-        <v>0.9975215395798449</v>
+        <v>0.9667342819189046</v>
       </c>
       <c r="F92" t="n">
-        <v>0.9979482509309764</v>
+        <v>0.9791393147026588</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0004267113511314813</v>
+        <v>0.01240503278375416</v>
       </c>
       <c r="H92" t="n">
-        <v>-564701.6406610188</v>
+        <v>4056808.460317051</v>
       </c>
       <c r="I92" t="n">
-        <v>-564701.6406610188</v>
+        <v>2028404.230158525</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>sr_dn</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3664,32 +3664,32 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>3M</t>
+          <t>1.5Y</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-563607788.72</v>
+        <v>453172829.04</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9903615297882993</v>
+        <v>0.9524015829683793</v>
       </c>
       <c r="F93" t="n">
-        <v>0.9920128235694623</v>
+        <v>0.9644142109405592</v>
       </c>
       <c r="G93" t="n">
-        <v>0.001651293781163021</v>
+        <v>0.01201262797217995</v>
       </c>
       <c r="H93" t="n">
-        <v>-930682.036528378</v>
+        <v>5443796.602357824</v>
       </c>
       <c r="I93" t="n">
-        <v>-930682.036528378</v>
+        <v>2721898.301178912</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>sr_dn</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3699,32 +3699,32 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>6M</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-639535554.92</v>
+        <v>706989755.74</v>
       </c>
       <c r="E94" t="n">
-        <v>0.9786688180301472</v>
+        <v>0.9333610479054046</v>
       </c>
       <c r="F94" t="n">
-        <v>0.9823425390584994</v>
+        <v>0.9433484145845135</v>
       </c>
       <c r="G94" t="n">
-        <v>0.003673721028352284</v>
+        <v>0.009987366679108822</v>
       </c>
       <c r="H94" t="n">
-        <v>-2349475.21648855</v>
+        <v>7060965.928948961</v>
       </c>
       <c r="I94" t="n">
-        <v>-2349475.21648855</v>
+        <v>3530482.964474481</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>sr_dn</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3734,32 +3734,32 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>9M</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>282089586.14</v>
+        <v>950082301.61</v>
       </c>
       <c r="E95" t="n">
-        <v>0.9655145554862491</v>
+        <v>0.9066754799235061</v>
       </c>
       <c r="F95" t="n">
-        <v>0.9715653890248274</v>
+        <v>0.9132110526012888</v>
       </c>
       <c r="G95" t="n">
-        <v>0.006050833538578271</v>
+        <v>0.006535572677782708</v>
       </c>
       <c r="H95" t="n">
-        <v>1706877.128699576</v>
+        <v>6209331.932047226</v>
       </c>
       <c r="I95" t="n">
-        <v>853438.564349788</v>
+        <v>3104665.966023613</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>sr_dn</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3769,32 +3769,32 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>319161024.12</v>
+        <v>1131433784.31</v>
       </c>
       <c r="E96" t="n">
-        <v>0.9530263468310431</v>
+        <v>0.8730418834956067</v>
       </c>
       <c r="F96" t="n">
-        <v>0.9613995716390219</v>
+        <v>0.8762774350947117</v>
       </c>
       <c r="G96" t="n">
-        <v>0.008373224807978752</v>
+        <v>0.003235551599104936</v>
       </c>
       <c r="H96" t="n">
-        <v>2672407.004901489</v>
+        <v>3660812.390105569</v>
       </c>
       <c r="I96" t="n">
-        <v>1336203.502450744</v>
+        <v>1830406.195052784</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>sr_dn</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3804,32 +3804,32 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1.5Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>533754600.58</v>
+        <v>725856199.14</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9378479178638877</v>
+        <v>0.839886760163754</v>
       </c>
       <c r="F97" t="n">
-        <v>0.9496441759214491</v>
+        <v>0.8413575520904415</v>
       </c>
       <c r="G97" t="n">
-        <v>0.01179625805756146</v>
+        <v>0.001470791926687531</v>
       </c>
       <c r="H97" t="n">
-        <v>6296307.007852323</v>
+        <v>1067583.437631209</v>
       </c>
       <c r="I97" t="n">
-        <v>3148153.503926162</v>
+        <v>533791.7188156045</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>sr_dn</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3839,32 +3839,32 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>725837405.03</v>
+        <v>135257246.09</v>
       </c>
       <c r="E98" t="n">
-        <v>0.914020029743317</v>
+        <v>0.8060794216350962</v>
       </c>
       <c r="F98" t="n">
-        <v>0.9301558102536122</v>
+        <v>0.8067138067384347</v>
       </c>
       <c r="G98" t="n">
-        <v>0.01613578051029518</v>
+        <v>0.000634385103338575</v>
       </c>
       <c r="H98" t="n">
-        <v>11711953.0537263</v>
+        <v>85805.18203809572</v>
       </c>
       <c r="I98" t="n">
-        <v>5855976.526863152</v>
+        <v>42902.59101904786</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>sr_dn</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3874,32 +3874,32 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1456815524.71</v>
+        <v>290934368.76</v>
       </c>
       <c r="E99" t="n">
-        <v>0.8793551938327786</v>
+        <v>0.7725125366488534</v>
       </c>
       <c r="F99" t="n">
-        <v>0.9016155859299932</v>
+        <v>0.7727766922643421</v>
       </c>
       <c r="G99" t="n">
-        <v>0.02226039209721464</v>
+        <v>0.0002641556154886482</v>
       </c>
       <c r="H99" t="n">
-        <v>32429284.79335409</v>
+        <v>76851.94724659914</v>
       </c>
       <c r="I99" t="n">
-        <v>16214642.39667704</v>
+        <v>38425.97362329957</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>sr_dn</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3909,32 +3909,32 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>8Y</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>436647272.55</v>
+        <v>293928244.15</v>
       </c>
       <c r="E100" t="n">
-        <v>0.8350903091634028</v>
+        <v>0.7390723504327896</v>
       </c>
       <c r="F100" t="n">
-        <v>0.864835634020792</v>
+        <v>0.7391795637870715</v>
       </c>
       <c r="G100" t="n">
-        <v>0.02974532485738923</v>
+        <v>0.0001072133542818765</v>
       </c>
       <c r="H100" t="n">
-        <v>12988214.97009273</v>
+        <v>31513.03297350384</v>
       </c>
       <c r="I100" t="n">
-        <v>6494107.485046363</v>
+        <v>15756.51648675192</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>sr_dn</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>9Y</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>857024694.1899999</v>
+        <v>240687365.15</v>
       </c>
       <c r="E101" t="n">
-        <v>0.7929814256230181</v>
+        <v>0.7058360643204235</v>
       </c>
       <c r="F101" t="n">
-        <v>0.8294805679220334</v>
+        <v>0.7058782487438041</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0364991422990153</v>
+        <v>4.218442338066453e-05</v>
       </c>
       <c r="H101" t="n">
-        <v>31280666.26701088</v>
+        <v>10153.2577138642</v>
       </c>
       <c r="I101" t="n">
-        <v>15640333.13350544</v>
+        <v>5076.6288569321</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>sr_dn</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>98149543.74000001</v>
+        <v>152144703.2</v>
       </c>
       <c r="E102" t="n">
-        <v>0.7529410815413444</v>
+        <v>0.6740936305925465</v>
       </c>
       <c r="F102" t="n">
-        <v>0.7955126273253091</v>
+        <v>0.6741102300413852</v>
       </c>
       <c r="G102" t="n">
-        <v>0.04257154578396471</v>
+        <v>1.659944883869446e-05</v>
       </c>
       <c r="H102" t="n">
-        <v>4178377.795002658</v>
+        <v>2525.518216846754</v>
       </c>
       <c r="I102" t="n">
-        <v>2089188.897501329</v>
+        <v>1262.759108423377</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>sr_dn</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4014,26 +4014,26 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>15Y</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>317275857.88</v>
+        <v>11282921.34</v>
       </c>
       <c r="E103" t="n">
-        <v>0.7148807043542068</v>
+        <v>0.5835756277426192</v>
       </c>
       <c r="F103" t="n">
-        <v>0.762890923118997</v>
+        <v>0.5835765210563073</v>
       </c>
       <c r="G103" t="n">
-        <v>0.04801021876479017</v>
+        <v>8.933136881328352e-07</v>
       </c>
       <c r="H103" t="n">
-        <v>15232483.34560527</v>
+        <v>10.07918807514807</v>
       </c>
       <c r="I103" t="n">
-        <v>7616241.672802637</v>
+        <v>5.039594037574036</v>
       </c>
     </row>
     <row r="104">
@@ -4049,26 +4049,26 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>8Y</t>
+          <t>Overnight</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>305998789.65</v>
+        <v>-1357868945.18</v>
       </c>
       <c r="E104" t="n">
-        <v>0.6787119945050498</v>
+        <v>0.999906031812547</v>
       </c>
       <c r="F104" t="n">
-        <v>0.7315725866506247</v>
+        <v>0.9999666821952055</v>
       </c>
       <c r="G104" t="n">
-        <v>0.05286059214557493</v>
+        <v>6.06503826584559e-05</v>
       </c>
       <c r="H104" t="n">
-        <v>16175277.21672822</v>
+        <v>-82355.27112520089</v>
       </c>
       <c r="I104" t="n">
-        <v>8087638.608364111</v>
+        <v>-82355.27112520089</v>
       </c>
     </row>
     <row r="105">
@@ -4084,26 +4084,26 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>9Y</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>213878647.01</v>
+        <v>-273538406.96</v>
       </c>
       <c r="E105" t="n">
-        <v>0.6443492036977719</v>
+        <v>0.9983821828874917</v>
       </c>
       <c r="F105" t="n">
-        <v>0.7015136281311324</v>
+        <v>0.9988108186041668</v>
       </c>
       <c r="G105" t="n">
-        <v>0.05716442443336045</v>
+        <v>0.0004286357166750632</v>
       </c>
       <c r="H105" t="n">
-        <v>12226249.75491252</v>
+        <v>-117248.3311054547</v>
       </c>
       <c r="I105" t="n">
-        <v>6113124.877456259</v>
+        <v>-117248.3311054547</v>
       </c>
     </row>
     <row r="106">
@@ -4119,26 +4119,516 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>-391346094.59</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.9936563817038003</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.9953136645003735</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.001657282796573178</v>
+      </c>
+      <c r="H106" t="n">
+        <v>-648571.1500701067</v>
+      </c>
+      <c r="I106" t="n">
+        <v>-648571.1500701067</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>-784700756.36</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.9856536327098718</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.9893554238463047</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.003701791136432875</v>
+      </c>
+      <c r="H107" t="n">
+        <v>-2904798.304645621</v>
+      </c>
+      <c r="I107" t="n">
+        <v>-2904798.304645621</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>106194068.06</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.9761318955535195</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.9822507602923535</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.00611886473883394</v>
+      </c>
+      <c r="H108" t="n">
+        <v>649787.1385256656</v>
+      </c>
+      <c r="I108" t="n">
+        <v>324893.5692628328</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>327029241.36</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.9667342819189046</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.9752290091867239</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.008494727267819302</v>
+      </c>
+      <c r="H109" t="n">
+        <v>2778024.213955052</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1389012.106977526</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>1.5Y</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>453172829.04</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.9524015829683793</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.9643812441965655</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.01197966122818617</v>
+      </c>
+      <c r="H110" t="n">
+        <v>5428856.969717926</v>
+      </c>
+      <c r="I110" t="n">
+        <v>2714428.484858963</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>706989755.74</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.9333610479054046</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.9498385926790147</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.01647754477361008</v>
+      </c>
+      <c r="H111" t="n">
+        <v>11649455.3546895</v>
+      </c>
+      <c r="I111" t="n">
+        <v>5824727.677344751</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>950082301.61</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.9066754799235061</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.9296275124845146</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.02295203256100853</v>
+      </c>
+      <c r="H112" t="n">
+        <v>21806319.92219065</v>
+      </c>
+      <c r="I112" t="n">
+        <v>10903159.96109532</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>4Y</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1131433784.31</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.8730418834956067</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.9041391543762624</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.03109727088065561</v>
+      </c>
+      <c r="H113" t="n">
+        <v>35184502.87421335</v>
+      </c>
+      <c r="I113" t="n">
+        <v>17592251.43710667</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>725856199.14</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.839886760163754</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.8785448976256938</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.0386581374619398</v>
+      </c>
+      <c r="H114" t="n">
+        <v>28060248.72395527</v>
+      </c>
+      <c r="I114" t="n">
+        <v>14030124.36197763</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>6Y</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>135257246.09</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.8060794216350962</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.8516556228627923</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.04557620122769612</v>
+      </c>
+      <c r="H115" t="n">
+        <v>6164511.465301855</v>
+      </c>
+      <c r="I115" t="n">
+        <v>3082255.732650927</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>7Y</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>290934368.76</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.7725125366488534</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.8243935807346117</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.05188104408575822</v>
+      </c>
+      <c r="H116" t="n">
+        <v>15093978.8116998</v>
+      </c>
+      <c r="I116" t="n">
+        <v>7546989.405849899</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>8Y</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>293928244.15</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.7390723504327896</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.7966342616211253</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.05756191118833565</v>
+      </c>
+      <c r="H117" t="n">
+        <v>16919071.48550573</v>
+      </c>
+      <c r="I117" t="n">
+        <v>8459535.742752867</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>9Y</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>240687365.15</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7058360643204235</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.7684551601375782</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.06261909581715475</v>
+      </c>
+      <c r="H118" t="n">
+        <v>15071625.18030636</v>
+      </c>
+      <c r="I118" t="n">
+        <v>7535812.590153181</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
           <t>10Y</t>
         </is>
       </c>
-      <c r="D106" t="n">
-        <v>6012265.48</v>
-      </c>
-      <c r="E106" t="n">
-        <v>0.6117079401756688</v>
-      </c>
-      <c r="F106" t="n">
-        <v>0.6726696846576002</v>
-      </c>
-      <c r="G106" t="n">
-        <v>0.06096174448193148</v>
-      </c>
-      <c r="H106" t="n">
-        <v>366518.1919492972</v>
-      </c>
-      <c r="I106" t="n">
-        <v>183259.0959746486</v>
+      <c r="D119" t="n">
+        <v>152144703.2</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.6740936305925465</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.7412728311916278</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.06717920059908133</v>
+      </c>
+      <c r="H119" t="n">
+        <v>10220959.53636049</v>
+      </c>
+      <c r="I119" t="n">
+        <v>5110479.768180246</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>15Y</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11282921.34</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.5835756277426192</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.6612777498325166</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.07770212208989746</v>
+      </c>
+      <c r="H120" t="n">
+        <v>876706.9314913895</v>
+      </c>
+      <c r="I120" t="n">
+        <v>438353.4657456948</v>
       </c>
     </row>
   </sheetData>
@@ -4214,22 +4704,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="D2" t="n">
-        <v>2135795552.07</v>
+        <v>1899204219.51</v>
       </c>
       <c r="E2" t="n">
-        <v>-56451590.77999997</v>
+        <v>-109259092.9100001</v>
       </c>
       <c r="F2" t="n">
-        <v>-56451590.77999997</v>
+        <v>-109259092.9100001</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.704299231666664</v>
+        <v>-9.104924409166674</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.704299231666664</v>
+        <v>-9.104924409166674</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -4247,22 +4737,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="D3" t="n">
-        <v>2253653018.34</v>
+        <v>2128346249.82</v>
       </c>
       <c r="E3" t="n">
-        <v>61405875.49000025</v>
+        <v>119882937.3999999</v>
       </c>
       <c r="F3" t="n">
-        <v>30702937.74500012</v>
+        <v>59941468.69999993</v>
       </c>
       <c r="G3" t="n">
-        <v>5.117156290833353</v>
+        <v>9.990244783333321</v>
       </c>
       <c r="H3" t="n">
-        <v>2.558578145416677</v>
+        <v>4.99512239166666</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -4280,22 +4770,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="D4" t="n">
-        <v>2188335533.43</v>
+        <v>1969035458.72</v>
       </c>
       <c r="E4" t="n">
-        <v>-3911609.420000076</v>
+        <v>-39427853.70000005</v>
       </c>
       <c r="F4" t="n">
-        <v>-3911609.420000076</v>
+        <v>-39427853.70000005</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.325967451666673</v>
+        <v>-3.285654475000004</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.325967451666673</v>
+        <v>-3.285654475000004</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -4313,22 +4803,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="D5" t="n">
-        <v>2190935799.46</v>
+        <v>2038240148.16</v>
       </c>
       <c r="E5" t="n">
-        <v>-1311343.389999866</v>
+        <v>29776835.74000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1311343.389999866</v>
+        <v>14888417.87</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1092786158333222</v>
+        <v>2.481402978333334</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1092786158333222</v>
+        <v>1.240701489166667</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -4346,22 +4836,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="D6" t="n">
-        <v>2167308510.39</v>
+        <v>1988438779.55</v>
       </c>
       <c r="E6" t="n">
-        <v>-24938632.46000004</v>
+        <v>-20024532.87000012</v>
       </c>
       <c r="F6" t="n">
-        <v>-24938632.46000004</v>
+        <v>-20024532.87000012</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.07821937166667</v>
+        <v>-1.66871107250001</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.07821937166667</v>
+        <v>-1.66871107250001</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -4379,22 +4869,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="D7" t="n">
-        <v>2219037258.94</v>
+        <v>2028925382.35</v>
       </c>
       <c r="E7" t="n">
-        <v>26790116.09000015</v>
+        <v>20462069.92999983</v>
       </c>
       <c r="F7" t="n">
-        <v>13395058.04500008</v>
+        <v>10231034.96499991</v>
       </c>
       <c r="G7" t="n">
-        <v>2.232509674166679</v>
+        <v>1.705172494166652</v>
       </c>
       <c r="H7" t="n">
-        <v>1.11625483708334</v>
+        <v>0.8525862470833262</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -4412,22 +4902,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="D8" t="n">
-        <v>2216973654.4</v>
+        <v>2055152460</v>
       </c>
       <c r="E8" t="n">
-        <v>24726511.55000019</v>
+        <v>46689147.57999992</v>
       </c>
       <c r="F8" t="n">
-        <v>12363255.7750001</v>
+        <v>23344573.78999996</v>
       </c>
       <c r="G8" t="n">
-        <v>2.060542629166683</v>
+        <v>3.890762298333327</v>
       </c>
       <c r="H8" t="n">
-        <v>1.030271314583341</v>
+        <v>1.945381149166663</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -4557,34 +5047,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G2" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="J2" t="n">
         <v>-680000000</v>
       </c>
       <c r="K2" t="n">
-        <v>-750323402.3400002</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1050151041880321</v>
+        <v>0.03432749872940843</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07754352080482141</v>
+        <v>0.05933231753539991</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.02747158338321065</v>
+        <v>0.02500481880599148</v>
       </c>
       <c r="O2" t="n">
-        <v>20556099.11199939</v>
+        <v>-32421705.62942012</v>
       </c>
       <c r="P2" t="n">
-        <v>10278049.55599969</v>
+        <v>-32421705.62942012</v>
       </c>
     </row>
     <row r="3">
@@ -4615,34 +5105,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G3" t="n">
-        <v>425995266.0600001</v>
+        <v>912642221.4799999</v>
       </c>
       <c r="H3" t="n">
-        <v>-90269181.22613968</v>
+        <v>-89542810.95890412</v>
       </c>
       <c r="I3" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="J3" t="n">
         <v>-68000000</v>
       </c>
       <c r="K3" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05822765833026367</v>
+        <v>0.03782665436246635</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08337755773034683</v>
+        <v>0.06293247021270165</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02514989940008316</v>
+        <v>0.0251058158502353</v>
       </c>
       <c r="O3" t="n">
-        <v>7739854.154592426</v>
+        <v>18942533.70806487</v>
       </c>
       <c r="P3" t="n">
-        <v>3869927.077296213</v>
+        <v>9471266.854032435</v>
       </c>
     </row>
     <row r="4">
@@ -4673,34 +5163,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>2339361769.16</v>
+        <v>879884659.5500001</v>
       </c>
       <c r="H4" t="n">
-        <v>-51490547.94520548</v>
+        <v>-50934753.42465753</v>
       </c>
       <c r="I4" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="J4" t="n">
-        <v>-68000000</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05839364669442126</v>
+        <v>0.03830470017405307</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08369379184910075</v>
+        <v>0.06351793262205963</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02530014515467949</v>
+        <v>0.02521323244800655</v>
       </c>
       <c r="O4" t="n">
-        <v>48236228.32662344</v>
+        <v>17417088.89240956</v>
       </c>
       <c r="P4" t="n">
-        <v>24118114.16331172</v>
+        <v>8708544.446204778</v>
       </c>
     </row>
     <row r="5">
@@ -4731,34 +5221,34 @@
         <v>0.75</v>
       </c>
       <c r="G5" t="n">
-        <v>368810148.66</v>
+        <v>1240710907.89</v>
       </c>
       <c r="H5" t="n">
-        <v>-92049904.10958904</v>
+        <v>-91346794.52054794</v>
       </c>
       <c r="I5" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="J5" t="n">
-        <v>-68000000</v>
+        <v>-136000000</v>
       </c>
       <c r="K5" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05851824187679444</v>
+        <v>0.03852218097221538</v>
       </c>
       <c r="M5" t="n">
-        <v>0.08396522087656511</v>
+        <v>0.06384244431183639</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02544697899977066</v>
+        <v>0.02532026333962101</v>
       </c>
       <c r="O5" t="n">
-        <v>5282034.098284275</v>
+        <v>21826651.5177184</v>
       </c>
       <c r="P5" t="n">
-        <v>2641017.049142138</v>
+        <v>10913325.7588592</v>
       </c>
     </row>
     <row r="6">
@@ -4789,34 +5279,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>-180822610.01</v>
+        <v>-201932841.91</v>
       </c>
       <c r="H6" t="n">
-        <v>-51458493.15068493</v>
+        <v>-50972657.53424658</v>
       </c>
       <c r="I6" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="J6" t="n">
         <v>-68000000</v>
       </c>
       <c r="K6" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05821004393128892</v>
+        <v>0.03873510939427094</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08380359375583302</v>
+        <v>0.06416383416053839</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02559354982454409</v>
+        <v>0.02542872476626745</v>
       </c>
       <c r="O6" t="n">
-        <v>-3963265.324695371</v>
+        <v>-4287376.224828769</v>
       </c>
       <c r="P6" t="n">
-        <v>-3963265.324695371</v>
+        <v>-4287376.224828769</v>
       </c>
     </row>
     <row r="7">
@@ -4847,34 +5337,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>396368601.78</v>
+        <v>-196825268.73</v>
       </c>
       <c r="H7" t="n">
-        <v>-51445520.54794521</v>
+        <v>-50988356.16438356</v>
       </c>
       <c r="I7" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="J7" t="n">
         <v>-68000000</v>
       </c>
       <c r="K7" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05808035784574397</v>
+        <v>0.03888939094511485</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08381995594343969</v>
+        <v>0.064427603552231</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02573959809769572</v>
+        <v>0.02553821260711615</v>
       </c>
       <c r="O7" t="n">
-        <v>5178939.199893634</v>
+        <v>-3691751.606370857</v>
       </c>
       <c r="P7" t="n">
-        <v>2589469.599946817</v>
+        <v>-3691751.606370857</v>
       </c>
     </row>
     <row r="8">
@@ -4905,34 +5395,34 @@
         <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>270725457.28</v>
+        <v>69886647.3499999</v>
       </c>
       <c r="H8" t="n">
-        <v>-90799555.08645856</v>
+        <v>-89968608.21917808</v>
       </c>
       <c r="I8" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="J8" t="n">
         <v>-34000000</v>
       </c>
       <c r="K8" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0579990267461179</v>
+        <v>0.03901400018340251</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08388647441583164</v>
+        <v>0.06466175178617339</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02588744766971374</v>
+        <v>0.02564775160277089</v>
       </c>
       <c r="O8" t="n">
-        <v>2328911.188730668</v>
+        <v>-257528.5720346234</v>
       </c>
       <c r="P8" t="n">
-        <v>1164455.594365334</v>
+        <v>-257528.5720346234</v>
       </c>
     </row>
     <row r="9">
@@ -4963,34 +5453,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G9" t="n">
-        <v>-35174959.2</v>
+        <v>-81388394.01999998</v>
       </c>
       <c r="H9" t="n">
-        <v>2247136.761733663</v>
+        <v>2250000</v>
       </c>
       <c r="I9" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="J9" t="n">
         <v>-34000000</v>
       </c>
       <c r="K9" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05738520780446178</v>
+        <v>0.03908855826627113</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08341197750438349</v>
+        <v>0.06484684505880736</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02602676969992171</v>
+        <v>0.02575828679253624</v>
       </c>
       <c r="O9" t="n">
-        <v>-357085.3547169468</v>
+        <v>-849362.2706116225</v>
       </c>
       <c r="P9" t="n">
-        <v>-357085.3547169468</v>
+        <v>-849362.2706116225</v>
       </c>
     </row>
     <row r="10">
@@ -5021,34 +5511,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G10" t="n">
-        <v>-35427280.72000001</v>
+        <v>-24300588.46000001</v>
       </c>
       <c r="H10" t="n">
-        <v>2266152.03233775</v>
+        <v>2250000</v>
       </c>
       <c r="I10" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="J10" t="n">
         <v>-34000000</v>
       </c>
       <c r="K10" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05695407285841891</v>
+        <v>0.03915884386251234</v>
       </c>
       <c r="M10" t="n">
-        <v>0.08312099411366869</v>
+        <v>0.06502656643195814</v>
       </c>
       <c r="N10" t="n">
-        <v>0.02616692125524978</v>
+        <v>0.02586772256944581</v>
       </c>
       <c r="O10" t="n">
-        <v>-289241.5477017542</v>
+        <v>-190132.8349254345</v>
       </c>
       <c r="P10" t="n">
-        <v>-289241.5477017542</v>
+        <v>-190132.8349254345</v>
       </c>
     </row>
     <row r="11">
@@ -5079,34 +5569,34 @@
         <v>0.25</v>
       </c>
       <c r="G11" t="n">
-        <v>-35839034.46</v>
+        <v>-25229792.01000001</v>
       </c>
       <c r="H11" t="n">
-        <v>2248181.001571974</v>
+        <v>2250000</v>
       </c>
       <c r="I11" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="J11" t="n">
         <v>-34000000</v>
       </c>
       <c r="K11" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05664439372837885</v>
+        <v>0.03922681220647117</v>
       </c>
       <c r="M11" t="n">
-        <v>0.08295275176741097</v>
+        <v>0.06520531674627043</v>
       </c>
       <c r="N11" t="n">
-        <v>0.02630835803903212</v>
+        <v>0.02597850453979926</v>
       </c>
       <c r="O11" t="n">
-        <v>-220930.0499052462</v>
+        <v>-149245.157763857</v>
       </c>
       <c r="P11" t="n">
-        <v>-220930.0499052462</v>
+        <v>-149245.157763857</v>
       </c>
     </row>
     <row r="12">
@@ -5137,34 +5627,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G12" t="n">
-        <v>-35777615.53999999</v>
+        <v>43083900.58</v>
       </c>
       <c r="H12" t="n">
-        <v>2248686.278913092</v>
+        <v>2250000</v>
       </c>
       <c r="I12" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="J12" t="n">
         <v>-34000000</v>
       </c>
       <c r="K12" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05642057743315654</v>
+        <v>0.03929424848359133</v>
       </c>
       <c r="M12" t="n">
-        <v>0.08287071239183845</v>
+        <v>0.06538378070787436</v>
       </c>
       <c r="N12" t="n">
-        <v>0.02645013495868191</v>
+        <v>0.02608953222428303</v>
       </c>
       <c r="O12" t="n">
-        <v>-147807.4506626412</v>
+        <v>197123.3766723921</v>
       </c>
       <c r="P12" t="n">
-        <v>-147807.4506626412</v>
+        <v>98561.68833619606</v>
       </c>
     </row>
     <row r="13">
@@ -5195,34 +5685,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G13" t="n">
-        <v>-35715304.73</v>
+        <v>32635075.89</v>
       </c>
       <c r="H13" t="n">
-        <v>2261537.165955536</v>
+        <v>2262328.767123288</v>
       </c>
       <c r="I13" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="J13" t="n">
-        <v>-34000000</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05625883751011833</v>
+        <v>0.03936107056455495</v>
       </c>
       <c r="M13" t="n">
-        <v>0.08285170738618473</v>
+        <v>0.06556220011090294</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02659286987606641</v>
+        <v>0.02620112954634799</v>
       </c>
       <c r="O13" t="n">
-        <v>-74135.97397456717</v>
+        <v>76195.95168771796</v>
       </c>
       <c r="P13" t="n">
-        <v>-74135.97397456717</v>
+        <v>38097.97584385898</v>
       </c>
     </row>
     <row r="14">
@@ -5253,28 +5743,28 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-36430105.95000001</v>
+        <v>-85065078.76000001</v>
       </c>
       <c r="H14" t="n">
-        <v>4044566.584325174</v>
+        <v>4045068.493150685</v>
       </c>
       <c r="I14" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="J14" t="n">
-        <v>-34000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K14" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05611688274594639</v>
+        <v>0.03942868733737526</v>
       </c>
       <c r="M14" t="n">
-        <v>0.08285261130760024</v>
+        <v>0.06574199337207398</v>
       </c>
       <c r="N14" t="n">
-        <v>0.02673572856165385</v>
+        <v>0.02631330603469872</v>
       </c>
       <c r="O14" t="n">
         <v>-0</v>
@@ -5311,34 +5801,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G15" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="J15" t="n">
         <v>-680000000</v>
       </c>
       <c r="K15" t="n">
-        <v>-750323402.3400002</v>
+        <v>-620180437.28</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1050151041880321</v>
+        <v>0.03432749872940843</v>
       </c>
       <c r="M15" t="n">
-        <v>0.02753748516008958</v>
+        <v>0.00932749994446147</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.07747761902794248</v>
+        <v>-0.02499999878494696</v>
       </c>
       <c r="O15" t="n">
-        <v>57974001.47941458</v>
+        <v>15462032.06836994</v>
       </c>
       <c r="P15" t="n">
-        <v>28987000.73970729</v>
+        <v>7731016.034184968</v>
       </c>
     </row>
     <row r="16">
@@ -5369,34 +5859,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G16" t="n">
-        <v>425995266.0600001</v>
+        <v>912642221.4799999</v>
       </c>
       <c r="H16" t="n">
-        <v>-90269181.22613968</v>
+        <v>-89542810.95890412</v>
       </c>
       <c r="I16" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="J16" t="n">
         <v>-68000000</v>
       </c>
       <c r="K16" t="n">
-        <v>403726084.8338604</v>
+        <v>891099410.5210958</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05822765833026367</v>
+        <v>0.03782665436246635</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0331349453908647</v>
+        <v>0.01277490186754093</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.02509271293939896</v>
+        <v>-0.02505175249492542</v>
       </c>
       <c r="O16" t="n">
-        <v>-9286367.523476534</v>
+        <v>-20463301.72401939</v>
       </c>
       <c r="P16" t="n">
-        <v>-9286367.523476534</v>
+        <v>-20463301.72401939</v>
       </c>
     </row>
     <row r="17">
@@ -5427,34 +5917,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G17" t="n">
-        <v>2339361769.16</v>
+        <v>879884659.5500001</v>
       </c>
       <c r="H17" t="n">
-        <v>-51490547.94520548</v>
+        <v>-50934753.42465753</v>
       </c>
       <c r="I17" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="J17" t="n">
-        <v>-68000000</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2355871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="L17" t="n">
-        <v>0.05839364669442126</v>
+        <v>0.03830470017405307</v>
       </c>
       <c r="M17" t="n">
-        <v>0.03320699258664073</v>
+        <v>0.01319862907416969</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.02518665410778054</v>
+        <v>-0.02510607109988339</v>
       </c>
       <c r="O17" t="n">
-        <v>-49447094.6426763</v>
+        <v>-17343062.73452042</v>
       </c>
       <c r="P17" t="n">
-        <v>-49447094.6426763</v>
+        <v>-17343062.73452042</v>
       </c>
     </row>
     <row r="18">
@@ -5485,34 +5975,34 @@
         <v>0.75</v>
       </c>
       <c r="G18" t="n">
-        <v>368810148.66</v>
+        <v>1240710907.89</v>
       </c>
       <c r="H18" t="n">
-        <v>-92049904.10958904</v>
+        <v>-91346794.52054794</v>
       </c>
       <c r="I18" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="J18" t="n">
-        <v>-68000000</v>
+        <v>-136000000</v>
       </c>
       <c r="K18" t="n">
-        <v>344760244.5504109</v>
+        <v>1285364113.369452</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05851824187679444</v>
+        <v>0.03852218097221538</v>
       </c>
       <c r="M18" t="n">
-        <v>0.03323339261266689</v>
+        <v>0.01336057997554096</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.02528484926412755</v>
+        <v>-0.02516160099667442</v>
       </c>
       <c r="O18" t="n">
-        <v>-6537908.111790668</v>
+        <v>-24256364.21703475</v>
       </c>
       <c r="P18" t="n">
-        <v>-6537908.111790668</v>
+        <v>-24256364.21703475</v>
       </c>
     </row>
     <row r="19">
@@ -5543,34 +6033,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>-180822610.01</v>
+        <v>-201932841.91</v>
       </c>
       <c r="H19" t="n">
-        <v>-51458493.15068493</v>
+        <v>-50972657.53424658</v>
       </c>
       <c r="I19" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="J19" t="n">
         <v>-68000000</v>
       </c>
       <c r="K19" t="n">
-        <v>-164281103.1606849</v>
+        <v>-184905499.4442466</v>
       </c>
       <c r="L19" t="n">
-        <v>0.05821004393128892</v>
+        <v>0.03873510939427094</v>
       </c>
       <c r="M19" t="n">
-        <v>0.03283281915676661</v>
+        <v>0.01351767801483916</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.02537722477452231</v>
+        <v>-0.02521743137943178</v>
       </c>
       <c r="O19" t="n">
-        <v>2779332.32074346</v>
+        <v>3108561.1626099</v>
       </c>
       <c r="P19" t="n">
-        <v>1389666.16037173</v>
+        <v>1554280.58130495</v>
       </c>
     </row>
     <row r="20">
@@ -5601,34 +6091,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>396368601.78</v>
+        <v>-196825268.73</v>
       </c>
       <c r="H20" t="n">
-        <v>-51445520.54794521</v>
+        <v>-50988356.16438356</v>
       </c>
       <c r="I20" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="J20" t="n">
         <v>-68000000</v>
       </c>
       <c r="K20" t="n">
-        <v>412923081.2320548</v>
+        <v>-179813624.8943836</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05808035784574397</v>
+        <v>0.03888939094511485</v>
       </c>
       <c r="M20" t="n">
-        <v>0.03260901053869531</v>
+        <v>0.01361649928042201</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.02547134730704866</v>
+        <v>-0.02527289166469284</v>
       </c>
       <c r="O20" t="n">
-        <v>-6135329.207675694</v>
+        <v>2650905.986045025</v>
       </c>
       <c r="P20" t="n">
-        <v>-6135329.207675694</v>
+        <v>1325452.993022513</v>
       </c>
     </row>
     <row r="21">
@@ -5659,34 +6149,34 @@
         <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>270725457.28</v>
+        <v>69886647.3499999</v>
       </c>
       <c r="H21" t="n">
-        <v>-90799555.08645856</v>
+        <v>-89968608.21917808</v>
       </c>
       <c r="I21" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="J21" t="n">
         <v>-34000000</v>
       </c>
       <c r="K21" t="n">
-        <v>213925902.1935414</v>
+        <v>13918039.13082182</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0579990267461179</v>
+        <v>0.03901400018340251</v>
       </c>
       <c r="M21" t="n">
-        <v>0.03243513705883272</v>
+        <v>0.01368509298833365</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.02556388968728518</v>
+        <v>-0.02532890719506886</v>
       </c>
       <c r="O21" t="n">
-        <v>-2734389.082464326</v>
+        <v>-176264.3607409614</v>
       </c>
       <c r="P21" t="n">
-        <v>-2734389.082464326</v>
+        <v>-176264.3607409614</v>
       </c>
     </row>
     <row r="22">
@@ -5717,34 +6207,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G22" t="n">
-        <v>-35174959.2</v>
+        <v>-81388394.01999998</v>
       </c>
       <c r="H22" t="n">
-        <v>2247136.761733663</v>
+        <v>2250000</v>
       </c>
       <c r="I22" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="J22" t="n">
         <v>-34000000</v>
       </c>
       <c r="K22" t="n">
-        <v>1072177.561733659</v>
+        <v>-45138394.01999998</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05738520780446178</v>
+        <v>0.03908855826627113</v>
       </c>
       <c r="M22" t="n">
-        <v>0.03173641088008074</v>
+        <v>0.01370492491423558</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.02564879692438105</v>
+        <v>-0.02538363335203554</v>
       </c>
       <c r="O22" t="n">
-        <v>-11458.3602282436</v>
+        <v>477406.8516264138</v>
       </c>
       <c r="P22" t="n">
-        <v>-11458.3602282436</v>
+        <v>238703.4258132069</v>
       </c>
     </row>
     <row r="23">
@@ -5775,34 +6265,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>-35427280.72000001</v>
+        <v>-24300588.46000001</v>
       </c>
       <c r="H23" t="n">
-        <v>2266152.03233775</v>
+        <v>2250000</v>
       </c>
       <c r="I23" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="J23" t="n">
         <v>-34000000</v>
       </c>
       <c r="K23" t="n">
-        <v>838871.312337745</v>
+        <v>11949411.53999999</v>
       </c>
       <c r="L23" t="n">
-        <v>0.05695407285841891</v>
+        <v>0.03915884386251234</v>
       </c>
       <c r="M23" t="n">
-        <v>0.03122012932187956</v>
+        <v>0.01371890926742469</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.02573394353653935</v>
+        <v>-0.02543993459508764</v>
       </c>
       <c r="O23" t="n">
-        <v>-7195.8223287074</v>
+        <v>-101330.7493424618</v>
       </c>
       <c r="P23" t="n">
-        <v>-7195.8223287074</v>
+        <v>-101330.7493424618</v>
       </c>
     </row>
     <row r="24">
@@ -5833,34 +6323,34 @@
         <v>0.25</v>
       </c>
       <c r="G24" t="n">
-        <v>-35839034.46</v>
+        <v>-25229792.01000001</v>
       </c>
       <c r="H24" t="n">
-        <v>2248181.001571974</v>
+        <v>2250000</v>
       </c>
       <c r="I24" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="J24" t="n">
         <v>-34000000</v>
       </c>
       <c r="K24" t="n">
-        <v>409146.5415719748</v>
+        <v>11020207.98999999</v>
       </c>
       <c r="L24" t="n">
-        <v>0.05664439372837885</v>
+        <v>0.03922681220647117</v>
       </c>
       <c r="M24" t="n">
-        <v>0.03082552007485706</v>
+        <v>0.01373128881977485</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.02581887365352179</v>
+        <v>-0.02549552338669633</v>
       </c>
       <c r="O24" t="n">
-        <v>-2640.925715655555</v>
+        <v>-70241.49263382565</v>
       </c>
       <c r="P24" t="n">
-        <v>-2640.925715655555</v>
+        <v>-70241.49263382565</v>
       </c>
     </row>
     <row r="25">
@@ -5891,34 +6381,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G25" t="n">
-        <v>-35777615.53999999</v>
+        <v>43083900.58</v>
       </c>
       <c r="H25" t="n">
-        <v>2248686.278913092</v>
+        <v>2250000</v>
       </c>
       <c r="I25" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="J25" t="n">
         <v>-34000000</v>
       </c>
       <c r="K25" t="n">
-        <v>471070.7389131002</v>
+        <v>79333900.58</v>
       </c>
       <c r="L25" t="n">
-        <v>0.05642057743315654</v>
+        <v>0.03929424848359133</v>
       </c>
       <c r="M25" t="n">
-        <v>0.03051606872334229</v>
+        <v>0.01374277691480819</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.02590450870981425</v>
+        <v>-0.02555147156878314</v>
       </c>
       <c r="O25" t="n">
-        <v>-2033.809343185506</v>
+        <v>-337849.6508517564</v>
       </c>
       <c r="P25" t="n">
-        <v>-2033.809343185506</v>
+        <v>-337849.6508517564</v>
       </c>
     </row>
     <row r="26">
@@ -5949,34 +6439,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G26" t="n">
-        <v>-35715304.73</v>
+        <v>32635075.89</v>
       </c>
       <c r="H26" t="n">
-        <v>2261537.165955536</v>
+        <v>2262328.767123288</v>
       </c>
       <c r="I26" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="J26" t="n">
-        <v>-34000000</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>546232.4359555319</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="L26" t="n">
-        <v>0.05625883751011833</v>
+        <v>0.03936107056455495</v>
       </c>
       <c r="M26" t="n">
-        <v>0.03026857544468633</v>
+        <v>0.01375362077121506</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.025990262065432</v>
+        <v>-0.02560744979333988</v>
       </c>
       <c r="O26" t="n">
-        <v>-1183.060346593632</v>
+        <v>-74469.46147292921</v>
       </c>
       <c r="P26" t="n">
-        <v>-1183.060346593632</v>
+        <v>-74469.46147292921</v>
       </c>
     </row>
     <row r="27">
@@ -6007,34 +6497,34 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-36430105.95000001</v>
+        <v>-85065078.76000001</v>
       </c>
       <c r="H27" t="n">
-        <v>4044566.584325174</v>
+        <v>4045068.493150685</v>
       </c>
       <c r="I27" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="J27" t="n">
-        <v>-34000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K27" t="n">
-        <v>1614460.634325162</v>
+        <v>-13020010.26684932</v>
       </c>
       <c r="L27" t="n">
-        <v>0.05611688274594639</v>
+        <v>0.03942868733737526</v>
       </c>
       <c r="M27" t="n">
-        <v>0.030041267032894</v>
+        <v>0.01376514673139084</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.02607561571305239</v>
+        <v>-0.02566354060598441</v>
       </c>
       <c r="O27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -6065,34 +6555,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G28" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="J28" t="n">
         <v>-680000000</v>
       </c>
       <c r="K28" t="n">
-        <v>-750323402.3400002</v>
+        <v>-620180437.28</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1050151041880321</v>
+        <v>0.03432749872940843</v>
       </c>
       <c r="M28" t="n">
-        <v>0.02998523830907041</v>
+        <v>0.01167814650917531</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.07502986587896165</v>
+        <v>-0.02264935222023312</v>
       </c>
       <c r="O28" t="n">
-        <v>56142426.80713306</v>
+        <v>14008201.0951103</v>
       </c>
       <c r="P28" t="n">
-        <v>28071213.40356653</v>
+        <v>7004100.547555152</v>
       </c>
     </row>
     <row r="29">
@@ -6123,34 +6613,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G29" t="n">
-        <v>425995266.0600001</v>
+        <v>912642221.4799999</v>
       </c>
       <c r="H29" t="n">
-        <v>-90269181.22613968</v>
+        <v>-89542810.95890412</v>
       </c>
       <c r="I29" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="J29" t="n">
         <v>-68000000</v>
       </c>
       <c r="K29" t="n">
-        <v>403726084.8338604</v>
+        <v>891099410.5210958</v>
       </c>
       <c r="L29" t="n">
-        <v>0.05822765833026367</v>
+        <v>0.03782665436246635</v>
       </c>
       <c r="M29" t="n">
-        <v>0.03834659693956599</v>
+        <v>0.01796790037339591</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.01988106139069767</v>
+        <v>-0.01985875398907044</v>
       </c>
       <c r="O29" t="n">
-        <v>-7357627.821140663</v>
+        <v>-16221446.97556545</v>
       </c>
       <c r="P29" t="n">
-        <v>-7357627.821140663</v>
+        <v>-16221446.97556545</v>
       </c>
     </row>
     <row r="30">
@@ -6181,34 +6671,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G30" t="n">
-        <v>2339361769.16</v>
+        <v>879884659.5500001</v>
       </c>
       <c r="H30" t="n">
-        <v>-51490547.94520548</v>
+        <v>-50934753.42465753</v>
       </c>
       <c r="I30" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="J30" t="n">
-        <v>-68000000</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>2355871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="L30" t="n">
-        <v>0.05839364669442126</v>
+        <v>0.03830470017405307</v>
       </c>
       <c r="M30" t="n">
-        <v>0.04113736359982756</v>
+        <v>0.02108193610380882</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.01725628309459371</v>
+        <v>-0.01722276407024426</v>
       </c>
       <c r="O30" t="n">
-        <v>-33877983.93974058</v>
+        <v>-11897340.54937325</v>
       </c>
       <c r="P30" t="n">
-        <v>-33877983.93974058</v>
+        <v>-11897340.54937325</v>
       </c>
     </row>
     <row r="31">
@@ -6239,34 +6729,34 @@
         <v>0.75</v>
       </c>
       <c r="G31" t="n">
-        <v>368810148.66</v>
+        <v>1240710907.89</v>
       </c>
       <c r="H31" t="n">
-        <v>-92049904.10958904</v>
+        <v>-91346794.52054794</v>
       </c>
       <c r="I31" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="J31" t="n">
-        <v>-68000000</v>
+        <v>-136000000</v>
       </c>
       <c r="K31" t="n">
-        <v>344760244.5504109</v>
+        <v>1285364113.369452</v>
       </c>
       <c r="L31" t="n">
-        <v>0.05851824187679444</v>
+        <v>0.03852218097221538</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0436276127705737</v>
+        <v>0.02369222481558175</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.01489062910622074</v>
+        <v>-0.01482995615663363</v>
       </c>
       <c r="O31" t="n">
-        <v>-3850272.699127598</v>
+        <v>-14296420.08493442</v>
       </c>
       <c r="P31" t="n">
-        <v>-3850272.699127598</v>
+        <v>-14296420.08493442</v>
       </c>
     </row>
     <row r="32">
@@ -6297,34 +6787,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G32" t="n">
-        <v>-180822610.01</v>
+        <v>-201932841.91</v>
       </c>
       <c r="H32" t="n">
-        <v>-51458493.15068493</v>
+        <v>-50972657.53424658</v>
       </c>
       <c r="I32" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="J32" t="n">
         <v>-68000000</v>
       </c>
       <c r="K32" t="n">
-        <v>-164281103.1606849</v>
+        <v>-184905499.4442466</v>
       </c>
       <c r="L32" t="n">
-        <v>0.05821004393128892</v>
+        <v>0.03873510939427094</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0455480154500596</v>
+        <v>0.02612995067642809</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.01266202848122933</v>
+        <v>-0.01260515871784285</v>
       </c>
       <c r="O32" t="n">
-        <v>1386754.671432244</v>
+        <v>1553842.112197821</v>
       </c>
       <c r="P32" t="n">
-        <v>693377.3357161219</v>
+        <v>776921.0560989103</v>
       </c>
     </row>
     <row r="33">
@@ -6355,34 +6845,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G33" t="n">
-        <v>396368601.78</v>
+        <v>-196825268.73</v>
       </c>
       <c r="H33" t="n">
-        <v>-51445520.54794521</v>
+        <v>-50988356.16438356</v>
       </c>
       <c r="I33" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="J33" t="n">
         <v>-68000000</v>
       </c>
       <c r="K33" t="n">
-        <v>412923081.2320548</v>
+        <v>-179813624.8943836</v>
       </c>
       <c r="L33" t="n">
-        <v>0.05808035784574397</v>
+        <v>0.03888939094511485</v>
       </c>
       <c r="M33" t="n">
-        <v>0.04746456405164672</v>
+        <v>0.02835546395408812</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.01061579379409725</v>
+        <v>-0.01053392699102673</v>
       </c>
       <c r="O33" t="n">
-        <v>-2557045.331856611</v>
+        <v>1104917.09803376</v>
       </c>
       <c r="P33" t="n">
-        <v>-2557045.331856611</v>
+        <v>552458.54901688</v>
       </c>
     </row>
     <row r="34">
@@ -6413,34 +6903,34 @@
         <v>0.5</v>
       </c>
       <c r="G34" t="n">
-        <v>270725457.28</v>
+        <v>69886647.3499999</v>
       </c>
       <c r="H34" t="n">
-        <v>-90799555.08645856</v>
+        <v>-89968608.21917808</v>
       </c>
       <c r="I34" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="J34" t="n">
         <v>-34000000</v>
       </c>
       <c r="K34" t="n">
-        <v>213925902.1935414</v>
+        <v>13918039.13082182</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0579990267461179</v>
+        <v>0.03901400018340251</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0492972557825806</v>
+        <v>0.03038307855295308</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.008701770963537303</v>
+        <v>-0.008630921630449429</v>
       </c>
       <c r="O34" t="n">
-        <v>-930767.1020281399</v>
+        <v>-60062.75249382582</v>
       </c>
       <c r="P34" t="n">
-        <v>-930767.1020281399</v>
+        <v>-60062.75249382582</v>
       </c>
     </row>
     <row r="35">
@@ -6471,34 +6961,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G35" t="n">
-        <v>-35174959.2</v>
+        <v>-81388394.01999998</v>
       </c>
       <c r="H35" t="n">
-        <v>2247136.761733663</v>
+        <v>2250000</v>
       </c>
       <c r="I35" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="J35" t="n">
         <v>-34000000</v>
       </c>
       <c r="K35" t="n">
-        <v>1072177.561733659</v>
+        <v>-45138394.01999998</v>
       </c>
       <c r="L35" t="n">
-        <v>0.05738520780446178</v>
+        <v>0.03908855826627113</v>
       </c>
       <c r="M35" t="n">
-        <v>0.05045136439179869</v>
+        <v>0.03223800298531072</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.006933843412663093</v>
+        <v>-0.006850555280960409</v>
       </c>
       <c r="O35" t="n">
-        <v>-3097.629718180046</v>
+        <v>128842.9431365761</v>
       </c>
       <c r="P35" t="n">
-        <v>-3097.629718180046</v>
+        <v>64421.47156828804</v>
       </c>
     </row>
     <row r="36">
@@ -6529,34 +7019,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G36" t="n">
-        <v>-35427280.72000001</v>
+        <v>-24300588.46000001</v>
       </c>
       <c r="H36" t="n">
-        <v>2266152.03233775</v>
+        <v>2250000</v>
       </c>
       <c r="I36" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="J36" t="n">
         <v>-34000000</v>
       </c>
       <c r="K36" t="n">
-        <v>838871.312337745</v>
+        <v>11949411.53999999</v>
       </c>
       <c r="L36" t="n">
-        <v>0.05695407285841891</v>
+        <v>0.03915884386251234</v>
       </c>
       <c r="M36" t="n">
-        <v>0.05166029289831464</v>
+        <v>0.03392512279467386</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.005293779960104272</v>
+        <v>-0.005233721067838482</v>
       </c>
       <c r="O36" t="n">
-        <v>-1480.266714119976</v>
+        <v>-20846.62897505674</v>
       </c>
       <c r="P36" t="n">
-        <v>-1480.266714119976</v>
+        <v>-20846.62897505674</v>
       </c>
     </row>
     <row r="37">
@@ -6587,34 +7077,34 @@
         <v>0.25</v>
       </c>
       <c r="G37" t="n">
-        <v>-35839034.46</v>
+        <v>-25229792.01000001</v>
       </c>
       <c r="H37" t="n">
-        <v>2248181.001571974</v>
+        <v>2250000</v>
       </c>
       <c r="I37" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="J37" t="n">
         <v>-34000000</v>
       </c>
       <c r="K37" t="n">
-        <v>409146.5415719748</v>
+        <v>11020207.98999999</v>
       </c>
       <c r="L37" t="n">
-        <v>0.05664439372837885</v>
+        <v>0.03922681220647117</v>
       </c>
       <c r="M37" t="n">
-        <v>0.05287569440126383</v>
+        <v>0.03550516138352163</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.003768699327115023</v>
+        <v>-0.003721650822949542</v>
       </c>
       <c r="O37" t="n">
-        <v>-385.487573978435</v>
+        <v>-10253.34153376465</v>
       </c>
       <c r="P37" t="n">
-        <v>-385.487573978435</v>
+        <v>-10253.34153376465</v>
       </c>
     </row>
     <row r="38">
@@ -6645,34 +7135,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G38" t="n">
-        <v>-35777615.53999999</v>
+        <v>43083900.58</v>
       </c>
       <c r="H38" t="n">
-        <v>2248686.278913092</v>
+        <v>2250000</v>
       </c>
       <c r="I38" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="J38" t="n">
         <v>-34000000</v>
       </c>
       <c r="K38" t="n">
-        <v>471070.7389131002</v>
+        <v>79333900.58</v>
       </c>
       <c r="L38" t="n">
-        <v>0.05642057743315654</v>
+        <v>0.03929424848359133</v>
       </c>
       <c r="M38" t="n">
-        <v>0.0540637033638335</v>
+        <v>0.03696944528723573</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.002356874069323035</v>
+        <v>-0.002324803196355599</v>
       </c>
       <c r="O38" t="n">
-        <v>-185.0424015601879</v>
+        <v>-30739.28427462354</v>
       </c>
       <c r="P38" t="n">
-        <v>-185.0424015601879</v>
+        <v>-30739.28427462354</v>
       </c>
     </row>
     <row r="39">
@@ -6703,34 +7193,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G39" t="n">
-        <v>-35715304.73</v>
+        <v>32635075.89</v>
       </c>
       <c r="H39" t="n">
-        <v>2261537.165955536</v>
+        <v>2262328.767123288</v>
       </c>
       <c r="I39" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="J39" t="n">
-        <v>-34000000</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>546232.4359555319</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="L39" t="n">
-        <v>0.05625883751011833</v>
+        <v>0.03936107056455495</v>
       </c>
       <c r="M39" t="n">
-        <v>0.05521394741144346</v>
+        <v>0.03833155059502284</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.001044890098674874</v>
+        <v>-0.001029519969532107</v>
       </c>
       <c r="O39" t="n">
-        <v>-47.56273865874938</v>
+        <v>-2993.964581612599</v>
       </c>
       <c r="P39" t="n">
-        <v>-47.56273865874938</v>
+        <v>-2993.964581612599</v>
       </c>
     </row>
     <row r="40">
@@ -6761,28 +7251,28 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-36430105.95000001</v>
+        <v>-85065078.76000001</v>
       </c>
       <c r="H40" t="n">
-        <v>4044566.584325174</v>
+        <v>4045068.493150685</v>
       </c>
       <c r="I40" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="J40" t="n">
-        <v>-34000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K40" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="L40" t="n">
-        <v>0.05611688274594639</v>
+        <v>0.03942868733737526</v>
       </c>
       <c r="M40" t="n">
-        <v>0.05629090260522096</v>
+        <v>0.03959996871170457</v>
       </c>
       <c r="N40" t="n">
-        <v>0.0001740198592745656</v>
+        <v>0.0001712813743293129</v>
       </c>
       <c r="O40" t="n">
         <v>-0</v>
@@ -6819,34 +7309,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G41" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="J41" t="n">
         <v>-680000000</v>
       </c>
       <c r="K41" t="n">
-        <v>-750323402.3400002</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="L41" t="n">
-        <v>0.1050151041880321</v>
+        <v>0.03432749872940843</v>
       </c>
       <c r="M41" t="n">
-        <v>0.08033035812803568</v>
+        <v>0.06222029331429346</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.02468474605999638</v>
+        <v>0.02789279458488503</v>
       </c>
       <c r="O41" t="n">
-        <v>18470798.69717064</v>
+        <v>-36166307.87167858</v>
       </c>
       <c r="P41" t="n">
-        <v>9235399.348585319</v>
+        <v>-36166307.87167858</v>
       </c>
     </row>
     <row r="42">
@@ -6877,34 +7367,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G42" t="n">
-        <v>425995266.0600001</v>
+        <v>912642221.4799999</v>
       </c>
       <c r="H42" t="n">
-        <v>-90269181.22613968</v>
+        <v>-89542810.95890412</v>
       </c>
       <c r="I42" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="J42" t="n">
         <v>-68000000</v>
       </c>
       <c r="K42" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="L42" t="n">
-        <v>0.05822765833026367</v>
+        <v>0.03782665436246635</v>
       </c>
       <c r="M42" t="n">
-        <v>0.08318615436787802</v>
+        <v>0.06275211257538338</v>
       </c>
       <c r="N42" t="n">
-        <v>0.02495849603761435</v>
+        <v>0.02492545821291703</v>
       </c>
       <c r="O42" t="n">
-        <v>7680949.978212211</v>
+        <v>18806452.46518519</v>
       </c>
       <c r="P42" t="n">
-        <v>3840474.989106106</v>
+        <v>9403226.232592596</v>
       </c>
     </row>
     <row r="43">
@@ -6935,34 +7425,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G43" t="n">
-        <v>2339361769.16</v>
+        <v>879884659.5500001</v>
       </c>
       <c r="H43" t="n">
-        <v>-51490547.94520548</v>
+        <v>-50934753.42465753</v>
       </c>
       <c r="I43" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="J43" t="n">
-        <v>-68000000</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="L43" t="n">
-        <v>0.05839364669442126</v>
+        <v>0.03830470017405307</v>
       </c>
       <c r="M43" t="n">
-        <v>0.08055379157089071</v>
+        <v>0.06041097162232134</v>
       </c>
       <c r="N43" t="n">
-        <v>0.02216014487646945</v>
+        <v>0.02210627144826827</v>
       </c>
       <c r="O43" t="n">
-        <v>42249631.43402077</v>
+        <v>15270826.3681861</v>
       </c>
       <c r="P43" t="n">
-        <v>21124815.71701039</v>
+        <v>7635413.18409305</v>
       </c>
     </row>
     <row r="44">
@@ -6993,34 +7483,34 @@
         <v>0.75</v>
       </c>
       <c r="G44" t="n">
-        <v>368810148.66</v>
+        <v>1240710907.89</v>
       </c>
       <c r="H44" t="n">
-        <v>-92049904.10958904</v>
+        <v>-91346794.52054794</v>
       </c>
       <c r="I44" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="J44" t="n">
-        <v>-68000000</v>
+        <v>-136000000</v>
       </c>
       <c r="K44" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="L44" t="n">
-        <v>0.05851824187679444</v>
+        <v>0.03852218097221538</v>
       </c>
       <c r="M44" t="n">
-        <v>0.07813840667889771</v>
+        <v>0.05805669396429369</v>
       </c>
       <c r="N44" t="n">
-        <v>0.01962016480210327</v>
+        <v>0.01953451299207831</v>
       </c>
       <c r="O44" t="n">
-        <v>4072561.206562099</v>
+        <v>16839201.1539331</v>
       </c>
       <c r="P44" t="n">
-        <v>2036280.60328105</v>
+        <v>8419600.57696655</v>
       </c>
     </row>
     <row r="45">
@@ -7051,34 +7541,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G45" t="n">
-        <v>-180822610.01</v>
+        <v>-201932841.91</v>
       </c>
       <c r="H45" t="n">
-        <v>-51458493.15068493</v>
+        <v>-50972657.53424658</v>
       </c>
       <c r="I45" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="J45" t="n">
         <v>-68000000</v>
       </c>
       <c r="K45" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="L45" t="n">
-        <v>0.05821004393128892</v>
+        <v>0.03873510939427094</v>
       </c>
       <c r="M45" t="n">
-        <v>0.07543344707084598</v>
+        <v>0.05587093092788775</v>
       </c>
       <c r="N45" t="n">
-        <v>0.01722340313955706</v>
+        <v>0.01713582153361681</v>
       </c>
       <c r="O45" t="n">
-        <v>-2667114.054291679</v>
+        <v>-2889162.335564557</v>
       </c>
       <c r="P45" t="n">
-        <v>-2667114.054291679</v>
+        <v>-2889162.335564557</v>
       </c>
     </row>
     <row r="46">
@@ -7109,34 +7599,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G46" t="n">
-        <v>396368601.78</v>
+        <v>-196825268.73</v>
       </c>
       <c r="H46" t="n">
-        <v>-51445520.54794521</v>
+        <v>-50988356.16438356</v>
       </c>
       <c r="I46" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="J46" t="n">
         <v>-68000000</v>
       </c>
       <c r="K46" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="L46" t="n">
-        <v>0.05808035784574397</v>
+        <v>0.03888939094511485</v>
       </c>
       <c r="M46" t="n">
-        <v>0.07309558198160494</v>
+        <v>0.05378762523899869</v>
       </c>
       <c r="N46" t="n">
-        <v>0.01501522413586098</v>
+        <v>0.01489823429388384</v>
       </c>
       <c r="O46" t="n">
-        <v>3021140.135026467</v>
+        <v>-2153658.176187682</v>
       </c>
       <c r="P46" t="n">
-        <v>1510570.067513233</v>
+        <v>-2153658.176187682</v>
       </c>
     </row>
     <row r="47">
@@ -7167,34 +7657,34 @@
         <v>0.5</v>
       </c>
       <c r="G47" t="n">
-        <v>270725457.28</v>
+        <v>69886647.3499999</v>
       </c>
       <c r="H47" t="n">
-        <v>-90799555.08645856</v>
+        <v>-89968608.21917808</v>
       </c>
       <c r="I47" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="J47" t="n">
         <v>-34000000</v>
       </c>
       <c r="K47" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="L47" t="n">
-        <v>0.0579990267461179</v>
+        <v>0.03901400018340251</v>
       </c>
       <c r="M47" t="n">
-        <v>0.07094844672146827</v>
+        <v>0.05185246316878578</v>
       </c>
       <c r="N47" t="n">
-        <v>0.01294941997535037</v>
+        <v>0.01283846298538327</v>
       </c>
       <c r="O47" t="n">
-        <v>1164968.035973991</v>
+        <v>-128910.7556464296</v>
       </c>
       <c r="P47" t="n">
-        <v>582484.0179869956</v>
+        <v>-128910.7556464296</v>
       </c>
     </row>
     <row r="48">
@@ -7225,34 +7715,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G48" t="n">
-        <v>-35174959.2</v>
+        <v>-81388394.01999998</v>
       </c>
       <c r="H48" t="n">
-        <v>2247136.761733663</v>
+        <v>2250000</v>
       </c>
       <c r="I48" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="J48" t="n">
         <v>-34000000</v>
       </c>
       <c r="K48" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="L48" t="n">
-        <v>0.05738520780446178</v>
+        <v>0.03908855826627113</v>
       </c>
       <c r="M48" t="n">
-        <v>0.06842305743571853</v>
+        <v>0.05000022680113198</v>
       </c>
       <c r="N48" t="n">
-        <v>0.01103784963125674</v>
+        <v>0.01091166853486086</v>
       </c>
       <c r="O48" t="n">
-        <v>-151438.4803159607</v>
+        <v>-359804.968303106</v>
       </c>
       <c r="P48" t="n">
-        <v>-151438.4803159607</v>
+        <v>-359804.968303106</v>
       </c>
     </row>
     <row r="49">
@@ -7283,34 +7773,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G49" t="n">
-        <v>-35427280.72000001</v>
+        <v>-24300588.46000001</v>
       </c>
       <c r="H49" t="n">
-        <v>2266152.03233775</v>
+        <v>2250000</v>
       </c>
       <c r="I49" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="J49" t="n">
         <v>-34000000</v>
       </c>
       <c r="K49" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="L49" t="n">
-        <v>0.05695407285841891</v>
+        <v>0.03915884386251234</v>
       </c>
       <c r="M49" t="n">
-        <v>0.06621878897479672</v>
+        <v>0.04831788295882744</v>
       </c>
       <c r="N49" t="n">
-        <v>0.009264716116377802</v>
+        <v>0.009159039096315102</v>
       </c>
       <c r="O49" t="n">
-        <v>-102409.4811299543</v>
+        <v>-67320.7339339649</v>
       </c>
       <c r="P49" t="n">
-        <v>-102409.4811299543</v>
+        <v>-67320.7339339649</v>
       </c>
     </row>
     <row r="50">
@@ -7341,34 +7831,34 @@
         <v>0.25</v>
       </c>
       <c r="G50" t="n">
-        <v>-35839034.46</v>
+        <v>-25229792.01000001</v>
       </c>
       <c r="H50" t="n">
-        <v>2248181.001571974</v>
+        <v>2250000</v>
       </c>
       <c r="I50" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="J50" t="n">
         <v>-34000000</v>
       </c>
       <c r="K50" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="L50" t="n">
-        <v>0.05664439372837885</v>
+        <v>0.03922681220647117</v>
       </c>
       <c r="M50" t="n">
-        <v>0.06426245745541011</v>
+        <v>0.04674923289971685</v>
       </c>
       <c r="N50" t="n">
-        <v>0.007618063727031256</v>
+        <v>0.007522420693245678</v>
       </c>
       <c r="O50" t="n">
-        <v>-63974.31557291824</v>
+        <v>-43215.91573562643</v>
       </c>
       <c r="P50" t="n">
-        <v>-63974.31557291824</v>
+        <v>-43215.91573562643</v>
       </c>
     </row>
     <row r="51">
@@ -7399,34 +7889,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G51" t="n">
-        <v>-35777615.53999999</v>
+        <v>43083900.58</v>
       </c>
       <c r="H51" t="n">
-        <v>2248686.278913092</v>
+        <v>2250000</v>
       </c>
       <c r="I51" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="J51" t="n">
         <v>-34000000</v>
       </c>
       <c r="K51" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="L51" t="n">
-        <v>0.05642057743315654</v>
+        <v>0.03929424848359133</v>
       </c>
       <c r="M51" t="n">
-        <v>0.06251548466460592</v>
+        <v>0.04530601718826172</v>
       </c>
       <c r="N51" t="n">
-        <v>0.006094907231449384</v>
+        <v>0.006011768704670392</v>
       </c>
       <c r="O51" t="n">
-        <v>-34059.28556935889</v>
+        <v>45422.82079458048</v>
       </c>
       <c r="P51" t="n">
-        <v>-34059.28556935889</v>
+        <v>22711.41039729024</v>
       </c>
     </row>
     <row r="52">
@@ -7457,34 +7947,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G52" t="n">
-        <v>-35715304.73</v>
+        <v>32635075.89</v>
       </c>
       <c r="H52" t="n">
-        <v>2261537.165955536</v>
+        <v>2262328.767123288</v>
       </c>
       <c r="I52" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="J52" t="n">
-        <v>-34000000</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="L52" t="n">
-        <v>0.05625883751011833</v>
+        <v>0.03936107056455495</v>
       </c>
       <c r="M52" t="n">
-        <v>0.06094126886514148</v>
+        <v>0.04397450230184618</v>
       </c>
       <c r="N52" t="n">
-        <v>0.004682431355023151</v>
+        <v>0.004613431737291229</v>
       </c>
       <c r="O52" t="n">
-        <v>-13053.74751546153</v>
+        <v>13416.39951618895</v>
       </c>
       <c r="P52" t="n">
-        <v>-13053.74751546153</v>
+        <v>6708.199758094475</v>
       </c>
     </row>
     <row r="53">
@@ -7515,28 +8005,28 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>-36430105.95000001</v>
+        <v>-85065078.76000001</v>
       </c>
       <c r="H53" t="n">
-        <v>4044566.584325174</v>
+        <v>4045068.493150685</v>
       </c>
       <c r="I53" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="J53" t="n">
-        <v>-34000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K53" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="L53" t="n">
-        <v>0.05611688274594639</v>
+        <v>0.03942868733737526</v>
       </c>
       <c r="M53" t="n">
-        <v>0.05949006088389019</v>
+        <v>0.042748642330797</v>
       </c>
       <c r="N53" t="n">
-        <v>0.0033731781379438</v>
+        <v>0.003319954993421748</v>
       </c>
       <c r="O53" t="n">
         <v>-0</v>
@@ -7573,34 +8063,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G54" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="J54" t="n">
         <v>-680000000</v>
       </c>
       <c r="K54" t="n">
-        <v>-750323402.3400002</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="L54" t="n">
-        <v>0.1050151041880321</v>
+        <v>0.03432749872940843</v>
       </c>
       <c r="M54" t="n">
-        <v>0.08735529861555014</v>
+        <v>0.06923584480754363</v>
       </c>
       <c r="N54" t="n">
-        <v>-0.01765980557248192</v>
+        <v>0.0349083460781352</v>
       </c>
       <c r="O54" t="n">
-        <v>13214262.48289847</v>
+        <v>-45262800.31607471</v>
       </c>
       <c r="P54" t="n">
-        <v>6607131.241449235</v>
+        <v>-45262800.31607471</v>
       </c>
     </row>
     <row r="55">
@@ -7631,34 +8121,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G55" t="n">
-        <v>425995266.0600001</v>
+        <v>912642221.4799999</v>
       </c>
       <c r="H55" t="n">
-        <v>-90269181.22613968</v>
+        <v>-89542810.95890412</v>
       </c>
       <c r="I55" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="J55" t="n">
         <v>-68000000</v>
       </c>
       <c r="K55" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="L55" t="n">
-        <v>0.05822765833026367</v>
+        <v>0.03782665436246635</v>
       </c>
       <c r="M55" t="n">
-        <v>0.09058485068408295</v>
+        <v>0.0701370260460914</v>
       </c>
       <c r="N55" t="n">
-        <v>0.03235719235381929</v>
+        <v>0.03231037168362505</v>
       </c>
       <c r="O55" t="n">
-        <v>9957890.713066883</v>
+        <v>24378427.22930017</v>
       </c>
       <c r="P55" t="n">
-        <v>4978945.356533442</v>
+        <v>12189213.61465009</v>
       </c>
     </row>
     <row r="56">
@@ -7689,34 +8179,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G56" t="n">
-        <v>2339361769.16</v>
+        <v>879884659.5500001</v>
       </c>
       <c r="H56" t="n">
-        <v>-51490547.94520548</v>
+        <v>-50934753.42465753</v>
       </c>
       <c r="I56" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="J56" t="n">
-        <v>-68000000</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="L56" t="n">
-        <v>0.05839364669442126</v>
+        <v>0.03830470017405307</v>
       </c>
       <c r="M56" t="n">
-        <v>0.08832183864296361</v>
+        <v>0.06815087156775412</v>
       </c>
       <c r="N56" t="n">
-        <v>0.02992819194854235</v>
+        <v>0.02984617139370105</v>
       </c>
       <c r="O56" t="n">
-        <v>57059874.21838531</v>
+        <v>20617484.14584114</v>
       </c>
       <c r="P56" t="n">
-        <v>28529937.10919265</v>
+        <v>10308742.07292057</v>
       </c>
     </row>
     <row r="57">
@@ -7747,34 +8237,34 @@
         <v>0.75</v>
       </c>
       <c r="G57" t="n">
-        <v>368810148.66</v>
+        <v>1240710907.89</v>
       </c>
       <c r="H57" t="n">
-        <v>-92049904.10958904</v>
+        <v>-91346794.52054794</v>
       </c>
       <c r="I57" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="J57" t="n">
-        <v>-68000000</v>
+        <v>-136000000</v>
       </c>
       <c r="K57" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="L57" t="n">
-        <v>0.05851824187679444</v>
+        <v>0.03852218097221538</v>
       </c>
       <c r="M57" t="n">
-        <v>0.08624486047266533</v>
+        <v>0.06612186834857425</v>
       </c>
       <c r="N57" t="n">
-        <v>0.02772661859587089</v>
+        <v>0.02759968737635887</v>
       </c>
       <c r="O57" t="n">
-        <v>5755219.307361899</v>
+        <v>23791567.65795208</v>
       </c>
       <c r="P57" t="n">
-        <v>2877609.653680949</v>
+        <v>11895783.82897604</v>
       </c>
     </row>
     <row r="58">
@@ -7805,34 +8295,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G58" t="n">
-        <v>-180822610.01</v>
+        <v>-201932841.91</v>
       </c>
       <c r="H58" t="n">
-        <v>-51458493.15068493</v>
+        <v>-50972657.53424658</v>
       </c>
       <c r="I58" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="J58" t="n">
         <v>-68000000</v>
       </c>
       <c r="K58" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="L58" t="n">
-        <v>0.05821004393128892</v>
+        <v>0.03873510939427094</v>
       </c>
       <c r="M58" t="n">
-        <v>0.08385907763058897</v>
+        <v>0.06424038509770957</v>
       </c>
       <c r="N58" t="n">
-        <v>0.02564903369930005</v>
+        <v>0.02550527570343863</v>
       </c>
       <c r="O58" t="n">
-        <v>-3971857.228452666</v>
+        <v>-4300282.993494238</v>
       </c>
       <c r="P58" t="n">
-        <v>-3971857.228452666</v>
+        <v>-4300282.993494238</v>
       </c>
     </row>
     <row r="59">
@@ -7863,34 +8353,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G59" t="n">
-        <v>396368601.78</v>
+        <v>-196825268.73</v>
       </c>
       <c r="H59" t="n">
-        <v>-51445520.54794521</v>
+        <v>-50988356.16438356</v>
       </c>
       <c r="I59" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="J59" t="n">
         <v>-68000000</v>
       </c>
       <c r="K59" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="L59" t="n">
-        <v>0.05808035784574397</v>
+        <v>0.03888939094511485</v>
       </c>
       <c r="M59" t="n">
-        <v>0.08181758148143689</v>
+        <v>0.06244146758862694</v>
       </c>
       <c r="N59" t="n">
-        <v>0.02373722363569292</v>
+        <v>0.02355207664351209</v>
       </c>
       <c r="O59" t="n">
-        <v>4776051.184518578</v>
+        <v>-3404639.867311128</v>
       </c>
       <c r="P59" t="n">
-        <v>2388025.592259289</v>
+        <v>-3404639.867311128</v>
       </c>
     </row>
     <row r="60">
@@ -7921,34 +8411,34 @@
         <v>0.5</v>
       </c>
       <c r="G60" t="n">
-        <v>270725457.28</v>
+        <v>69886647.3499999</v>
       </c>
       <c r="H60" t="n">
-        <v>-90799555.08645856</v>
+        <v>-89968608.21917808</v>
       </c>
       <c r="I60" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="J60" t="n">
         <v>-34000000</v>
       </c>
       <c r="K60" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="L60" t="n">
-        <v>0.0579990267461179</v>
+        <v>0.03901400018340251</v>
       </c>
       <c r="M60" t="n">
-        <v>0.07994919825034419</v>
+        <v>0.06076922424633224</v>
       </c>
       <c r="N60" t="n">
-        <v>0.02195017150422629</v>
+        <v>0.02175522406292973</v>
       </c>
       <c r="O60" t="n">
-        <v>1974702.20560044</v>
+        <v>-218443.7791659792</v>
       </c>
       <c r="P60" t="n">
-        <v>987351.1028002198</v>
+        <v>-218443.7791659792</v>
       </c>
     </row>
     <row r="61">
@@ -7979,34 +8469,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G61" t="n">
-        <v>-35174959.2</v>
+        <v>-81388394.01999998</v>
       </c>
       <c r="H61" t="n">
-        <v>2247136.761733663</v>
+        <v>2250000</v>
       </c>
       <c r="I61" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="J61" t="n">
         <v>-34000000</v>
       </c>
       <c r="K61" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="L61" t="n">
-        <v>0.05738520780446178</v>
+        <v>0.03908855826627113</v>
       </c>
       <c r="M61" t="n">
-        <v>0.07768043009699076</v>
+        <v>0.05916330438233811</v>
       </c>
       <c r="N61" t="n">
-        <v>0.02029522229252897</v>
+        <v>0.02007474611606698</v>
       </c>
       <c r="O61" t="n">
-        <v>-278448.9483306411</v>
+        <v>-661951.3199936553</v>
       </c>
       <c r="P61" t="n">
-        <v>-278448.9483306411</v>
+        <v>-661951.3199936553</v>
       </c>
     </row>
     <row r="62">
@@ -8037,34 +8527,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G62" t="n">
-        <v>-35427280.72000001</v>
+        <v>-24300588.46000001</v>
       </c>
       <c r="H62" t="n">
-        <v>2266152.03233775</v>
+        <v>2250000</v>
       </c>
       <c r="I62" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="J62" t="n">
         <v>-34000000</v>
       </c>
       <c r="K62" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="L62" t="n">
-        <v>0.05695407285841891</v>
+        <v>0.03915884386251234</v>
       </c>
       <c r="M62" t="n">
-        <v>0.07571604046176417</v>
+        <v>0.05770655223741961</v>
       </c>
       <c r="N62" t="n">
-        <v>0.01876196760334525</v>
+        <v>0.01854770837490727</v>
       </c>
       <c r="O62" t="n">
-        <v>-207389.3407094274</v>
+        <v>-136329.2947503919</v>
       </c>
       <c r="P62" t="n">
-        <v>-207389.3407094274</v>
+        <v>-136329.2947503919</v>
       </c>
     </row>
     <row r="63">
@@ -8095,34 +8585,34 @@
         <v>0.25</v>
       </c>
       <c r="G63" t="n">
-        <v>-35839034.46</v>
+        <v>-25229792.01000001</v>
       </c>
       <c r="H63" t="n">
-        <v>2248181.001571974</v>
+        <v>2250000</v>
       </c>
       <c r="I63" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="J63" t="n">
         <v>-34000000</v>
       </c>
       <c r="K63" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="L63" t="n">
-        <v>0.05664439372837885</v>
+        <v>0.03922681220647117</v>
       </c>
       <c r="M63" t="n">
-        <v>0.07398436000341994</v>
+        <v>0.05634932501465103</v>
       </c>
       <c r="N63" t="n">
-        <v>0.01733996627504109</v>
+        <v>0.01712251280817986</v>
       </c>
       <c r="O63" t="n">
-        <v>-145616.0665297474</v>
+        <v>-98367.94575513355</v>
       </c>
       <c r="P63" t="n">
-        <v>-145616.0665297474</v>
+        <v>-98367.94575513355</v>
       </c>
     </row>
     <row r="64">
@@ -8153,34 +8643,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G64" t="n">
-        <v>-35777615.53999999</v>
+        <v>43083900.58</v>
       </c>
       <c r="H64" t="n">
-        <v>2248686.278913092</v>
+        <v>2250000</v>
       </c>
       <c r="I64" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="J64" t="n">
         <v>-34000000</v>
       </c>
       <c r="K64" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="L64" t="n">
-        <v>0.05642057743315654</v>
+        <v>0.03929424848359133</v>
       </c>
       <c r="M64" t="n">
-        <v>0.07244727948281815</v>
+        <v>0.05510242140223998</v>
       </c>
       <c r="N64" t="n">
-        <v>0.01602670204966161</v>
+        <v>0.01580817291864865</v>
       </c>
       <c r="O64" t="n">
-        <v>-89559.69321860342</v>
+        <v>119441.023240911</v>
       </c>
       <c r="P64" t="n">
-        <v>-89559.69321860342</v>
+        <v>59720.51162045549</v>
       </c>
     </row>
     <row r="65">
@@ -8211,34 +8701,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G65" t="n">
-        <v>-35715304.73</v>
+        <v>32635075.89</v>
       </c>
       <c r="H65" t="n">
-        <v>2261537.165955536</v>
+        <v>2262328.767123288</v>
       </c>
       <c r="I65" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="J65" t="n">
-        <v>-34000000</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="L65" t="n">
-        <v>0.05625883751011833</v>
+        <v>0.03936107056455495</v>
       </c>
       <c r="M65" t="n">
-        <v>0.0710697595917701</v>
+        <v>0.05395379482856789</v>
       </c>
       <c r="N65" t="n">
-        <v>0.01481092208165177</v>
+        <v>0.01459272426401294</v>
       </c>
       <c r="O65" t="n">
-        <v>-41290.09539406269</v>
+        <v>42437.35030759013</v>
       </c>
       <c r="P65" t="n">
-        <v>-41290.09539406269</v>
+        <v>21218.67515379507</v>
       </c>
     </row>
     <row r="66">
@@ -8269,28 +8759,28 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>-36430105.95000001</v>
+        <v>-85065078.76000001</v>
       </c>
       <c r="H66" t="n">
-        <v>4044566.584325174</v>
+        <v>4045068.493150685</v>
       </c>
       <c r="I66" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="J66" t="n">
-        <v>-34000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K66" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="L66" t="n">
-        <v>0.05611688274594639</v>
+        <v>0.03942868733737526</v>
       </c>
       <c r="M66" t="n">
-        <v>0.06980273792339808</v>
+        <v>0.05289836689808713</v>
       </c>
       <c r="N66" t="n">
-        <v>0.01368585517745169</v>
+        <v>0.01346967956071188</v>
       </c>
       <c r="O66" t="n">
         <v>-0</v>
@@ -8327,34 +8817,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G67" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="J67" t="n">
         <v>-680000000</v>
       </c>
       <c r="K67" t="n">
-        <v>-750323402.3400002</v>
+        <v>-620180437.28</v>
       </c>
       <c r="L67" t="n">
-        <v>0.1050151041880321</v>
+        <v>0.03432749872940843</v>
       </c>
       <c r="M67" t="n">
-        <v>0.01772687293857378</v>
+        <v>3.905509319279687e-06</v>
       </c>
       <c r="N67" t="n">
-        <v>-0.08728823124945828</v>
+        <v>-0.03432359322008915</v>
       </c>
       <c r="O67" t="n">
-        <v>65314965.9357306</v>
+        <v>21228500.99457832</v>
       </c>
       <c r="P67" t="n">
-        <v>32657482.9678653</v>
+        <v>10614250.49728916</v>
       </c>
     </row>
     <row r="68">
@@ -8385,34 +8875,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G68" t="n">
-        <v>425995266.0600001</v>
+        <v>912642221.4799999</v>
       </c>
       <c r="H68" t="n">
-        <v>-90269181.22613968</v>
+        <v>-89542810.95890412</v>
       </c>
       <c r="I68" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="J68" t="n">
         <v>-68000000</v>
       </c>
       <c r="K68" t="n">
-        <v>403726084.8338604</v>
+        <v>891099410.5210958</v>
       </c>
       <c r="L68" t="n">
-        <v>0.05822765833026367</v>
+        <v>0.03782665436246635</v>
       </c>
       <c r="M68" t="n">
-        <v>0.02596200736148457</v>
+        <v>0.005604549383080304</v>
       </c>
       <c r="N68" t="n">
-        <v>-0.03226565096877909</v>
+        <v>-0.03222210497938605</v>
       </c>
       <c r="O68" t="n">
-        <v>-11940944.52855428</v>
+        <v>-26320340.52347312</v>
       </c>
       <c r="P68" t="n">
-        <v>-11940944.52855428</v>
+        <v>-26320340.52347312</v>
       </c>
     </row>
     <row r="69">
@@ -8443,34 +8933,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G69" t="n">
-        <v>2339361769.16</v>
+        <v>879884659.5500001</v>
       </c>
       <c r="H69" t="n">
-        <v>-51490547.94520548</v>
+        <v>-50934753.42465753</v>
       </c>
       <c r="I69" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="J69" t="n">
-        <v>-68000000</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>2355871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="L69" t="n">
-        <v>0.05839364669442126</v>
+        <v>0.03830470017405307</v>
       </c>
       <c r="M69" t="n">
-        <v>0.02862082930181886</v>
+        <v>0.008607652840505686</v>
       </c>
       <c r="N69" t="n">
-        <v>-0.0297728173926024</v>
+        <v>-0.02969704733354739</v>
       </c>
       <c r="O69" t="n">
-        <v>-58450769.72476275</v>
+        <v>-20514470.4994533</v>
       </c>
       <c r="P69" t="n">
-        <v>-58450769.72476275</v>
+        <v>-20514470.4994533</v>
       </c>
     </row>
     <row r="70">
@@ -8501,34 +8991,34 @@
         <v>0.75</v>
       </c>
       <c r="G70" t="n">
-        <v>368810148.66</v>
+        <v>1240710907.89</v>
       </c>
       <c r="H70" t="n">
-        <v>-92049904.10958904</v>
+        <v>-91346794.52054794</v>
       </c>
       <c r="I70" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="J70" t="n">
-        <v>-68000000</v>
+        <v>-136000000</v>
       </c>
       <c r="K70" t="n">
-        <v>344760244.5504109</v>
+        <v>1285364113.369452</v>
       </c>
       <c r="L70" t="n">
-        <v>0.05851824187679444</v>
+        <v>0.03852218097221538</v>
       </c>
       <c r="M70" t="n">
-        <v>0.03098334217962151</v>
+        <v>0.01111073063790968</v>
       </c>
       <c r="N70" t="n">
-        <v>-0.02753489969717293</v>
+        <v>-0.0274114503343057</v>
       </c>
       <c r="O70" t="n">
-        <v>-7119704.064951282</v>
+        <v>-26425270.91634421</v>
       </c>
       <c r="P70" t="n">
-        <v>-7119704.064951282</v>
+        <v>-26425270.91634421</v>
       </c>
     </row>
     <row r="71">
@@ -8559,34 +9049,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G71" t="n">
-        <v>-180822610.01</v>
+        <v>-201932841.91</v>
       </c>
       <c r="H71" t="n">
-        <v>-51458493.15068493</v>
+        <v>-50972657.53424658</v>
       </c>
       <c r="I71" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="J71" t="n">
         <v>-68000000</v>
       </c>
       <c r="K71" t="n">
-        <v>-164281103.1606849</v>
+        <v>-184905499.4442466</v>
       </c>
       <c r="L71" t="n">
-        <v>0.05821004393128892</v>
+        <v>0.03873510939427094</v>
       </c>
       <c r="M71" t="n">
-        <v>0.0327782499425886</v>
+        <v>0.01344239168081884</v>
       </c>
       <c r="N71" t="n">
-        <v>-0.02543179398870032</v>
+        <v>-0.0252927177134521</v>
       </c>
       <c r="O71" t="n">
-        <v>2785308.781212643</v>
+        <v>3117841.734072135</v>
       </c>
       <c r="P71" t="n">
-        <v>1392654.390606322</v>
+        <v>1558920.867036068</v>
       </c>
     </row>
     <row r="72">
@@ -8617,34 +9107,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G72" t="n">
-        <v>396368601.78</v>
+        <v>-196825268.73</v>
       </c>
       <c r="H72" t="n">
-        <v>-51445520.54794521</v>
+        <v>-50988356.16438356</v>
       </c>
       <c r="I72" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="J72" t="n">
         <v>-68000000</v>
       </c>
       <c r="K72" t="n">
-        <v>412923081.2320548</v>
+        <v>-179813624.8943836</v>
       </c>
       <c r="L72" t="n">
-        <v>0.05808035784574397</v>
+        <v>0.03888939094511485</v>
       </c>
       <c r="M72" t="n">
-        <v>0.03457168212681622</v>
+        <v>0.01556325719149214</v>
       </c>
       <c r="N72" t="n">
-        <v>-0.02350867571892774</v>
+        <v>-0.02332613375362271</v>
       </c>
       <c r="O72" t="n">
-        <v>-5662576.97456782</v>
+        <v>2446708.054589245</v>
       </c>
       <c r="P72" t="n">
-        <v>-5662576.97456782</v>
+        <v>1223354.027294622</v>
       </c>
     </row>
     <row r="73">
@@ -8675,34 +9165,34 @@
         <v>0.5</v>
       </c>
       <c r="G73" t="n">
-        <v>270725457.28</v>
+        <v>69886647.3499999</v>
       </c>
       <c r="H73" t="n">
-        <v>-90799555.08645856</v>
+        <v>-89968608.21917808</v>
       </c>
       <c r="I73" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="J73" t="n">
         <v>-34000000</v>
       </c>
       <c r="K73" t="n">
-        <v>213925902.1935414</v>
+        <v>13918039.13082182</v>
       </c>
       <c r="L73" t="n">
-        <v>0.0579990267461179</v>
+        <v>0.03901400018340251</v>
       </c>
       <c r="M73" t="n">
-        <v>0.03628245893619209</v>
+        <v>0.01748869575344569</v>
       </c>
       <c r="N73" t="n">
-        <v>-0.02171656780992581</v>
+        <v>-0.02152530442995682</v>
       </c>
       <c r="O73" t="n">
-        <v>-2322868.180642799</v>
+        <v>-149795.0146794957</v>
       </c>
       <c r="P73" t="n">
-        <v>-2322868.180642799</v>
+        <v>-149795.0146794957</v>
       </c>
     </row>
     <row r="74">
@@ -8733,34 +9223,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G74" t="n">
-        <v>-35174959.2</v>
+        <v>-81388394.01999998</v>
       </c>
       <c r="H74" t="n">
-        <v>2247136.761733663</v>
+        <v>2250000</v>
       </c>
       <c r="I74" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="J74" t="n">
         <v>-34000000</v>
       </c>
       <c r="K74" t="n">
-        <v>1072177.561733659</v>
+        <v>-45138394.01999998</v>
       </c>
       <c r="L74" t="n">
-        <v>0.05738520780446178</v>
+        <v>0.03908855826627113</v>
       </c>
       <c r="M74" t="n">
-        <v>0.03732101742477235</v>
+        <v>0.01924277012483852</v>
       </c>
       <c r="N74" t="n">
-        <v>-0.02006419037968943</v>
+        <v>-0.01984578814143261</v>
       </c>
       <c r="O74" t="n">
-        <v>-8963.489466439732</v>
+        <v>373252.9186522617</v>
       </c>
       <c r="P74" t="n">
-        <v>-8963.489466439732</v>
+        <v>186626.4593261308</v>
       </c>
     </row>
     <row r="75">
@@ -8791,34 +9281,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G75" t="n">
-        <v>-35427280.72000001</v>
+        <v>-24300588.46000001</v>
       </c>
       <c r="H75" t="n">
-        <v>2266152.03233775</v>
+        <v>2250000</v>
       </c>
       <c r="I75" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="J75" t="n">
         <v>-34000000</v>
       </c>
       <c r="K75" t="n">
-        <v>838871.312337745</v>
+        <v>11949411.53999999</v>
       </c>
       <c r="L75" t="n">
-        <v>0.05695407285841891</v>
+        <v>0.03915884386251234</v>
       </c>
       <c r="M75" t="n">
-        <v>0.03841598150227232</v>
+        <v>0.02083222112667182</v>
       </c>
       <c r="N75" t="n">
-        <v>-0.01853809135614659</v>
+        <v>-0.01832662273584051</v>
       </c>
       <c r="O75" t="n">
-        <v>-5183.6910080559</v>
+        <v>-72997.45240295962</v>
       </c>
       <c r="P75" t="n">
-        <v>-5183.6910080559</v>
+        <v>-72997.45240295962</v>
       </c>
     </row>
     <row r="76">
@@ -8849,34 +9339,34 @@
         <v>0.25</v>
       </c>
       <c r="G76" t="n">
-        <v>-35839034.46</v>
+        <v>-25229792.01000001</v>
       </c>
       <c r="H76" t="n">
-        <v>2248181.001571974</v>
+        <v>2250000</v>
       </c>
       <c r="I76" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="J76" t="n">
         <v>-34000000</v>
       </c>
       <c r="K76" t="n">
-        <v>409146.5415719748</v>
+        <v>11020207.98999999</v>
       </c>
       <c r="L76" t="n">
-        <v>0.05664439372837885</v>
+        <v>0.03922681220647117</v>
       </c>
       <c r="M76" t="n">
-        <v>0.03951885651063976</v>
+        <v>0.02231570526743809</v>
       </c>
       <c r="N76" t="n">
-        <v>-0.01712553721773909</v>
+        <v>-0.01691110693903308</v>
       </c>
       <c r="O76" t="n">
-        <v>-1751.713581300022</v>
+        <v>-46590.97895231918</v>
       </c>
       <c r="P76" t="n">
-        <v>-1751.713581300022</v>
+        <v>-46590.97895231918</v>
       </c>
     </row>
     <row r="77">
@@ -8907,34 +9397,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G77" t="n">
-        <v>-35777615.53999999</v>
+        <v>43083900.58</v>
       </c>
       <c r="H77" t="n">
-        <v>2248686.278913092</v>
+        <v>2250000</v>
       </c>
       <c r="I77" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="J77" t="n">
         <v>-34000000</v>
       </c>
       <c r="K77" t="n">
-        <v>471070.7389131002</v>
+        <v>79333900.58</v>
       </c>
       <c r="L77" t="n">
-        <v>0.05642057743315654</v>
+        <v>0.03929424848359133</v>
       </c>
       <c r="M77" t="n">
-        <v>0.0405960223903211</v>
+        <v>0.0236853362338775</v>
       </c>
       <c r="N77" t="n">
-        <v>-0.01582455504283544</v>
+        <v>-0.01560891224971384</v>
       </c>
       <c r="O77" t="n">
-        <v>-1242.414139499919</v>
+        <v>-206385.9820967902</v>
       </c>
       <c r="P77" t="n">
-        <v>-1242.414139499919</v>
+        <v>-206385.9820967902</v>
       </c>
     </row>
     <row r="78">
@@ -8965,34 +9455,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G78" t="n">
-        <v>-35715304.73</v>
+        <v>32635075.89</v>
       </c>
       <c r="H78" t="n">
-        <v>2261537.165955536</v>
+        <v>2262328.767123288</v>
       </c>
       <c r="I78" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="J78" t="n">
-        <v>-34000000</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>546232.4359555319</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="L78" t="n">
-        <v>0.05625883751011833</v>
+        <v>0.03936107056455495</v>
       </c>
       <c r="M78" t="n">
-        <v>0.04163683720489108</v>
+        <v>0.02495441337388436</v>
       </c>
       <c r="N78" t="n">
-        <v>-0.01462200030522725</v>
+        <v>-0.01440665719067059</v>
       </c>
       <c r="O78" t="n">
-        <v>-665.5842371055679</v>
+        <v>-41896.24547827392</v>
       </c>
       <c r="P78" t="n">
-        <v>-665.5842371055679</v>
+        <v>-41896.24547827392</v>
       </c>
     </row>
     <row r="79">
@@ -9023,34 +9513,34 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>-36430105.95000001</v>
+        <v>-85065078.76000001</v>
       </c>
       <c r="H79" t="n">
-        <v>4044566.584325174</v>
+        <v>4045068.493150685</v>
       </c>
       <c r="I79" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="J79" t="n">
-        <v>-34000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K79" t="n">
-        <v>1614460.634325162</v>
+        <v>-13020010.26684932</v>
       </c>
       <c r="L79" t="n">
-        <v>0.05611688274594639</v>
+        <v>0.03942868733737526</v>
       </c>
       <c r="M79" t="n">
-        <v>0.04260611853542318</v>
+        <v>0.02613142037969185</v>
       </c>
       <c r="N79" t="n">
-        <v>-0.01351076421052322</v>
+        <v>-0.01329726695768341</v>
       </c>
       <c r="O79" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -9081,34 +9571,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G80" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="J80" t="n">
         <v>-680000000</v>
       </c>
       <c r="K80" t="n">
-        <v>-750323402.3400002</v>
+        <v>-620180437.28</v>
       </c>
       <c r="L80" t="n">
-        <v>0.1050151041880321</v>
+        <v>0.03432749872940843</v>
       </c>
       <c r="M80" t="n">
-        <v>0.04253896657148259</v>
+        <v>0.02432604806207772</v>
       </c>
       <c r="N80" t="n">
-        <v>-0.06247613761654947</v>
+        <v>-0.01000145066733071</v>
       </c>
       <c r="O80" t="n">
-        <v>46748877.16030184</v>
+        <v>6185710.33857814</v>
       </c>
       <c r="P80" t="n">
-        <v>23374438.58015092</v>
+        <v>3092855.16928907</v>
       </c>
     </row>
     <row r="81">
@@ -9139,34 +9629,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G81" t="n">
-        <v>425995266.0600001</v>
+        <v>912642221.4799999</v>
       </c>
       <c r="H81" t="n">
-        <v>-90269181.22613968</v>
+        <v>-89542810.95890412</v>
       </c>
       <c r="I81" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="J81" t="n">
         <v>-68000000</v>
       </c>
       <c r="K81" t="n">
-        <v>403726084.8338604</v>
+        <v>891099410.5210958</v>
       </c>
       <c r="L81" t="n">
-        <v>0.05822765833026367</v>
+        <v>0.03782665436246635</v>
       </c>
       <c r="M81" t="n">
-        <v>0.04818573491561828</v>
+        <v>0.02780019384037136</v>
       </c>
       <c r="N81" t="n">
-        <v>-0.01004192341464538</v>
+        <v>-0.01002646052209499</v>
       </c>
       <c r="O81" t="n">
-        <v>-3716337.555696563</v>
+        <v>-8190025.305780896</v>
       </c>
       <c r="P81" t="n">
-        <v>-3716337.555696563</v>
+        <v>-8190025.305780896</v>
       </c>
     </row>
     <row r="82">
@@ -9197,34 +9687,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G82" t="n">
-        <v>2339361769.16</v>
+        <v>879884659.5500001</v>
       </c>
       <c r="H82" t="n">
-        <v>-51490547.94520548</v>
+        <v>-50934753.42465753</v>
       </c>
       <c r="I82" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="J82" t="n">
-        <v>-68000000</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>2355871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="L82" t="n">
-        <v>0.05839364669442126</v>
+        <v>0.03830470017405307</v>
       </c>
       <c r="M82" t="n">
-        <v>0.04830891037354634</v>
+        <v>0.02825040386828537</v>
       </c>
       <c r="N82" t="n">
-        <v>-0.01008473632087492</v>
+        <v>-0.01005429630576771</v>
       </c>
       <c r="O82" t="n">
-        <v>-19798616.726574</v>
+        <v>-6945423.315685432</v>
       </c>
       <c r="P82" t="n">
-        <v>-19798616.726574</v>
+        <v>-6945423.315685432</v>
       </c>
     </row>
     <row r="83">
@@ -9255,34 +9745,34 @@
         <v>0.75</v>
       </c>
       <c r="G83" t="n">
-        <v>368810148.66</v>
+        <v>1240710907.89</v>
       </c>
       <c r="H83" t="n">
-        <v>-92049904.10958904</v>
+        <v>-91346794.52054794</v>
       </c>
       <c r="I83" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="J83" t="n">
-        <v>-68000000</v>
+        <v>-136000000</v>
       </c>
       <c r="K83" t="n">
-        <v>344760244.5504109</v>
+        <v>1285364113.369452</v>
       </c>
       <c r="L83" t="n">
-        <v>0.05851824187679444</v>
+        <v>0.03852218097221538</v>
       </c>
       <c r="M83" t="n">
-        <v>0.04838641196094517</v>
+        <v>0.02843895423713594</v>
       </c>
       <c r="N83" t="n">
-        <v>-0.01013182991584927</v>
+        <v>-0.01008322673507944</v>
       </c>
       <c r="O83" t="n">
-        <v>-2619789.119648522</v>
+        <v>-9720463.344178906</v>
       </c>
       <c r="P83" t="n">
-        <v>-2619789.119648522</v>
+        <v>-9720463.344178906</v>
       </c>
     </row>
     <row r="84">
@@ -9313,34 +9803,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G84" t="n">
-        <v>-180822610.01</v>
+        <v>-201932841.91</v>
       </c>
       <c r="H84" t="n">
-        <v>-51458493.15068493</v>
+        <v>-50972657.53424658</v>
       </c>
       <c r="I84" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="J84" t="n">
         <v>-68000000</v>
       </c>
       <c r="K84" t="n">
-        <v>-164281103.1606849</v>
+        <v>-184905499.4442466</v>
       </c>
       <c r="L84" t="n">
-        <v>0.05821004393128892</v>
+        <v>0.03873510939427094</v>
       </c>
       <c r="M84" t="n">
-        <v>0.04803495850217376</v>
+        <v>0.02862299468186214</v>
       </c>
       <c r="N84" t="n">
-        <v>-0.01017508542911516</v>
+        <v>-0.0101121147124088</v>
       </c>
       <c r="O84" t="n">
-        <v>1114382.839366167</v>
+        <v>1246523.747556976</v>
       </c>
       <c r="P84" t="n">
-        <v>557191.4196830833</v>
+        <v>623261.873778488</v>
       </c>
     </row>
     <row r="85">
@@ -9371,34 +9861,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G85" t="n">
-        <v>396368601.78</v>
+        <v>-196825268.73</v>
       </c>
       <c r="H85" t="n">
-        <v>-51445520.54794521</v>
+        <v>-50988356.16438356</v>
       </c>
       <c r="I85" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="J85" t="n">
         <v>-68000000</v>
       </c>
       <c r="K85" t="n">
-        <v>412923081.2320548</v>
+        <v>-179813624.8943836</v>
       </c>
       <c r="L85" t="n">
-        <v>0.05808035784574397</v>
+        <v>0.03888939094511485</v>
       </c>
       <c r="M85" t="n">
-        <v>0.04786041751529452</v>
+        <v>0.02874882009588635</v>
       </c>
       <c r="N85" t="n">
-        <v>-0.01021994033044944</v>
+        <v>-0.0101405708492285</v>
       </c>
       <c r="O85" t="n">
-        <v>-2461695.396566541</v>
+        <v>1063657.468357222</v>
       </c>
       <c r="P85" t="n">
-        <v>-2461695.396566541</v>
+        <v>531828.7341786108</v>
       </c>
     </row>
     <row r="86">
@@ -9429,34 +9919,34 @@
         <v>0.5</v>
       </c>
       <c r="G86" t="n">
-        <v>270725457.28</v>
+        <v>69886647.3499999</v>
       </c>
       <c r="H86" t="n">
-        <v>-90799555.08645856</v>
+        <v>-89968608.21917808</v>
       </c>
       <c r="I86" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="J86" t="n">
         <v>-34000000</v>
       </c>
       <c r="K86" t="n">
-        <v>213925902.1935414</v>
+        <v>13918039.13082182</v>
       </c>
       <c r="L86" t="n">
-        <v>0.0579990267461179</v>
+        <v>0.03901400018340251</v>
       </c>
       <c r="M86" t="n">
-        <v>0.04773570697588347</v>
+        <v>0.02884450571632646</v>
       </c>
       <c r="N86" t="n">
-        <v>-0.01026331977023442</v>
+        <v>-0.01016949446707605</v>
       </c>
       <c r="O86" t="n">
-        <v>-1097794.970674105</v>
+        <v>-70769.71096672022</v>
       </c>
       <c r="P86" t="n">
-        <v>-1097794.970674105</v>
+        <v>-70769.71096672022</v>
       </c>
     </row>
     <row r="87">
@@ -9487,34 +9977,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G87" t="n">
-        <v>-35174959.2</v>
+        <v>-81388394.01999998</v>
       </c>
       <c r="H87" t="n">
-        <v>2247136.761733663</v>
+        <v>2250000</v>
       </c>
       <c r="I87" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="J87" t="n">
         <v>-34000000</v>
       </c>
       <c r="K87" t="n">
-        <v>1072177.561733659</v>
+        <v>-45138394.01999998</v>
       </c>
       <c r="L87" t="n">
-        <v>0.05738520780446178</v>
+        <v>0.03908855826627113</v>
       </c>
       <c r="M87" t="n">
-        <v>0.04708113683929442</v>
+        <v>0.02889118764186969</v>
       </c>
       <c r="N87" t="n">
-        <v>-0.01030407096516736</v>
+        <v>-0.01019737062440143</v>
       </c>
       <c r="O87" t="n">
-        <v>-4603.247368068223</v>
+        <v>191788.7221717521</v>
       </c>
       <c r="P87" t="n">
-        <v>-4603.247368068223</v>
+        <v>95894.36108587607</v>
       </c>
     </row>
     <row r="88">
@@ -9545,34 +10035,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G88" t="n">
-        <v>-35427280.72000001</v>
+        <v>-24300588.46000001</v>
       </c>
       <c r="H88" t="n">
-        <v>2266152.03233775</v>
+        <v>2250000</v>
       </c>
       <c r="I88" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="J88" t="n">
         <v>-34000000</v>
       </c>
       <c r="K88" t="n">
-        <v>838871.312337745</v>
+        <v>11949411.53999999</v>
       </c>
       <c r="L88" t="n">
-        <v>0.05695407285841891</v>
+        <v>0.03915884386251234</v>
       </c>
       <c r="M88" t="n">
-        <v>0.04660915432675217</v>
+        <v>0.02893202524084604</v>
       </c>
       <c r="N88" t="n">
-        <v>-0.01034491853166675</v>
+        <v>-0.0102268186216663</v>
       </c>
       <c r="O88" t="n">
-        <v>-2892.685128228781</v>
+        <v>-40734.82148507537</v>
       </c>
       <c r="P88" t="n">
-        <v>-2892.685128228781</v>
+        <v>-40734.82148507537</v>
       </c>
     </row>
     <row r="89">
@@ -9603,34 +10093,34 @@
         <v>0.25</v>
       </c>
       <c r="G89" t="n">
-        <v>-35839034.46</v>
+        <v>-25229792.01000001</v>
       </c>
       <c r="H89" t="n">
-        <v>2248181.001571974</v>
+        <v>2250000</v>
       </c>
       <c r="I89" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="J89" t="n">
         <v>-34000000</v>
       </c>
       <c r="K89" t="n">
-        <v>409146.5415719748</v>
+        <v>11020207.98999999</v>
       </c>
       <c r="L89" t="n">
-        <v>0.05664439372837885</v>
+        <v>0.03922681220647117</v>
       </c>
       <c r="M89" t="n">
-        <v>0.04625895250573434</v>
+        <v>0.02897133545183994</v>
       </c>
       <c r="N89" t="n">
-        <v>-0.01038544122264451</v>
+        <v>-0.01025547675463123</v>
       </c>
       <c r="O89" t="n">
-        <v>-1062.291839736006</v>
+        <v>-28254.37171816158</v>
       </c>
       <c r="P89" t="n">
-        <v>-1062.291839736006</v>
+        <v>-28254.37171816158</v>
       </c>
     </row>
     <row r="90">
@@ -9661,34 +10151,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>-35777615.53999999</v>
+        <v>43083900.58</v>
       </c>
       <c r="H90" t="n">
-        <v>2248686.278913092</v>
+        <v>2250000</v>
       </c>
       <c r="I90" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="J90" t="n">
         <v>-34000000</v>
       </c>
       <c r="K90" t="n">
-        <v>471070.7389131002</v>
+        <v>79333900.58</v>
       </c>
       <c r="L90" t="n">
-        <v>0.05642057743315654</v>
+        <v>0.03929424848359133</v>
       </c>
       <c r="M90" t="n">
-        <v>0.04599405363004969</v>
+        <v>0.02900978976389527</v>
       </c>
       <c r="N90" t="n">
-        <v>-0.01042652380310684</v>
+        <v>-0.01028445871969606</v>
       </c>
       <c r="O90" t="n">
-        <v>-818.6050453707613</v>
+        <v>-135984.3709312468</v>
       </c>
       <c r="P90" t="n">
-        <v>-818.6050453707613</v>
+        <v>-135984.3709312468</v>
       </c>
     </row>
     <row r="91">
@@ -9719,34 +10209,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G91" t="n">
-        <v>-35715304.73</v>
+        <v>32635075.89</v>
       </c>
       <c r="H91" t="n">
-        <v>2261537.165955536</v>
+        <v>2262328.767123288</v>
       </c>
       <c r="I91" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="J91" t="n">
-        <v>-34000000</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>546232.4359555319</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="L91" t="n">
-        <v>0.05625883751011833</v>
+        <v>0.03936107056455495</v>
       </c>
       <c r="M91" t="n">
-        <v>0.04579124656081188</v>
+        <v>0.02904763456151544</v>
       </c>
       <c r="N91" t="n">
-        <v>-0.01046759094930644</v>
+        <v>-0.01031343600303951</v>
       </c>
       <c r="O91" t="n">
-        <v>-476.478141902145</v>
+        <v>-29992.67913361784</v>
       </c>
       <c r="P91" t="n">
-        <v>-476.478141902145</v>
+        <v>-29992.67913361784</v>
       </c>
     </row>
     <row r="92">
@@ -9777,34 +10267,34 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>-36430105.95000001</v>
+        <v>-85065078.76000001</v>
       </c>
       <c r="H92" t="n">
-        <v>4044566.584325174</v>
+        <v>4045068.493150685</v>
       </c>
       <c r="I92" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="J92" t="n">
-        <v>-34000000</v>
+        <v>-68000000</v>
       </c>
       <c r="K92" t="n">
-        <v>1614460.634325162</v>
+        <v>-13020010.26684932</v>
       </c>
       <c r="L92" t="n">
-        <v>0.05611688274594639</v>
+        <v>0.03942868733737526</v>
       </c>
       <c r="M92" t="n">
-        <v>0.04560834936885638</v>
+        <v>0.02908625014097033</v>
       </c>
       <c r="N92" t="n">
-        <v>-0.01050853337709001</v>
+        <v>-0.01034243719640493</v>
       </c>
       <c r="O92" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9880,22 +10370,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="D2" t="n">
-        <v>673143847.5700001</v>
+        <v>572674499.95</v>
       </c>
       <c r="E2" t="n">
-        <v>61073262.91000009</v>
+        <v>42411854.98000002</v>
       </c>
       <c r="F2" t="n">
-        <v>30536631.45500004</v>
+        <v>21205927.49000001</v>
       </c>
       <c r="G2" t="n">
-        <v>5.08943857583334</v>
+        <v>3.534321248333335</v>
       </c>
       <c r="H2" t="n">
-        <v>2.54471928791667</v>
+        <v>1.767160624166668</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -9913,22 +10403,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="D3" t="n">
-        <v>555254424.24</v>
+        <v>484366736.45</v>
       </c>
       <c r="E3" t="n">
-        <v>-56816160.41999996</v>
+        <v>-45895908.52000004</v>
       </c>
       <c r="F3" t="n">
-        <v>-56816160.41999996</v>
+        <v>-45895908.52000004</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.734680034999996</v>
+        <v>-3.824659043333337</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.734680034999996</v>
+        <v>-3.824659043333337</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -9946,22 +10436,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="D4" t="n">
-        <v>638606894.7</v>
+        <v>552727420.49</v>
       </c>
       <c r="E4" t="n">
-        <v>26536310.04000008</v>
+        <v>22464775.51999998</v>
       </c>
       <c r="F4" t="n">
-        <v>13268155.02000004</v>
+        <v>11232387.75999999</v>
       </c>
       <c r="G4" t="n">
-        <v>2.211359170000007</v>
+        <v>1.872064626666665</v>
       </c>
       <c r="H4" t="n">
-        <v>1.105679585000003</v>
+        <v>0.9360323133333326</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -9979,22 +10469,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="D5" t="n">
-        <v>595587989.5599999</v>
+        <v>508247205.35</v>
       </c>
       <c r="E5" t="n">
-        <v>-16482595.10000002</v>
+        <v>-22015439.62</v>
       </c>
       <c r="F5" t="n">
-        <v>-16482595.10000002</v>
+        <v>-22015439.62</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.373549591666669</v>
+        <v>-1.834619968333334</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.373549591666669</v>
+        <v>-1.834619968333334</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -10012,22 +10502,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="D6" t="n">
-        <v>621226231.51</v>
+        <v>528129393.9</v>
       </c>
       <c r="E6" t="n">
-        <v>9155646.850000024</v>
+        <v>-2133251.070000052</v>
       </c>
       <c r="F6" t="n">
-        <v>4577823.425000012</v>
+        <v>-2133251.070000052</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7629705708333353</v>
+        <v>-0.1777709225000044</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3814852854166677</v>
+        <v>-0.1777709225000044</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -10045,22 +10535,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="D7" t="n">
-        <v>606993370.22</v>
+        <v>528746533.87</v>
       </c>
       <c r="E7" t="n">
-        <v>-5077214.439999938</v>
+        <v>-1516111.100000024</v>
       </c>
       <c r="F7" t="n">
-        <v>-5077214.439999938</v>
+        <v>-1516111.100000024</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4231012033333282</v>
+        <v>-0.1263425916666686</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4231012033333282</v>
+        <v>-0.1263425916666686</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -10078,22 +10568,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="D8" t="n">
-        <v>590585952.03</v>
+        <v>510874107.55</v>
       </c>
       <c r="E8" t="n">
-        <v>-21484632.63</v>
+        <v>-19388537.42000002</v>
       </c>
       <c r="F8" t="n">
-        <v>-21484632.63</v>
+        <v>-19388537.42000002</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.790386052499999</v>
+        <v>-1.615711451666668</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.790386052499999</v>
+        <v>-1.615711451666668</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>

--- a/irrbb_calc/output/eba_sot_results.xlsx
+++ b/irrbb_calc/output/eba_sot_results.xlsx
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1357868945.18</v>
+        <v>-1410564079.41</v>
       </c>
       <c r="E2" t="n">
         <v>0.999906031812547</v>
@@ -495,10 +495,10 @@
         <v>1.270756758997571e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>-17255.21139920387</v>
+        <v>-17924.83837909444</v>
       </c>
       <c r="I2" t="n">
-        <v>-17255.21139920387</v>
+        <v>-17924.83837909444</v>
       </c>
     </row>
     <row r="3">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-273538406.96</v>
+        <v>-210789268.91</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983821828874917</v>
@@ -530,10 +530,10 @@
         <v>-0.001074720528931317</v>
       </c>
       <c r="H3" t="n">
-        <v>293977.3414110809</v>
+        <v>226539.5545760007</v>
       </c>
       <c r="I3" t="n">
-        <v>146988.6707055405</v>
+        <v>113269.7772880004</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-391346094.59</v>
+        <v>-466347525.5</v>
       </c>
       <c r="E4" t="n">
         <v>0.9936563817038003</v>
@@ -565,10 +565,10 @@
         <v>-0.004131807575030844</v>
       </c>
       <c r="H4" t="n">
-        <v>1616966.758085699</v>
+        <v>1926858.238457789</v>
       </c>
       <c r="I4" t="n">
-        <v>808483.3790428495</v>
+        <v>963429.1192288947</v>
       </c>
     </row>
     <row r="5">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-784700756.36</v>
+        <v>-928106565.37</v>
       </c>
       <c r="E5" t="n">
         <v>0.9856536327098718</v>
@@ -600,10 +600,10 @@
         <v>-0.009198654711137122</v>
       </c>
       <c r="H5" t="n">
-        <v>7218191.309323777</v>
+        <v>8537331.829978043</v>
       </c>
       <c r="I5" t="n">
-        <v>3609095.654661889</v>
+        <v>4268665.914989022</v>
       </c>
     </row>
     <row r="6">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>106194068.06</v>
+        <v>325613046.1</v>
       </c>
       <c r="E6" t="n">
         <v>0.9761318955535195</v>
@@ -635,10 +635,10 @@
         <v>-0.01513456126685975</v>
       </c>
       <c r="H6" t="n">
-        <v>-1607200.629231144</v>
+        <v>-4928010.595489277</v>
       </c>
       <c r="I6" t="n">
-        <v>-1607200.629231144</v>
+        <v>-4928010.595489277</v>
       </c>
     </row>
     <row r="7">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>327029241.36</v>
+        <v>263741483.93</v>
       </c>
       <c r="E7" t="n">
         <v>0.9667342819189046</v>
@@ -670,10 +670,10 @@
         <v>-0.02091896253201642</v>
       </c>
       <c r="H7" t="n">
-        <v>-6841112.446883594</v>
+        <v>-5517198.22047008</v>
       </c>
       <c r="I7" t="n">
-        <v>-6841112.446883594</v>
+        <v>-5517198.22047008</v>
       </c>
     </row>
     <row r="8">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>453172829.04</v>
+        <v>589973763.67</v>
       </c>
       <c r="E8" t="n">
         <v>0.9524015829683793</v>
@@ -705,10 +705,10 @@
         <v>-0.02930239133147783</v>
       </c>
       <c r="H8" t="n">
-        <v>-13279047.57732298</v>
+        <v>-17287642.09836316</v>
       </c>
       <c r="I8" t="n">
-        <v>-13279047.57732298</v>
+        <v>-17287642.09836316</v>
       </c>
     </row>
     <row r="9">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>706989755.74</v>
+        <v>612295005.0700001</v>
       </c>
       <c r="E9" t="n">
         <v>0.9333610479054046</v>
@@ -740,10 +740,10 @@
         <v>-0.03995420556806362</v>
       </c>
       <c r="H9" t="n">
-        <v>-28247214.03535105</v>
+        <v>-24463760.50086534</v>
       </c>
       <c r="I9" t="n">
-        <v>-28247214.03535105</v>
+        <v>-24463760.50086534</v>
       </c>
     </row>
     <row r="10">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>950082301.61</v>
+        <v>773886472.84</v>
       </c>
       <c r="E10" t="n">
         <v>0.9066754799235061</v>
@@ -775,10 +775,10 @@
         <v>-0.05493320652757383</v>
       </c>
       <c r="H10" t="n">
-        <v>-52191067.29253482</v>
+        <v>-42512065.44141538</v>
       </c>
       <c r="I10" t="n">
-        <v>-52191067.29253482</v>
+        <v>-42512065.44141538</v>
       </c>
     </row>
     <row r="11">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1131433784.31</v>
+        <v>752632597.09</v>
       </c>
       <c r="E11" t="n">
         <v>0.8730418834956067</v>
@@ -810,10 +810,10 @@
         <v>-0.07314463828611695</v>
       </c>
       <c r="H11" t="n">
-        <v>-82758314.8980474</v>
+        <v>-55051039.07648885</v>
       </c>
       <c r="I11" t="n">
-        <v>-82758314.8980474</v>
+        <v>-55051039.07648885</v>
       </c>
     </row>
     <row r="12">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>725856199.14</v>
+        <v>1376408988.27</v>
       </c>
       <c r="E12" t="n">
         <v>0.839886760163754</v>
@@ -845,10 +845,10 @@
         <v>-0.0893662269184845</v>
       </c>
       <c r="H12" t="n">
-        <v>-64867029.80253392</v>
+        <v>-123004477.9783785</v>
       </c>
       <c r="I12" t="n">
-        <v>-64867029.80253392</v>
+        <v>-123004477.9783785</v>
       </c>
     </row>
     <row r="13">
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>135257246.09</v>
+        <v>171337663.91</v>
       </c>
       <c r="E13" t="n">
         <v>0.8060794216350962</v>
@@ -880,10 +880,10 @@
         <v>-0.1035535335270944</v>
       </c>
       <c r="H13" t="n">
-        <v>-14006365.76776327</v>
+        <v>-17742620.52415822</v>
       </c>
       <c r="I13" t="n">
-        <v>-14006365.76776327</v>
+        <v>-17742620.52415822</v>
       </c>
     </row>
     <row r="14">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>290934368.76</v>
+        <v>304374885.85</v>
       </c>
       <c r="E14" t="n">
         <v>0.7725125366488534</v>
@@ -915,10 +915,10 @@
         <v>-0.1158645673464029</v>
       </c>
       <c r="H14" t="n">
-        <v>-33708984.76257624</v>
+        <v>-35266264.46012104</v>
       </c>
       <c r="I14" t="n">
-        <v>-33708984.76257624</v>
+        <v>-35266264.46012104</v>
       </c>
     </row>
     <row r="15">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>293928244.15</v>
+        <v>295856253.29</v>
       </c>
       <c r="E15" t="n">
         <v>0.7390723504327896</v>
@@ -950,10 +950,10 @@
         <v>-0.1263599384343468</v>
       </c>
       <c r="H15" t="n">
-        <v>-37140754.83490965</v>
+        <v>-37384377.95114091</v>
       </c>
       <c r="I15" t="n">
-        <v>-37140754.83490965</v>
+        <v>-37384377.95114091</v>
       </c>
     </row>
     <row r="16">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>240687365.15</v>
+        <v>240713355.56</v>
       </c>
       <c r="E16" t="n">
         <v>0.7058360643204235</v>
@@ -985,10 +985,10 @@
         <v>-0.135125484853127</v>
       </c>
       <c r="H16" t="n">
-        <v>-32522996.91391538</v>
+        <v>-32526508.88066816</v>
       </c>
       <c r="I16" t="n">
-        <v>-32522996.91391538</v>
+        <v>-32526508.88066816</v>
       </c>
     </row>
     <row r="17">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>152144703.2</v>
+        <v>150836878.06</v>
       </c>
       <c r="E17" t="n">
         <v>0.6740936305925465</v>
@@ -1020,10 +1020,10 @@
         <v>-0.142505629537688</v>
       </c>
       <c r="H17" t="n">
-        <v>-21681476.71034069</v>
+        <v>-21495104.26543977</v>
       </c>
       <c r="I17" t="n">
-        <v>-21681476.71034069</v>
+        <v>-21495104.26543977</v>
       </c>
     </row>
     <row r="18">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11282921.34</v>
+        <v>12616901.91</v>
       </c>
       <c r="E18" t="n">
         <v>0.5835756277426192</v>
@@ -1055,10 +1055,10 @@
         <v>-0.1566226182330579</v>
       </c>
       <c r="H18" t="n">
-        <v>-1767160.681588442</v>
+        <v>-1976092.211133869</v>
       </c>
       <c r="I18" t="n">
-        <v>-1767160.681588442</v>
+        <v>-1976092.211133869</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-1357868945.18</v>
+        <v>-1410564079.41</v>
       </c>
       <c r="E19" t="n">
         <v>0.999906031812547</v>
@@ -1090,10 +1090,10 @@
         <v>8.119444430232381e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>-110251.4144392727</v>
+        <v>-114529.9665805139</v>
       </c>
       <c r="I19" t="n">
-        <v>-110251.4144392727</v>
+        <v>-114529.9665805139</v>
       </c>
     </row>
     <row r="20">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-273538406.96</v>
+        <v>-210789268.91</v>
       </c>
       <c r="E20" t="n">
         <v>0.9983821828874917</v>
@@ -1125,10 +1125,10 @@
         <v>0.001073618328581993</v>
       </c>
       <c r="H20" t="n">
-        <v>-293675.8472833763</v>
+        <v>-226307.2225701745</v>
       </c>
       <c r="I20" t="n">
-        <v>-293675.8472833763</v>
+        <v>-226307.2225701745</v>
       </c>
     </row>
     <row r="21">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-391346094.59</v>
+        <v>-466347525.5</v>
       </c>
       <c r="E21" t="n">
         <v>0.9936563817038003</v>
@@ -1160,10 +1160,10 @@
         <v>0.004148675157226389</v>
       </c>
       <c r="H21" t="n">
-        <v>-1623567.820503101</v>
+        <v>-1934724.39367585</v>
       </c>
       <c r="I21" t="n">
-        <v>-1623567.820503101</v>
+        <v>-1934724.39367585</v>
       </c>
     </row>
     <row r="22">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-784700756.36</v>
+        <v>-928106565.37</v>
       </c>
       <c r="E22" t="n">
         <v>0.9856536327098718</v>
@@ -1195,10 +1195,10 @@
         <v>0.009282592027197278</v>
       </c>
       <c r="H22" t="n">
-        <v>-7284056.98472301</v>
+        <v>-8615234.604093011</v>
       </c>
       <c r="I22" t="n">
-        <v>-7284056.98472301</v>
+        <v>-8615234.604093011</v>
       </c>
     </row>
     <row r="23">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>106194068.06</v>
+        <v>325613046.1</v>
       </c>
       <c r="E23" t="n">
         <v>0.9761318955535195</v>
@@ -1230,10 +1230,10 @@
         <v>0.01537076312862229</v>
       </c>
       <c r="H23" t="n">
-        <v>1632283.865815054</v>
+        <v>5004921.003192269</v>
       </c>
       <c r="I23" t="n">
-        <v>816141.932907527</v>
+        <v>2502460.501596135</v>
       </c>
     </row>
     <row r="24">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>327029241.36</v>
+        <v>263741483.93</v>
       </c>
       <c r="E24" t="n">
         <v>0.9667342819189046</v>
@@ -1265,10 +1265,10 @@
         <v>0.02137897737503558</v>
       </c>
       <c r="H24" t="n">
-        <v>6991550.75201049</v>
+        <v>5638523.21779778</v>
       </c>
       <c r="I24" t="n">
-        <v>3495775.376005245</v>
+        <v>2819261.60889889</v>
       </c>
     </row>
     <row r="25">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>453172829.04</v>
+        <v>589973763.67</v>
       </c>
       <c r="E25" t="n">
         <v>0.9524015829683793</v>
@@ -1300,10 +1300,10 @@
         <v>0.03023239035728253</v>
       </c>
       <c r="H25" t="n">
-        <v>13700497.86685134</v>
+        <v>17836317.12382659</v>
       </c>
       <c r="I25" t="n">
-        <v>6850248.933425671</v>
+        <v>8918158.561913297</v>
       </c>
     </row>
     <row r="26">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>706989755.74</v>
+        <v>612295005.0700001</v>
       </c>
       <c r="E26" t="n">
         <v>0.9333610479054046</v>
@@ -1335,10 +1335,10 @@
         <v>0.04174093883572272</v>
       </c>
       <c r="H26" t="n">
-        <v>29510416.15182589</v>
+        <v>25557768.3560454</v>
       </c>
       <c r="I26" t="n">
-        <v>14755208.07591294</v>
+        <v>12778884.1780227</v>
       </c>
     </row>
     <row r="27">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>950082301.61</v>
+        <v>773886472.84</v>
       </c>
       <c r="E27" t="n">
         <v>0.9066754799235061</v>
@@ -1370,10 +1370,10 @@
         <v>0.05847495853512397</v>
       </c>
       <c r="H27" t="n">
-        <v>55556023.19159989</v>
+        <v>45252979.41021234</v>
       </c>
       <c r="I27" t="n">
-        <v>27778011.59579995</v>
+        <v>22626489.70510617</v>
       </c>
     </row>
     <row r="28">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1131433784.31</v>
+        <v>752632597.09</v>
       </c>
       <c r="E28" t="n">
         <v>0.8730418834956067</v>
@@ -1405,10 +1405,10 @@
         <v>0.07983268361646123</v>
       </c>
       <c r="H28" t="n">
-        <v>90325395.33579566</v>
+        <v>60084680.00292151</v>
       </c>
       <c r="I28" t="n">
-        <v>45162697.66789783</v>
+        <v>30042340.00146076</v>
       </c>
     </row>
     <row r="29">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>725856199.14</v>
+        <v>1376408988.27</v>
       </c>
       <c r="E29" t="n">
         <v>0.839886760163754</v>
@@ -1440,10 +1440,10 @@
         <v>0.1000071588498553</v>
       </c>
       <c r="H29" t="n">
-        <v>72590816.20954621</v>
+        <v>137650752.3322866</v>
       </c>
       <c r="I29" t="n">
-        <v>36295408.1047731</v>
+        <v>68825376.16614328</v>
       </c>
     </row>
     <row r="30">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>135257246.09</v>
+        <v>171337663.91</v>
       </c>
       <c r="E30" t="n">
         <v>0.8060794216350962</v>
@@ -1475,10 +1475,10 @@
         <v>0.1188174585554111</v>
       </c>
       <c r="H30" t="n">
-        <v>16070922.23161762</v>
+        <v>20357905.78060739</v>
       </c>
       <c r="I30" t="n">
-        <v>8035461.115808811</v>
+        <v>10178952.89030369</v>
       </c>
     </row>
     <row r="31">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>290934368.76</v>
+        <v>304374885.85</v>
       </c>
       <c r="E31" t="n">
         <v>0.7725125366488534</v>
@@ -1510,10 +1510,10 @@
         <v>0.1363083780988569</v>
       </c>
       <c r="H31" t="n">
-        <v>39656791.93889033</v>
+        <v>41488847.02423821</v>
       </c>
       <c r="I31" t="n">
-        <v>19828395.96944517</v>
+        <v>20744423.5121191</v>
       </c>
     </row>
     <row r="32">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>293928244.15</v>
+        <v>295856253.29</v>
       </c>
       <c r="E32" t="n">
         <v>0.7390723504327896</v>
@@ -1545,10 +1545,10 @@
         <v>0.1524189448946068</v>
       </c>
       <c r="H32" t="n">
-        <v>44800232.84806739</v>
+        <v>45094097.96693335</v>
       </c>
       <c r="I32" t="n">
-        <v>22400116.42403369</v>
+        <v>22547048.98346668</v>
       </c>
     </row>
     <row r="33">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>240687365.15</v>
+        <v>240713355.56</v>
       </c>
       <c r="E33" t="n">
         <v>0.7058360643204235</v>
@@ -1580,10 +1580,10 @@
         <v>0.1671173700222426</v>
       </c>
       <c r="H33" t="n">
-        <v>40223039.46145117</v>
+        <v>40227382.91041616</v>
       </c>
       <c r="I33" t="n">
-        <v>20111519.73072558</v>
+        <v>20113691.45520808</v>
       </c>
     </row>
     <row r="34">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>152144703.2</v>
+        <v>150836878.06</v>
       </c>
       <c r="E34" t="n">
         <v>0.6740936305925465</v>
@@ -1615,10 +1615,10 @@
         <v>0.1807074230390667</v>
       </c>
       <c r="H34" t="n">
-        <v>27493677.24431565</v>
+        <v>27257343.53348054</v>
       </c>
       <c r="I34" t="n">
-        <v>13746838.62215782</v>
+        <v>13628671.76674027</v>
       </c>
     </row>
     <row r="35">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11282921.34</v>
+        <v>12616901.91</v>
       </c>
       <c r="E35" t="n">
         <v>0.5835756277426192</v>
@@ -1650,10 +1650,10 @@
         <v>0.2140775985160066</v>
       </c>
       <c r="H35" t="n">
-        <v>2415420.704712203</v>
+        <v>2700996.061604817</v>
       </c>
       <c r="I35" t="n">
-        <v>1207710.352356102</v>
+        <v>1350498.030802408</v>
       </c>
     </row>
     <row r="36">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-1357868945.18</v>
+        <v>-1410564079.41</v>
       </c>
       <c r="E36" t="n">
         <v>0.999906031812547</v>
@@ -1685,10 +1685,10 @@
         <v>7.797724224745117e-05</v>
       </c>
       <c r="H36" t="n">
-        <v>-105882.8756785919</v>
+        <v>-109991.8969257065</v>
       </c>
       <c r="I36" t="n">
-        <v>-105882.8756785919</v>
+        <v>-109991.8969257065</v>
       </c>
     </row>
     <row r="37">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-273538406.96</v>
+        <v>-210789268.91</v>
       </c>
       <c r="E37" t="n">
         <v>0.9983821828874917</v>
@@ -1720,10 +1720,10 @@
         <v>0.000857634379940464</v>
       </c>
       <c r="H37" t="n">
-        <v>-234595.9420430419</v>
+        <v>-180780.1239397316</v>
       </c>
       <c r="I37" t="n">
-        <v>-234595.9420430419</v>
+        <v>-180780.1239397316</v>
       </c>
     </row>
     <row r="38">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-391346094.59</v>
+        <v>-466347525.5</v>
       </c>
       <c r="E38" t="n">
         <v>0.9936563817038003</v>
@@ -1755,10 +1755,10 @@
         <v>0.002842264830571484</v>
       </c>
       <c r="H38" t="n">
-        <v>-1112309.241234658</v>
+        <v>-1325483.170552688</v>
       </c>
       <c r="I38" t="n">
-        <v>-1112309.241234658</v>
+        <v>-1325483.170552688</v>
       </c>
     </row>
     <row r="39">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-784700756.36</v>
+        <v>-928106565.37</v>
       </c>
       <c r="E39" t="n">
         <v>0.9856536327098718</v>
@@ -1790,10 +1790,10 @@
         <v>0.004190624857375314</v>
       </c>
       <c r="H39" t="n">
-        <v>-3288386.495203426</v>
+        <v>-3889346.443132748</v>
       </c>
       <c r="I39" t="n">
-        <v>-3288386.495203426</v>
+        <v>-3889346.443132748</v>
       </c>
     </row>
     <row r="40">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>106194068.06</v>
+        <v>325613046.1</v>
       </c>
       <c r="E40" t="n">
         <v>0.9761318955535195</v>
@@ -1825,10 +1825,10 @@
         <v>0.003588231255082563</v>
       </c>
       <c r="H40" t="n">
-        <v>381048.874117257</v>
+        <v>1168374.909078659</v>
       </c>
       <c r="I40" t="n">
-        <v>190524.4370586285</v>
+        <v>584187.4545393297</v>
       </c>
     </row>
     <row r="41">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>327029241.36</v>
+        <v>263741483.93</v>
       </c>
       <c r="E41" t="n">
         <v>0.9667342819189046</v>
@@ -1860,10 +1860,10 @@
         <v>0.001347768023809648</v>
       </c>
       <c r="H41" t="n">
-        <v>440759.5543557356</v>
+        <v>355462.3385929601</v>
       </c>
       <c r="I41" t="n">
-        <v>220379.7771778678</v>
+        <v>177731.16929648</v>
       </c>
     </row>
     <row r="42">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>453172829.04</v>
+        <v>589973763.67</v>
       </c>
       <c r="E42" t="n">
         <v>0.9524015829683793</v>
@@ -1895,10 +1895,10 @@
         <v>-0.003700723745374557</v>
       </c>
       <c r="H42" t="n">
-        <v>-1677067.449186892</v>
+        <v>-2183329.916361566</v>
       </c>
       <c r="I42" t="n">
-        <v>-1677067.449186892</v>
+        <v>-2183329.916361566</v>
       </c>
     </row>
     <row r="43">
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>706989755.74</v>
+        <v>612295005.0700001</v>
       </c>
       <c r="E43" t="n">
         <v>0.9333610479054046</v>
@@ -1930,10 +1930,10 @@
         <v>-0.01168774742577749</v>
       </c>
       <c r="H43" t="n">
-        <v>-8263117.697701245</v>
+        <v>-7156349.369323311</v>
       </c>
       <c r="I43" t="n">
-        <v>-8263117.697701245</v>
+        <v>-7156349.369323311</v>
       </c>
     </row>
     <row r="44">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>950082301.61</v>
+        <v>773886472.84</v>
       </c>
       <c r="E44" t="n">
         <v>0.9066754799235061</v>
@@ -1965,10 +1965,10 @@
         <v>-0.02354447052112385</v>
       </c>
       <c r="H44" t="n">
-        <v>-22369184.74289814</v>
+        <v>-18220747.24647789</v>
       </c>
       <c r="I44" t="n">
-        <v>-22369184.74289814</v>
+        <v>-18220747.24647789</v>
       </c>
     </row>
     <row r="45">
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1131433784.31</v>
+        <v>752632597.09</v>
       </c>
       <c r="E45" t="n">
         <v>0.8730418834956067</v>
@@ -2000,10 +2000,10 @@
         <v>-0.03709517753986769</v>
       </c>
       <c r="H45" t="n">
-        <v>-41970737.10358381</v>
+        <v>-27919039.81134525</v>
       </c>
       <c r="I45" t="n">
-        <v>-41970737.10358381</v>
+        <v>-27919039.81134525</v>
       </c>
     </row>
     <row r="46">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>725856199.14</v>
+        <v>1376408988.27</v>
       </c>
       <c r="E46" t="n">
         <v>0.839886760163754</v>
@@ -2035,10 +2035,10 @@
         <v>-0.04807062925974992</v>
       </c>
       <c r="H46" t="n">
-        <v>-34892364.24475015</v>
+        <v>-66164846.18491465</v>
       </c>
       <c r="I46" t="n">
-        <v>-34892364.24475015</v>
+        <v>-66164846.18491465</v>
       </c>
     </row>
     <row r="47">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>135257246.09</v>
+        <v>171337663.91</v>
       </c>
       <c r="E47" t="n">
         <v>0.8060794216350962</v>
@@ -2070,10 +2070,10 @@
         <v>-0.05707337113962196</v>
       </c>
       <c r="H47" t="n">
-        <v>-7719587.005417752</v>
+        <v>-9778818.082531242</v>
       </c>
       <c r="I47" t="n">
-        <v>-7719587.005417752</v>
+        <v>-9778818.082531242</v>
       </c>
     </row>
     <row r="48">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>290934368.76</v>
+        <v>304374885.85</v>
       </c>
       <c r="E48" t="n">
         <v>0.7725125366488534</v>
@@ -2105,10 +2105,10 @@
         <v>-0.06464828621749663</v>
       </c>
       <c r="H48" t="n">
-        <v>-18808408.34210319</v>
+        <v>-19677314.73784867</v>
       </c>
       <c r="I48" t="n">
-        <v>-18808408.34210319</v>
+        <v>-19677314.73784867</v>
       </c>
     </row>
     <row r="49">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>293928244.15</v>
+        <v>295856253.29</v>
       </c>
       <c r="E49" t="n">
         <v>0.7390723504327896</v>
@@ -2140,10 +2140,10 @@
         <v>-0.07106709005817402</v>
       </c>
       <c r="H49" t="n">
-        <v>-20888624.99764901</v>
+        <v>-21025642.99683437</v>
       </c>
       <c r="I49" t="n">
-        <v>-20888624.99764901</v>
+        <v>-21025642.99683437</v>
       </c>
     </row>
     <row r="50">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>240687365.15</v>
+        <v>240713355.56</v>
       </c>
       <c r="E50" t="n">
         <v>0.7058360643204235</v>
@@ -2175,10 +2175,10 @@
         <v>-0.07648141160373034</v>
       </c>
       <c r="H50" t="n">
-        <v>-18408109.44185449</v>
+        <v>-18410097.22509945</v>
       </c>
       <c r="I50" t="n">
-        <v>-18408109.44185449</v>
+        <v>-18410097.22509945</v>
       </c>
     </row>
     <row r="51">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>152144703.2</v>
+        <v>150836878.06</v>
       </c>
       <c r="E51" t="n">
         <v>0.6740936305925465</v>
@@ -2210,10 +2210,10 @@
         <v>-0.08112320091848635</v>
       </c>
       <c r="H51" t="n">
-        <v>-12342465.32637707</v>
+        <v>-12236370.36477861</v>
       </c>
       <c r="I51" t="n">
-        <v>-12342465.32637707</v>
+        <v>-12236370.36477861</v>
       </c>
     </row>
     <row r="52">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11282921.34</v>
+        <v>12616901.91</v>
       </c>
       <c r="E52" t="n">
         <v>0.5835756277426192</v>
@@ -2245,10 +2245,10 @@
         <v>-0.09061680299551267</v>
       </c>
       <c r="H52" t="n">
-        <v>-1022422.260280646</v>
+        <v>-1143303.314792177</v>
       </c>
       <c r="I52" t="n">
-        <v>-1022422.260280646</v>
+        <v>-1143303.314792177</v>
       </c>
     </row>
     <row r="53">
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-1357868945.18</v>
+        <v>-1410564079.41</v>
       </c>
       <c r="E53" t="n">
         <v>0.999906031812547</v>
@@ -2280,10 +2280,10 @@
         <v>8.749858685930256e-06</v>
       </c>
       <c r="H53" t="n">
-        <v>-11881.16138433818</v>
+        <v>-12342.23636228681</v>
       </c>
       <c r="I53" t="n">
-        <v>-11881.16138433818</v>
+        <v>-12342.23636228681</v>
       </c>
     </row>
     <row r="54">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-273538406.96</v>
+        <v>-210789268.91</v>
       </c>
       <c r="E54" t="n">
         <v>0.9983821828874917</v>
@@ -2315,10 +2315,10 @@
         <v>-0.00107465764159409</v>
       </c>
       <c r="H54" t="n">
-        <v>293960.139309038</v>
+        <v>226526.298600163</v>
       </c>
       <c r="I54" t="n">
-        <v>146980.069654519</v>
+        <v>113263.1493000815</v>
       </c>
     </row>
     <row r="55">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-391346094.59</v>
+        <v>-466347525.5</v>
       </c>
       <c r="E55" t="n">
         <v>0.9936563817038003</v>
@@ -2350,10 +2350,10 @@
         <v>-0.003624512892459575</v>
       </c>
       <c r="H55" t="n">
-        <v>1418438.965255159</v>
+        <v>1690282.61854137</v>
       </c>
       <c r="I55" t="n">
-        <v>709219.4826275796</v>
+        <v>845141.3092706852</v>
       </c>
     </row>
     <row r="56">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-784700756.36</v>
+        <v>-928106565.37</v>
       </c>
       <c r="E56" t="n">
         <v>0.9856536327098718</v>
@@ -2385,10 +2385,10 @@
         <v>-0.00575832701755552</v>
       </c>
       <c r="H56" t="n">
-        <v>4518563.56604404</v>
+        <v>5344341.11054073</v>
       </c>
       <c r="I56" t="n">
-        <v>2259281.78302202</v>
+        <v>2672170.555270365</v>
       </c>
     </row>
     <row r="57">
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>106194068.06</v>
+        <v>325613046.1</v>
       </c>
       <c r="E57" t="n">
         <v>0.9761318955535195</v>
@@ -2420,10 +2420,10 @@
         <v>-0.005916553585663675</v>
       </c>
       <c r="H57" t="n">
-        <v>-628302.8941566054</v>
+        <v>-1926507.035441826</v>
       </c>
       <c r="I57" t="n">
-        <v>-628302.8941566054</v>
+        <v>-1926507.035441826</v>
       </c>
     </row>
     <row r="58">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>327029241.36</v>
+        <v>263741483.93</v>
       </c>
       <c r="E58" t="n">
         <v>0.9667342819189046</v>
@@ -2455,10 +2455,10 @@
         <v>-0.004299740059850787</v>
       </c>
       <c r="H58" t="n">
-        <v>-1406140.729818204</v>
+        <v>-1134019.823898314</v>
       </c>
       <c r="I58" t="n">
-        <v>-1406140.729818204</v>
+        <v>-1134019.823898314</v>
       </c>
     </row>
     <row r="59">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>453172829.04</v>
+        <v>589973763.67</v>
       </c>
       <c r="E59" t="n">
         <v>0.9524015829683793</v>
@@ -2490,10 +2490,10 @@
         <v>5.935525280276188e-06</v>
       </c>
       <c r="H59" t="n">
-        <v>2689.818783101199</v>
+        <v>3501.804188962974</v>
       </c>
       <c r="I59" t="n">
-        <v>1344.9093915506</v>
+        <v>1750.902094481487</v>
       </c>
     </row>
     <row r="60">
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>706989755.74</v>
+        <v>612295005.0700001</v>
       </c>
       <c r="E60" t="n">
         <v>0.9333610479054046</v>
@@ -2525,10 +2525,10 @@
         <v>0.007262963541339373</v>
       </c>
       <c r="H60" t="n">
-        <v>5134840.820040049</v>
+        <v>4447076.298367617</v>
       </c>
       <c r="I60" t="n">
-        <v>2567420.410020025</v>
+        <v>2223538.149183808</v>
       </c>
     </row>
     <row r="61">
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>950082301.61</v>
+        <v>773886472.84</v>
       </c>
       <c r="E61" t="n">
         <v>0.9066754799235061</v>
@@ -2560,10 +2560,10 @@
         <v>0.01838001221226671</v>
       </c>
       <c r="H61" t="n">
-        <v>17462524.30625026</v>
+        <v>14224042.82170721</v>
       </c>
       <c r="I61" t="n">
-        <v>8731262.15312513</v>
+        <v>7112021.410853603</v>
       </c>
     </row>
     <row r="62">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1131433784.31</v>
+        <v>752632597.09</v>
       </c>
       <c r="E62" t="n">
         <v>0.8730418834956067</v>
@@ -2595,10 +2595,10 @@
         <v>0.03130191235040702</v>
       </c>
       <c r="H62" t="n">
-        <v>35416041.14676094</v>
+        <v>23558839.58617039</v>
       </c>
       <c r="I62" t="n">
-        <v>17708020.57338047</v>
+        <v>11779419.79308519</v>
       </c>
     </row>
     <row r="63">
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>725856199.14</v>
+        <v>1376408988.27</v>
       </c>
       <c r="E63" t="n">
         <v>0.839886760163754</v>
@@ -2630,10 +2630,10 @@
         <v>0.04188199495808165</v>
       </c>
       <c r="H63" t="n">
-        <v>30400305.67267379</v>
+        <v>57646754.3069824</v>
       </c>
       <c r="I63" t="n">
-        <v>15200152.83633689</v>
+        <v>28823377.1534912</v>
       </c>
     </row>
     <row r="64">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>135257246.09</v>
+        <v>171337663.91</v>
       </c>
       <c r="E64" t="n">
         <v>0.8060794216350962</v>
@@ -2665,10 +2665,10 @@
         <v>0.05069529339115386</v>
       </c>
       <c r="H64" t="n">
-        <v>6856905.773812049</v>
+        <v>8686013.140872365</v>
       </c>
       <c r="I64" t="n">
-        <v>3428452.886906025</v>
+        <v>4343006.570436182</v>
       </c>
     </row>
     <row r="65">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>290934368.76</v>
+        <v>304374885.85</v>
       </c>
       <c r="E65" t="n">
         <v>0.7725125366488534</v>
@@ -2700,10 +2700,10 @@
         <v>0.05828777906690807</v>
       </c>
       <c r="H65" t="n">
-        <v>16957918.20925324</v>
+        <v>17741336.09994017</v>
       </c>
       <c r="I65" t="n">
-        <v>8478959.10462662</v>
+        <v>8870668.049970083</v>
       </c>
     </row>
     <row r="66">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>293928244.15</v>
+        <v>295856253.29</v>
       </c>
       <c r="E66" t="n">
         <v>0.7390723504327896</v>
@@ -2735,10 +2735,10 @@
         <v>0.06493454530509235</v>
       </c>
       <c r="H66" t="n">
-        <v>19086096.88620442</v>
+        <v>19211291.28305439</v>
       </c>
       <c r="I66" t="n">
-        <v>9543048.443102209</v>
+        <v>9605645.641527193</v>
       </c>
     </row>
     <row r="67">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>240687365.15</v>
+        <v>240713355.56</v>
       </c>
       <c r="E67" t="n">
         <v>0.7058360643204235</v>
@@ -2770,10 +2770,10 @@
         <v>0.0707747284866409</v>
       </c>
       <c r="H67" t="n">
-        <v>17034582.91865624</v>
+        <v>17036422.38286725</v>
       </c>
       <c r="I67" t="n">
-        <v>8517291.459328122</v>
+        <v>8518211.191433627</v>
       </c>
     </row>
     <row r="68">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>152144703.2</v>
+        <v>150836878.06</v>
       </c>
       <c r="E68" t="n">
         <v>0.6740936305925465</v>
@@ -2805,10 +2805,10 @@
         <v>0.07601335275394061</v>
       </c>
       <c r="H68" t="n">
-        <v>11565028.9939852</v>
+        <v>11465616.82027791</v>
       </c>
       <c r="I68" t="n">
-        <v>5782514.496992598</v>
+        <v>5732808.410138953</v>
       </c>
     </row>
     <row r="69">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11282921.34</v>
+        <v>12616901.91</v>
       </c>
       <c r="E69" t="n">
         <v>0.5835756277426192</v>
@@ -2840,10 +2840,10 @@
         <v>0.08811450570325163</v>
       </c>
       <c r="H69" t="n">
-        <v>994189.0367627696</v>
+        <v>1111732.075306061</v>
       </c>
       <c r="I69" t="n">
-        <v>497094.5183813848</v>
+        <v>555866.0376530307</v>
       </c>
     </row>
     <row r="70">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-1357868945.18</v>
+        <v>-1410564079.41</v>
       </c>
       <c r="E70" t="n">
         <v>0.999906031812547</v>
@@ -2875,10 +2875,10 @@
         <v>-8.56716656616463e-07</v>
       </c>
       <c r="H70" t="n">
-        <v>1163.308942837933</v>
+        <v>1208.453742055414</v>
       </c>
       <c r="I70" t="n">
-        <v>581.6544714189665</v>
+        <v>604.2268710277071</v>
       </c>
     </row>
     <row r="71">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-273538406.96</v>
+        <v>-210789268.91</v>
       </c>
       <c r="E71" t="n">
         <v>0.9983821828874917</v>
@@ -2910,10 +2910,10 @@
         <v>-0.001389003495161578</v>
       </c>
       <c r="H71" t="n">
-        <v>379945.8033283702</v>
+        <v>292787.0312585438</v>
       </c>
       <c r="I71" t="n">
-        <v>189972.9016641851</v>
+        <v>146393.5156292719</v>
       </c>
     </row>
     <row r="72">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-391346094.59</v>
+        <v>-466347525.5</v>
       </c>
       <c r="E72" t="n">
         <v>0.9936563817038003</v>
@@ -2945,10 +2945,10 @@
         <v>-0.004887294219023786</v>
       </c>
       <c r="H72" t="n">
-        <v>1912623.505727242</v>
+        <v>2279177.565432197</v>
       </c>
       <c r="I72" t="n">
-        <v>956311.7528636212</v>
+        <v>1139588.782716099</v>
       </c>
     </row>
     <row r="73">
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-784700756.36</v>
+        <v>-928106565.37</v>
       </c>
       <c r="E73" t="n">
         <v>0.9856536327098718</v>
@@ -2980,10 +2980,10 @@
         <v>-0.008818310314522182</v>
       </c>
       <c r="H73" t="n">
-        <v>6919734.773622746</v>
+        <v>8184331.698378026</v>
       </c>
       <c r="I73" t="n">
-        <v>3459867.386811373</v>
+        <v>4092165.849189013</v>
       </c>
     </row>
     <row r="74">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>106194068.06</v>
+        <v>325613046.1</v>
       </c>
       <c r="E74" t="n">
         <v>0.9761318955535195</v>
@@ -3015,10 +3015,10 @@
         <v>-0.01134588039219331</v>
       </c>
       <c r="H74" t="n">
-        <v>-1204865.194569196</v>
+        <v>-3694366.675188325</v>
       </c>
       <c r="I74" t="n">
-        <v>-1204865.194569196</v>
+        <v>-3694366.675188325</v>
       </c>
     </row>
     <row r="75">
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>327029241.36</v>
+        <v>263741483.93</v>
       </c>
       <c r="E75" t="n">
         <v>0.9667342819189046</v>
@@ -3050,10 +3050,10 @@
         <v>-0.01225043827690986</v>
       </c>
       <c r="H75" t="n">
-        <v>-4006251.536025337</v>
+        <v>-3230948.769945079</v>
       </c>
       <c r="I75" t="n">
-        <v>-4006251.536025337</v>
+        <v>-3230948.769945079</v>
       </c>
     </row>
     <row r="76">
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>453172829.04</v>
+        <v>589973763.67</v>
       </c>
       <c r="E76" t="n">
         <v>0.9524015829683793</v>
@@ -3085,10 +3085,10 @@
         <v>-0.01186315201310806</v>
       </c>
       <c r="H76" t="n">
-        <v>-5376058.15911175</v>
+        <v>-6998948.442162698</v>
       </c>
       <c r="I76" t="n">
-        <v>-5376058.15911175</v>
+        <v>-6998948.442162698</v>
       </c>
     </row>
     <row r="77">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>706989755.74</v>
+        <v>612295005.0700001</v>
       </c>
       <c r="E77" t="n">
         <v>0.9333610479054046</v>
@@ -3120,10 +3120,10 @@
         <v>-0.009881694503488636</v>
       </c>
       <c r="H77" t="n">
-        <v>-6986256.783318732</v>
+        <v>-6050512.186113766</v>
       </c>
       <c r="I77" t="n">
-        <v>-6986256.783318732</v>
+        <v>-6050512.186113766</v>
       </c>
     </row>
     <row r="78">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>950082301.61</v>
+        <v>773886472.84</v>
       </c>
       <c r="E78" t="n">
         <v>0.9066754799235061</v>
@@ -3155,10 +3155,10 @@
         <v>-0.006489882432710758</v>
       </c>
       <c r="H78" t="n">
-        <v>-6165922.438848143</v>
+        <v>-5022432.224996808</v>
       </c>
       <c r="I78" t="n">
-        <v>-6165922.438848143</v>
+        <v>-5022432.224996808</v>
       </c>
     </row>
     <row r="79">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1131433784.31</v>
+        <v>752632597.09</v>
       </c>
       <c r="E79" t="n">
         <v>0.8730418834956067</v>
@@ -3190,10 +3190,10 @@
         <v>-0.003224039784762822</v>
       </c>
       <c r="H79" t="n">
-        <v>-3647787.534440198</v>
+        <v>-2426517.436327528</v>
       </c>
       <c r="I79" t="n">
-        <v>-3647787.534440198</v>
+        <v>-2426517.436327528</v>
       </c>
     </row>
     <row r="80">
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>725856199.14</v>
+        <v>1376408988.27</v>
       </c>
       <c r="E80" t="n">
         <v>0.839886760163754</v>
@@ -3225,10 +3225,10 @@
         <v>-0.001468318235875343</v>
       </c>
       <c r="H80" t="n">
-        <v>-1065787.893820427</v>
+        <v>-2021006.417499573</v>
       </c>
       <c r="I80" t="n">
-        <v>-1065787.893820427</v>
+        <v>-2021006.417499573</v>
       </c>
     </row>
     <row r="81">
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>135257246.09</v>
+        <v>171337663.91</v>
       </c>
       <c r="E81" t="n">
         <v>0.8060794216350962</v>
@@ -3260,10 +3260,10 @@
         <v>-0.000633919618590939</v>
       </c>
       <c r="H81" t="n">
-        <v>-85742.22185303358</v>
+        <v>-108614.3065560897</v>
       </c>
       <c r="I81" t="n">
-        <v>-85742.22185303358</v>
+        <v>-108614.3065560897</v>
       </c>
     </row>
     <row r="82">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>290934368.76</v>
+        <v>304374885.85</v>
       </c>
       <c r="E82" t="n">
         <v>0.7725125366488534</v>
@@ -3295,10 +3295,10 @@
         <v>-0.0002643337202767881</v>
       </c>
       <c r="H82" t="n">
-        <v>-76903.76405070977</v>
+        <v>-80456.54593555322</v>
       </c>
       <c r="I82" t="n">
-        <v>-76903.76405070977</v>
+        <v>-80456.54593555322</v>
       </c>
     </row>
     <row r="83">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>293928244.15</v>
+        <v>295856253.29</v>
       </c>
       <c r="E83" t="n">
         <v>0.7390723504327896</v>
@@ -3330,10 +3330,10 @@
         <v>-0.0001074027017012869</v>
       </c>
       <c r="H83" t="n">
-        <v>-31568.68752802546</v>
+        <v>-31775.76091856624</v>
       </c>
       <c r="I83" t="n">
-        <v>-31568.68752802546</v>
+        <v>-31775.76091856624</v>
       </c>
     </row>
     <row r="84">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>240687365.15</v>
+        <v>240713355.56</v>
       </c>
       <c r="E84" t="n">
         <v>0.7058360643204235</v>
@@ -3365,10 +3365,10 @@
         <v>-4.329964913651896e-05</v>
       </c>
       <c r="H84" t="n">
-        <v>-10421.67846258822</v>
+        <v>-10422.80383822213</v>
       </c>
       <c r="I84" t="n">
-        <v>-10421.67846258822</v>
+        <v>-10422.80383822213</v>
       </c>
     </row>
     <row r="85">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>152144703.2</v>
+        <v>150836878.06</v>
       </c>
       <c r="E85" t="n">
         <v>0.6740936305925465</v>
@@ -3400,10 +3400,10 @@
         <v>-1.696070784418247e-05</v>
       </c>
       <c r="H85" t="n">
-        <v>-2580.481861015053</v>
+        <v>-2558.300220904236</v>
       </c>
       <c r="I85" t="n">
-        <v>-2580.481861015053</v>
+        <v>-2558.300220904236</v>
       </c>
     </row>
     <row r="86">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11282921.34</v>
+        <v>12616901.91</v>
       </c>
       <c r="E86" t="n">
         <v>0.5835756277426192</v>
@@ -3435,10 +3435,10 @@
         <v>-1.008678731428958e-06</v>
       </c>
       <c r="H86" t="n">
-        <v>-11.38084278404392</v>
+        <v>-12.7264006131424</v>
       </c>
       <c r="I86" t="n">
-        <v>-11.38084278404392</v>
+        <v>-12.7264006131424</v>
       </c>
     </row>
     <row r="87">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-1357868945.18</v>
+        <v>-1410564079.41</v>
       </c>
       <c r="E87" t="n">
         <v>0.999906031812547</v>
@@ -3470,10 +3470,10 @@
         <v>9.39681874529974e-05</v>
       </c>
       <c r="H87" t="n">
-        <v>-127596.4835772781</v>
+        <v>-132548.1498284636</v>
       </c>
       <c r="I87" t="n">
-        <v>-127596.4835772781</v>
+        <v>-132548.1498284636</v>
       </c>
     </row>
     <row r="88">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-273538406.96</v>
+        <v>-210789268.91</v>
       </c>
       <c r="E88" t="n">
         <v>0.9983821828874917</v>
@@ -3505,10 +3505,10 @@
         <v>0.001387899570778783</v>
       </c>
       <c r="H88" t="n">
-        <v>-379643.8376112962</v>
+        <v>-292554.3358449625</v>
       </c>
       <c r="I88" t="n">
-        <v>-379643.8376112962</v>
+        <v>-292554.3358449625</v>
       </c>
     </row>
     <row r="89">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-391346094.59</v>
+        <v>-466347525.5</v>
       </c>
       <c r="E89" t="n">
         <v>0.9936563817038003</v>
@@ -3540,10 +3540,10 @@
         <v>0.004911064643535079</v>
       </c>
       <c r="H89" t="n">
-        <v>-1921925.968526484</v>
+        <v>-2290262.844083124</v>
       </c>
       <c r="I89" t="n">
-        <v>-1921925.968526484</v>
+        <v>-2290262.844083124</v>
       </c>
     </row>
     <row r="90">
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>-784700756.36</v>
+        <v>-928106565.37</v>
       </c>
       <c r="E90" t="n">
         <v>0.9856536327098718</v>
@@ -3575,10 +3575,10 @@
         <v>0.008895199983645741</v>
       </c>
       <c r="H90" t="n">
-        <v>-6980070.155140272</v>
+        <v>-8255693.505100729</v>
       </c>
       <c r="I90" t="n">
-        <v>-6980070.155140272</v>
+        <v>-8255693.505100729</v>
       </c>
     </row>
     <row r="91">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>106194068.06</v>
+        <v>325613046.1</v>
       </c>
       <c r="E91" t="n">
         <v>0.9761318955535195</v>
@@ -3610,10 +3610,10 @@
         <v>0.01147716903300178</v>
       </c>
       <c r="H91" t="n">
-        <v>1218807.269426715</v>
+        <v>3737115.9694403</v>
       </c>
       <c r="I91" t="n">
-        <v>609403.6347133575</v>
+        <v>1868557.98472015</v>
       </c>
     </row>
     <row r="92">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>327029241.36</v>
+        <v>263741483.93</v>
       </c>
       <c r="E92" t="n">
         <v>0.9667342819189046</v>
@@ -3645,10 +3645,10 @@
         <v>0.01240503278375416</v>
       </c>
       <c r="H92" t="n">
-        <v>4056808.460317051</v>
+        <v>3271721.75458762</v>
       </c>
       <c r="I92" t="n">
-        <v>2028404.230158525</v>
+        <v>1635860.87729381</v>
       </c>
     </row>
     <row r="93">
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>453172829.04</v>
+        <v>589973763.67</v>
       </c>
       <c r="E93" t="n">
         <v>0.9524015829683793</v>
@@ -3680,10 +3680,10 @@
         <v>0.01201262797217995</v>
       </c>
       <c r="H93" t="n">
-        <v>5443796.602357824</v>
+        <v>7087135.336314522</v>
       </c>
       <c r="I93" t="n">
-        <v>2721898.301178912</v>
+        <v>3543567.668157261</v>
       </c>
     </row>
     <row r="94">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>706989755.74</v>
+        <v>612295005.0700001</v>
       </c>
       <c r="E94" t="n">
         <v>0.9333610479054046</v>
@@ -3715,10 +3715,10 @@
         <v>0.009987366679108822</v>
       </c>
       <c r="H94" t="n">
-        <v>7060965.928948961</v>
+        <v>6115214.731420886</v>
       </c>
       <c r="I94" t="n">
-        <v>3530482.964474481</v>
+        <v>3057607.365710443</v>
       </c>
     </row>
     <row r="95">
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>950082301.61</v>
+        <v>773886472.84</v>
       </c>
       <c r="E95" t="n">
         <v>0.9066754799235061</v>
@@ -3750,10 +3750,10 @@
         <v>0.006535572677782708</v>
       </c>
       <c r="H95" t="n">
-        <v>6209331.932047226</v>
+        <v>5057791.287598734</v>
       </c>
       <c r="I95" t="n">
-        <v>3104665.966023613</v>
+        <v>2528895.643799367</v>
       </c>
     </row>
     <row r="96">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1131433784.31</v>
+        <v>752632597.09</v>
       </c>
       <c r="E96" t="n">
         <v>0.8730418834956067</v>
@@ -3785,10 +3785,10 @@
         <v>0.003235551599104936</v>
       </c>
       <c r="H96" t="n">
-        <v>3660812.390105569</v>
+        <v>2435181.60305305</v>
       </c>
       <c r="I96" t="n">
-        <v>1830406.195052784</v>
+        <v>1217590.801526525</v>
       </c>
     </row>
     <row r="97">
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>725856199.14</v>
+        <v>1376408988.27</v>
       </c>
       <c r="E97" t="n">
         <v>0.839886760163754</v>
@@ -3820,10 +3820,10 @@
         <v>0.001470791926687531</v>
       </c>
       <c r="H97" t="n">
-        <v>1067583.437631209</v>
+        <v>2024411.227767669</v>
       </c>
       <c r="I97" t="n">
-        <v>533791.7188156045</v>
+        <v>1012205.613883834</v>
       </c>
     </row>
     <row r="98">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>135257246.09</v>
+        <v>171337663.91</v>
       </c>
       <c r="E98" t="n">
         <v>0.8060794216350962</v>
@@ -3855,10 +3855,10 @@
         <v>0.000634385103338575</v>
       </c>
       <c r="H98" t="n">
-        <v>85805.18203809572</v>
+        <v>108694.0616253354</v>
       </c>
       <c r="I98" t="n">
-        <v>42902.59101904786</v>
+        <v>54347.03081266769</v>
       </c>
     </row>
     <row r="99">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>290934368.76</v>
+        <v>304374885.85</v>
       </c>
       <c r="E99" t="n">
         <v>0.7725125366488534</v>
@@ -3890,10 +3890,10 @@
         <v>0.0002641556154886482</v>
       </c>
       <c r="H99" t="n">
-        <v>76851.94724659914</v>
+        <v>80402.33531099379</v>
       </c>
       <c r="I99" t="n">
-        <v>38425.97362329957</v>
+        <v>40201.16765549689</v>
       </c>
     </row>
     <row r="100">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>293928244.15</v>
+        <v>295856253.29</v>
       </c>
       <c r="E100" t="n">
         <v>0.7390723504327896</v>
@@ -3925,10 +3925,10 @@
         <v>0.0001072133542818765</v>
       </c>
       <c r="H100" t="n">
-        <v>31513.03297350384</v>
+        <v>31719.74130048936</v>
       </c>
       <c r="I100" t="n">
-        <v>15756.51648675192</v>
+        <v>15859.87065024468</v>
       </c>
     </row>
     <row r="101">
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>240687365.15</v>
+        <v>240713355.56</v>
       </c>
       <c r="E101" t="n">
         <v>0.7058360643204235</v>
@@ -3960,10 +3960,10 @@
         <v>4.218442338066453e-05</v>
       </c>
       <c r="H101" t="n">
-        <v>10153.2577138642</v>
+        <v>10154.35410432348</v>
       </c>
       <c r="I101" t="n">
-        <v>5076.6288569321</v>
+        <v>5077.177052161739</v>
       </c>
     </row>
     <row r="102">
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>152144703.2</v>
+        <v>150836878.06</v>
       </c>
       <c r="E102" t="n">
         <v>0.6740936305925465</v>
@@ -3995,10 +3995,10 @@
         <v>1.659944883869446e-05</v>
       </c>
       <c r="H102" t="n">
-        <v>2525.518216846754</v>
+        <v>2503.809040345366</v>
       </c>
       <c r="I102" t="n">
-        <v>1262.759108423377</v>
+        <v>1251.904520172683</v>
       </c>
     </row>
     <row r="103">
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11282921.34</v>
+        <v>12616901.91</v>
       </c>
       <c r="E103" t="n">
         <v>0.5835756277426192</v>
@@ -4030,10 +4030,10 @@
         <v>8.933136881328352e-07</v>
       </c>
       <c r="H103" t="n">
-        <v>10.07918807514807</v>
+        <v>11.27085117803231</v>
       </c>
       <c r="I103" t="n">
-        <v>5.039594037574036</v>
+        <v>5.635425589016156</v>
       </c>
     </row>
     <row r="104">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-1357868945.18</v>
+        <v>-1410564079.41</v>
       </c>
       <c r="E104" t="n">
         <v>0.999906031812547</v>
@@ -4065,10 +4065,10 @@
         <v>6.06503826584559e-05</v>
       </c>
       <c r="H104" t="n">
-        <v>-82355.27112520089</v>
+        <v>-85551.25118048908</v>
       </c>
       <c r="I104" t="n">
-        <v>-82355.27112520089</v>
+        <v>-85551.25118048908</v>
       </c>
     </row>
     <row r="105">
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>-273538406.96</v>
+        <v>-210789268.91</v>
       </c>
       <c r="E105" t="n">
         <v>0.9983821828874917</v>
@@ -4100,10 +4100,10 @@
         <v>0.0004286357166750632</v>
       </c>
       <c r="H105" t="n">
-        <v>-117248.3311054547</v>
+        <v>-90351.80934665047</v>
       </c>
       <c r="I105" t="n">
-        <v>-117248.3311054547</v>
+        <v>-90351.80934665047</v>
       </c>
     </row>
     <row r="106">
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>-391346094.59</v>
+        <v>-466347525.5</v>
       </c>
       <c r="E106" t="n">
         <v>0.9936563817038003</v>
@@ -4135,10 +4135,10 @@
         <v>0.001657282796573178</v>
       </c>
       <c r="H106" t="n">
-        <v>-648571.1500701067</v>
+        <v>-772869.7312356216</v>
       </c>
       <c r="I106" t="n">
-        <v>-648571.1500701067</v>
+        <v>-772869.7312356216</v>
       </c>
     </row>
     <row r="107">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>-784700756.36</v>
+        <v>-928106565.37</v>
       </c>
       <c r="E107" t="n">
         <v>0.9856536327098718</v>
@@ -4170,10 +4170,10 @@
         <v>0.003701791136432875</v>
       </c>
       <c r="H107" t="n">
-        <v>-2904798.304645621</v>
+        <v>-3435656.657351824</v>
       </c>
       <c r="I107" t="n">
-        <v>-2904798.304645621</v>
+        <v>-3435656.657351824</v>
       </c>
     </row>
     <row r="108">
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>106194068.06</v>
+        <v>325613046.1</v>
       </c>
       <c r="E108" t="n">
         <v>0.9761318955535195</v>
@@ -4205,10 +4205,10 @@
         <v>0.00611886473883394</v>
       </c>
       <c r="H108" t="n">
-        <v>649787.1385256656</v>
+        <v>1992382.1862856</v>
       </c>
       <c r="I108" t="n">
-        <v>324893.5692628328</v>
+        <v>996191.0931428</v>
       </c>
     </row>
     <row r="109">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>327029241.36</v>
+        <v>263741483.93</v>
       </c>
       <c r="E109" t="n">
         <v>0.9667342819189046</v>
@@ -4240,10 +4240,10 @@
         <v>0.008494727267819302</v>
       </c>
       <c r="H109" t="n">
-        <v>2778024.213955052</v>
+        <v>2240411.975195298</v>
       </c>
       <c r="I109" t="n">
-        <v>1389012.106977526</v>
+        <v>1120205.987597649</v>
       </c>
     </row>
     <row r="110">
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>453172829.04</v>
+        <v>589973763.67</v>
       </c>
       <c r="E110" t="n">
         <v>0.9524015829683793</v>
@@ -4275,10 +4275,10 @@
         <v>0.01197966122818617</v>
       </c>
       <c r="H110" t="n">
-        <v>5428856.969717926</v>
+        <v>7067685.822284567</v>
       </c>
       <c r="I110" t="n">
-        <v>2714428.484858963</v>
+        <v>3533842.911142284</v>
       </c>
     </row>
     <row r="111">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>706989755.74</v>
+        <v>612295005.0700001</v>
       </c>
       <c r="E111" t="n">
         <v>0.9333610479054046</v>
@@ -4310,10 +4310,10 @@
         <v>0.01647754477361008</v>
       </c>
       <c r="H111" t="n">
-        <v>11649455.3546895</v>
+        <v>10089118.36069873</v>
       </c>
       <c r="I111" t="n">
-        <v>5824727.677344751</v>
+        <v>5044559.180349367</v>
       </c>
     </row>
     <row r="112">
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>950082301.61</v>
+        <v>773886472.84</v>
       </c>
       <c r="E112" t="n">
         <v>0.9066754799235061</v>
@@ -4345,10 +4345,10 @@
         <v>0.02295203256100853</v>
       </c>
       <c r="H112" t="n">
-        <v>21806319.92219065</v>
+        <v>17762267.52314772</v>
       </c>
       <c r="I112" t="n">
-        <v>10903159.96109532</v>
+        <v>8881133.761573862</v>
       </c>
     </row>
     <row r="113">
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1131433784.31</v>
+        <v>752632597.09</v>
       </c>
       <c r="E113" t="n">
         <v>0.8730418834956067</v>
@@ -4380,10 +4380,10 @@
         <v>0.03109727088065561</v>
       </c>
       <c r="H113" t="n">
-        <v>35184502.87421335</v>
+        <v>23404819.74531907</v>
       </c>
       <c r="I113" t="n">
-        <v>17592251.43710667</v>
+        <v>11702409.87265953</v>
       </c>
     </row>
     <row r="114">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>725856199.14</v>
+        <v>1376408988.27</v>
       </c>
       <c r="E114" t="n">
         <v>0.839886760163754</v>
@@ -4415,10 +4415,10 @@
         <v>0.0386581374619398</v>
       </c>
       <c r="H114" t="n">
-        <v>28060248.72395527</v>
+        <v>53209407.87239115</v>
       </c>
       <c r="I114" t="n">
-        <v>14030124.36197763</v>
+        <v>26604703.93619557</v>
       </c>
     </row>
     <row r="115">
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>135257246.09</v>
+        <v>171337663.91</v>
       </c>
       <c r="E115" t="n">
         <v>0.8060794216350962</v>
@@ -4450,10 +4450,10 @@
         <v>0.04557620122769612</v>
       </c>
       <c r="H115" t="n">
-        <v>6164511.465301855</v>
+        <v>7808919.848245528</v>
       </c>
       <c r="I115" t="n">
-        <v>3082255.732650927</v>
+        <v>3904459.924122764</v>
       </c>
     </row>
     <row r="116">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>290934368.76</v>
+        <v>304374885.85</v>
       </c>
       <c r="E116" t="n">
         <v>0.7725125366488534</v>
@@ -4485,10 +4485,10 @@
         <v>0.05188104408575822</v>
       </c>
       <c r="H116" t="n">
-        <v>15093978.8116998</v>
+        <v>15791286.87138148</v>
       </c>
       <c r="I116" t="n">
-        <v>7546989.405849899</v>
+        <v>7895643.435690738</v>
       </c>
     </row>
     <row r="117">
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>293928244.15</v>
+        <v>295856253.29</v>
       </c>
       <c r="E117" t="n">
         <v>0.7390723504327896</v>
@@ -4520,10 +4520,10 @@
         <v>0.05756191118833565</v>
       </c>
       <c r="H117" t="n">
-        <v>16919071.48550573</v>
+        <v>17030051.37639272</v>
       </c>
       <c r="I117" t="n">
-        <v>8459535.742752867</v>
+        <v>8515025.688196359</v>
       </c>
     </row>
     <row r="118">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>240687365.15</v>
+        <v>240713355.56</v>
       </c>
       <c r="E118" t="n">
         <v>0.7058360643204235</v>
@@ -4555,10 +4555,10 @@
         <v>0.06261909581715475</v>
       </c>
       <c r="H118" t="n">
-        <v>15071625.18030636</v>
+        <v>15073252.67628048</v>
       </c>
       <c r="I118" t="n">
-        <v>7535812.590153181</v>
+        <v>7536626.33814024</v>
       </c>
     </row>
     <row r="119">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>152144703.2</v>
+        <v>150836878.06</v>
       </c>
       <c r="E119" t="n">
         <v>0.6740936305925465</v>
@@ -4590,10 +4590,10 @@
         <v>0.06717920059908133</v>
       </c>
       <c r="H119" t="n">
-        <v>10220959.53636049</v>
+        <v>10133100.88893191</v>
       </c>
       <c r="I119" t="n">
-        <v>5110479.768180246</v>
+        <v>5066550.444465955</v>
       </c>
     </row>
     <row r="120">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11282921.34</v>
+        <v>12616901.91</v>
       </c>
       <c r="E120" t="n">
         <v>0.5835756277426192</v>
@@ -4625,10 +4625,10 @@
         <v>0.07770212208989746</v>
       </c>
       <c r="H120" t="n">
-        <v>876706.9314913895</v>
+        <v>980360.0526070805</v>
       </c>
       <c r="I120" t="n">
-        <v>438353.4657456948</v>
+        <v>490180.0263035403</v>
       </c>
     </row>
   </sheetData>
@@ -4704,22 +4704,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="D2" t="n">
-        <v>1899204219.51</v>
+        <v>1973036350.02</v>
       </c>
       <c r="E2" t="n">
-        <v>-109259092.9100001</v>
+        <v>-121961996.8800001</v>
       </c>
       <c r="F2" t="n">
-        <v>-109259092.9100001</v>
+        <v>-121961996.8800001</v>
       </c>
       <c r="G2" t="n">
-        <v>-9.104924409166674</v>
+        <v>-10.16349974000001</v>
       </c>
       <c r="H2" t="n">
-        <v>-9.104924409166674</v>
+        <v>-10.16349974000001</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -4737,22 +4737,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="D3" t="n">
-        <v>2128346249.82</v>
+        <v>2229316540.08</v>
       </c>
       <c r="E3" t="n">
-        <v>119882937.3999999</v>
+        <v>134318193.1799998</v>
       </c>
       <c r="F3" t="n">
-        <v>59941468.69999993</v>
+        <v>67159096.58999991</v>
       </c>
       <c r="G3" t="n">
-        <v>9.990244783333321</v>
+        <v>11.19318276499999</v>
       </c>
       <c r="H3" t="n">
-        <v>4.99512239166666</v>
+        <v>5.596591382499993</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -4770,22 +4770,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="D4" t="n">
-        <v>1969035458.72</v>
+        <v>2049526125.86</v>
       </c>
       <c r="E4" t="n">
-        <v>-39427853.70000005</v>
+        <v>-45472221.0400002</v>
       </c>
       <c r="F4" t="n">
-        <v>-39427853.70000005</v>
+        <v>-45472221.0400002</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.285654475000004</v>
+        <v>-3.78935175333335</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.285654475000004</v>
+        <v>-3.78935175333335</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -4803,22 +4803,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="D5" t="n">
-        <v>2038240148.16</v>
+        <v>2129901580.06</v>
       </c>
       <c r="E5" t="n">
-        <v>29776835.74000001</v>
+        <v>34903233.15999985</v>
       </c>
       <c r="F5" t="n">
-        <v>14888417.87</v>
+        <v>17451616.57999992</v>
       </c>
       <c r="G5" t="n">
-        <v>2.481402978333334</v>
+        <v>2.908602763333321</v>
       </c>
       <c r="H5" t="n">
-        <v>1.240701489166667</v>
+        <v>1.45430138166666</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -4836,22 +4836,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="D6" t="n">
-        <v>1988438779.55</v>
+        <v>2073987061.46</v>
       </c>
       <c r="E6" t="n">
-        <v>-20024532.87000012</v>
+        <v>-21011285.44000006</v>
       </c>
       <c r="F6" t="n">
-        <v>-20024532.87000012</v>
+        <v>-21011285.44000006</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.66871107250001</v>
+        <v>-1.750940453333338</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.66871107250001</v>
+        <v>-1.750940453333338</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -4869,22 +4869,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="D7" t="n">
-        <v>2028925382.35</v>
+        <v>2116476598.37</v>
       </c>
       <c r="E7" t="n">
-        <v>20462069.92999983</v>
+        <v>21478251.46999979</v>
       </c>
       <c r="F7" t="n">
-        <v>10231034.96499991</v>
+        <v>10739125.7349999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.705172494166652</v>
+        <v>1.789854289166649</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8525862470833262</v>
+        <v>0.8949271445833246</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -4902,22 +4902,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="D8" t="n">
-        <v>2055152460</v>
+        <v>2147240980.85</v>
       </c>
       <c r="E8" t="n">
-        <v>46689147.57999992</v>
+        <v>52242633.94999981</v>
       </c>
       <c r="F8" t="n">
-        <v>23344573.78999996</v>
+        <v>26121316.9749999</v>
       </c>
       <c r="G8" t="n">
-        <v>3.890762298333327</v>
+        <v>4.353552829166651</v>
       </c>
       <c r="H8" t="n">
-        <v>1.945381149166663</v>
+        <v>2.176776414583325</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -5047,19 +5047,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G2" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="J2" t="n">
-        <v>-680000000</v>
+        <v>-620000000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="L2" t="n">
         <v>0.03432749872940843</v>
@@ -5071,10 +5071,10 @@
         <v>0.02500481880599148</v>
       </c>
       <c r="O2" t="n">
-        <v>-32421705.62942012</v>
+        <v>-33619463.21620177</v>
       </c>
       <c r="P2" t="n">
-        <v>-32421705.62942012</v>
+        <v>-33619463.21620177</v>
       </c>
     </row>
     <row r="3">
@@ -5105,19 +5105,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G3" t="n">
-        <v>912642221.4799999</v>
+        <v>974764849.6000001</v>
       </c>
       <c r="H3" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I3" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="J3" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K3" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="L3" t="n">
         <v>0.03782665436246635</v>
@@ -5129,10 +5129,10 @@
         <v>0.0251058158502353</v>
       </c>
       <c r="O3" t="n">
-        <v>18942533.70806487</v>
+        <v>20372203.03130213</v>
       </c>
       <c r="P3" t="n">
-        <v>9471266.854032435</v>
+        <v>10186101.51565107</v>
       </c>
     </row>
     <row r="4">
@@ -5163,19 +5163,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>879884659.5500001</v>
+        <v>871985042.7</v>
       </c>
       <c r="H4" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I4" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="L4" t="n">
         <v>0.03830470017405307</v>
@@ -5187,10 +5187,10 @@
         <v>0.02521323244800655</v>
       </c>
       <c r="O4" t="n">
-        <v>17417088.89240956</v>
+        <v>17251109.82916852</v>
       </c>
       <c r="P4" t="n">
-        <v>8708544.446204778</v>
+        <v>8625554.914584262</v>
       </c>
     </row>
     <row r="5">
@@ -5221,19 +5221,19 @@
         <v>0.75</v>
       </c>
       <c r="G5" t="n">
-        <v>1240710907.89</v>
+        <v>1005206416.05</v>
       </c>
       <c r="H5" t="n">
-        <v>-91346794.52054794</v>
+        <v>-130312887.6712329</v>
       </c>
       <c r="I5" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="J5" t="n">
-        <v>-136000000</v>
+        <v>-124000000</v>
       </c>
       <c r="K5" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="L5" t="n">
         <v>0.03852218097221538</v>
@@ -5245,10 +5245,10 @@
         <v>0.02532026333962101</v>
       </c>
       <c r="O5" t="n">
-        <v>21826651.5177184</v>
+        <v>16614400.89951043</v>
       </c>
       <c r="P5" t="n">
-        <v>10913325.7588592</v>
+        <v>8307200.449755214</v>
       </c>
     </row>
     <row r="6">
@@ -5279,19 +5279,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>-201932841.91</v>
+        <v>-243337598.87</v>
       </c>
       <c r="H6" t="n">
-        <v>-50972657.53424658</v>
+        <v>-89950783.56164384</v>
       </c>
       <c r="I6" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="J6" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K6" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="L6" t="n">
         <v>0.03873510939427094</v>
@@ -5303,10 +5303,10 @@
         <v>0.02542872476626745</v>
       </c>
       <c r="O6" t="n">
-        <v>-4287376.224828769</v>
+        <v>-5650065.696432507</v>
       </c>
       <c r="P6" t="n">
-        <v>-4287376.224828769</v>
+        <v>-5650065.696432507</v>
       </c>
     </row>
     <row r="7">
@@ -5337,19 +5337,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>-196825268.73</v>
+        <v>-241428019.53</v>
       </c>
       <c r="H7" t="n">
-        <v>-50988356.16438356</v>
+        <v>-89973452.05479452</v>
       </c>
       <c r="I7" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="J7" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K7" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="L7" t="n">
         <v>0.03888939094511485</v>
@@ -5361,10 +5361,10 @@
         <v>0.02553821260711615</v>
       </c>
       <c r="O7" t="n">
-        <v>-3691751.606370857</v>
+        <v>-4936984.056458791</v>
       </c>
       <c r="P7" t="n">
-        <v>-3691751.606370857</v>
+        <v>-4936984.056458791</v>
       </c>
     </row>
     <row r="8">
@@ -5395,19 +5395,19 @@
         <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>69886647.3499999</v>
+        <v>149216557.22</v>
       </c>
       <c r="H8" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I8" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="J8" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K8" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="L8" t="n">
         <v>0.03901400018340251</v>
@@ -5419,10 +5419,10 @@
         <v>0.02564775160277089</v>
       </c>
       <c r="O8" t="n">
-        <v>-257528.5720346234</v>
+        <v>759788.3394733594</v>
       </c>
       <c r="P8" t="n">
-        <v>-257528.5720346234</v>
+        <v>379894.1697366797</v>
       </c>
     </row>
     <row r="9">
@@ -5453,19 +5453,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G9" t="n">
-        <v>-81388394.01999998</v>
+        <v>116432754.21</v>
       </c>
       <c r="H9" t="n">
         <v>2250000</v>
       </c>
       <c r="I9" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="J9" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K9" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="L9" t="n">
         <v>0.03908855826627113</v>
@@ -5477,10 +5477,10 @@
         <v>0.02575828679253624</v>
       </c>
       <c r="O9" t="n">
-        <v>-849362.2706116225</v>
+        <v>1273776.841778861</v>
       </c>
       <c r="P9" t="n">
-        <v>-849362.2706116225</v>
+        <v>636888.4208894307</v>
       </c>
     </row>
     <row r="10">
@@ -5511,19 +5511,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G10" t="n">
-        <v>-24300588.46000001</v>
+        <v>-21021772.08000001</v>
       </c>
       <c r="H10" t="n">
         <v>2250000</v>
       </c>
       <c r="I10" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K10" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="L10" t="n">
         <v>0.03915884386251234</v>
@@ -5535,10 +5535,10 @@
         <v>0.02586772256944581</v>
       </c>
       <c r="O10" t="n">
-        <v>-190132.8349254345</v>
+        <v>-161860.997434103</v>
       </c>
       <c r="P10" t="n">
-        <v>-190132.8349254345</v>
+        <v>-161860.997434103</v>
       </c>
     </row>
     <row r="11">
@@ -5569,19 +5569,19 @@
         <v>0.25</v>
       </c>
       <c r="G11" t="n">
-        <v>-25229792.01000001</v>
+        <v>-19025601.68</v>
       </c>
       <c r="H11" t="n">
         <v>2250000</v>
       </c>
       <c r="I11" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="J11" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K11" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="L11" t="n">
         <v>0.03922681220647117</v>
@@ -5593,10 +5593,10 @@
         <v>0.02597850453979926</v>
       </c>
       <c r="O11" t="n">
-        <v>-149245.157763857</v>
+        <v>-108951.261100436</v>
       </c>
       <c r="P11" t="n">
-        <v>-149245.157763857</v>
+        <v>-108951.261100436</v>
       </c>
     </row>
     <row r="12">
@@ -5627,19 +5627,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G12" t="n">
-        <v>43083900.58</v>
+        <v>101044465.29</v>
       </c>
       <c r="H12" t="n">
         <v>2250000</v>
       </c>
       <c r="I12" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="J12" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K12" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="L12" t="n">
         <v>0.03929424848359133</v>
@@ -5651,10 +5651,10 @@
         <v>0.02608953222428303</v>
       </c>
       <c r="O12" t="n">
-        <v>197123.3766723921</v>
+        <v>449150.7134622567</v>
       </c>
       <c r="P12" t="n">
-        <v>98561.68833619606</v>
+        <v>224575.3567311283</v>
       </c>
     </row>
     <row r="13">
@@ -5685,19 +5685,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G13" t="n">
-        <v>32635075.89</v>
+        <v>34292018.08</v>
       </c>
       <c r="H13" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I13" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="L13" t="n">
         <v>0.03936107056455495</v>
@@ -5709,10 +5709,10 @@
         <v>0.02620112954634799</v>
       </c>
       <c r="O13" t="n">
-        <v>76195.95168771796</v>
+        <v>79813.76476863457</v>
       </c>
       <c r="P13" t="n">
-        <v>38097.97584385898</v>
+        <v>39906.88238431729</v>
       </c>
     </row>
     <row r="14">
@@ -5743,19 +5743,19 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-85065078.76000001</v>
+        <v>-76962502.42</v>
       </c>
       <c r="H14" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I14" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="J14" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K14" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="L14" t="n">
         <v>0.03942868733737526</v>
@@ -5801,19 +5801,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G15" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="J15" t="n">
-        <v>-680000000</v>
+        <v>-620000000</v>
       </c>
       <c r="K15" t="n">
-        <v>-620180437.28</v>
+        <v>-728213104.0599999</v>
       </c>
       <c r="L15" t="n">
         <v>0.03432749872940843</v>
@@ -5825,10 +5825,10 @@
         <v>-0.02499999878494696</v>
       </c>
       <c r="O15" t="n">
-        <v>15462032.06836994</v>
+        <v>18155449.10923949</v>
       </c>
       <c r="P15" t="n">
-        <v>7731016.034184968</v>
+        <v>9077724.554619746</v>
       </c>
     </row>
     <row r="16">
@@ -5859,19 +5859,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G16" t="n">
-        <v>912642221.4799999</v>
+        <v>974764849.6000001</v>
       </c>
       <c r="H16" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I16" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="J16" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K16" t="n">
-        <v>891099410.5210958</v>
+        <v>947222038.641096</v>
       </c>
       <c r="L16" t="n">
         <v>0.03782665436246635</v>
@@ -5883,10 +5883,10 @@
         <v>-0.02505175249492542</v>
       </c>
       <c r="O16" t="n">
-        <v>-20463301.72401939</v>
+        <v>-21752107.73062747</v>
       </c>
       <c r="P16" t="n">
-        <v>-20463301.72401939</v>
+        <v>-21752107.73062747</v>
       </c>
     </row>
     <row r="17">
@@ -5917,19 +5917,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G17" t="n">
-        <v>879884659.5500001</v>
+        <v>871985042.7</v>
       </c>
       <c r="H17" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I17" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="L17" t="n">
         <v>0.03830470017405307</v>
@@ -5941,10 +5941,10 @@
         <v>-0.02510607109988339</v>
       </c>
       <c r="O17" t="n">
-        <v>-17343062.73452042</v>
+        <v>-17177789.11593881</v>
       </c>
       <c r="P17" t="n">
-        <v>-17343062.73452042</v>
+        <v>-17177789.11593881</v>
       </c>
     </row>
     <row r="18">
@@ -5975,19 +5975,19 @@
         <v>0.75</v>
       </c>
       <c r="G18" t="n">
-        <v>1240710907.89</v>
+        <v>1005206416.05</v>
       </c>
       <c r="H18" t="n">
-        <v>-91346794.52054794</v>
+        <v>-130312887.6712329</v>
       </c>
       <c r="I18" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="J18" t="n">
-        <v>-136000000</v>
+        <v>-124000000</v>
       </c>
       <c r="K18" t="n">
-        <v>1285364113.369452</v>
+        <v>998893528.3787673</v>
       </c>
       <c r="L18" t="n">
         <v>0.03852218097221538</v>
@@ -5999,10 +5999,10 @@
         <v>-0.02516160099667442</v>
       </c>
       <c r="O18" t="n">
-        <v>-24256364.21703475</v>
+        <v>-18850320.29942011</v>
       </c>
       <c r="P18" t="n">
-        <v>-24256364.21703475</v>
+        <v>-18850320.29942011</v>
       </c>
     </row>
     <row r="19">
@@ -6033,19 +6033,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>-201932841.91</v>
+        <v>-243337598.87</v>
       </c>
       <c r="H19" t="n">
-        <v>-50972657.53424658</v>
+        <v>-89950783.56164384</v>
       </c>
       <c r="I19" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="J19" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K19" t="n">
-        <v>-184905499.4442466</v>
+        <v>-271288382.4316438</v>
       </c>
       <c r="L19" t="n">
         <v>0.03873510939427094</v>
@@ -6057,10 +6057,10 @@
         <v>-0.02521743137943178</v>
       </c>
       <c r="O19" t="n">
-        <v>3108561.1626099</v>
+        <v>4560797.445338016</v>
       </c>
       <c r="P19" t="n">
-        <v>1554280.58130495</v>
+        <v>2280398.722669008</v>
       </c>
     </row>
     <row r="20">
@@ -6091,19 +6091,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>-196825268.73</v>
+        <v>-241428019.53</v>
       </c>
       <c r="H20" t="n">
-        <v>-50988356.16438356</v>
+        <v>-89973452.05479452</v>
       </c>
       <c r="I20" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="J20" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K20" t="n">
-        <v>-179813624.8943836</v>
+        <v>-269401471.5847945</v>
       </c>
       <c r="L20" t="n">
         <v>0.03888939094511485</v>
@@ -6115,10 +6115,10 @@
         <v>-0.02527289166469284</v>
       </c>
       <c r="O20" t="n">
-        <v>2650905.986045025</v>
+        <v>3971656.619974947</v>
       </c>
       <c r="P20" t="n">
-        <v>1325452.993022513</v>
+        <v>1985828.309987474</v>
       </c>
     </row>
     <row r="21">
@@ -6149,19 +6149,19 @@
         <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>69886647.3499999</v>
+        <v>149216557.22</v>
       </c>
       <c r="H21" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I21" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="J21" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K21" t="n">
-        <v>13918039.13082182</v>
+        <v>90247949.00082195</v>
       </c>
       <c r="L21" t="n">
         <v>0.03901400018340251</v>
@@ -6173,10 +6173,10 @@
         <v>-0.02532890719506886</v>
       </c>
       <c r="O21" t="n">
-        <v>-176264.3607409614</v>
+        <v>-1142940.962393563</v>
       </c>
       <c r="P21" t="n">
-        <v>-176264.3607409614</v>
+        <v>-1142940.962393563</v>
       </c>
     </row>
     <row r="22">
@@ -6207,19 +6207,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G22" t="n">
-        <v>-81388394.01999998</v>
+        <v>116432754.21</v>
       </c>
       <c r="H22" t="n">
         <v>2250000</v>
       </c>
       <c r="I22" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="J22" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K22" t="n">
-        <v>-45138394.01999998</v>
+        <v>149682754.21</v>
       </c>
       <c r="L22" t="n">
         <v>0.03908855826627113</v>
@@ -6231,10 +6231,10 @@
         <v>-0.02538363335203554</v>
       </c>
       <c r="O22" t="n">
-        <v>477406.8516264138</v>
+        <v>-1583121.729995623</v>
       </c>
       <c r="P22" t="n">
-        <v>238703.4258132069</v>
+        <v>-1583121.729995623</v>
       </c>
     </row>
     <row r="23">
@@ -6265,19 +6265,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>-24300588.46000001</v>
+        <v>-21021772.08000001</v>
       </c>
       <c r="H23" t="n">
         <v>2250000</v>
       </c>
       <c r="I23" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K23" t="n">
-        <v>11949411.53999999</v>
+        <v>12228227.91999999</v>
       </c>
       <c r="L23" t="n">
         <v>0.03915884386251234</v>
@@ -6289,10 +6289,10 @@
         <v>-0.02543993459508764</v>
       </c>
       <c r="O23" t="n">
-        <v>-101330.7493424618</v>
+        <v>-103695.1061662082</v>
       </c>
       <c r="P23" t="n">
-        <v>-101330.7493424618</v>
+        <v>-103695.1061662082</v>
       </c>
     </row>
     <row r="24">
@@ -6323,19 +6323,19 @@
         <v>0.25</v>
       </c>
       <c r="G24" t="n">
-        <v>-25229792.01000001</v>
+        <v>-19025601.68</v>
       </c>
       <c r="H24" t="n">
         <v>2250000</v>
       </c>
       <c r="I24" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="J24" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K24" t="n">
-        <v>11020207.98999999</v>
+        <v>14224398.32</v>
       </c>
       <c r="L24" t="n">
         <v>0.03922681220647117</v>
@@ -6347,10 +6347,10 @@
         <v>-0.02549552338669633</v>
       </c>
       <c r="O24" t="n">
-        <v>-70241.49263382565</v>
+        <v>-90664.62000731099</v>
       </c>
       <c r="P24" t="n">
-        <v>-70241.49263382565</v>
+        <v>-90664.62000731099</v>
       </c>
     </row>
     <row r="25">
@@ -6381,19 +6381,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G25" t="n">
-        <v>43083900.58</v>
+        <v>101044465.29</v>
       </c>
       <c r="H25" t="n">
         <v>2250000</v>
       </c>
       <c r="I25" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="J25" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K25" t="n">
-        <v>79333900.58</v>
+        <v>134294465.29</v>
       </c>
       <c r="L25" t="n">
         <v>0.03929424848359133</v>
@@ -6405,10 +6405,10 @@
         <v>-0.02555147156878314</v>
       </c>
       <c r="O25" t="n">
-        <v>-337849.6508517564</v>
+        <v>-571903.5352837283</v>
       </c>
       <c r="P25" t="n">
-        <v>-337849.6508517564</v>
+        <v>-571903.5352837283</v>
       </c>
     </row>
     <row r="26">
@@ -6439,19 +6439,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G26" t="n">
-        <v>32635075.89</v>
+        <v>34292018.08</v>
       </c>
       <c r="H26" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I26" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="L26" t="n">
         <v>0.03936107056455495</v>
@@ -6463,10 +6463,10 @@
         <v>-0.02560744979333988</v>
       </c>
       <c r="O26" t="n">
-        <v>-74469.46147292921</v>
+        <v>-78005.30013467018</v>
       </c>
       <c r="P26" t="n">
-        <v>-74469.46147292921</v>
+        <v>-78005.30013467018</v>
       </c>
     </row>
     <row r="27">
@@ -6497,19 +6497,19 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-85065078.76000001</v>
+        <v>-76962502.42</v>
       </c>
       <c r="H27" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I27" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="J27" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K27" t="n">
-        <v>-13020010.26684932</v>
+        <v>-10917433.92684932</v>
       </c>
       <c r="L27" t="n">
         <v>0.03942868733737526</v>
@@ -6555,19 +6555,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G28" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="J28" t="n">
-        <v>-680000000</v>
+        <v>-620000000</v>
       </c>
       <c r="K28" t="n">
-        <v>-620180437.28</v>
+        <v>-728213104.0599999</v>
       </c>
       <c r="L28" t="n">
         <v>0.03432749872940843</v>
@@ -6579,10 +6579,10 @@
         <v>-0.02264935222023312</v>
       </c>
       <c r="O28" t="n">
-        <v>14008201.0951103</v>
+        <v>16448367.26309286</v>
       </c>
       <c r="P28" t="n">
-        <v>7004100.547555152</v>
+        <v>8224183.631546429</v>
       </c>
     </row>
     <row r="29">
@@ -6613,19 +6613,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G29" t="n">
-        <v>912642221.4799999</v>
+        <v>974764849.6000001</v>
       </c>
       <c r="H29" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I29" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="J29" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K29" t="n">
-        <v>891099410.5210958</v>
+        <v>947222038.641096</v>
       </c>
       <c r="L29" t="n">
         <v>0.03782665436246635</v>
@@ -6637,10 +6637,10 @@
         <v>-0.01985875398907044</v>
       </c>
       <c r="O29" t="n">
-        <v>-16221446.97556545</v>
+        <v>-17243095.31853269</v>
       </c>
       <c r="P29" t="n">
-        <v>-16221446.97556545</v>
+        <v>-17243095.31853269</v>
       </c>
     </row>
     <row r="30">
@@ -6671,19 +6671,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G30" t="n">
-        <v>879884659.5500001</v>
+        <v>871985042.7</v>
       </c>
       <c r="H30" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I30" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="L30" t="n">
         <v>0.03830470017405307</v>
@@ -6695,10 +6695,10 @@
         <v>-0.01722276407024426</v>
       </c>
       <c r="O30" t="n">
-        <v>-11897340.54937325</v>
+        <v>-11783962.85166252</v>
       </c>
       <c r="P30" t="n">
-        <v>-11897340.54937325</v>
+        <v>-11783962.85166252</v>
       </c>
     </row>
     <row r="31">
@@ -6729,19 +6729,19 @@
         <v>0.75</v>
       </c>
       <c r="G31" t="n">
-        <v>1240710907.89</v>
+        <v>1005206416.05</v>
       </c>
       <c r="H31" t="n">
-        <v>-91346794.52054794</v>
+        <v>-130312887.6712329</v>
       </c>
       <c r="I31" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="J31" t="n">
-        <v>-136000000</v>
+        <v>-124000000</v>
       </c>
       <c r="K31" t="n">
-        <v>1285364113.369452</v>
+        <v>998893528.3787673</v>
       </c>
       <c r="L31" t="n">
         <v>0.03852218097221538</v>
@@ -6753,10 +6753,10 @@
         <v>-0.01482995615663363</v>
       </c>
       <c r="O31" t="n">
-        <v>-14296420.08493442</v>
+        <v>-11110160.42325164</v>
       </c>
       <c r="P31" t="n">
-        <v>-14296420.08493442</v>
+        <v>-11110160.42325164</v>
       </c>
     </row>
     <row r="32">
@@ -6787,19 +6787,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G32" t="n">
-        <v>-201932841.91</v>
+        <v>-243337598.87</v>
       </c>
       <c r="H32" t="n">
-        <v>-50972657.53424658</v>
+        <v>-89950783.56164384</v>
       </c>
       <c r="I32" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="J32" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K32" t="n">
-        <v>-184905499.4442466</v>
+        <v>-271288382.4316438</v>
       </c>
       <c r="L32" t="n">
         <v>0.03873510939427094</v>
@@ -6811,10 +6811,10 @@
         <v>-0.01260515871784285</v>
       </c>
       <c r="O32" t="n">
-        <v>1553842.112197821</v>
+        <v>2279755.412571813</v>
       </c>
       <c r="P32" t="n">
-        <v>776921.0560989103</v>
+        <v>1139877.706285907</v>
       </c>
     </row>
     <row r="33">
@@ -6845,19 +6845,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G33" t="n">
-        <v>-196825268.73</v>
+        <v>-241428019.53</v>
       </c>
       <c r="H33" t="n">
-        <v>-50988356.16438356</v>
+        <v>-89973452.05479452</v>
       </c>
       <c r="I33" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="J33" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K33" t="n">
-        <v>-179813624.8943836</v>
+        <v>-269401471.5847945</v>
       </c>
       <c r="L33" t="n">
         <v>0.03888939094511485</v>
@@ -6869,10 +6869,10 @@
         <v>-0.01053392699102673</v>
       </c>
       <c r="O33" t="n">
-        <v>1104917.09803376</v>
+        <v>1655415.669220475</v>
       </c>
       <c r="P33" t="n">
-        <v>552458.54901688</v>
+        <v>827707.8346102377</v>
       </c>
     </row>
     <row r="34">
@@ -6903,19 +6903,19 @@
         <v>0.5</v>
       </c>
       <c r="G34" t="n">
-        <v>69886647.3499999</v>
+        <v>149216557.22</v>
       </c>
       <c r="H34" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I34" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="J34" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K34" t="n">
-        <v>13918039.13082182</v>
+        <v>90247949.00082195</v>
       </c>
       <c r="L34" t="n">
         <v>0.03901400018340251</v>
@@ -6927,10 +6927,10 @@
         <v>-0.008630921630449429</v>
       </c>
       <c r="O34" t="n">
-        <v>-60062.75249382582</v>
+        <v>-389461.4875674455</v>
       </c>
       <c r="P34" t="n">
-        <v>-60062.75249382582</v>
+        <v>-389461.4875674455</v>
       </c>
     </row>
     <row r="35">
@@ -6961,19 +6961,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G35" t="n">
-        <v>-81388394.01999998</v>
+        <v>116432754.21</v>
       </c>
       <c r="H35" t="n">
         <v>2250000</v>
       </c>
       <c r="I35" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="J35" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K35" t="n">
-        <v>-45138394.01999998</v>
+        <v>149682754.21</v>
       </c>
       <c r="L35" t="n">
         <v>0.03908855826627113</v>
@@ -6985,10 +6985,10 @@
         <v>-0.006850555280960409</v>
       </c>
       <c r="O35" t="n">
-        <v>128842.9431365761</v>
+        <v>-427254.1593008393</v>
       </c>
       <c r="P35" t="n">
-        <v>64421.47156828804</v>
+        <v>-427254.1593008393</v>
       </c>
     </row>
     <row r="36">
@@ -7019,19 +7019,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G36" t="n">
-        <v>-24300588.46000001</v>
+        <v>-21021772.08000001</v>
       </c>
       <c r="H36" t="n">
         <v>2250000</v>
       </c>
       <c r="I36" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="J36" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K36" t="n">
-        <v>11949411.53999999</v>
+        <v>12228227.91999999</v>
       </c>
       <c r="L36" t="n">
         <v>0.03915884386251234</v>
@@ -7043,10 +7043,10 @@
         <v>-0.005233721067838482</v>
       </c>
       <c r="O36" t="n">
-        <v>-20846.62897505674</v>
+        <v>-21333.04469574491</v>
       </c>
       <c r="P36" t="n">
-        <v>-20846.62897505674</v>
+        <v>-21333.04469574491</v>
       </c>
     </row>
     <row r="37">
@@ -7077,19 +7077,19 @@
         <v>0.25</v>
       </c>
       <c r="G37" t="n">
-        <v>-25229792.01000001</v>
+        <v>-19025601.68</v>
       </c>
       <c r="H37" t="n">
         <v>2250000</v>
       </c>
       <c r="I37" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="J37" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K37" t="n">
-        <v>11020207.98999999</v>
+        <v>14224398.32</v>
       </c>
       <c r="L37" t="n">
         <v>0.03922681220647117</v>
@@ -7101,10 +7101,10 @@
         <v>-0.003721650822949542</v>
       </c>
       <c r="O37" t="n">
-        <v>-10253.34153376465</v>
+        <v>-13234.56092839752</v>
       </c>
       <c r="P37" t="n">
-        <v>-10253.34153376465</v>
+        <v>-13234.56092839752</v>
       </c>
     </row>
     <row r="38">
@@ -7135,19 +7135,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G38" t="n">
-        <v>43083900.58</v>
+        <v>101044465.29</v>
       </c>
       <c r="H38" t="n">
         <v>2250000</v>
       </c>
       <c r="I38" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="J38" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K38" t="n">
-        <v>79333900.58</v>
+        <v>134294465.29</v>
       </c>
       <c r="L38" t="n">
         <v>0.03929424848359133</v>
@@ -7159,10 +7159,10 @@
         <v>-0.002324803196355599</v>
       </c>
       <c r="O38" t="n">
-        <v>-30739.28427462354</v>
+        <v>-52034.700359843</v>
       </c>
       <c r="P38" t="n">
-        <v>-30739.28427462354</v>
+        <v>-52034.700359843</v>
       </c>
     </row>
     <row r="39">
@@ -7193,19 +7193,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G39" t="n">
-        <v>32635075.89</v>
+        <v>34292018.08</v>
       </c>
       <c r="H39" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I39" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="L39" t="n">
         <v>0.03936107056455495</v>
@@ -7217,10 +7217,10 @@
         <v>-0.001029519969532107</v>
       </c>
       <c r="O39" t="n">
-        <v>-2993.964581612599</v>
+        <v>-3136.119171026371</v>
       </c>
       <c r="P39" t="n">
-        <v>-2993.964581612599</v>
+        <v>-3136.119171026371</v>
       </c>
     </row>
     <row r="40">
@@ -7251,19 +7251,19 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-85065078.76000001</v>
+        <v>-76962502.42</v>
       </c>
       <c r="H40" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I40" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="J40" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K40" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="L40" t="n">
         <v>0.03942868733737526</v>
@@ -7309,19 +7309,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G41" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="J41" t="n">
-        <v>-680000000</v>
+        <v>-620000000</v>
       </c>
       <c r="K41" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="L41" t="n">
         <v>0.03432749872940843</v>
@@ -7333,10 +7333,10 @@
         <v>0.02789279458488503</v>
       </c>
       <c r="O41" t="n">
-        <v>-36166307.87167858</v>
+        <v>-37502402.5896528</v>
       </c>
       <c r="P41" t="n">
-        <v>-36166307.87167858</v>
+        <v>-37502402.5896528</v>
       </c>
     </row>
     <row r="42">
@@ -7367,19 +7367,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G42" t="n">
-        <v>912642221.4799999</v>
+        <v>974764849.6000001</v>
       </c>
       <c r="H42" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I42" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="J42" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K42" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="L42" t="n">
         <v>0.03782665436246635</v>
@@ -7391,10 +7391,10 @@
         <v>0.02492545821291703</v>
       </c>
       <c r="O42" t="n">
-        <v>18806452.46518519</v>
+        <v>20225851.18886004</v>
       </c>
       <c r="P42" t="n">
-        <v>9403226.232592596</v>
+        <v>10112925.59443002</v>
       </c>
     </row>
     <row r="43">
@@ -7425,19 +7425,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G43" t="n">
-        <v>879884659.5500001</v>
+        <v>871985042.7</v>
       </c>
       <c r="H43" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I43" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="L43" t="n">
         <v>0.03830470017405307</v>
@@ -7449,10 +7449,10 @@
         <v>0.02210627144826827</v>
       </c>
       <c r="O43" t="n">
-        <v>15270826.3681861</v>
+        <v>15125300.47283325</v>
       </c>
       <c r="P43" t="n">
-        <v>7635413.18409305</v>
+        <v>7562650.236416627</v>
       </c>
     </row>
     <row r="44">
@@ -7483,19 +7483,19 @@
         <v>0.75</v>
       </c>
       <c r="G44" t="n">
-        <v>1240710907.89</v>
+        <v>1005206416.05</v>
       </c>
       <c r="H44" t="n">
-        <v>-91346794.52054794</v>
+        <v>-130312887.6712329</v>
       </c>
       <c r="I44" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="J44" t="n">
-        <v>-136000000</v>
+        <v>-124000000</v>
       </c>
       <c r="K44" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="L44" t="n">
         <v>0.03852218097221538</v>
@@ -7507,10 +7507,10 @@
         <v>0.01953451299207831</v>
       </c>
       <c r="O44" t="n">
-        <v>16839201.1539331</v>
+        <v>12817964.2476002</v>
       </c>
       <c r="P44" t="n">
-        <v>8419600.57696655</v>
+        <v>6408982.1238001</v>
       </c>
     </row>
     <row r="45">
@@ -7541,19 +7541,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G45" t="n">
-        <v>-201932841.91</v>
+        <v>-243337598.87</v>
       </c>
       <c r="H45" t="n">
-        <v>-50972657.53424658</v>
+        <v>-89950783.56164384</v>
       </c>
       <c r="I45" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="J45" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K45" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="L45" t="n">
         <v>0.03873510939427094</v>
@@ -7565,10 +7565,10 @@
         <v>0.01713582153361681</v>
       </c>
       <c r="O45" t="n">
-        <v>-2889162.335564557</v>
+        <v>-3807446.827050986</v>
       </c>
       <c r="P45" t="n">
-        <v>-2889162.335564557</v>
+        <v>-3807446.827050986</v>
       </c>
     </row>
     <row r="46">
@@ -7599,19 +7599,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G46" t="n">
-        <v>-196825268.73</v>
+        <v>-241428019.53</v>
       </c>
       <c r="H46" t="n">
-        <v>-50988356.16438356</v>
+        <v>-89973452.05479452</v>
       </c>
       <c r="I46" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="J46" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K46" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="L46" t="n">
         <v>0.03888939094511485</v>
@@ -7623,10 +7623,10 @@
         <v>0.01489823429388384</v>
       </c>
       <c r="O46" t="n">
-        <v>-2153658.176187682</v>
+        <v>-2880089.781921424</v>
       </c>
       <c r="P46" t="n">
-        <v>-2153658.176187682</v>
+        <v>-2880089.781921424</v>
       </c>
     </row>
     <row r="47">
@@ -7657,19 +7657,19 @@
         <v>0.5</v>
       </c>
       <c r="G47" t="n">
-        <v>69886647.3499999</v>
+        <v>149216557.22</v>
       </c>
       <c r="H47" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I47" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="J47" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K47" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="L47" t="n">
         <v>0.03901400018340251</v>
@@ -7681,10 +7681,10 @@
         <v>0.01283846298538327</v>
       </c>
       <c r="O47" t="n">
-        <v>-128910.7556464296</v>
+        <v>380326.3001034642</v>
       </c>
       <c r="P47" t="n">
-        <v>-128910.7556464296</v>
+        <v>190163.1500517321</v>
       </c>
     </row>
     <row r="48">
@@ -7715,19 +7715,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G48" t="n">
-        <v>-81388394.01999998</v>
+        <v>116432754.21</v>
       </c>
       <c r="H48" t="n">
         <v>2250000</v>
       </c>
       <c r="I48" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="J48" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K48" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="L48" t="n">
         <v>0.03908855826627113</v>
@@ -7739,10 +7739,10 @@
         <v>0.01091166853486086</v>
       </c>
       <c r="O48" t="n">
-        <v>-359804.968303106</v>
+        <v>539594.5311432841</v>
       </c>
       <c r="P48" t="n">
-        <v>-359804.968303106</v>
+        <v>269797.265571642</v>
       </c>
     </row>
     <row r="49">
@@ -7773,19 +7773,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G49" t="n">
-        <v>-24300588.46000001</v>
+        <v>-21021772.08000001</v>
       </c>
       <c r="H49" t="n">
         <v>2250000</v>
       </c>
       <c r="I49" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="J49" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K49" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="L49" t="n">
         <v>0.03915884386251234</v>
@@ -7797,10 +7797,10 @@
         <v>0.009159039096315102</v>
       </c>
       <c r="O49" t="n">
-        <v>-67320.7339339649</v>
+        <v>-57310.46479594545</v>
       </c>
       <c r="P49" t="n">
-        <v>-67320.7339339649</v>
+        <v>-57310.46479594545</v>
       </c>
     </row>
     <row r="50">
@@ -7831,19 +7831,19 @@
         <v>0.25</v>
       </c>
       <c r="G50" t="n">
-        <v>-25229792.01000001</v>
+        <v>-19025601.68</v>
       </c>
       <c r="H50" t="n">
         <v>2250000</v>
       </c>
       <c r="I50" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="J50" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K50" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="L50" t="n">
         <v>0.03922681220647117</v>
@@ -7855,10 +7855,10 @@
         <v>0.007522420693245678</v>
       </c>
       <c r="O50" t="n">
-        <v>-43215.91573562643</v>
+        <v>-31548.28330481974</v>
       </c>
       <c r="P50" t="n">
-        <v>-43215.91573562643</v>
+        <v>-31548.28330481974</v>
       </c>
     </row>
     <row r="51">
@@ -7889,19 +7889,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G51" t="n">
-        <v>43083900.58</v>
+        <v>101044465.29</v>
       </c>
       <c r="H51" t="n">
         <v>2250000</v>
       </c>
       <c r="I51" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="J51" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K51" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="L51" t="n">
         <v>0.03929424848359133</v>
@@ -7913,10 +7913,10 @@
         <v>0.006011768704670392</v>
       </c>
       <c r="O51" t="n">
-        <v>45422.82079458048</v>
+        <v>103497.0722993473</v>
       </c>
       <c r="P51" t="n">
-        <v>22711.41039729024</v>
+        <v>51748.53614967367</v>
       </c>
     </row>
     <row r="52">
@@ -7947,19 +7947,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G52" t="n">
-        <v>32635075.89</v>
+        <v>34292018.08</v>
       </c>
       <c r="H52" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I52" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="L52" t="n">
         <v>0.03936107056455495</v>
@@ -7971,10 +7971,10 @@
         <v>0.004613431737291229</v>
       </c>
       <c r="O52" t="n">
-        <v>13416.39951618895</v>
+        <v>14053.41532337252</v>
       </c>
       <c r="P52" t="n">
-        <v>6708.199758094475</v>
+        <v>7026.70766168626</v>
       </c>
     </row>
     <row r="53">
@@ -8005,19 +8005,19 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>-85065078.76000001</v>
+        <v>-76962502.42</v>
       </c>
       <c r="H53" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I53" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="J53" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K53" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="L53" t="n">
         <v>0.03942868733737526</v>
@@ -8063,19 +8063,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G54" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="J54" t="n">
-        <v>-680000000</v>
+        <v>-620000000</v>
       </c>
       <c r="K54" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="L54" t="n">
         <v>0.03432749872940843</v>
@@ -8087,10 +8087,10 @@
         <v>0.0349083460781352</v>
       </c>
       <c r="O54" t="n">
-        <v>-45262800.31607471</v>
+        <v>-46934947.46025104</v>
       </c>
       <c r="P54" t="n">
-        <v>-45262800.31607471</v>
+        <v>-46934947.46025104</v>
       </c>
     </row>
     <row r="55">
@@ -8121,19 +8121,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G55" t="n">
-        <v>912642221.4799999</v>
+        <v>974764849.6000001</v>
       </c>
       <c r="H55" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I55" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="J55" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K55" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="L55" t="n">
         <v>0.03782665436246635</v>
@@ -8145,10 +8145,10 @@
         <v>0.03231037168362505</v>
       </c>
       <c r="O55" t="n">
-        <v>24378427.22930017</v>
+        <v>26218365.33344426</v>
       </c>
       <c r="P55" t="n">
-        <v>12189213.61465009</v>
+        <v>13109182.66672213</v>
       </c>
     </row>
     <row r="56">
@@ -8179,19 +8179,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G56" t="n">
-        <v>879884659.5500001</v>
+        <v>871985042.7</v>
       </c>
       <c r="H56" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I56" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="L56" t="n">
         <v>0.03830470017405307</v>
@@ -8203,10 +8203,10 @@
         <v>0.02984617139370105</v>
       </c>
       <c r="O56" t="n">
-        <v>20617484.14584114</v>
+        <v>20421006.38046642</v>
       </c>
       <c r="P56" t="n">
-        <v>10308742.07292057</v>
+        <v>10210503.19023321</v>
       </c>
     </row>
     <row r="57">
@@ -8237,19 +8237,19 @@
         <v>0.75</v>
       </c>
       <c r="G57" t="n">
-        <v>1240710907.89</v>
+        <v>1005206416.05</v>
       </c>
       <c r="H57" t="n">
-        <v>-91346794.52054794</v>
+        <v>-130312887.6712329</v>
       </c>
       <c r="I57" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="J57" t="n">
-        <v>-136000000</v>
+        <v>-124000000</v>
       </c>
       <c r="K57" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="L57" t="n">
         <v>0.03852218097221538</v>
@@ -8261,10 +8261,10 @@
         <v>0.02759968737635887</v>
       </c>
       <c r="O57" t="n">
-        <v>23791567.65795208</v>
+        <v>18110090.90314015</v>
       </c>
       <c r="P57" t="n">
-        <v>11895783.82897604</v>
+        <v>9055045.451570075</v>
       </c>
     </row>
     <row r="58">
@@ -8295,19 +8295,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G58" t="n">
-        <v>-201932841.91</v>
+        <v>-243337598.87</v>
       </c>
       <c r="H58" t="n">
-        <v>-50972657.53424658</v>
+        <v>-89950783.56164384</v>
       </c>
       <c r="I58" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="J58" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K58" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="L58" t="n">
         <v>0.03873510939427094</v>
@@ -8319,10 +8319,10 @@
         <v>0.02550527570343863</v>
       </c>
       <c r="O58" t="n">
-        <v>-4300282.993494238</v>
+        <v>-5667074.721781447</v>
       </c>
       <c r="P58" t="n">
-        <v>-4300282.993494238</v>
+        <v>-5667074.721781447</v>
       </c>
     </row>
     <row r="59">
@@ -8353,19 +8353,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G59" t="n">
-        <v>-196825268.73</v>
+        <v>-241428019.53</v>
       </c>
       <c r="H59" t="n">
-        <v>-50988356.16438356</v>
+        <v>-89973452.05479452</v>
       </c>
       <c r="I59" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="J59" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K59" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="L59" t="n">
         <v>0.03888939094511485</v>
@@ -8377,10 +8377,10 @@
         <v>0.02355207664351209</v>
       </c>
       <c r="O59" t="n">
-        <v>-3404639.867311128</v>
+        <v>-4553029.167480368</v>
       </c>
       <c r="P59" t="n">
-        <v>-3404639.867311128</v>
+        <v>-4553029.167480368</v>
       </c>
     </row>
     <row r="60">
@@ -8411,19 +8411,19 @@
         <v>0.5</v>
       </c>
       <c r="G60" t="n">
-        <v>69886647.3499999</v>
+        <v>149216557.22</v>
       </c>
       <c r="H60" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I60" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="J60" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K60" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="L60" t="n">
         <v>0.03901400018340251</v>
@@ -8435,10 +8435,10 @@
         <v>0.02175522406292973</v>
       </c>
       <c r="O60" t="n">
-        <v>-218443.7791659792</v>
+        <v>644476.2028909577</v>
       </c>
       <c r="P60" t="n">
-        <v>-218443.7791659792</v>
+        <v>322238.1014454789</v>
       </c>
     </row>
     <row r="61">
@@ -8469,19 +8469,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G61" t="n">
-        <v>-81388394.01999998</v>
+        <v>116432754.21</v>
       </c>
       <c r="H61" t="n">
         <v>2250000</v>
       </c>
       <c r="I61" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="J61" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K61" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="L61" t="n">
         <v>0.03908855826627113</v>
@@ -8493,10 +8493,10 @@
         <v>0.02007474611606698</v>
       </c>
       <c r="O61" t="n">
-        <v>-661951.3199936553</v>
+        <v>992719.2329672207</v>
       </c>
       <c r="P61" t="n">
-        <v>-661951.3199936553</v>
+        <v>496359.6164836104</v>
       </c>
     </row>
     <row r="62">
@@ -8527,19 +8527,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G62" t="n">
-        <v>-24300588.46000001</v>
+        <v>-21021772.08000001</v>
       </c>
       <c r="H62" t="n">
         <v>2250000</v>
       </c>
       <c r="I62" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="J62" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K62" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="L62" t="n">
         <v>0.03915884386251234</v>
@@ -8551,10 +8551,10 @@
         <v>0.01854770837490727</v>
       </c>
       <c r="O62" t="n">
-        <v>-136329.2947503919</v>
+        <v>-116057.7847400222</v>
       </c>
       <c r="P62" t="n">
-        <v>-136329.2947503919</v>
+        <v>-116057.7847400222</v>
       </c>
     </row>
     <row r="63">
@@ -8585,19 +8585,19 @@
         <v>0.25</v>
       </c>
       <c r="G63" t="n">
-        <v>-25229792.01000001</v>
+        <v>-19025601.68</v>
       </c>
       <c r="H63" t="n">
         <v>2250000</v>
       </c>
       <c r="I63" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="J63" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K63" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="L63" t="n">
         <v>0.03922681220647117</v>
@@ -8609,10 +8609,10 @@
         <v>0.01712251280817986</v>
       </c>
       <c r="O63" t="n">
-        <v>-98367.94575513355</v>
+        <v>-71810.11365768088</v>
       </c>
       <c r="P63" t="n">
-        <v>-98367.94575513355</v>
+        <v>-71810.11365768088</v>
       </c>
     </row>
     <row r="64">
@@ -8643,19 +8643,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G64" t="n">
-        <v>43083900.58</v>
+        <v>101044465.29</v>
       </c>
       <c r="H64" t="n">
         <v>2250000</v>
       </c>
       <c r="I64" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="J64" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K64" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="L64" t="n">
         <v>0.03929424848359133</v>
@@ -8667,10 +8667,10 @@
         <v>0.01580817291864865</v>
       </c>
       <c r="O64" t="n">
-        <v>119441.023240911</v>
+        <v>272149.4614739451</v>
       </c>
       <c r="P64" t="n">
-        <v>59720.51162045549</v>
+        <v>136074.7307369725</v>
       </c>
     </row>
     <row r="65">
@@ -8701,19 +8701,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G65" t="n">
-        <v>32635075.89</v>
+        <v>34292018.08</v>
       </c>
       <c r="H65" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I65" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="L65" t="n">
         <v>0.03936107056455495</v>
@@ -8725,10 +8725,10 @@
         <v>0.01459272426401294</v>
       </c>
       <c r="O65" t="n">
-        <v>42437.35030759013</v>
+        <v>44452.29201593011</v>
       </c>
       <c r="P65" t="n">
-        <v>21218.67515379507</v>
+        <v>22226.14600796506</v>
       </c>
     </row>
     <row r="66">
@@ -8759,19 +8759,19 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>-85065078.76000001</v>
+        <v>-76962502.42</v>
       </c>
       <c r="H66" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I66" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="J66" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K66" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="L66" t="n">
         <v>0.03942868733737526</v>
@@ -8817,19 +8817,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G67" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="J67" t="n">
-        <v>-680000000</v>
+        <v>-620000000</v>
       </c>
       <c r="K67" t="n">
-        <v>-620180437.28</v>
+        <v>-728213104.0599999</v>
       </c>
       <c r="L67" t="n">
         <v>0.03432749872940843</v>
@@ -8841,10 +8841,10 @@
         <v>-0.03432359322008915</v>
       </c>
       <c r="O67" t="n">
-        <v>21228500.99457832</v>
+        <v>24926411.20961912</v>
       </c>
       <c r="P67" t="n">
-        <v>10614250.49728916</v>
+        <v>12463205.60480956</v>
       </c>
     </row>
     <row r="68">
@@ -8875,19 +8875,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G68" t="n">
-        <v>912642221.4799999</v>
+        <v>974764849.6000001</v>
       </c>
       <c r="H68" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I68" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="J68" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K68" t="n">
-        <v>891099410.5210958</v>
+        <v>947222038.641096</v>
       </c>
       <c r="L68" t="n">
         <v>0.03782665436246635</v>
@@ -8899,10 +8899,10 @@
         <v>-0.03222210497938605</v>
       </c>
       <c r="O68" t="n">
-        <v>-26320340.52347312</v>
+        <v>-27978030.63722467</v>
       </c>
       <c r="P68" t="n">
-        <v>-26320340.52347312</v>
+        <v>-27978030.63722467</v>
       </c>
     </row>
     <row r="69">
@@ -8933,19 +8933,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G69" t="n">
-        <v>879884659.5500001</v>
+        <v>871985042.7</v>
       </c>
       <c r="H69" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I69" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="L69" t="n">
         <v>0.03830470017405307</v>
@@ -8957,10 +8957,10 @@
         <v>-0.02969704733354739</v>
       </c>
       <c r="O69" t="n">
-        <v>-20514470.4994533</v>
+        <v>-20318974.41986052</v>
       </c>
       <c r="P69" t="n">
-        <v>-20514470.4994533</v>
+        <v>-20318974.41986052</v>
       </c>
     </row>
     <row r="70">
@@ -8991,19 +8991,19 @@
         <v>0.75</v>
       </c>
       <c r="G70" t="n">
-        <v>1240710907.89</v>
+        <v>1005206416.05</v>
       </c>
       <c r="H70" t="n">
-        <v>-91346794.52054794</v>
+        <v>-130312887.6712329</v>
       </c>
       <c r="I70" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="J70" t="n">
-        <v>-136000000</v>
+        <v>-124000000</v>
       </c>
       <c r="K70" t="n">
-        <v>1285364113.369452</v>
+        <v>998893528.3787673</v>
       </c>
       <c r="L70" t="n">
         <v>0.03852218097221538</v>
@@ -9015,10 +9015,10 @@
         <v>-0.0274114503343057</v>
       </c>
       <c r="O70" t="n">
-        <v>-26425270.91634421</v>
+        <v>-20535840.25681047</v>
       </c>
       <c r="P70" t="n">
-        <v>-26425270.91634421</v>
+        <v>-20535840.25681047</v>
       </c>
     </row>
     <row r="71">
@@ -9049,19 +9049,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G71" t="n">
-        <v>-201932841.91</v>
+        <v>-243337598.87</v>
       </c>
       <c r="H71" t="n">
-        <v>-50972657.53424658</v>
+        <v>-89950783.56164384</v>
       </c>
       <c r="I71" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="J71" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K71" t="n">
-        <v>-184905499.4442466</v>
+        <v>-271288382.4316438</v>
       </c>
       <c r="L71" t="n">
         <v>0.03873510939427094</v>
@@ -9073,10 +9073,10 @@
         <v>-0.0252927177134521</v>
       </c>
       <c r="O71" t="n">
-        <v>3117841.734072135</v>
+        <v>4574413.650521738</v>
       </c>
       <c r="P71" t="n">
-        <v>1558920.867036068</v>
+        <v>2287206.825260869</v>
       </c>
     </row>
     <row r="72">
@@ -9107,19 +9107,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G72" t="n">
-        <v>-196825268.73</v>
+        <v>-241428019.53</v>
       </c>
       <c r="H72" t="n">
-        <v>-50988356.16438356</v>
+        <v>-89973452.05479452</v>
       </c>
       <c r="I72" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="J72" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K72" t="n">
-        <v>-179813624.8943836</v>
+        <v>-269401471.5847945</v>
       </c>
       <c r="L72" t="n">
         <v>0.03888939094511485</v>
@@ -9131,10 +9131,10 @@
         <v>-0.02332613375362271</v>
       </c>
       <c r="O72" t="n">
-        <v>2446708.054589245</v>
+        <v>3665721.943105661</v>
       </c>
       <c r="P72" t="n">
-        <v>1223354.027294622</v>
+        <v>1832860.971552831</v>
       </c>
     </row>
     <row r="73">
@@ -9165,19 +9165,19 @@
         <v>0.5</v>
       </c>
       <c r="G73" t="n">
-        <v>69886647.3499999</v>
+        <v>149216557.22</v>
       </c>
       <c r="H73" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I73" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="J73" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K73" t="n">
-        <v>13918039.13082182</v>
+        <v>90247949.00082195</v>
       </c>
       <c r="L73" t="n">
         <v>0.03901400018340251</v>
@@ -9189,10 +9189,10 @@
         <v>-0.02152530442995682</v>
       </c>
       <c r="O73" t="n">
-        <v>-149795.0146794957</v>
+        <v>-971307.2882109547</v>
       </c>
       <c r="P73" t="n">
-        <v>-149795.0146794957</v>
+        <v>-971307.2882109547</v>
       </c>
     </row>
     <row r="74">
@@ -9223,19 +9223,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G74" t="n">
-        <v>-81388394.01999998</v>
+        <v>116432754.21</v>
       </c>
       <c r="H74" t="n">
         <v>2250000</v>
       </c>
       <c r="I74" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="J74" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K74" t="n">
-        <v>-45138394.01999998</v>
+        <v>149682754.21</v>
       </c>
       <c r="L74" t="n">
         <v>0.03908855826627113</v>
@@ -9247,10 +9247,10 @@
         <v>-0.01984578814143261</v>
       </c>
       <c r="O74" t="n">
-        <v>373252.9186522617</v>
+        <v>-1237738.428532413</v>
       </c>
       <c r="P74" t="n">
-        <v>186626.4593261308</v>
+        <v>-1237738.428532413</v>
       </c>
     </row>
     <row r="75">
@@ -9281,19 +9281,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G75" t="n">
-        <v>-24300588.46000001</v>
+        <v>-21021772.08000001</v>
       </c>
       <c r="H75" t="n">
         <v>2250000</v>
       </c>
       <c r="I75" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="J75" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K75" t="n">
-        <v>11949411.53999999</v>
+        <v>12228227.91999999</v>
       </c>
       <c r="L75" t="n">
         <v>0.03915884386251234</v>
@@ -9305,10 +9305,10 @@
         <v>-0.01832662273584051</v>
       </c>
       <c r="O75" t="n">
-        <v>-72997.45240295962</v>
+        <v>-74700.70660590389</v>
       </c>
       <c r="P75" t="n">
-        <v>-72997.45240295962</v>
+        <v>-74700.70660590389</v>
       </c>
     </row>
     <row r="76">
@@ -9339,19 +9339,19 @@
         <v>0.25</v>
       </c>
       <c r="G76" t="n">
-        <v>-25229792.01000001</v>
+        <v>-19025601.68</v>
       </c>
       <c r="H76" t="n">
         <v>2250000</v>
       </c>
       <c r="I76" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="J76" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K76" t="n">
-        <v>11020207.98999999</v>
+        <v>14224398.32</v>
       </c>
       <c r="L76" t="n">
         <v>0.03922681220647117</v>
@@ -9363,10 +9363,10 @@
         <v>-0.01691110693903308</v>
       </c>
       <c r="O76" t="n">
-        <v>-46590.97895231918</v>
+        <v>-60137.58028323063</v>
       </c>
       <c r="P76" t="n">
-        <v>-46590.97895231918</v>
+        <v>-60137.58028323063</v>
       </c>
     </row>
     <row r="77">
@@ -9397,19 +9397,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G77" t="n">
-        <v>43083900.58</v>
+        <v>101044465.29</v>
       </c>
       <c r="H77" t="n">
         <v>2250000</v>
       </c>
       <c r="I77" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="J77" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K77" t="n">
-        <v>79333900.58</v>
+        <v>134294465.29</v>
       </c>
       <c r="L77" t="n">
         <v>0.03929424848359133</v>
@@ -9421,10 +9421,10 @@
         <v>-0.01560891224971384</v>
       </c>
       <c r="O77" t="n">
-        <v>-206385.9820967902</v>
+        <v>-349365.0873889751</v>
       </c>
       <c r="P77" t="n">
-        <v>-206385.9820967902</v>
+        <v>-349365.0873889751</v>
       </c>
     </row>
     <row r="78">
@@ -9455,19 +9455,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G78" t="n">
-        <v>32635075.89</v>
+        <v>34292018.08</v>
       </c>
       <c r="H78" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I78" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="L78" t="n">
         <v>0.03936107056455495</v>
@@ -9479,10 +9479,10 @@
         <v>-0.01440665719067059</v>
       </c>
       <c r="O78" t="n">
-        <v>-41896.24547827392</v>
+        <v>-43885.49532128132</v>
       </c>
       <c r="P78" t="n">
-        <v>-41896.24547827392</v>
+        <v>-43885.49532128132</v>
       </c>
     </row>
     <row r="79">
@@ -9513,19 +9513,19 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>-85065078.76000001</v>
+        <v>-76962502.42</v>
       </c>
       <c r="H79" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I79" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="J79" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K79" t="n">
-        <v>-13020010.26684932</v>
+        <v>-10917433.92684932</v>
       </c>
       <c r="L79" t="n">
         <v>0.03942868733737526</v>
@@ -9571,19 +9571,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G80" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="J80" t="n">
-        <v>-680000000</v>
+        <v>-620000000</v>
       </c>
       <c r="K80" t="n">
-        <v>-620180437.28</v>
+        <v>-728213104.0599999</v>
       </c>
       <c r="L80" t="n">
         <v>0.03432749872940843</v>
@@ -9595,10 +9595,10 @@
         <v>-0.01000145066733071</v>
       </c>
       <c r="O80" t="n">
-        <v>6185710.33857814</v>
+        <v>7263233.497380241</v>
       </c>
       <c r="P80" t="n">
-        <v>3092855.16928907</v>
+        <v>3631616.74869012</v>
       </c>
     </row>
     <row r="81">
@@ -9629,19 +9629,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G81" t="n">
-        <v>912642221.4799999</v>
+        <v>974764849.6000001</v>
       </c>
       <c r="H81" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I81" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="J81" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K81" t="n">
-        <v>891099410.5210958</v>
+        <v>947222038.641096</v>
       </c>
       <c r="L81" t="n">
         <v>0.03782665436246635</v>
@@ -9653,10 +9653,10 @@
         <v>-0.01002646052209499</v>
       </c>
       <c r="O81" t="n">
-        <v>-8190025.305780896</v>
+        <v>-8705844.011418846</v>
       </c>
       <c r="P81" t="n">
-        <v>-8190025.305780896</v>
+        <v>-8705844.011418846</v>
       </c>
     </row>
     <row r="82">
@@ -9687,19 +9687,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G82" t="n">
-        <v>879884659.5500001</v>
+        <v>871985042.7</v>
       </c>
       <c r="H82" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I82" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="L82" t="n">
         <v>0.03830470017405307</v>
@@ -9711,10 +9711,10 @@
         <v>-0.01005429630576771</v>
       </c>
       <c r="O82" t="n">
-        <v>-6945423.315685432</v>
+        <v>-6879235.741925485</v>
       </c>
       <c r="P82" t="n">
-        <v>-6945423.315685432</v>
+        <v>-6879235.741925485</v>
       </c>
     </row>
     <row r="83">
@@ -9745,19 +9745,19 @@
         <v>0.75</v>
       </c>
       <c r="G83" t="n">
-        <v>1240710907.89</v>
+        <v>1005206416.05</v>
       </c>
       <c r="H83" t="n">
-        <v>-91346794.52054794</v>
+        <v>-130312887.6712329</v>
       </c>
       <c r="I83" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="J83" t="n">
-        <v>-136000000</v>
+        <v>-124000000</v>
       </c>
       <c r="K83" t="n">
-        <v>1285364113.369452</v>
+        <v>998893528.3787673</v>
       </c>
       <c r="L83" t="n">
         <v>0.03852218097221538</v>
@@ -9769,10 +9769,10 @@
         <v>-0.01008322673507944</v>
       </c>
       <c r="O83" t="n">
-        <v>-9720463.344178906</v>
+        <v>-7554052.448134966</v>
       </c>
       <c r="P83" t="n">
-        <v>-9720463.344178906</v>
+        <v>-7554052.448134966</v>
       </c>
     </row>
     <row r="84">
@@ -9803,19 +9803,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G84" t="n">
-        <v>-201932841.91</v>
+        <v>-243337598.87</v>
       </c>
       <c r="H84" t="n">
-        <v>-50972657.53424658</v>
+        <v>-89950783.56164384</v>
       </c>
       <c r="I84" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="J84" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K84" t="n">
-        <v>-184905499.4442466</v>
+        <v>-271288382.4316438</v>
       </c>
       <c r="L84" t="n">
         <v>0.03873510939427094</v>
@@ -9827,10 +9827,10 @@
         <v>-0.0101121147124088</v>
       </c>
       <c r="O84" t="n">
-        <v>1246523.747556976</v>
+        <v>1828866.162195075</v>
       </c>
       <c r="P84" t="n">
-        <v>623261.873778488</v>
+        <v>914433.0810975374</v>
       </c>
     </row>
     <row r="85">
@@ -9861,19 +9861,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G85" t="n">
-        <v>-196825268.73</v>
+        <v>-241428019.53</v>
       </c>
       <c r="H85" t="n">
-        <v>-50988356.16438356</v>
+        <v>-89973452.05479452</v>
       </c>
       <c r="I85" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="J85" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K85" t="n">
-        <v>-179813624.8943836</v>
+        <v>-269401471.5847945</v>
       </c>
       <c r="L85" t="n">
         <v>0.03888939094511485</v>
@@ -9885,10 +9885,10 @@
         <v>-0.0101405708492285</v>
       </c>
       <c r="O85" t="n">
-        <v>1063657.468357222</v>
+        <v>1593599.413870349</v>
       </c>
       <c r="P85" t="n">
-        <v>531828.7341786108</v>
+        <v>796799.7069351746</v>
       </c>
     </row>
     <row r="86">
@@ -9919,19 +9919,19 @@
         <v>0.5</v>
       </c>
       <c r="G86" t="n">
-        <v>69886647.3499999</v>
+        <v>149216557.22</v>
       </c>
       <c r="H86" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I86" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="J86" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K86" t="n">
-        <v>13918039.13082182</v>
+        <v>90247949.00082195</v>
       </c>
       <c r="L86" t="n">
         <v>0.03901400018340251</v>
@@ -9943,10 +9943,10 @@
         <v>-0.01016949446707605</v>
       </c>
       <c r="O86" t="n">
-        <v>-70769.71096672022</v>
+        <v>-458888.00901441</v>
       </c>
       <c r="P86" t="n">
-        <v>-70769.71096672022</v>
+        <v>-458888.00901441</v>
       </c>
     </row>
     <row r="87">
@@ -9977,19 +9977,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G87" t="n">
-        <v>-81388394.01999998</v>
+        <v>116432754.21</v>
       </c>
       <c r="H87" t="n">
         <v>2250000</v>
       </c>
       <c r="I87" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="J87" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K87" t="n">
-        <v>-45138394.01999998</v>
+        <v>149682754.21</v>
       </c>
       <c r="L87" t="n">
         <v>0.03908855826627113</v>
@@ -10001,10 +10001,10 @@
         <v>-0.01019737062440143</v>
       </c>
       <c r="O87" t="n">
-        <v>191788.7221717521</v>
+        <v>-635987.7169835642</v>
       </c>
       <c r="P87" t="n">
-        <v>95894.36108587607</v>
+        <v>-635987.7169835642</v>
       </c>
     </row>
     <row r="88">
@@ -10035,19 +10035,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G88" t="n">
-        <v>-24300588.46000001</v>
+        <v>-21021772.08000001</v>
       </c>
       <c r="H88" t="n">
         <v>2250000</v>
       </c>
       <c r="I88" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="J88" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K88" t="n">
-        <v>11949411.53999999</v>
+        <v>12228227.91999999</v>
       </c>
       <c r="L88" t="n">
         <v>0.03915884386251234</v>
@@ -10059,10 +10059,10 @@
         <v>-0.0102268186216663</v>
       </c>
       <c r="O88" t="n">
-        <v>-40734.82148507537</v>
+        <v>-41685.28966741191</v>
       </c>
       <c r="P88" t="n">
-        <v>-40734.82148507537</v>
+        <v>-41685.28966741191</v>
       </c>
     </row>
     <row r="89">
@@ -10093,19 +10093,19 @@
         <v>0.25</v>
       </c>
       <c r="G89" t="n">
-        <v>-25229792.01000001</v>
+        <v>-19025601.68</v>
       </c>
       <c r="H89" t="n">
         <v>2250000</v>
       </c>
       <c r="I89" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="J89" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K89" t="n">
-        <v>11020207.98999999</v>
+        <v>14224398.32</v>
       </c>
       <c r="L89" t="n">
         <v>0.03922681220647117</v>
@@ -10117,10 +10117,10 @@
         <v>-0.01025547675463123</v>
       </c>
       <c r="O89" t="n">
-        <v>-28254.37171816158</v>
+        <v>-36469.49657984389</v>
       </c>
       <c r="P89" t="n">
-        <v>-28254.37171816158</v>
+        <v>-36469.49657984389</v>
       </c>
     </row>
     <row r="90">
@@ -10151,19 +10151,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>43083900.58</v>
+        <v>101044465.29</v>
       </c>
       <c r="H90" t="n">
         <v>2250000</v>
       </c>
       <c r="I90" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="J90" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="K90" t="n">
-        <v>79333900.58</v>
+        <v>134294465.29</v>
       </c>
       <c r="L90" t="n">
         <v>0.03929424848359133</v>
@@ -10175,10 +10175,10 @@
         <v>-0.01028445871969606</v>
       </c>
       <c r="O90" t="n">
-        <v>-135984.3709312468</v>
+        <v>-230190.9807597766</v>
       </c>
       <c r="P90" t="n">
-        <v>-135984.3709312468</v>
+        <v>-230190.9807597766</v>
       </c>
     </row>
     <row r="91">
@@ -10209,19 +10209,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G91" t="n">
-        <v>32635075.89</v>
+        <v>34292018.08</v>
       </c>
       <c r="H91" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I91" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="L91" t="n">
         <v>0.03936107056455495</v>
@@ -10233,10 +10233,10 @@
         <v>-0.01031343600303951</v>
       </c>
       <c r="O91" t="n">
-        <v>-29992.67913361784</v>
+        <v>-31416.7430700596</v>
       </c>
       <c r="P91" t="n">
-        <v>-29992.67913361784</v>
+        <v>-31416.7430700596</v>
       </c>
     </row>
     <row r="92">
@@ -10267,19 +10267,19 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>-85065078.76000001</v>
+        <v>-76962502.42</v>
       </c>
       <c r="H92" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I92" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="J92" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="K92" t="n">
-        <v>-13020010.26684932</v>
+        <v>-10917433.92684932</v>
       </c>
       <c r="L92" t="n">
         <v>0.03942868733737526</v>
@@ -10370,22 +10370,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="D2" t="n">
-        <v>572674499.95</v>
+        <v>567239502.7</v>
       </c>
       <c r="E2" t="n">
-        <v>42411854.98000002</v>
+        <v>38693708.36000007</v>
       </c>
       <c r="F2" t="n">
-        <v>21205927.49000001</v>
+        <v>19346854.18000004</v>
       </c>
       <c r="G2" t="n">
-        <v>3.534321248333335</v>
+        <v>3.224475696666672</v>
       </c>
       <c r="H2" t="n">
-        <v>1.767160624166668</v>
+        <v>1.612237848333336</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -10403,22 +10403,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="D3" t="n">
-        <v>484366736.45</v>
+        <v>486337695.77</v>
       </c>
       <c r="E3" t="n">
-        <v>-45895908.52000004</v>
+        <v>-42208098.56999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-45895908.52000004</v>
+        <v>-42208098.56999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.824659043333337</v>
+        <v>-3.5173415475</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.824659043333337</v>
+        <v>-3.5173415475</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -10436,22 +10436,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="D4" t="n">
-        <v>552727420.49</v>
+        <v>552265384.9</v>
       </c>
       <c r="E4" t="n">
-        <v>22464775.51999998</v>
+        <v>23719590.56</v>
       </c>
       <c r="F4" t="n">
-        <v>11232387.75999999</v>
+        <v>11859795.28</v>
       </c>
       <c r="G4" t="n">
-        <v>1.872064626666665</v>
+        <v>1.976632546666667</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9360323133333326</v>
+        <v>0.9883162733333334</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -10469,22 +10469,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="D5" t="n">
-        <v>508247205.35</v>
+        <v>504658759.42</v>
       </c>
       <c r="E5" t="n">
-        <v>-22015439.62</v>
+        <v>-23887034.91999996</v>
       </c>
       <c r="F5" t="n">
-        <v>-22015439.62</v>
+        <v>-23887034.91999996</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.834619968333334</v>
+        <v>-1.99058624333333</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.834619968333334</v>
+        <v>-1.99058624333333</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -10502,22 +10502,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="D6" t="n">
-        <v>528129393.9</v>
+        <v>523259508.19</v>
       </c>
       <c r="E6" t="n">
-        <v>-2133251.070000052</v>
+        <v>-5286286.149999976</v>
       </c>
       <c r="F6" t="n">
-        <v>-2133251.070000052</v>
+        <v>-5286286.149999976</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1777709225000044</v>
+        <v>-0.4405238458333314</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1777709225000044</v>
+        <v>-0.4405238458333314</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -10535,22 +10535,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="D7" t="n">
-        <v>528746533.87</v>
+        <v>530093342.62</v>
       </c>
       <c r="E7" t="n">
-        <v>-1516111.100000024</v>
+        <v>1547548.280000031</v>
       </c>
       <c r="F7" t="n">
-        <v>-1516111.100000024</v>
+        <v>773774.1400000155</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1263425916666686</v>
+        <v>0.1289623566666692</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1263425916666686</v>
+        <v>0.06448117833333462</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -10568,22 +10568,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="D8" t="n">
-        <v>510874107.55</v>
+        <v>510628634.11</v>
       </c>
       <c r="E8" t="n">
-        <v>-19388537.42000002</v>
+        <v>-17917160.22999996</v>
       </c>
       <c r="F8" t="n">
-        <v>-19388537.42000002</v>
+        <v>-17917160.22999996</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.615711451666668</v>
+        <v>-1.49309668583333</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.615711451666668</v>
+        <v>-1.49309668583333</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
